--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:35:13</t>
+          <t>2026-09-06 05:42:14</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4686,7 +4686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4807,25 +4807,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4861,19 +4881,19 @@
         <v>5552427</v>
       </c>
       <c r="I2" t="n">
-        <v>8995653</v>
+        <v>8941566</v>
       </c>
       <c r="J2" t="n">
         <v>340132134912</v>
       </c>
       <c r="K2" t="n">
-        <v>22.18788</v>
+        <v>22.120846</v>
       </c>
       <c r="L2" t="n">
         <v>19.789724</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6</v>
+        <v>6.62</v>
       </c>
       <c r="N2" t="n">
         <v>167.25</v>
@@ -4909,29 +4929,41 @@
       <c r="W2" t="n">
         <v>0.677</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>22.947</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.381662</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.155</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2322672312</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Household &amp; Personal Products</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.pginvestor.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide. It operates through five segments: Beauty; Grooming; Health Care; Fabric &amp; Home Care; and Baby, Feminine &amp; Family Care. The company offers conditioners, shampoos, styling aids, and treatments under the Head &amp; Shoulders, Herbal Essences, Pantene, and Rejoice brands; antiperspirants, deodorants, and personal cleansing products under the Native, Old Spice, Safeguard, and Secret brands; and facial moisturizers, cleaners, and treatments under the Olay and SK-II brands. It also provides blades, razors, shave products, appliances, and other grooming products under the Braun, Gillette, and Venus brands. In addition, the company offers toothbrushes, toothpastes, and other oral care products under the Crest and Oral-B brands; and gastrointestinal, pain relief, rapid diagnostics, respiratory, vitamins/minerals/supplements, and other personal health care products under the Metamucil, Neurobion, Pepto-Bismol, and Vicks brands. Further, it provides fabric enhancers, and laundry additives and detergents under the Ariel, Downy, Gain, and Tide brands; and air and dish care, P&amp;G professional, and surface care under the Cascade, Dawn, Fairy, Febreze, Mr. Clean, and Swiffer brands. Additionally, the company offers baby wipes, taped diapers, and pants under the Luvs and Pampers brands; adult incontinence and menstrual care products under the Always, Always Discreet, and Tampax brands; and paper towels, tissues, and toilet papers under the Bounty, Charmin, and Puffs brands. It sells its products through mass merchandisers, social ecommerce channels, grocery and specialty beauty stores, membership club stores, drug and department stores, distributors, wholesalers, airport duty-free and high-frequency stores, pharmacies, electronics stores, and professional channels, as well as directly to consumers. The company was founded in 1837 and is headquartered in Cincinnati, Ohio.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:42:14</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:10:17</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:10:17</t>
+          <t>2026-09-06 16:24:52</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:52</t>
+          <t>2026-09-06 16:34:47</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:47</t>
+          <t>2026-09-06 16:49:21</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4907,15 +4907,11 @@
       <c r="Q2" t="n">
         <v>2.97</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.18437</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.22084999</v>
       </c>
       <c r="T2" t="n">
         <v>0.30290002</v>
@@ -4963,7 +4959,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:21</t>
+          <t>2026-09-06 16:59:52</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4686,7 +4686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4827,25 +4827,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4937,29 +4952,38 @@
       <c r="AA2" t="n">
         <v>2322672312</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>87031996416</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>366458961920</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>24752001024</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Household &amp; Personal Products</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.pginvestor.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>The Procter &amp; Gamble Company provides branded consumer packaged goods worldwide. It operates through five segments: Beauty; Grooming; Health Care; Fabric &amp; Home Care; and Baby, Feminine &amp; Family Care. The company offers conditioners, shampoos, styling aids, and treatments under the Head &amp; Shoulders, Herbal Essences, Pantene, and Rejoice brands; antiperspirants, deodorants, and personal cleansing products under the Native, Old Spice, Safeguard, and Secret brands; and facial moisturizers, cleaners, and treatments under the Olay and SK-II brands. It also provides blades, razors, shave products, appliances, and other grooming products under the Braun, Gillette, and Venus brands. In addition, the company offers toothbrushes, toothpastes, and other oral care products under the Crest and Oral-B brands; and gastrointestinal, pain relief, rapid diagnostics, respiratory, vitamins/minerals/supplements, and other personal health care products under the Metamucil, Neurobion, Pepto-Bismol, and Vicks brands. Further, it provides fabric enhancers, and laundry additives and detergents under the Ariel, Downy, Gain, and Tide brands; and air and dish care, P&amp;G professional, and surface care under the Cascade, Dawn, Fairy, Febreze, Mr. Clean, and Swiffer brands. Additionally, the company offers baby wipes, taped diapers, and pants under the Luvs and Pampers brands; adult incontinence and menstrual care products under the Always, Always Discreet, and Tampax brands; and paper towels, tissues, and toilet papers under the Bounty, Charmin, and Puffs brands. It sells its products through mass merchandisers, social ecommerce channels, grocery and specialty beauty stores, membership club stores, drug and department stores, distributors, wholesalers, airport duty-free and high-frequency stores, pharmacies, electronics stores, and professional channels, as well as directly to consumers. The company was founded in 1837 and is headquartered in Cincinnati, Ohio.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:52</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:20:57</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:20:57</t>
+          <t>2026-09-06 22:41:51</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:51</t>
+          <t>2026-09-06 22:59:46</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>147.8500061035156</v>
+        <v>154.0207528479355</v>
       </c>
       <c r="C2" t="n">
-        <v>147.8500061035156</v>
+        <v>155.9733284468274</v>
       </c>
       <c r="D2" t="n">
-        <v>144.6600036621094</v>
+        <v>153.8847527787027</v>
       </c>
       <c r="E2" t="n">
-        <v>146.8000030517578</v>
+        <v>155.4487609863281</v>
       </c>
       <c r="F2" t="n">
-        <v>9753300</v>
+        <v>6436200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>147.8200073242188</v>
+        <v>155.0504715071257</v>
       </c>
       <c r="C3" t="n">
-        <v>148.5</v>
+        <v>155.6916210504824</v>
       </c>
       <c r="D3" t="n">
-        <v>145.4499969482422</v>
+        <v>153.7293216100101</v>
       </c>
       <c r="E3" t="n">
-        <v>146.9700012207031</v>
+        <v>154.4676055908203</v>
       </c>
       <c r="F3" t="n">
-        <v>8766700</v>
+        <v>7178400</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>144.8999938964844</v>
+        <v>154.0790456134228</v>
       </c>
       <c r="C4" t="n">
-        <v>146</v>
+        <v>155.3030463091189</v>
       </c>
       <c r="D4" t="n">
-        <v>143.8800048828125</v>
+        <v>153.6807543788681</v>
       </c>
       <c r="E4" t="n">
-        <v>145.7899932861328</v>
+        <v>154.9047698974609</v>
       </c>
       <c r="F4" t="n">
-        <v>7565500</v>
+        <v>4984900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>144.7299957275391</v>
+        <v>154.0693331751388</v>
       </c>
       <c r="C5" t="n">
-        <v>146.4600067138672</v>
+        <v>154.3996169522188</v>
       </c>
       <c r="D5" t="n">
-        <v>144.1499938964844</v>
+        <v>151.4367423098323</v>
       </c>
       <c r="E5" t="n">
-        <v>146.4400024414062</v>
+        <v>152.8550415039062</v>
       </c>
       <c r="F5" t="n">
-        <v>7386500</v>
+        <v>6205500</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>145.4100036621094</v>
+        <v>153.2144723004245</v>
       </c>
       <c r="C6" t="n">
-        <v>145.7100067138672</v>
+        <v>154.7979134368329</v>
       </c>
       <c r="D6" t="n">
-        <v>143.9299926757812</v>
+        <v>152.8938975095807</v>
       </c>
       <c r="E6" t="n">
-        <v>145.2100067138672</v>
+        <v>154.0984802246094</v>
       </c>
       <c r="F6" t="n">
-        <v>7936700</v>
+        <v>5819500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>144.0500030517578</v>
+        <v>153.4184545574236</v>
       </c>
       <c r="C7" t="n">
-        <v>144.9400024414062</v>
+        <v>154.5841863803252</v>
       </c>
       <c r="D7" t="n">
-        <v>143.7899932861328</v>
+        <v>153.2727454910088</v>
       </c>
       <c r="E7" t="n">
-        <v>144.0800018310547</v>
+        <v>153.3893127441406</v>
       </c>
       <c r="F7" t="n">
-        <v>7195000</v>
+        <v>5957000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>144.5899963378906</v>
+        <v>153.3698919481564</v>
       </c>
       <c r="C8" t="n">
-        <v>145.8000030517578</v>
+        <v>153.9916086583258</v>
       </c>
       <c r="D8" t="n">
-        <v>144</v>
+        <v>151.7378763196521</v>
       </c>
       <c r="E8" t="n">
-        <v>144.2599945068359</v>
+        <v>152.3498840332031</v>
       </c>
       <c r="F8" t="n">
-        <v>7491300</v>
+        <v>5995000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>144.3300018310547</v>
+        <v>152.6510415007772</v>
       </c>
       <c r="C9" t="n">
-        <v>144.9100036621094</v>
+        <v>153.8653332318267</v>
       </c>
       <c r="D9" t="n">
-        <v>143.4199981689453</v>
+        <v>152.4081831545673</v>
       </c>
       <c r="E9" t="n">
-        <v>144.5500030517578</v>
+        <v>153.5350494384766</v>
       </c>
       <c r="F9" t="n">
-        <v>7249600</v>
+        <v>6559600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>143.6399993896484</v>
+        <v>153.9041611382593</v>
       </c>
       <c r="C10" t="n">
-        <v>143.9700012207031</v>
+        <v>157.0516101729205</v>
       </c>
       <c r="D10" t="n">
-        <v>142.4799957275391</v>
+        <v>153.9041611382593</v>
       </c>
       <c r="E10" t="n">
-        <v>143.1199951171875</v>
+        <v>155.7498931884766</v>
       </c>
       <c r="F10" t="n">
-        <v>9867500</v>
+        <v>6764200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>143.2799987792969</v>
+        <v>153.6321891685915</v>
       </c>
       <c r="C11" t="n">
-        <v>144.4199981689453</v>
+        <v>154.4773463220477</v>
       </c>
       <c r="D11" t="n">
-        <v>142.6799926757812</v>
+        <v>152.670479571169</v>
       </c>
       <c r="E11" t="n">
-        <v>143.4499969482422</v>
+        <v>152.8259124755859</v>
       </c>
       <c r="F11" t="n">
-        <v>12746100</v>
+        <v>7651500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>144.3000030517578</v>
+        <v>153.1076006094224</v>
       </c>
       <c r="C12" t="n">
-        <v>146.2299957275391</v>
+        <v>153.1173096060279</v>
       </c>
       <c r="D12" t="n">
-        <v>143.6199951171875</v>
+        <v>151.5144506152748</v>
       </c>
       <c r="E12" t="n">
-        <v>144.3800048828125</v>
+        <v>151.5824432373047</v>
       </c>
       <c r="F12" t="n">
-        <v>13948500</v>
+        <v>17224800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>144.4700012207031</v>
+        <v>151.6213204761912</v>
       </c>
       <c r="C13" t="n">
-        <v>144.9199981689453</v>
+        <v>151.6213204761912</v>
       </c>
       <c r="D13" t="n">
-        <v>142.5599975585938</v>
+        <v>148.677878583773</v>
       </c>
       <c r="E13" t="n">
-        <v>142.9700012207031</v>
+        <v>148.6973114013672</v>
       </c>
       <c r="F13" t="n">
-        <v>15794100</v>
+        <v>8712900</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>143.0200042724609</v>
+        <v>148.8235855824238</v>
       </c>
       <c r="C14" t="n">
-        <v>145.2700042724609</v>
+        <v>148.9110110260332</v>
       </c>
       <c r="D14" t="n">
-        <v>142.1399993896484</v>
+        <v>146.657293372131</v>
       </c>
       <c r="E14" t="n">
-        <v>144.6799926757812</v>
+        <v>148.1435852050781</v>
       </c>
       <c r="F14" t="n">
-        <v>9785200</v>
+        <v>8853400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>145.2400054931641</v>
+        <v>147.7064465894999</v>
       </c>
       <c r="C15" t="n">
-        <v>146.8000030517578</v>
+        <v>149.2413130899007</v>
       </c>
       <c r="D15" t="n">
-        <v>145</v>
+        <v>147.4538644271308</v>
       </c>
       <c r="E15" t="n">
-        <v>146.6000061035156</v>
+        <v>148.0658721923828</v>
       </c>
       <c r="F15" t="n">
-        <v>7061800</v>
+        <v>6483300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>145.7299957275391</v>
+        <v>148.8527387391331</v>
       </c>
       <c r="C16" t="n">
-        <v>146.1199951171875</v>
+        <v>149.4841793556296</v>
       </c>
       <c r="D16" t="n">
-        <v>144.9499969482422</v>
+        <v>147.4441632452525</v>
       </c>
       <c r="E16" t="n">
-        <v>145.3999938964844</v>
+        <v>147.8035888671875</v>
       </c>
       <c r="F16" t="n">
-        <v>9125700</v>
+        <v>7511400</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>145.2799987792969</v>
+        <v>147.8812940513532</v>
       </c>
       <c r="C17" t="n">
-        <v>145.9299926757812</v>
+        <v>148.3184360922971</v>
       </c>
       <c r="D17" t="n">
-        <v>144.5</v>
+        <v>147.2012936740075</v>
       </c>
       <c r="E17" t="n">
-        <v>145</v>
+        <v>148.1435852050781</v>
       </c>
       <c r="F17" t="n">
-        <v>8249100</v>
+        <v>5721100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>143.6999969482422</v>
+        <v>148.0658582502614</v>
       </c>
       <c r="C18" t="n">
-        <v>144.1499938964844</v>
+        <v>149.3287244745027</v>
       </c>
       <c r="D18" t="n">
-        <v>142.7100067138672</v>
+        <v>147.453850542637</v>
       </c>
       <c r="E18" t="n">
-        <v>143.1399993896484</v>
+        <v>149.1441497802734</v>
       </c>
       <c r="F18" t="n">
-        <v>7817200</v>
+        <v>8139700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>143.25</v>
+        <v>149.0761670451376</v>
       </c>
       <c r="C19" t="n">
-        <v>144.3999938964844</v>
+        <v>149.9698839401892</v>
       </c>
       <c r="D19" t="n">
-        <v>143.0099945068359</v>
+        <v>148.4738682940947</v>
       </c>
       <c r="E19" t="n">
-        <v>143.7799987792969</v>
+        <v>149.2607269287109</v>
       </c>
       <c r="F19" t="n">
-        <v>5868900</v>
+        <v>7762600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>143.4400024414062</v>
+        <v>149.3093029348087</v>
       </c>
       <c r="C20" t="n">
-        <v>145.8999938964844</v>
+        <v>149.4938776429776</v>
       </c>
       <c r="D20" t="n">
-        <v>142.5</v>
+        <v>147.0847270853178</v>
       </c>
       <c r="E20" t="n">
-        <v>145.1199951171875</v>
+        <v>148.8041534423828</v>
       </c>
       <c r="F20" t="n">
-        <v>12097900</v>
+        <v>7566000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>145.7599945068359</v>
+        <v>148.3572946891603</v>
       </c>
       <c r="C21" t="n">
-        <v>148.3600006103516</v>
+        <v>148.4350111318697</v>
       </c>
       <c r="D21" t="n">
-        <v>145.0899963378906</v>
+        <v>147.2984359501739</v>
       </c>
       <c r="E21" t="n">
-        <v>146.2100067138672</v>
+        <v>147.7064361572266</v>
       </c>
       <c r="F21" t="n">
-        <v>8503800</v>
+        <v>6892100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>146.4199981689453</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="C22" t="n">
-        <v>148.3200073242188</v>
+        <v>149.0470174793467</v>
       </c>
       <c r="D22" t="n">
-        <v>145.7899932861328</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="E22" t="n">
-        <v>147.6399993896484</v>
+        <v>147.920166015625</v>
       </c>
       <c r="F22" t="n">
-        <v>7431100</v>
+        <v>5212600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>147.6799926757812</v>
+        <v>147.1721399535571</v>
       </c>
       <c r="C23" t="n">
-        <v>148.2200012207031</v>
+        <v>147.9687223475034</v>
       </c>
       <c r="D23" t="n">
-        <v>146.5</v>
+        <v>146.1035574306768</v>
       </c>
       <c r="E23" t="n">
-        <v>146.9199981689453</v>
+        <v>146.11328125</v>
       </c>
       <c r="F23" t="n">
-        <v>6105800</v>
+        <v>6737000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>146.4532839352596</v>
+      </c>
+      <c r="C24" t="n">
+        <v>148.7944418250997</v>
+      </c>
+      <c r="D24" t="n">
+        <v>145.7635745697061</v>
+      </c>
+      <c r="E24" t="n">
+        <v>148.1824340820312</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6844400</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>148.4252854332665</v>
+      </c>
+      <c r="C25" t="n">
+        <v>148.4252854332665</v>
+      </c>
+      <c r="D25" t="n">
+        <v>146.3270007982578</v>
+      </c>
+      <c r="E25" t="n">
+        <v>146.3852844238281</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5254700</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>146.4338600084891</v>
+      </c>
+      <c r="C26" t="n">
+        <v>146.5601362570837</v>
+      </c>
+      <c r="D26" t="n">
+        <v>145.3069938304567</v>
+      </c>
+      <c r="E26" t="n">
+        <v>146.2784271240234</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6134500</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>146.6281558533259</v>
+      </c>
+      <c r="C27" t="n">
+        <v>147.1818651686376</v>
+      </c>
+      <c r="D27" t="n">
+        <v>145.1807147897232</v>
+      </c>
+      <c r="E27" t="n">
+        <v>145.4138641357422</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7374000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>144.7435772439311</v>
+      </c>
+      <c r="C28" t="n">
+        <v>145.1612864927987</v>
+      </c>
+      <c r="D28" t="n">
+        <v>142.7715686189899</v>
+      </c>
+      <c r="E28" t="n">
+        <v>143.2767181396484</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7511100</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>143.3544266058526</v>
+      </c>
+      <c r="C29" t="n">
+        <v>144.9864275192193</v>
+      </c>
+      <c r="D29" t="n">
+        <v>142.8784189280057</v>
+      </c>
+      <c r="E29" t="n">
+        <v>144.8990020751953</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8585300</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>144.2869860075292</v>
+      </c>
+      <c r="C30" t="n">
+        <v>145.1418520497865</v>
+      </c>
+      <c r="D30" t="n">
+        <v>143.0629853930302</v>
+      </c>
+      <c r="E30" t="n">
+        <v>143.2086944580078</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10003100</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>143.7818410230574</v>
+      </c>
+      <c r="C31" t="n">
+        <v>146.1035660756974</v>
+      </c>
+      <c r="D31" t="n">
+        <v>143.6944155813474</v>
+      </c>
+      <c r="E31" t="n">
+        <v>145.3264312744141</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8809700</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>146.2687203464973</v>
+      </c>
+      <c r="C32" t="n">
+        <v>147.6870046758011</v>
+      </c>
+      <c r="D32" t="n">
+        <v>146.1327054533545</v>
+      </c>
+      <c r="E32" t="n">
+        <v>147.0749969482422</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8612900</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>147.2595781352121</v>
+      </c>
+      <c r="C33" t="n">
+        <v>148.0367277806686</v>
+      </c>
+      <c r="D33" t="n">
+        <v>146.9778689854687</v>
+      </c>
+      <c r="E33" t="n">
+        <v>147.6190185546875</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5601300</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>147.6190101337839</v>
+      </c>
+      <c r="C34" t="n">
+        <v>147.9298610804961</v>
+      </c>
+      <c r="D34" t="n">
+        <v>146.5601365760907</v>
+      </c>
+      <c r="E34" t="n">
+        <v>147.2887115478516</v>
+      </c>
+      <c r="F34" t="n">
+        <v>6013400</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>146.9778583106544</v>
+      </c>
+      <c r="C35" t="n">
+        <v>149.076157754121</v>
+      </c>
+      <c r="D35" t="n">
+        <v>146.4824178509246</v>
+      </c>
+      <c r="E35" t="n">
+        <v>147.8521423339844</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6394400</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>147.9978775181488</v>
+      </c>
+      <c r="C36" t="n">
+        <v>148.9207362405373</v>
+      </c>
+      <c r="D36" t="n">
+        <v>146.2784363299136</v>
+      </c>
+      <c r="E36" t="n">
+        <v>147.8618774414062</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8205400</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>152.9946080342638</v>
+      </c>
+      <c r="C37" t="n">
+        <v>153.9728344665201</v>
+      </c>
+      <c r="D37" t="n">
+        <v>148.2306500856719</v>
+      </c>
+      <c r="E37" t="n">
+        <v>149.1697540283203</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11968500</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>148.3089067227305</v>
+      </c>
+      <c r="C38" t="n">
+        <v>148.4556347137148</v>
+      </c>
+      <c r="D38" t="n">
+        <v>146.8611358143341</v>
+      </c>
+      <c r="E38" t="n">
+        <v>148.4360809326172</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7775300</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>147.8295858278712</v>
+      </c>
+      <c r="C39" t="n">
+        <v>149.8349531642864</v>
+      </c>
+      <c r="D39" t="n">
+        <v>147.3404725715042</v>
+      </c>
+      <c r="E39" t="n">
+        <v>148.0741424560547</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5819300</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>147.3795937684592</v>
+      </c>
+      <c r="C40" t="n">
+        <v>147.6828415657792</v>
+      </c>
+      <c r="D40" t="n">
+        <v>145.2372755531334</v>
+      </c>
+      <c r="E40" t="n">
+        <v>145.5307464599609</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7405500</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>146.2155146062609</v>
+      </c>
+      <c r="C41" t="n">
+        <v>147.5165576287185</v>
+      </c>
+      <c r="D41" t="n">
+        <v>146.0883403861062</v>
+      </c>
+      <c r="E41" t="n">
+        <v>146.3231201171875</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6760700</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>145.4720720722042</v>
+      </c>
+      <c r="C42" t="n">
+        <v>147.8100328533669</v>
+      </c>
+      <c r="D42" t="n">
+        <v>145.2959835371417</v>
+      </c>
+      <c r="E42" t="n">
+        <v>147.0959167480469</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7930300</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>146.8318015049148</v>
+      </c>
+      <c r="C43" t="n">
+        <v>146.9491839067269</v>
+      </c>
+      <c r="D43" t="n">
+        <v>144.5525320015707</v>
+      </c>
+      <c r="E43" t="n">
+        <v>144.7970886230469</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8946400</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>145.3644630798614</v>
+      </c>
+      <c r="C44" t="n">
+        <v>146.2448609544514</v>
+      </c>
+      <c r="D44" t="n">
+        <v>143.0656248467459</v>
+      </c>
+      <c r="E44" t="n">
+        <v>143.9655914306641</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9295400</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>143.6721174868199</v>
+      </c>
+      <c r="C45" t="n">
+        <v>144.210145032931</v>
+      </c>
+      <c r="D45" t="n">
+        <v>142.478679994192</v>
+      </c>
+      <c r="E45" t="n">
+        <v>142.6156311035156</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11199900</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>142.703685564269</v>
+      </c>
+      <c r="C46" t="n">
+        <v>143.4862548173669</v>
+      </c>
+      <c r="D46" t="n">
+        <v>141.3146057355029</v>
+      </c>
+      <c r="E46" t="n">
+        <v>142.9482421875</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10024500</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>143.750363265088</v>
+      </c>
+      <c r="C47" t="n">
+        <v>144.7188127528882</v>
+      </c>
+      <c r="D47" t="n">
+        <v>142.8210511912767</v>
+      </c>
+      <c r="E47" t="n">
+        <v>143.7797088623047</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8500100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>143.1927990477494</v>
+      </c>
+      <c r="C48" t="n">
+        <v>143.4275638534467</v>
+      </c>
+      <c r="D48" t="n">
+        <v>140.9526520163762</v>
+      </c>
+      <c r="E48" t="n">
+        <v>142.3319549560547</v>
+      </c>
+      <c r="F48" t="n">
+        <v>10208100</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>142.7819294237856</v>
+      </c>
+      <c r="C49" t="n">
+        <v>145.4133458556324</v>
+      </c>
+      <c r="D49" t="n">
+        <v>142.4982354138606</v>
+      </c>
+      <c r="E49" t="n">
+        <v>145.3057403564453</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7332500</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>145.2959744173796</v>
+      </c>
+      <c r="C50" t="n">
+        <v>145.9024700440282</v>
+      </c>
+      <c r="D50" t="n">
+        <v>144.298179252126</v>
+      </c>
+      <c r="E50" t="n">
+        <v>144.7872924804688</v>
+      </c>
+      <c r="F50" t="n">
+        <v>7851100</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>144.9535841420777</v>
+      </c>
+      <c r="C51" t="n">
+        <v>145.7557369733869</v>
+      </c>
+      <c r="D51" t="n">
+        <v>144.4253484415343</v>
+      </c>
+      <c r="E51" t="n">
+        <v>144.7383880615234</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7566800</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>145.8535682267802</v>
+      </c>
+      <c r="C52" t="n">
+        <v>146.1274704359541</v>
+      </c>
+      <c r="D52" t="n">
+        <v>144.3960054571006</v>
+      </c>
+      <c r="E52" t="n">
+        <v>144.4546966552734</v>
+      </c>
+      <c r="F52" t="n">
+        <v>9150800</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>144.5329589094707</v>
+      </c>
+      <c r="C53" t="n">
+        <v>144.7579468149716</v>
+      </c>
+      <c r="D53" t="n">
+        <v>141.8526130458145</v>
+      </c>
+      <c r="E53" t="n">
+        <v>142.6449890136719</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9902300</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>143.1438871838678</v>
+      </c>
+      <c r="C54" t="n">
+        <v>144.1808048975551</v>
+      </c>
+      <c r="D54" t="n">
+        <v>142.3417342798896</v>
+      </c>
+      <c r="E54" t="n">
+        <v>143.7895202636719</v>
+      </c>
+      <c r="F54" t="n">
+        <v>10735200</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>143.7601746624582</v>
+      </c>
+      <c r="C55" t="n">
+        <v>144.3275329036233</v>
+      </c>
+      <c r="D55" t="n">
+        <v>142.6841195294514</v>
+      </c>
+      <c r="E55" t="n">
+        <v>143.7895202636719</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6367000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>143.4471249350237</v>
+      </c>
+      <c r="C56" t="n">
+        <v>145.4231465283615</v>
+      </c>
+      <c r="D56" t="n">
+        <v>142.9482348228936</v>
+      </c>
+      <c r="E56" t="n">
+        <v>144.96337890625</v>
+      </c>
+      <c r="F56" t="n">
+        <v>9021300</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>145.1492529070371</v>
+      </c>
+      <c r="C57" t="n">
+        <v>148.2013148118135</v>
+      </c>
+      <c r="D57" t="n">
+        <v>145.0709929958182</v>
+      </c>
+      <c r="E57" t="n">
+        <v>147.6339416503906</v>
+      </c>
+      <c r="F57" t="n">
+        <v>12018000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>146.8317853117887</v>
+      </c>
+      <c r="C58" t="n">
+        <v>147.1350331007276</v>
+      </c>
+      <c r="D58" t="n">
+        <v>143.3492868677268</v>
+      </c>
+      <c r="E58" t="n">
+        <v>143.7797088623047</v>
+      </c>
+      <c r="F58" t="n">
+        <v>13846900</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>144.112328038909</v>
+      </c>
+      <c r="C59" t="n">
+        <v>145.4133560843928</v>
+      </c>
+      <c r="D59" t="n">
+        <v>144.0144994231119</v>
+      </c>
+      <c r="E59" t="n">
+        <v>145.2568511962891</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10477700</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>144.6992477048879</v>
+      </c>
+      <c r="C60" t="n">
+        <v>145.7263884130947</v>
+      </c>
+      <c r="D60" t="n">
+        <v>144.3959999082808</v>
+      </c>
+      <c r="E60" t="n">
+        <v>145.0220642089844</v>
+      </c>
+      <c r="F60" t="n">
+        <v>9238500</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>144.5818741313487</v>
+      </c>
+      <c r="C61" t="n">
+        <v>145.4720637945254</v>
+      </c>
+      <c r="D61" t="n">
+        <v>143.9753635745919</v>
+      </c>
+      <c r="E61" t="n">
+        <v>144.9340362548828</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4707200</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>144.8753541574702</v>
+      </c>
+      <c r="C62" t="n">
+        <v>145.6481465436537</v>
+      </c>
+      <c r="D62" t="n">
+        <v>144.1416842645591</v>
+      </c>
+      <c r="E62" t="n">
+        <v>144.2297210693359</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8240700</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>142.1265314991037</v>
+      </c>
+      <c r="C63" t="n">
+        <v>143.0069443662482</v>
+      </c>
+      <c r="D63" t="n">
+        <v>139.4070628341484</v>
+      </c>
+      <c r="E63" t="n">
+        <v>142.6841278076172</v>
+      </c>
+      <c r="F63" t="n">
+        <v>16376800</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>142.7428176597282</v>
+      </c>
+      <c r="C64" t="n">
+        <v>145.0612098274382</v>
+      </c>
+      <c r="D64" t="n">
+        <v>142.6841264544524</v>
+      </c>
+      <c r="E64" t="n">
+        <v>143.515625</v>
+      </c>
+      <c r="F64" t="n">
+        <v>9125300</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>143.4764816751874</v>
+      </c>
+      <c r="C65" t="n">
+        <v>144.210151564052</v>
+      </c>
+      <c r="D65" t="n">
+        <v>141.3537319212585</v>
+      </c>
+      <c r="E65" t="n">
+        <v>142.1950073242188</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10479300</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>141.9993576904224</v>
+      </c>
+      <c r="C66" t="n">
+        <v>142.4591253245491</v>
+      </c>
+      <c r="D66" t="n">
+        <v>140.1309415539968</v>
+      </c>
+      <c r="E66" t="n">
+        <v>140.3265838623047</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12791700</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>139.7983368458492</v>
+      </c>
+      <c r="C67" t="n">
+        <v>139.7983368458492</v>
+      </c>
+      <c r="D67" t="n">
+        <v>135.1321927905018</v>
+      </c>
+      <c r="E67" t="n">
+        <v>135.3278350830078</v>
+      </c>
+      <c r="F67" t="n">
+        <v>17507500</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>136.1593302081787</v>
+      </c>
+      <c r="C68" t="n">
+        <v>137.8125351541944</v>
+      </c>
+      <c r="D68" t="n">
+        <v>135.9734648104776</v>
+      </c>
+      <c r="E68" t="n">
+        <v>136.5897521972656</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10375700</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>136.6093231272403</v>
+      </c>
+      <c r="C69" t="n">
+        <v>138.2038370797448</v>
+      </c>
+      <c r="D69" t="n">
+        <v>136.5017176164599</v>
+      </c>
+      <c r="E69" t="n">
+        <v>136.775634765625</v>
+      </c>
+      <c r="F69" t="n">
+        <v>13650400</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>137.9299396510316</v>
+      </c>
+      <c r="C70" t="n">
+        <v>138.7516463474312</v>
+      </c>
+      <c r="D70" t="n">
+        <v>137.3038752737911</v>
+      </c>
+      <c r="E70" t="n">
+        <v>137.6951599121094</v>
+      </c>
+      <c r="F70" t="n">
+        <v>11798000</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>137.9299404283357</v>
+      </c>
+      <c r="C71" t="n">
+        <v>139.9939989991835</v>
+      </c>
+      <c r="D71" t="n">
+        <v>137.7734206015055</v>
+      </c>
+      <c r="E71" t="n">
+        <v>139.7298736572266</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10268800</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>140.1504995323008</v>
+      </c>
+      <c r="C72" t="n">
+        <v>142.155866623658</v>
+      </c>
+      <c r="D72" t="n">
+        <v>140.0820165200331</v>
+      </c>
+      <c r="E72" t="n">
+        <v>141.9700012207031</v>
+      </c>
+      <c r="F72" t="n">
+        <v>13877700</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>142.918899809868</v>
+      </c>
+      <c r="C73" t="n">
+        <v>143.3493069381574</v>
+      </c>
+      <c r="D73" t="n">
+        <v>141.5004594218987</v>
+      </c>
+      <c r="E73" t="n">
+        <v>142.0482788085938</v>
+      </c>
+      <c r="F73" t="n">
+        <v>10251700</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>143.496050619897</v>
+      </c>
+      <c r="C74" t="n">
+        <v>145.2177239216924</v>
+      </c>
+      <c r="D74" t="n">
+        <v>143.2612708815172</v>
+      </c>
+      <c r="E74" t="n">
+        <v>144.5916595458984</v>
+      </c>
+      <c r="F74" t="n">
+        <v>9833300</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>143.4275568592265</v>
+      </c>
+      <c r="C75" t="n">
+        <v>144.2884009089423</v>
+      </c>
+      <c r="D75" t="n">
+        <v>142.1852200188561</v>
+      </c>
+      <c r="E75" t="n">
+        <v>142.3515167236328</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12239900</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>142.3417469587507</v>
+      </c>
+      <c r="C76" t="n">
+        <v>142.8699976807533</v>
+      </c>
+      <c r="D76" t="n">
+        <v>140.8059389610799</v>
+      </c>
+      <c r="E76" t="n">
+        <v>141.3146209716797</v>
+      </c>
+      <c r="F76" t="n">
+        <v>19345600</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>140.5809250079643</v>
+      </c>
+      <c r="C77" t="n">
+        <v>141.2558886976474</v>
+      </c>
+      <c r="D77" t="n">
+        <v>139.3190045706883</v>
+      </c>
+      <c r="E77" t="n">
+        <v>139.5831298828125</v>
+      </c>
+      <c r="F77" t="n">
+        <v>11731400</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>139.3875057049937</v>
+      </c>
+      <c r="C78" t="n">
+        <v>140.6004970672291</v>
+      </c>
+      <c r="D78" t="n">
+        <v>138.9864292393599</v>
+      </c>
+      <c r="E78" t="n">
+        <v>140.0624694824219</v>
+      </c>
+      <c r="F78" t="n">
+        <v>9541600</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>139.7885569290329</v>
+      </c>
+      <c r="C79" t="n">
+        <v>141.5885049823468</v>
+      </c>
+      <c r="D79" t="n">
+        <v>139.7200888377747</v>
+      </c>
+      <c r="E79" t="n">
+        <v>141.3439483642578</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3259200</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>141.1678710570003</v>
+      </c>
+      <c r="C80" t="n">
+        <v>142.4689141598225</v>
+      </c>
+      <c r="D80" t="n">
+        <v>141.1678710570003</v>
+      </c>
+      <c r="E80" t="n">
+        <v>141.5885162353516</v>
+      </c>
+      <c r="F80" t="n">
+        <v>4711500</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>141.6472138894812</v>
+      </c>
+      <c r="C81" t="n">
+        <v>141.9113392494694</v>
+      </c>
+      <c r="D81" t="n">
+        <v>140.8157153134141</v>
+      </c>
+      <c r="E81" t="n">
+        <v>141.4222259521484</v>
+      </c>
+      <c r="F81" t="n">
+        <v>7662100</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>141.1482932462777</v>
+      </c>
+      <c r="C82" t="n">
+        <v>141.3146048844386</v>
+      </c>
+      <c r="D82" t="n">
+        <v>140.4439839080415</v>
+      </c>
+      <c r="E82" t="n">
+        <v>140.9135284423828</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6006400</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>140.8646148984387</v>
+      </c>
+      <c r="C83" t="n">
+        <v>141.0015660103057</v>
+      </c>
+      <c r="D83" t="n">
+        <v>140.1113763198945</v>
+      </c>
+      <c r="E83" t="n">
+        <v>140.1896362304688</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5293200</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>139.9939944106823</v>
+      </c>
+      <c r="C84" t="n">
+        <v>140.2189823252813</v>
+      </c>
+      <c r="D84" t="n">
+        <v>138.164715640037</v>
+      </c>
+      <c r="E84" t="n">
+        <v>138.7027282714844</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8946100</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>138.0277604772737</v>
+      </c>
+      <c r="C85" t="n">
+        <v>138.2723170940466</v>
+      </c>
+      <c r="D85" t="n">
+        <v>136.560420776636</v>
+      </c>
+      <c r="E85" t="n">
+        <v>137.3136444091797</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12297300</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>137.3332072243459</v>
+      </c>
+      <c r="C86" t="n">
+        <v>138.3407792480867</v>
+      </c>
+      <c r="D86" t="n">
+        <v>136.4723631937515</v>
+      </c>
+      <c r="E86" t="n">
+        <v>136.8636627197266</v>
+      </c>
+      <c r="F86" t="n">
+        <v>10421800</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>136.7560662263838</v>
+      </c>
+      <c r="C87" t="n">
+        <v>136.7560662263838</v>
+      </c>
+      <c r="D87" t="n">
+        <v>134.6235247173271</v>
+      </c>
+      <c r="E87" t="n">
+        <v>135.0343780517578</v>
+      </c>
+      <c r="F87" t="n">
+        <v>14369100</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>134.8876360609042</v>
+      </c>
+      <c r="C88" t="n">
+        <v>138.6929361136317</v>
+      </c>
+      <c r="D88" t="n">
+        <v>134.8191679755417</v>
+      </c>
+      <c r="E88" t="n">
+        <v>138.4483795166016</v>
+      </c>
+      <c r="F88" t="n">
+        <v>9297100</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>138.6146786440839</v>
+      </c>
+      <c r="C89" t="n">
+        <v>139.2309660559118</v>
+      </c>
+      <c r="D89" t="n">
+        <v>137.7636264479789</v>
+      </c>
+      <c r="E89" t="n">
+        <v>138.7809753417969</v>
+      </c>
+      <c r="F89" t="n">
+        <v>9528500</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>139.1820801084355</v>
+      </c>
+      <c r="C90" t="n">
+        <v>140.7472486464177</v>
+      </c>
+      <c r="D90" t="n">
+        <v>138.624498705621</v>
+      </c>
+      <c r="E90" t="n">
+        <v>140.3363952636719</v>
+      </c>
+      <c r="F90" t="n">
+        <v>12812000</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>140.8646160183639</v>
+      </c>
+      <c r="C91" t="n">
+        <v>141.1972094460348</v>
+      </c>
+      <c r="D91" t="n">
+        <v>139.8570439173567</v>
+      </c>
+      <c r="E91" t="n">
+        <v>141.0993957519531</v>
+      </c>
+      <c r="F91" t="n">
+        <v>15549200</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>141.5297856973334</v>
+      </c>
+      <c r="C92" t="n">
+        <v>143.7014494581827</v>
+      </c>
+      <c r="D92" t="n">
+        <v>141.226537907345</v>
+      </c>
+      <c r="E92" t="n">
+        <v>143.1634368896484</v>
+      </c>
+      <c r="F92" t="n">
+        <v>13475000</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>142.5080371951474</v>
+      </c>
+      <c r="C93" t="n">
+        <v>143.1634621215703</v>
+      </c>
+      <c r="D93" t="n">
+        <v>141.2070090139386</v>
+      </c>
+      <c r="E93" t="n">
+        <v>141.4809112548828</v>
+      </c>
+      <c r="F93" t="n">
+        <v>10102800</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>140.6298333307039</v>
+      </c>
+      <c r="C94" t="n">
+        <v>141.5787142100195</v>
+      </c>
+      <c r="D94" t="n">
+        <v>140.5320196386769</v>
+      </c>
+      <c r="E94" t="n">
+        <v>141.3830718994141</v>
+      </c>
+      <c r="F94" t="n">
+        <v>11729300</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>141.314612307562</v>
+      </c>
+      <c r="C95" t="n">
+        <v>143.7993011474609</v>
+      </c>
+      <c r="D95" t="n">
+        <v>140.98200394032</v>
+      </c>
+      <c r="E95" t="n">
+        <v>143.7993011474609</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12901400</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>143.8579718826292</v>
+      </c>
+      <c r="C96" t="n">
+        <v>144.1612196781427</v>
+      </c>
+      <c r="D96" t="n">
+        <v>141.813482290609</v>
+      </c>
+      <c r="E96" t="n">
+        <v>142.8797454833984</v>
+      </c>
+      <c r="F96" t="n">
+        <v>14126800</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>144.8557716267987</v>
+      </c>
+      <c r="C97" t="n">
+        <v>147.6241542164368</v>
+      </c>
+      <c r="D97" t="n">
+        <v>144.2883985058945</v>
+      </c>
+      <c r="E97" t="n">
+        <v>146.6654815673828</v>
+      </c>
+      <c r="F97" t="n">
+        <v>18501900</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>148.6033244770038</v>
+      </c>
+      <c r="C98" t="n">
+        <v>149.401311303758</v>
+      </c>
+      <c r="D98" t="n">
+        <v>147.5787523243573</v>
+      </c>
+      <c r="E98" t="n">
+        <v>147.9235534667969</v>
+      </c>
+      <c r="F98" t="n">
+        <v>14562600</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>147.8939939935073</v>
+      </c>
+      <c r="C99" t="n">
+        <v>148.6427342237785</v>
+      </c>
+      <c r="D99" t="n">
+        <v>146.3177280457571</v>
+      </c>
+      <c r="E99" t="n">
+        <v>147.2733459472656</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12655700</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>145.8744105284403</v>
+      </c>
+      <c r="C100" t="n">
+        <v>147.4211225953709</v>
+      </c>
+      <c r="D100" t="n">
+        <v>145.7364720311358</v>
+      </c>
+      <c r="E100" t="n">
+        <v>146.1403961181641</v>
+      </c>
+      <c r="F100" t="n">
+        <v>9546000</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>145.8054294115807</v>
+      </c>
+      <c r="C101" t="n">
+        <v>146.5049080183409</v>
+      </c>
+      <c r="D101" t="n">
+        <v>144.6133648946463</v>
+      </c>
+      <c r="E101" t="n">
+        <v>145.1552124023438</v>
+      </c>
+      <c r="F101" t="n">
+        <v>7465800</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>145.1059620999764</v>
+      </c>
+      <c r="C102" t="n">
+        <v>147.9038617122788</v>
+      </c>
+      <c r="D102" t="n">
+        <v>144.9286383741246</v>
+      </c>
+      <c r="E102" t="n">
+        <v>147.6772613525391</v>
+      </c>
+      <c r="F102" t="n">
+        <v>11035600</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>148.1994047112546</v>
+      </c>
+      <c r="C103" t="n">
+        <v>149.7165778862847</v>
+      </c>
+      <c r="D103" t="n">
+        <v>146.9383858562462</v>
+      </c>
+      <c r="E103" t="n">
+        <v>149.5195465087891</v>
+      </c>
+      <c r="F103" t="n">
+        <v>12651400</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>150.1599009677594</v>
+      </c>
+      <c r="C104" t="n">
+        <v>151.4504737667986</v>
+      </c>
+      <c r="D104" t="n">
+        <v>149.0072516350481</v>
+      </c>
+      <c r="E104" t="n">
+        <v>150.9184875488281</v>
+      </c>
+      <c r="F104" t="n">
+        <v>10554900</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>150.3273766276017</v>
+      </c>
+      <c r="C105" t="n">
+        <v>154.2089563191786</v>
+      </c>
+      <c r="D105" t="n">
+        <v>149.9431601878661</v>
+      </c>
+      <c r="E105" t="n">
+        <v>153.0169067382812</v>
+      </c>
+      <c r="F105" t="n">
+        <v>12424700</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>153.8148971925123</v>
+      </c>
+      <c r="C106" t="n">
+        <v>156.0216726798457</v>
+      </c>
+      <c r="D106" t="n">
+        <v>153.450373358777</v>
+      </c>
+      <c r="E106" t="n">
+        <v>154.5439147949219</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12178500</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>156.4847030065954</v>
+      </c>
+      <c r="C107" t="n">
+        <v>157.2826898506833</v>
+      </c>
+      <c r="D107" t="n">
+        <v>153.8050342014295</v>
+      </c>
+      <c r="E107" t="n">
+        <v>156.2581176757812</v>
+      </c>
+      <c r="F107" t="n">
+        <v>13077700</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>155.8936117729111</v>
+      </c>
+      <c r="C108" t="n">
+        <v>157.6176626521585</v>
+      </c>
+      <c r="D108" t="n">
+        <v>155.6670114053594</v>
+      </c>
+      <c r="E108" t="n">
+        <v>156.809814453125</v>
+      </c>
+      <c r="F108" t="n">
+        <v>10441700</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>156.4058894678126</v>
+      </c>
+      <c r="C109" t="n">
+        <v>156.9181830781391</v>
+      </c>
+      <c r="D109" t="n">
+        <v>153.7065280129841</v>
+      </c>
+      <c r="E109" t="n">
+        <v>154.9971008300781</v>
+      </c>
+      <c r="F109" t="n">
+        <v>11439900</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>155.1941413082318</v>
+      </c>
+      <c r="C110" t="n">
+        <v>157.7752870937614</v>
+      </c>
+      <c r="D110" t="n">
+        <v>154.3961544070585</v>
+      </c>
+      <c r="E110" t="n">
+        <v>156.7211608886719</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9910100</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>156.2876831984424</v>
+      </c>
+      <c r="C111" t="n">
+        <v>158.7506131625079</v>
+      </c>
+      <c r="D111" t="n">
+        <v>155.8443588114169</v>
+      </c>
+      <c r="E111" t="n">
+        <v>157.6275177001953</v>
+      </c>
+      <c r="F111" t="n">
+        <v>10217300</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>157.6472078811371</v>
+      </c>
+      <c r="C112" t="n">
+        <v>160.7209393253002</v>
+      </c>
+      <c r="D112" t="n">
+        <v>157.2826840647245</v>
+      </c>
+      <c r="E112" t="n">
+        <v>158.8195648193359</v>
+      </c>
+      <c r="F112" t="n">
+        <v>13512900</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>159.3417228437737</v>
+      </c>
+      <c r="C113" t="n">
+        <v>160.1594173981944</v>
+      </c>
+      <c r="D113" t="n">
+        <v>157.3418249095697</v>
+      </c>
+      <c r="E113" t="n">
+        <v>157.6964874267578</v>
+      </c>
+      <c r="F113" t="n">
+        <v>13998900</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>157.5782363157609</v>
+      </c>
+      <c r="C114" t="n">
+        <v>159.765319051939</v>
+      </c>
+      <c r="D114" t="n">
+        <v>156.5241102403673</v>
+      </c>
+      <c r="E114" t="n">
+        <v>157.1841735839844</v>
+      </c>
+      <c r="F114" t="n">
+        <v>13319100</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>156.6226326022383</v>
+      </c>
+      <c r="C115" t="n">
+        <v>156.6226326022383</v>
+      </c>
+      <c r="D115" t="n">
+        <v>153.4602390569104</v>
+      </c>
+      <c r="E115" t="n">
+        <v>154.5340728759766</v>
+      </c>
+      <c r="F115" t="n">
+        <v>14434300</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>154.5045190368278</v>
+      </c>
+      <c r="C116" t="n">
+        <v>157.5881120570129</v>
+      </c>
+      <c r="D116" t="n">
+        <v>154.5045190368278</v>
+      </c>
+      <c r="E116" t="n">
+        <v>156.2088623046875</v>
+      </c>
+      <c r="F116" t="n">
+        <v>10724600</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>156.7704074552917</v>
+      </c>
+      <c r="C117" t="n">
+        <v>158.6717819848204</v>
+      </c>
+      <c r="D117" t="n">
+        <v>155.8147895206744</v>
+      </c>
+      <c r="E117" t="n">
+        <v>158.3959350585938</v>
+      </c>
+      <c r="F117" t="n">
+        <v>11508100</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>157.9427657722736</v>
+      </c>
+      <c r="C118" t="n">
+        <v>162.9080255197715</v>
+      </c>
+      <c r="D118" t="n">
+        <v>157.9230581252215</v>
+      </c>
+      <c r="E118" t="n">
+        <v>162.7208404541016</v>
+      </c>
+      <c r="F118" t="n">
+        <v>14772400</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>162.4548534700461</v>
+      </c>
+      <c r="C119" t="n">
+        <v>164.3956434730223</v>
+      </c>
+      <c r="D119" t="n">
+        <v>161.509096787574</v>
+      </c>
+      <c r="E119" t="n">
+        <v>162.8292236328125</v>
+      </c>
+      <c r="F119" t="n">
+        <v>9709500</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>162.1001810746762</v>
+      </c>
+      <c r="C120" t="n">
+        <v>162.5533667721119</v>
+      </c>
+      <c r="D120" t="n">
+        <v>159.6963742176143</v>
+      </c>
+      <c r="E120" t="n">
+        <v>160.9672393798828</v>
+      </c>
+      <c r="F120" t="n">
+        <v>7878500</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>161.7849314119297</v>
+      </c>
+      <c r="C121" t="n">
+        <v>162.0607783426765</v>
+      </c>
+      <c r="D121" t="n">
+        <v>160.4450970200751</v>
+      </c>
+      <c r="E121" t="n">
+        <v>161.3218994140625</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7028600</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>161.6075869258529</v>
+      </c>
+      <c r="C122" t="n">
+        <v>164.7699952425796</v>
+      </c>
+      <c r="D122" t="n">
+        <v>161.262785790902</v>
+      </c>
+      <c r="E122" t="n">
+        <v>164.7207336425781</v>
+      </c>
+      <c r="F122" t="n">
+        <v>14878500</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>162.8390539683353</v>
+      </c>
+      <c r="C123" t="n">
+        <v>164.0803801620515</v>
+      </c>
+      <c r="D123" t="n">
+        <v>161.0263413109597</v>
+      </c>
+      <c r="E123" t="n">
+        <v>161.08544921875</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9095500</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>159.7850452964264</v>
+      </c>
+      <c r="C124" t="n">
+        <v>159.7850452964264</v>
+      </c>
+      <c r="D124" t="n">
+        <v>156.267974124207</v>
+      </c>
+      <c r="E124" t="n">
+        <v>157.3516693115234</v>
+      </c>
+      <c r="F124" t="n">
+        <v>10161000</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>157.075808364692</v>
+      </c>
+      <c r="C125" t="n">
+        <v>157.2432857818942</v>
+      </c>
+      <c r="D125" t="n">
+        <v>154.9773874310153</v>
+      </c>
+      <c r="E125" t="n">
+        <v>155.9527130126953</v>
+      </c>
+      <c r="F125" t="n">
+        <v>8752700</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>154.6128732265148</v>
+      </c>
+      <c r="C126" t="n">
+        <v>154.7705043310175</v>
+      </c>
+      <c r="D126" t="n">
+        <v>151.4898802521365</v>
+      </c>
+      <c r="E126" t="n">
+        <v>151.7066192626953</v>
+      </c>
+      <c r="F126" t="n">
+        <v>10060300</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>151.3815131820191</v>
+      </c>
+      <c r="C127" t="n">
+        <v>152.1400846986481</v>
+      </c>
+      <c r="D127" t="n">
+        <v>149.6377547626651</v>
+      </c>
+      <c r="E127" t="n">
+        <v>151.3519592285156</v>
+      </c>
+      <c r="F127" t="n">
+        <v>8187900</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>150.8790677258081</v>
+      </c>
+      <c r="C128" t="n">
+        <v>153.9133989264833</v>
+      </c>
+      <c r="D128" t="n">
+        <v>150.6327747552909</v>
+      </c>
+      <c r="E128" t="n">
+        <v>152.9183807373047</v>
+      </c>
+      <c r="F128" t="n">
+        <v>12494900</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>153.1843767336366</v>
+      </c>
+      <c r="C129" t="n">
+        <v>154.8197505838155</v>
+      </c>
+      <c r="D129" t="n">
+        <v>151.322402533996</v>
+      </c>
+      <c r="E129" t="n">
+        <v>153.6966552734375</v>
+      </c>
+      <c r="F129" t="n">
+        <v>7756800</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>152.9282368144603</v>
+      </c>
+      <c r="C130" t="n">
+        <v>153.07602162573</v>
+      </c>
+      <c r="D130" t="n">
+        <v>149.1845804169242</v>
+      </c>
+      <c r="E130" t="n">
+        <v>151.0465698242188</v>
+      </c>
+      <c r="F130" t="n">
+        <v>8855100</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>149.9530221525258</v>
+      </c>
+      <c r="C131" t="n">
+        <v>150.7805629442461</v>
+      </c>
+      <c r="D131" t="n">
+        <v>148.100894162221</v>
+      </c>
+      <c r="E131" t="n">
+        <v>148.2683715820312</v>
+      </c>
+      <c r="F131" t="n">
+        <v>8489300</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>149.1254626514495</v>
+      </c>
+      <c r="C132" t="n">
+        <v>150.287973286658</v>
+      </c>
+      <c r="D132" t="n">
+        <v>147.9531057091528</v>
+      </c>
+      <c r="E132" t="n">
+        <v>148.4161376953125</v>
+      </c>
+      <c r="F132" t="n">
+        <v>7298900</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>149.6082100748309</v>
+      </c>
+      <c r="C133" t="n">
+        <v>150.3766429785721</v>
+      </c>
+      <c r="D133" t="n">
+        <v>148.4161454237534</v>
+      </c>
+      <c r="E133" t="n">
+        <v>149.8643493652344</v>
+      </c>
+      <c r="F133" t="n">
+        <v>6944000</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>150.7411528047512</v>
+      </c>
+      <c r="C134" t="n">
+        <v>151.184492202826</v>
+      </c>
+      <c r="D134" t="n">
+        <v>148.9579940023762</v>
+      </c>
+      <c r="E134" t="n">
+        <v>149.2338409423828</v>
+      </c>
+      <c r="F134" t="n">
+        <v>6147700</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>147.0960143427481</v>
+      </c>
+      <c r="C135" t="n">
+        <v>147.4014152272885</v>
+      </c>
+      <c r="D135" t="n">
+        <v>144.2882834404146</v>
+      </c>
+      <c r="E135" t="n">
+        <v>144.5345764160156</v>
+      </c>
+      <c r="F135" t="n">
+        <v>10059300</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>144.0518332623683</v>
+      </c>
+      <c r="C136" t="n">
+        <v>145.1946362491204</v>
+      </c>
+      <c r="D136" t="n">
+        <v>142.6430296593396</v>
+      </c>
+      <c r="E136" t="n">
+        <v>142.6922912597656</v>
+      </c>
+      <c r="F136" t="n">
+        <v>10340300</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>142.8400731159778</v>
+      </c>
+      <c r="C137" t="n">
+        <v>143.6577675620949</v>
+      </c>
+      <c r="D137" t="n">
+        <v>142.1110405292816</v>
+      </c>
+      <c r="E137" t="n">
+        <v>142.1405944824219</v>
+      </c>
+      <c r="F137" t="n">
+        <v>60620900</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>143.9828640073101</v>
+      </c>
+      <c r="C138" t="n">
+        <v>143.9828640073101</v>
+      </c>
+      <c r="D138" t="n">
+        <v>141.3524568960289</v>
+      </c>
+      <c r="E138" t="n">
+        <v>141.8549041748047</v>
+      </c>
+      <c r="F138" t="n">
+        <v>10315600</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>141.2046936096272</v>
+      </c>
+      <c r="C139" t="n">
+        <v>143.0765142514037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>140.1209984806846</v>
+      </c>
+      <c r="E139" t="n">
+        <v>141.0372161865234</v>
+      </c>
+      <c r="F139" t="n">
+        <v>8567600</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>141.6086107263538</v>
+      </c>
+      <c r="C140" t="n">
+        <v>141.9632732026604</v>
+      </c>
+      <c r="D140" t="n">
+        <v>140.1209915742622</v>
+      </c>
+      <c r="E140" t="n">
+        <v>141.7859344482422</v>
+      </c>
+      <c r="F140" t="n">
+        <v>8418100</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>141.5593542987915</v>
+      </c>
+      <c r="C141" t="n">
+        <v>142.4263103908934</v>
+      </c>
+      <c r="D141" t="n">
+        <v>140.1308580343274</v>
+      </c>
+      <c r="E141" t="n">
+        <v>140.3081817626953</v>
+      </c>
+      <c r="F141" t="n">
+        <v>6443200</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>140.6037336363113</v>
+      </c>
+      <c r="C142" t="n">
+        <v>141.9435680108036</v>
+      </c>
+      <c r="D142" t="n">
+        <v>139.9042549786409</v>
+      </c>
+      <c r="E142" t="n">
+        <v>140.5938873291016</v>
+      </c>
+      <c r="F142" t="n">
+        <v>11558300</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>140.9189847788946</v>
+      </c>
+      <c r="C143" t="n">
+        <v>143.4114835656516</v>
+      </c>
+      <c r="D143" t="n">
+        <v>140.4559678065659</v>
+      </c>
+      <c r="E143" t="n">
+        <v>142.5740814208984</v>
+      </c>
+      <c r="F143" t="n">
+        <v>11616300</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>142.6726031682958</v>
+      </c>
+      <c r="C144" t="n">
+        <v>142.7711113397407</v>
+      </c>
+      <c r="D144" t="n">
+        <v>140.1702580996175</v>
+      </c>
+      <c r="E144" t="n">
+        <v>142.2982330322266</v>
+      </c>
+      <c r="F144" t="n">
+        <v>10407500</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>141.7859527393269</v>
+      </c>
+      <c r="C145" t="n">
+        <v>142.8203863480455</v>
+      </c>
+      <c r="D145" t="n">
+        <v>141.0864890360487</v>
+      </c>
+      <c r="E145" t="n">
+        <v>141.9534301757812</v>
+      </c>
+      <c r="F145" t="n">
+        <v>8061700</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>141.9534207153344</v>
+      </c>
+      <c r="C146" t="n">
+        <v>142.0716515698294</v>
+      </c>
+      <c r="D146" t="n">
+        <v>140.4658165030053</v>
+      </c>
+      <c r="E146" t="n">
+        <v>140.997802734375</v>
+      </c>
+      <c r="F146" t="n">
+        <v>5941700</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>140.8894315190035</v>
+      </c>
+      <c r="C147" t="n">
+        <v>141.5396485970176</v>
+      </c>
+      <c r="D147" t="n">
+        <v>139.8155977290451</v>
+      </c>
+      <c r="E147" t="n">
+        <v>140.6529998779297</v>
+      </c>
+      <c r="F147" t="n">
+        <v>6823100</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>140.4066990917555</v>
+      </c>
+      <c r="C148" t="n">
+        <v>140.6529920592033</v>
+      </c>
+      <c r="D148" t="n">
+        <v>138.6530943661295</v>
+      </c>
+      <c r="E148" t="n">
+        <v>139.2047882080078</v>
+      </c>
+      <c r="F148" t="n">
+        <v>7207500</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>141.0273529653376</v>
+      </c>
+      <c r="C149" t="n">
+        <v>142.9582965240978</v>
+      </c>
+      <c r="D149" t="n">
+        <v>139.766334122587</v>
+      </c>
+      <c r="E149" t="n">
+        <v>142.7514038085938</v>
+      </c>
+      <c r="F149" t="n">
+        <v>10849700</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>142.2489765209199</v>
+      </c>
+      <c r="C150" t="n">
+        <v>144.7611679868877</v>
+      </c>
+      <c r="D150" t="n">
+        <v>140.8795881188284</v>
+      </c>
+      <c r="E150" t="n">
+        <v>144.4853210449219</v>
+      </c>
+      <c r="F150" t="n">
+        <v>6794800</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>144.7118962366312</v>
+      </c>
+      <c r="C151" t="n">
+        <v>144.7118962366312</v>
+      </c>
+      <c r="D151" t="n">
+        <v>142.6134753307435</v>
+      </c>
+      <c r="E151" t="n">
+        <v>143.0075531005859</v>
+      </c>
+      <c r="F151" t="n">
+        <v>9790300</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>142.8499157089539</v>
+      </c>
+      <c r="C152" t="n">
+        <v>142.9385775660697</v>
+      </c>
+      <c r="D152" t="n">
+        <v>140.5150632763963</v>
+      </c>
+      <c r="E152" t="n">
+        <v>141.4509735107422</v>
+      </c>
+      <c r="F152" t="n">
+        <v>7121400</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>141.1160402826616</v>
+      </c>
+      <c r="C153" t="n">
+        <v>142.5740906086617</v>
+      </c>
+      <c r="D153" t="n">
+        <v>140.6530082479637</v>
+      </c>
+      <c r="E153" t="n">
+        <v>142.2391357421875</v>
+      </c>
+      <c r="F153" t="n">
+        <v>6621600</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>142.2194162805844</v>
+      </c>
+      <c r="C154" t="n">
+        <v>142.2588165423252</v>
+      </c>
+      <c r="D154" t="n">
+        <v>140.1505492747316</v>
+      </c>
+      <c r="E154" t="n">
+        <v>141.2539520263672</v>
+      </c>
+      <c r="F154" t="n">
+        <v>7698200</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>141.0766226846627</v>
+      </c>
+      <c r="C155" t="n">
+        <v>142.1504565210129</v>
+      </c>
+      <c r="D155" t="n">
+        <v>140.5446364367332</v>
+      </c>
+      <c r="E155" t="n">
+        <v>140.9879608154297</v>
+      </c>
+      <c r="F155" t="n">
+        <v>6947100</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>141.2835176988996</v>
+      </c>
+      <c r="C156" t="n">
+        <v>145.4015293724886</v>
+      </c>
+      <c r="D156" t="n">
+        <v>141.0372247031338</v>
+      </c>
+      <c r="E156" t="n">
+        <v>144.7513122558594</v>
+      </c>
+      <c r="F156" t="n">
+        <v>10886000</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>143.894200416821</v>
+      </c>
+      <c r="C157" t="n">
+        <v>144.4853095497371</v>
+      </c>
+      <c r="D157" t="n">
+        <v>141.4608247039461</v>
+      </c>
+      <c r="E157" t="n">
+        <v>142.3474884033203</v>
+      </c>
+      <c r="F157" t="n">
+        <v>8084700</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>142.4755543482728</v>
+      </c>
+      <c r="C158" t="n">
+        <v>142.4755543482728</v>
+      </c>
+      <c r="D158" t="n">
+        <v>140.2096710205078</v>
+      </c>
+      <c r="E158" t="n">
+        <v>140.2096710205078</v>
+      </c>
+      <c r="F158" t="n">
+        <v>11197200</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>140.3869953464167</v>
+      </c>
+      <c r="C159" t="n">
+        <v>141.175135870657</v>
+      </c>
+      <c r="D159" t="n">
+        <v>140.1111484178121</v>
+      </c>
+      <c r="E159" t="n">
+        <v>140.7318115234375</v>
+      </c>
+      <c r="F159" t="n">
+        <v>7236300</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>141.2736481824844</v>
+      </c>
+      <c r="C160" t="n">
+        <v>144.0616865371081</v>
+      </c>
+      <c r="D160" t="n">
+        <v>141.2736481824844</v>
+      </c>
+      <c r="E160" t="n">
+        <v>143.5494079589844</v>
+      </c>
+      <c r="F160" t="n">
+        <v>11288800</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>150.8836541197979</v>
+      </c>
+      <c r="C161" t="n">
+        <v>151.2906197995367</v>
+      </c>
+      <c r="D161" t="n">
+        <v>146.5261830755894</v>
+      </c>
+      <c r="E161" t="n">
+        <v>147.08203125</v>
+      </c>
+      <c r="F161" t="n">
+        <v>13786200</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>146.3276654919543</v>
+      </c>
+      <c r="C162" t="n">
+        <v>148.59077024601</v>
+      </c>
+      <c r="D162" t="n">
+        <v>146.3276654919543</v>
+      </c>
+      <c r="E162" t="n">
+        <v>147.3003997802734</v>
+      </c>
+      <c r="F162" t="n">
+        <v>9166400</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>148.9183255527001</v>
+      </c>
+      <c r="C163" t="n">
+        <v>150.0697339670296</v>
+      </c>
+      <c r="D163" t="n">
+        <v>147.3301749711611</v>
+      </c>
+      <c r="E163" t="n">
+        <v>148.064697265625</v>
+      </c>
+      <c r="F163" t="n">
+        <v>7965700</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>147.2011489489405</v>
+      </c>
+      <c r="C164" t="n">
+        <v>147.6478115682369</v>
+      </c>
+      <c r="D164" t="n">
+        <v>144.8090026189782</v>
+      </c>
+      <c r="E164" t="n">
+        <v>145.3747863769531</v>
+      </c>
+      <c r="F164" t="n">
+        <v>9002400</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>146.0001068115234</v>
+      </c>
+      <c r="C165" t="n">
+        <v>146.6254435609453</v>
+      </c>
+      <c r="D165" t="n">
+        <v>144.8685544504002</v>
+      </c>
+      <c r="E165" t="n">
+        <v>146.0001068115234</v>
+      </c>
+      <c r="F165" t="n">
+        <v>9491700</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>146.7743191747914</v>
+      </c>
+      <c r="C166" t="n">
+        <v>148.1738750980608</v>
+      </c>
+      <c r="D166" t="n">
+        <v>145.3747783972478</v>
+      </c>
+      <c r="E166" t="n">
+        <v>146.1688385009766</v>
+      </c>
+      <c r="F166" t="n">
+        <v>6814800</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>144.977737605514</v>
+      </c>
+      <c r="C167" t="n">
+        <v>144.977737605514</v>
+      </c>
+      <c r="D167" t="n">
+        <v>142.2084173171452</v>
+      </c>
+      <c r="E167" t="n">
+        <v>142.3572998046875</v>
+      </c>
+      <c r="F167" t="n">
+        <v>9642800</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>142.3175981532361</v>
+      </c>
+      <c r="C168" t="n">
+        <v>144.8189147356386</v>
+      </c>
+      <c r="D168" t="n">
+        <v>141.1264777093581</v>
+      </c>
+      <c r="E168" t="n">
+        <v>143.8263244628906</v>
+      </c>
+      <c r="F168" t="n">
+        <v>7664300</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>145.3152221312864</v>
+      </c>
+      <c r="C169" t="n">
+        <v>147.8463305694715</v>
+      </c>
+      <c r="D169" t="n">
+        <v>144.8586390489098</v>
+      </c>
+      <c r="E169" t="n">
+        <v>146.8041076660156</v>
+      </c>
+      <c r="F169" t="n">
+        <v>9399500</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>146.8934445898874</v>
+      </c>
+      <c r="C170" t="n">
+        <v>146.8934445898874</v>
+      </c>
+      <c r="D170" t="n">
+        <v>144.9380404787042</v>
+      </c>
+      <c r="E170" t="n">
+        <v>144.9777374267578</v>
+      </c>
+      <c r="F170" t="n">
+        <v>9545800</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>145.4641093327384</v>
+      </c>
+      <c r="C171" t="n">
+        <v>146.4269231210903</v>
+      </c>
+      <c r="D171" t="n">
+        <v>145.1266322707271</v>
+      </c>
+      <c r="E171" t="n">
+        <v>145.3350677490234</v>
+      </c>
+      <c r="F171" t="n">
+        <v>5741000</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>144.7097318886224</v>
+      </c>
+      <c r="C172" t="n">
+        <v>144.8685499701872</v>
+      </c>
+      <c r="D172" t="n">
+        <v>140.9180448520501</v>
+      </c>
+      <c r="E172" t="n">
+        <v>142.2977447509766</v>
+      </c>
+      <c r="F172" t="n">
+        <v>7489500</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>143.280415861365</v>
+      </c>
+      <c r="C173" t="n">
+        <v>144.7792217618835</v>
+      </c>
+      <c r="D173" t="n">
+        <v>141.8014508619235</v>
+      </c>
+      <c r="E173" t="n">
+        <v>142.8436737060547</v>
+      </c>
+      <c r="F173" t="n">
+        <v>9051200</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>142.0892960817053</v>
+      </c>
+      <c r="C174" t="n">
+        <v>143.5980375858882</v>
+      </c>
+      <c r="D174" t="n">
+        <v>140.610346220736</v>
+      </c>
+      <c r="E174" t="n">
+        <v>141.1860504150391</v>
+      </c>
+      <c r="F174" t="n">
+        <v>6685900</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>142.1190761527801</v>
+      </c>
+      <c r="C175" t="n">
+        <v>143.2109315738657</v>
+      </c>
+      <c r="D175" t="n">
+        <v>141.5731635879637</v>
+      </c>
+      <c r="E175" t="n">
+        <v>141.6525726318359</v>
+      </c>
+      <c r="F175" t="n">
+        <v>9636200</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>142.337438212696</v>
+      </c>
+      <c r="C176" t="n">
+        <v>142.337438212696</v>
+      </c>
+      <c r="D176" t="n">
+        <v>140.1537426546991</v>
+      </c>
+      <c r="E176" t="n">
+        <v>140.5210113525391</v>
+      </c>
+      <c r="F176" t="n">
+        <v>6989400</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>141.0470859006894</v>
+      </c>
+      <c r="C177" t="n">
+        <v>143.3598079421396</v>
+      </c>
+      <c r="D177" t="n">
+        <v>140.5805672539439</v>
+      </c>
+      <c r="E177" t="n">
+        <v>141.3349304199219</v>
+      </c>
+      <c r="F177" t="n">
+        <v>7731200</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>141.4143347616525</v>
+      </c>
+      <c r="C178" t="n">
+        <v>142.6451521296186</v>
+      </c>
+      <c r="D178" t="n">
+        <v>139.8063433960926</v>
+      </c>
+      <c r="E178" t="n">
+        <v>140.2530059814453</v>
+      </c>
+      <c r="F178" t="n">
+        <v>8355800</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>140.4018973938673</v>
+      </c>
+      <c r="C179" t="n">
+        <v>142.1587864968038</v>
+      </c>
+      <c r="D179" t="n">
+        <v>139.578045612781</v>
+      </c>
+      <c r="E179" t="n">
+        <v>141.3845672607422</v>
+      </c>
+      <c r="F179" t="n">
+        <v>8375600</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>140.8287217143626</v>
+      </c>
+      <c r="C180" t="n">
+        <v>142.655084297577</v>
+      </c>
+      <c r="D180" t="n">
+        <v>139.0519765313656</v>
+      </c>
+      <c r="E180" t="n">
+        <v>142.3374481201172</v>
+      </c>
+      <c r="F180" t="n">
+        <v>6297300</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>142.8039672134308</v>
+      </c>
+      <c r="C181" t="n">
+        <v>143.5682660152007</v>
+      </c>
+      <c r="D181" t="n">
+        <v>142.4664901331732</v>
+      </c>
+      <c r="E181" t="n">
+        <v>143.3697509765625</v>
+      </c>
+      <c r="F181" t="n">
+        <v>4616700</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>143.439213854944</v>
+      </c>
+      <c r="C182" t="n">
+        <v>144.5310692055886</v>
+      </c>
+      <c r="D182" t="n">
+        <v>141.473889369509</v>
+      </c>
+      <c r="E182" t="n">
+        <v>141.9007110595703</v>
+      </c>
+      <c r="F182" t="n">
+        <v>8157200</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>142.397017874141</v>
+      </c>
+      <c r="C183" t="n">
+        <v>147.4393635097026</v>
+      </c>
+      <c r="D183" t="n">
+        <v>142.397017874141</v>
+      </c>
+      <c r="E183" t="n">
+        <v>146.3971557617188</v>
+      </c>
+      <c r="F183" t="n">
+        <v>10048900</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>145.612997111615</v>
+      </c>
+      <c r="C184" t="n">
+        <v>145.612997111615</v>
+      </c>
+      <c r="D184" t="n">
+        <v>143.9355170452321</v>
+      </c>
+      <c r="E184" t="n">
+        <v>144.828857421875</v>
+      </c>
+      <c r="F184" t="n">
+        <v>10196700</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>144.4417452563355</v>
+      </c>
+      <c r="C185" t="n">
+        <v>144.5608512461645</v>
+      </c>
+      <c r="D185" t="n">
+        <v>142.1389284814664</v>
+      </c>
+      <c r="E185" t="n">
+        <v>142.4962615966797</v>
+      </c>
+      <c r="F185" t="n">
+        <v>12355800</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>140.4713875281435</v>
+      </c>
+      <c r="C186" t="n">
+        <v>140.7691676558347</v>
+      </c>
+      <c r="D186" t="n">
+        <v>137.8310936193964</v>
+      </c>
+      <c r="E186" t="n">
+        <v>139.2405700683594</v>
+      </c>
+      <c r="F186" t="n">
+        <v>11093800</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>139.0817554467106</v>
+      </c>
+      <c r="C187" t="n">
+        <v>140.0743457999317</v>
+      </c>
+      <c r="D187" t="n">
+        <v>137.999835596674</v>
+      </c>
+      <c r="E187" t="n">
+        <v>139.7765808105469</v>
+      </c>
+      <c r="F187" t="n">
+        <v>9599500</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>139.8857522909846</v>
+      </c>
+      <c r="C188" t="n">
+        <v>141.3944938803485</v>
+      </c>
+      <c r="D188" t="n">
+        <v>138.9626505253011</v>
+      </c>
+      <c r="E188" t="n">
+        <v>139.1512451171875</v>
+      </c>
+      <c r="F188" t="n">
+        <v>9351000</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>141.6426337542266</v>
+      </c>
+      <c r="C189" t="n">
+        <v>142.079375912544</v>
+      </c>
+      <c r="D189" t="n">
+        <v>138.8534574153755</v>
+      </c>
+      <c r="E189" t="n">
+        <v>139.7368621826172</v>
+      </c>
+      <c r="F189" t="n">
+        <v>8194000</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>141.1661955784844</v>
+      </c>
+      <c r="C190" t="n">
+        <v>147.131657909349</v>
+      </c>
+      <c r="D190" t="n">
+        <v>140.7493094643581</v>
+      </c>
+      <c r="E190" t="n">
+        <v>145.4541778564453</v>
+      </c>
+      <c r="F190" t="n">
+        <v>10963200</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>144.709731142363</v>
+      </c>
+      <c r="C191" t="n">
+        <v>145.4641094530425</v>
+      </c>
+      <c r="D191" t="n">
+        <v>143.9454475270099</v>
+      </c>
+      <c r="E191" t="n">
+        <v>144.0248565673828</v>
+      </c>
+      <c r="F191" t="n">
+        <v>7200700</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>143.598043761205</v>
+      </c>
+      <c r="C192" t="n">
+        <v>148.3724009095588</v>
+      </c>
+      <c r="D192" t="n">
+        <v>143.4590817183783</v>
+      </c>
+      <c r="E192" t="n">
+        <v>147.5684051513672</v>
+      </c>
+      <c r="F192" t="n">
+        <v>8259300</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>148.7992154215363</v>
+      </c>
+      <c r="C193" t="n">
+        <v>149.3153514723138</v>
+      </c>
+      <c r="D193" t="n">
+        <v>147.2805534750766</v>
+      </c>
+      <c r="E193" t="n">
+        <v>147.9455871582031</v>
+      </c>
+      <c r="F193" t="n">
+        <v>7345900</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>147.598177848302</v>
+      </c>
+      <c r="C194" t="n">
+        <v>148.5113591270304</v>
+      </c>
+      <c r="D194" t="n">
+        <v>146.6750761188154</v>
+      </c>
+      <c r="E194" t="n">
+        <v>147.2408447265625</v>
+      </c>
+      <c r="F194" t="n">
+        <v>6684700</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>148.2731427996088</v>
+      </c>
+      <c r="C195" t="n">
+        <v>149.087058964007</v>
+      </c>
+      <c r="D195" t="n">
+        <v>147.2011434657927</v>
+      </c>
+      <c r="E195" t="n">
+        <v>148.5014343261719</v>
+      </c>
+      <c r="F195" t="n">
+        <v>6832000</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>147.6577229757893</v>
+      </c>
+      <c r="C196" t="n">
+        <v>150.377425765528</v>
+      </c>
+      <c r="D196" t="n">
+        <v>147.6577229757893</v>
+      </c>
+      <c r="E196" t="n">
+        <v>149.3451385498047</v>
+      </c>
+      <c r="F196" t="n">
+        <v>9158900</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>150.3873579771785</v>
+      </c>
+      <c r="C197" t="n">
+        <v>151.8861790939718</v>
+      </c>
+      <c r="D197" t="n">
+        <v>149.4344797259463</v>
+      </c>
+      <c r="E197" t="n">
+        <v>151.360107421875</v>
+      </c>
+      <c r="F197" t="n">
+        <v>8518900</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>151.2509186348782</v>
+      </c>
+      <c r="C198" t="n">
+        <v>151.8067667938</v>
+      </c>
+      <c r="D198" t="n">
+        <v>148.6602572796902</v>
+      </c>
+      <c r="E198" t="n">
+        <v>149.4443969726562</v>
+      </c>
+      <c r="F198" t="n">
+        <v>7055800</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>149.7520913576046</v>
+      </c>
+      <c r="C199" t="n">
+        <v>151.1615677439354</v>
+      </c>
+      <c r="D199" t="n">
+        <v>149.067201638067</v>
+      </c>
+      <c r="E199" t="n">
+        <v>149.2657318115234</v>
+      </c>
+      <c r="F199" t="n">
+        <v>17076100</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>148.9977261100366</v>
+      </c>
+      <c r="C200" t="n">
+        <v>149.7719453093657</v>
+      </c>
+      <c r="D200" t="n">
+        <v>146.4765534870951</v>
+      </c>
+      <c r="E200" t="n">
+        <v>146.5857238769531</v>
+      </c>
+      <c r="F200" t="n">
+        <v>10533000</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>148.5510669184904</v>
+      </c>
+      <c r="C201" t="n">
+        <v>150.2483878382925</v>
+      </c>
+      <c r="D201" t="n">
+        <v>148.2632072518497</v>
+      </c>
+      <c r="E201" t="n">
+        <v>149.7421722412109</v>
+      </c>
+      <c r="F201" t="n">
+        <v>7259600</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>150.8638042327417</v>
+      </c>
+      <c r="C202" t="n">
+        <v>152.213727638368</v>
+      </c>
+      <c r="D202" t="n">
+        <v>149.8017253482469</v>
+      </c>
+      <c r="E202" t="n">
+        <v>150.9134216308594</v>
+      </c>
+      <c r="F202" t="n">
+        <v>8618500</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>150.446917666229</v>
+      </c>
+      <c r="C203" t="n">
+        <v>151.1615687416308</v>
+      </c>
+      <c r="D203" t="n">
+        <v>146.7247040752409</v>
+      </c>
+      <c r="E203" t="n">
+        <v>147.399658203125</v>
+      </c>
+      <c r="F203" t="n">
+        <v>11197200</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>149.226028638664</v>
+      </c>
+      <c r="C204" t="n">
+        <v>149.7620359058753</v>
+      </c>
+      <c r="D204" t="n">
+        <v>147.3202569962244</v>
+      </c>
+      <c r="E204" t="n">
+        <v>147.9158172607422</v>
+      </c>
+      <c r="F204" t="n">
+        <v>16724600</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>147.627945424002</v>
+      </c>
+      <c r="C205" t="n">
+        <v>147.945581577785</v>
+      </c>
+      <c r="D205" t="n">
+        <v>145.9504654579339</v>
+      </c>
+      <c r="E205" t="n">
+        <v>147.3500213623047</v>
+      </c>
+      <c r="F205" t="n">
+        <v>10387700</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>146.4368410119005</v>
+      </c>
+      <c r="C206" t="n">
+        <v>146.4368410119005</v>
+      </c>
+      <c r="D206" t="n">
+        <v>143.1017371059213</v>
+      </c>
+      <c r="E206" t="n">
+        <v>145.5534362792969</v>
+      </c>
+      <c r="F206" t="n">
+        <v>9353800</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>145.4442602082673</v>
+      </c>
+      <c r="C207" t="n">
+        <v>146.4070740424418</v>
+      </c>
+      <c r="D207" t="n">
+        <v>144.4715259232294</v>
+      </c>
+      <c r="E207" t="n">
+        <v>146.3375854492188</v>
+      </c>
+      <c r="F207" t="n">
+        <v>9571700</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>147.4790688253476</v>
+      </c>
+      <c r="C208" t="n">
+        <v>150.5461692222369</v>
+      </c>
+      <c r="D208" t="n">
+        <v>146.6452966069997</v>
+      </c>
+      <c r="E208" t="n">
+        <v>150.2881011962891</v>
+      </c>
+      <c r="F208" t="n">
+        <v>9256000</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>149.5635029567411</v>
+      </c>
+      <c r="C209" t="n">
+        <v>150.0995102140475</v>
+      </c>
+      <c r="D209" t="n">
+        <v>145.8710808804345</v>
+      </c>
+      <c r="E209" t="n">
+        <v>148.2036590576172</v>
+      </c>
+      <c r="F209" t="n">
+        <v>8323100</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>151.5288345729856</v>
+      </c>
+      <c r="C210" t="n">
+        <v>152.3526863163115</v>
+      </c>
+      <c r="D210" t="n">
+        <v>149.4940214860459</v>
+      </c>
+      <c r="E210" t="n">
+        <v>151.6181640625</v>
+      </c>
+      <c r="F210" t="n">
+        <v>8061400</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>149.8414437624326</v>
+      </c>
+      <c r="C211" t="n">
+        <v>149.950629305204</v>
+      </c>
+      <c r="D211" t="n">
+        <v>147.2507823800627</v>
+      </c>
+      <c r="E211" t="n">
+        <v>147.3003997802734</v>
+      </c>
+      <c r="F211" t="n">
+        <v>14272300</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>145.6824775579256</v>
+      </c>
+      <c r="C212" t="n">
+        <v>146.5658822886928</v>
+      </c>
+      <c r="D212" t="n">
+        <v>144.5211487643815</v>
+      </c>
+      <c r="E212" t="n">
+        <v>145.7618865966797</v>
+      </c>
+      <c r="F212" t="n">
+        <v>7748000</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>146.0100381106733</v>
+      </c>
+      <c r="C213" t="n">
+        <v>147.4889879534934</v>
+      </c>
+      <c r="D213" t="n">
+        <v>145.6229285023594</v>
+      </c>
+      <c r="E213" t="n">
+        <v>145.9504699707031</v>
+      </c>
+      <c r="F213" t="n">
+        <v>12473000</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>146.9827701076717</v>
+      </c>
+      <c r="C214" t="n">
+        <v>148.9381741659779</v>
+      </c>
+      <c r="D214" t="n">
+        <v>146.0199563268518</v>
+      </c>
+      <c r="E214" t="n">
+        <v>147.2706146240234</v>
+      </c>
+      <c r="F214" t="n">
+        <v>7816100</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>147.2706141757336</v>
+      </c>
+      <c r="C215" t="n">
+        <v>147.6478033266625</v>
+      </c>
+      <c r="D215" t="n">
+        <v>144.5112144243791</v>
+      </c>
+      <c r="E215" t="n">
+        <v>144.9975891113281</v>
+      </c>
+      <c r="F215" t="n">
+        <v>7668100</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>144.2035234458952</v>
+      </c>
+      <c r="C216" t="n">
+        <v>147.4889950493996</v>
+      </c>
+      <c r="D216" t="n">
+        <v>143.5881222814616</v>
+      </c>
+      <c r="E216" t="n">
+        <v>146.9530029296875</v>
+      </c>
+      <c r="F216" t="n">
+        <v>6180000</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>148.3823251540053</v>
+      </c>
+      <c r="C217" t="n">
+        <v>150.3972821936961</v>
+      </c>
+      <c r="D217" t="n">
+        <v>147.0820191757993</v>
+      </c>
+      <c r="E217" t="n">
+        <v>150.3774261474609</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6485400</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>151.7273476549808</v>
+      </c>
+      <c r="C218" t="n">
+        <v>153.1765360977979</v>
+      </c>
+      <c r="D218" t="n">
+        <v>148.2036492050291</v>
+      </c>
+      <c r="E218" t="n">
+        <v>148.8686828613281</v>
+      </c>
+      <c r="F218" t="n">
+        <v>8917400</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>148.4518004486472</v>
+      </c>
+      <c r="C219" t="n">
+        <v>148.9878076836025</v>
+      </c>
+      <c r="D219" t="n">
+        <v>147.3301685811182</v>
+      </c>
+      <c r="E219" t="n">
+        <v>148.0249938964844</v>
+      </c>
+      <c r="F219" t="n">
+        <v>5788300</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>146.7643973953222</v>
+      </c>
+      <c r="C220" t="n">
+        <v>147.3103250709858</v>
+      </c>
+      <c r="D220" t="n">
+        <v>145.7916631750561</v>
+      </c>
+      <c r="E220" t="n">
+        <v>147.0026245117188</v>
+      </c>
+      <c r="F220" t="n">
+        <v>7027600</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>148.3922474549245</v>
+      </c>
+      <c r="C221" t="n">
+        <v>149.3451407916641</v>
+      </c>
+      <c r="D221" t="n">
+        <v>147.7172933317669</v>
+      </c>
+      <c r="E221" t="n">
+        <v>148.0249938964844</v>
+      </c>
+      <c r="F221" t="n">
+        <v>5371200</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>145.057144942689</v>
+      </c>
+      <c r="C222" t="n">
+        <v>146.5162538863596</v>
+      </c>
+      <c r="D222" t="n">
+        <v>144.5112172519064</v>
+      </c>
+      <c r="E222" t="n">
+        <v>145.8809967041016</v>
+      </c>
+      <c r="F222" t="n">
+        <v>6499200</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>146.4499969482422</v>
+      </c>
+      <c r="C223" t="n">
+        <v>147.9900054931641</v>
+      </c>
+      <c r="D223" t="n">
+        <v>145.3999938964844</v>
+      </c>
+      <c r="E223" t="n">
+        <v>147.4100036621094</v>
+      </c>
+      <c r="F223" t="n">
+        <v>6620700</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>147.8500061035156</v>
+      </c>
+      <c r="C224" t="n">
+        <v>150.25</v>
+      </c>
+      <c r="D224" t="n">
+        <v>147.8500061035156</v>
+      </c>
+      <c r="E224" t="n">
+        <v>148.6300048828125</v>
+      </c>
+      <c r="F224" t="n">
+        <v>7301800</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="C225" t="n">
+        <v>153.6799926757812</v>
+      </c>
+      <c r="D225" t="n">
+        <v>148.5200042724609</v>
+      </c>
+      <c r="E225" t="n">
+        <v>148.8800048828125</v>
+      </c>
+      <c r="F225" t="n">
+        <v>12848800</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>141.3800048828125</v>
+      </c>
+      <c r="C226" t="n">
+        <v>146.3800048828125</v>
+      </c>
+      <c r="D226" t="n">
+        <v>140.1999969482422</v>
+      </c>
+      <c r="E226" t="n">
+        <v>146.1000061035156</v>
+      </c>
+      <c r="F226" t="n">
+        <v>14616800</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>143.7599945068359</v>
+      </c>
+      <c r="C227" t="n">
+        <v>144.4499969482422</v>
+      </c>
+      <c r="D227" t="n">
+        <v>142.25</v>
+      </c>
+      <c r="E227" t="n">
+        <v>143.9600067138672</v>
+      </c>
+      <c r="F227" t="n">
+        <v>9571100</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>143.5099945068359</v>
+      </c>
+      <c r="C228" t="n">
+        <v>144.6999969482422</v>
+      </c>
+      <c r="D228" t="n">
+        <v>141.4600067138672</v>
+      </c>
+      <c r="E228" t="n">
+        <v>144.4900054931641</v>
+      </c>
+      <c r="F228" t="n">
+        <v>9152600</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>145.8500061035156</v>
+      </c>
+      <c r="C229" t="n">
+        <v>147.1499938964844</v>
+      </c>
+      <c r="D229" t="n">
+        <v>144.2599945068359</v>
+      </c>
+      <c r="E229" t="n">
+        <v>144.9700012207031</v>
+      </c>
+      <c r="F229" t="n">
+        <v>8843600</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>144.0399932861328</v>
+      </c>
+      <c r="C230" t="n">
+        <v>148.25</v>
+      </c>
+      <c r="D230" t="n">
+        <v>143.7899932861328</v>
+      </c>
+      <c r="E230" t="n">
+        <v>148.0099945068359</v>
+      </c>
+      <c r="F230" t="n">
+        <v>7362300</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>147.8500061035156</v>
+      </c>
+      <c r="C231" t="n">
+        <v>147.8500061035156</v>
+      </c>
+      <c r="D231" t="n">
+        <v>144.6600036621094</v>
+      </c>
+      <c r="E231" t="n">
+        <v>146.8000030517578</v>
+      </c>
+      <c r="F231" t="n">
+        <v>9753300</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>147.8200073242188</v>
+      </c>
+      <c r="C232" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="D232" t="n">
+        <v>145.4499969482422</v>
+      </c>
+      <c r="E232" t="n">
+        <v>146.9700012207031</v>
+      </c>
+      <c r="F232" t="n">
+        <v>8766700</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>144.8999938964844</v>
+      </c>
+      <c r="C233" t="n">
+        <v>146</v>
+      </c>
+      <c r="D233" t="n">
+        <v>143.8800048828125</v>
+      </c>
+      <c r="E233" t="n">
+        <v>145.7899932861328</v>
+      </c>
+      <c r="F233" t="n">
+        <v>7565500</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>144.7299957275391</v>
+      </c>
+      <c r="C234" t="n">
+        <v>146.4600067138672</v>
+      </c>
+      <c r="D234" t="n">
+        <v>144.1499938964844</v>
+      </c>
+      <c r="E234" t="n">
+        <v>146.4400024414062</v>
+      </c>
+      <c r="F234" t="n">
+        <v>7386500</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>145.4100036621094</v>
+      </c>
+      <c r="C235" t="n">
+        <v>145.7100067138672</v>
+      </c>
+      <c r="D235" t="n">
+        <v>143.9299926757812</v>
+      </c>
+      <c r="E235" t="n">
+        <v>145.2100067138672</v>
+      </c>
+      <c r="F235" t="n">
+        <v>7936700</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>144.0500030517578</v>
+      </c>
+      <c r="C236" t="n">
+        <v>144.9400024414062</v>
+      </c>
+      <c r="D236" t="n">
+        <v>143.7899932861328</v>
+      </c>
+      <c r="E236" t="n">
+        <v>144.0800018310547</v>
+      </c>
+      <c r="F236" t="n">
+        <v>7195000</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>144.5899963378906</v>
+      </c>
+      <c r="C237" t="n">
+        <v>145.8000030517578</v>
+      </c>
+      <c r="D237" t="n">
+        <v>144</v>
+      </c>
+      <c r="E237" t="n">
+        <v>144.2599945068359</v>
+      </c>
+      <c r="F237" t="n">
+        <v>7491300</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>144.3300018310547</v>
+      </c>
+      <c r="C238" t="n">
+        <v>144.9100036621094</v>
+      </c>
+      <c r="D238" t="n">
+        <v>143.4199981689453</v>
+      </c>
+      <c r="E238" t="n">
+        <v>144.5500030517578</v>
+      </c>
+      <c r="F238" t="n">
+        <v>7249600</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>143.6399993896484</v>
+      </c>
+      <c r="C239" t="n">
+        <v>143.9700012207031</v>
+      </c>
+      <c r="D239" t="n">
+        <v>142.4799957275391</v>
+      </c>
+      <c r="E239" t="n">
+        <v>143.1199951171875</v>
+      </c>
+      <c r="F239" t="n">
+        <v>9867500</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>143.2799987792969</v>
+      </c>
+      <c r="C240" t="n">
+        <v>144.4199981689453</v>
+      </c>
+      <c r="D240" t="n">
+        <v>142.6799926757812</v>
+      </c>
+      <c r="E240" t="n">
+        <v>143.4499969482422</v>
+      </c>
+      <c r="F240" t="n">
+        <v>12746100</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>144.3000030517578</v>
+      </c>
+      <c r="C241" t="n">
+        <v>146.2299957275391</v>
+      </c>
+      <c r="D241" t="n">
+        <v>143.6199951171875</v>
+      </c>
+      <c r="E241" t="n">
+        <v>144.3800048828125</v>
+      </c>
+      <c r="F241" t="n">
+        <v>13948500</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>144.4700012207031</v>
+      </c>
+      <c r="C242" t="n">
+        <v>144.9199981689453</v>
+      </c>
+      <c r="D242" t="n">
+        <v>142.5599975585938</v>
+      </c>
+      <c r="E242" t="n">
+        <v>142.9700012207031</v>
+      </c>
+      <c r="F242" t="n">
+        <v>15794100</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>143.0200042724609</v>
+      </c>
+      <c r="C243" t="n">
+        <v>145.2700042724609</v>
+      </c>
+      <c r="D243" t="n">
+        <v>142.1399993896484</v>
+      </c>
+      <c r="E243" t="n">
+        <v>144.6799926757812</v>
+      </c>
+      <c r="F243" t="n">
+        <v>9785200</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>145.2400054931641</v>
+      </c>
+      <c r="C244" t="n">
+        <v>146.8000030517578</v>
+      </c>
+      <c r="D244" t="n">
+        <v>145</v>
+      </c>
+      <c r="E244" t="n">
+        <v>146.6000061035156</v>
+      </c>
+      <c r="F244" t="n">
+        <v>7061800</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>145.7299957275391</v>
+      </c>
+      <c r="C245" t="n">
+        <v>146.1199951171875</v>
+      </c>
+      <c r="D245" t="n">
+        <v>144.9499969482422</v>
+      </c>
+      <c r="E245" t="n">
+        <v>145.3999938964844</v>
+      </c>
+      <c r="F245" t="n">
+        <v>9125700</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>145.2799987792969</v>
+      </c>
+      <c r="C246" t="n">
+        <v>145.9299926757812</v>
+      </c>
+      <c r="D246" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="E246" t="n">
+        <v>145</v>
+      </c>
+      <c r="F246" t="n">
+        <v>8249100</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>143.6999969482422</v>
+      </c>
+      <c r="C247" t="n">
+        <v>144.1499938964844</v>
+      </c>
+      <c r="D247" t="n">
+        <v>142.7100067138672</v>
+      </c>
+      <c r="E247" t="n">
+        <v>143.1399993896484</v>
+      </c>
+      <c r="F247" t="n">
+        <v>7817200</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="C248" t="n">
+        <v>144.3999938964844</v>
+      </c>
+      <c r="D248" t="n">
+        <v>143.0099945068359</v>
+      </c>
+      <c r="E248" t="n">
+        <v>143.7799987792969</v>
+      </c>
+      <c r="F248" t="n">
+        <v>5868900</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>143.4400024414062</v>
+      </c>
+      <c r="C249" t="n">
+        <v>145.8999938964844</v>
+      </c>
+      <c r="D249" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="E249" t="n">
+        <v>145.1199951171875</v>
+      </c>
+      <c r="F249" t="n">
+        <v>12097900</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>145.7599945068359</v>
+      </c>
+      <c r="C250" t="n">
+        <v>148.3600006103516</v>
+      </c>
+      <c r="D250" t="n">
+        <v>145.0899963378906</v>
+      </c>
+      <c r="E250" t="n">
+        <v>146.2100067138672</v>
+      </c>
+      <c r="F250" t="n">
+        <v>8503800</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>146.4199981689453</v>
+      </c>
+      <c r="C251" t="n">
+        <v>148.3200073242188</v>
+      </c>
+      <c r="D251" t="n">
+        <v>145.7899932861328</v>
+      </c>
+      <c r="E251" t="n">
+        <v>147.6399993896484</v>
+      </c>
+      <c r="F251" t="n">
+        <v>7431100</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>147.6799926757812</v>
+      </c>
+      <c r="C252" t="n">
+        <v>148.2200012207031</v>
+      </c>
+      <c r="D252" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="E252" t="n">
+        <v>146.9199981689453</v>
+      </c>
+      <c r="F252" t="n">
+        <v>6105800</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>146.4700012207031</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>147.1499938964844</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>145.8200073242188</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>146.4400024414062</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>5588200</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4983,7 +10937,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:46</t>
+          <t>2026-09-07 03:08:37</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -472,16 +472,16 @@
         <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>154.0207528479355</v>
+        <v>154.0207679665519</v>
       </c>
       <c r="C2" t="n">
-        <v>155.9733284468274</v>
+        <v>155.9733437571078</v>
       </c>
       <c r="D2" t="n">
-        <v>153.8847527787027</v>
+        <v>153.8847678839693</v>
       </c>
       <c r="E2" t="n">
-        <v>155.4487609863281</v>
+        <v>155.4487762451172</v>
       </c>
       <c r="F2" t="n">
         <v>6436200</v>
@@ -602,16 +602,16 @@
         <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>153.4184545574236</v>
+        <v>153.4184698191116</v>
       </c>
       <c r="C7" t="n">
-        <v>154.5841863803252</v>
+        <v>154.5842017579773</v>
       </c>
       <c r="D7" t="n">
-        <v>153.2727454910088</v>
+        <v>153.272760738202</v>
       </c>
       <c r="E7" t="n">
-        <v>153.3893127441406</v>
+        <v>153.3893280029297</v>
       </c>
       <c r="F7" t="n">
         <v>5957000</v>
@@ -680,16 +680,16 @@
         <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>153.9041611382593</v>
+        <v>153.9041762162224</v>
       </c>
       <c r="C10" t="n">
-        <v>157.0516101729205</v>
+        <v>157.0516255592386</v>
       </c>
       <c r="D10" t="n">
-        <v>153.9041611382593</v>
+        <v>153.9041762162224</v>
       </c>
       <c r="E10" t="n">
-        <v>155.7498931884766</v>
+        <v>155.7499084472656</v>
       </c>
       <c r="F10" t="n">
         <v>6764200</v>
@@ -758,16 +758,16 @@
         <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>151.6213204761912</v>
+        <v>151.6213360350316</v>
       </c>
       <c r="C13" t="n">
-        <v>151.6213204761912</v>
+        <v>151.6213360350316</v>
       </c>
       <c r="D13" t="n">
-        <v>148.677878583773</v>
+        <v>148.6778938405679</v>
       </c>
       <c r="E13" t="n">
-        <v>148.6973114013672</v>
+        <v>148.6973266601562</v>
       </c>
       <c r="F13" t="n">
         <v>8712900</v>
@@ -784,16 +784,16 @@
         <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>148.8235855824238</v>
+        <v>148.8235702535947</v>
       </c>
       <c r="C14" t="n">
-        <v>148.9110110260332</v>
+        <v>148.9109956881993</v>
       </c>
       <c r="D14" t="n">
-        <v>146.657293372131</v>
+        <v>146.65727826643</v>
       </c>
       <c r="E14" t="n">
-        <v>148.1435852050781</v>
+        <v>148.1435699462891</v>
       </c>
       <c r="F14" t="n">
         <v>8853400</v>
@@ -862,16 +862,16 @@
         <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>147.8812940513532</v>
+        <v>147.8812788195801</v>
       </c>
       <c r="C17" t="n">
-        <v>148.3184360922971</v>
+        <v>148.3184208154984</v>
       </c>
       <c r="D17" t="n">
-        <v>147.2012936740075</v>
+        <v>147.2012785122745</v>
       </c>
       <c r="E17" t="n">
-        <v>148.1435852050781</v>
+        <v>148.1435699462891</v>
       </c>
       <c r="F17" t="n">
         <v>5721100</v>
@@ -888,16 +888,16 @@
         <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>148.0658582502614</v>
+        <v>148.0658733987316</v>
       </c>
       <c r="C18" t="n">
-        <v>149.3287244745027</v>
+        <v>149.3287397521754</v>
       </c>
       <c r="D18" t="n">
-        <v>147.453850542637</v>
+        <v>147.4538656284933</v>
       </c>
       <c r="E18" t="n">
-        <v>149.1441497802734</v>
+        <v>149.1441650390625</v>
       </c>
       <c r="F18" t="n">
         <v>8139700</v>
@@ -914,16 +914,16 @@
         <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>149.0761670451376</v>
+        <v>149.0761518052159</v>
       </c>
       <c r="C19" t="n">
-        <v>149.9698839401892</v>
+        <v>149.9698686089037</v>
       </c>
       <c r="D19" t="n">
-        <v>148.4738682940947</v>
+        <v>148.4738531157455</v>
       </c>
       <c r="E19" t="n">
-        <v>149.2607269287109</v>
+        <v>149.2607116699219</v>
       </c>
       <c r="F19" t="n">
         <v>7762600</v>
@@ -1018,16 +1018,16 @@
         <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>147.1721399535571</v>
+        <v>147.1721553229241</v>
       </c>
       <c r="C23" t="n">
-        <v>147.9687223475034</v>
+        <v>147.9687378000585</v>
       </c>
       <c r="D23" t="n">
-        <v>146.1035574306768</v>
+        <v>146.1035726884504</v>
       </c>
       <c r="E23" t="n">
-        <v>146.11328125</v>
+        <v>146.1132965087891</v>
       </c>
       <c r="F23" t="n">
         <v>6737000</v>
@@ -1122,16 +1122,16 @@
         <v>45940</v>
       </c>
       <c r="B27" t="n">
-        <v>146.6281558533259</v>
+        <v>146.6281404671169</v>
       </c>
       <c r="C27" t="n">
-        <v>147.1818651686376</v>
+        <v>147.181849724326</v>
       </c>
       <c r="D27" t="n">
-        <v>145.1807147897232</v>
+        <v>145.1806995553993</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4138641357422</v>
+        <v>145.4138488769531</v>
       </c>
       <c r="F27" t="n">
         <v>7374000</v>
@@ -1148,16 +1148,16 @@
         <v>45943</v>
       </c>
       <c r="B28" t="n">
-        <v>144.7435772439311</v>
+        <v>144.7435618289234</v>
       </c>
       <c r="C28" t="n">
-        <v>145.1612864927987</v>
+        <v>145.1612710333055</v>
       </c>
       <c r="D28" t="n">
-        <v>142.7715686189899</v>
+        <v>142.7715534139986</v>
       </c>
       <c r="E28" t="n">
-        <v>143.2767181396484</v>
+        <v>143.2767028808594</v>
       </c>
       <c r="F28" t="n">
         <v>7511100</v>
@@ -1304,16 +1304,16 @@
         <v>45951</v>
       </c>
       <c r="B34" t="n">
-        <v>147.6190101337839</v>
+        <v>147.6190254267912</v>
       </c>
       <c r="C34" t="n">
-        <v>147.9298610804961</v>
+        <v>147.9298764057069</v>
       </c>
       <c r="D34" t="n">
-        <v>146.5601365760907</v>
+        <v>146.560151759401</v>
       </c>
       <c r="E34" t="n">
-        <v>147.2887115478516</v>
+        <v>147.2887268066406</v>
       </c>
       <c r="F34" t="n">
         <v>6013400</v>
@@ -1330,16 +1330,16 @@
         <v>45952</v>
       </c>
       <c r="B35" t="n">
-        <v>146.9778583106544</v>
+        <v>146.9778734792147</v>
       </c>
       <c r="C35" t="n">
-        <v>149.076157754121</v>
+        <v>149.0761731392322</v>
       </c>
       <c r="D35" t="n">
-        <v>146.4824178509246</v>
+        <v>146.4824329683539</v>
       </c>
       <c r="E35" t="n">
-        <v>147.8521423339844</v>
+        <v>147.8521575927734</v>
       </c>
       <c r="F35" t="n">
         <v>6394400</v>
@@ -1356,16 +1356,16 @@
         <v>45953</v>
       </c>
       <c r="B36" t="n">
-        <v>147.9978775181488</v>
+        <v>147.9978622453251</v>
       </c>
       <c r="C36" t="n">
-        <v>148.9207362405373</v>
+        <v>148.9207208724779</v>
       </c>
       <c r="D36" t="n">
-        <v>146.2784363299136</v>
+        <v>146.2784212345297</v>
       </c>
       <c r="E36" t="n">
-        <v>147.8618774414062</v>
+        <v>147.8618621826172</v>
       </c>
       <c r="F36" t="n">
         <v>8205400</v>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:37</t>
+          <t>2026-09-08 08:52:28</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>154.0207679665519</v>
+        <v>154.0790304359711</v>
       </c>
       <c r="C2" t="n">
-        <v>155.9733437571078</v>
+        <v>155.3030310110979</v>
       </c>
       <c r="D2" t="n">
-        <v>153.8847678839693</v>
+        <v>153.6807392406498</v>
       </c>
       <c r="E2" t="n">
-        <v>155.4487762451172</v>
+        <v>154.9047546386719</v>
       </c>
       <c r="F2" t="n">
-        <v>6436200</v>
+        <v>4984900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>155.0504715071257</v>
+        <v>154.0693177951327</v>
       </c>
       <c r="C3" t="n">
-        <v>155.6916210504824</v>
+        <v>154.3996015392422</v>
       </c>
       <c r="D3" t="n">
-        <v>153.7293216100101</v>
+        <v>151.4367271926253</v>
       </c>
       <c r="E3" t="n">
-        <v>154.4676055908203</v>
+        <v>152.8550262451172</v>
       </c>
       <c r="F3" t="n">
-        <v>7178400</v>
+        <v>6205500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>154.0790456134228</v>
+        <v>153.2144723004245</v>
       </c>
       <c r="C4" t="n">
-        <v>155.3030463091189</v>
+        <v>154.7979134368329</v>
       </c>
       <c r="D4" t="n">
-        <v>153.6807543788681</v>
+        <v>152.8938975095807</v>
       </c>
       <c r="E4" t="n">
-        <v>154.9047698974609</v>
+        <v>154.0984802246094</v>
       </c>
       <c r="F4" t="n">
-        <v>4984900</v>
+        <v>5819500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>154.0693331751388</v>
+        <v>153.4184545574236</v>
       </c>
       <c r="C5" t="n">
-        <v>154.3996169522188</v>
+        <v>154.5841863803252</v>
       </c>
       <c r="D5" t="n">
-        <v>151.4367423098323</v>
+        <v>153.2727454910088</v>
       </c>
       <c r="E5" t="n">
-        <v>152.8550415039062</v>
+        <v>153.3893127441406</v>
       </c>
       <c r="F5" t="n">
-        <v>6205500</v>
+        <v>5957000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>153.2144723004245</v>
+        <v>153.3698919481564</v>
       </c>
       <c r="C6" t="n">
-        <v>154.7979134368329</v>
+        <v>153.9916086583258</v>
       </c>
       <c r="D6" t="n">
-        <v>152.8938975095807</v>
+        <v>151.7378763196521</v>
       </c>
       <c r="E6" t="n">
-        <v>154.0984802246094</v>
+        <v>152.3498840332031</v>
       </c>
       <c r="F6" t="n">
-        <v>5819500</v>
+        <v>5995000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>153.4184698191116</v>
+        <v>152.6510415007772</v>
       </c>
       <c r="C7" t="n">
-        <v>154.5842017579773</v>
+        <v>153.8653332318267</v>
       </c>
       <c r="D7" t="n">
-        <v>153.272760738202</v>
+        <v>152.4081831545673</v>
       </c>
       <c r="E7" t="n">
-        <v>153.3893280029297</v>
+        <v>153.5350494384766</v>
       </c>
       <c r="F7" t="n">
-        <v>5957000</v>
+        <v>6559600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>153.3698919481564</v>
+        <v>153.9041611382593</v>
       </c>
       <c r="C8" t="n">
-        <v>153.9916086583258</v>
+        <v>157.0516101729205</v>
       </c>
       <c r="D8" t="n">
-        <v>151.7378763196521</v>
+        <v>153.9041611382593</v>
       </c>
       <c r="E8" t="n">
-        <v>152.3498840332031</v>
+        <v>155.7498931884766</v>
       </c>
       <c r="F8" t="n">
-        <v>5995000</v>
+        <v>6764200</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>152.6510415007772</v>
+        <v>153.6321891685915</v>
       </c>
       <c r="C9" t="n">
-        <v>153.8653332318267</v>
+        <v>154.4773463220477</v>
       </c>
       <c r="D9" t="n">
-        <v>152.4081831545673</v>
+        <v>152.670479571169</v>
       </c>
       <c r="E9" t="n">
-        <v>153.5350494384766</v>
+        <v>152.8259124755859</v>
       </c>
       <c r="F9" t="n">
-        <v>6559600</v>
+        <v>7651500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>153.9041762162224</v>
+        <v>153.1076006094224</v>
       </c>
       <c r="C10" t="n">
-        <v>157.0516255592386</v>
+        <v>153.1173096060279</v>
       </c>
       <c r="D10" t="n">
-        <v>153.9041762162224</v>
+        <v>151.5144506152748</v>
       </c>
       <c r="E10" t="n">
-        <v>155.7499084472656</v>
+        <v>151.5824432373047</v>
       </c>
       <c r="F10" t="n">
-        <v>6764200</v>
+        <v>17224800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>153.6321891685915</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="C11" t="n">
-        <v>154.4773463220477</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="D11" t="n">
-        <v>152.670479571169</v>
+        <v>148.677863326978</v>
       </c>
       <c r="E11" t="n">
-        <v>152.8259124755859</v>
+        <v>148.6972961425781</v>
       </c>
       <c r="F11" t="n">
-        <v>7651500</v>
+        <v>8712900</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>153.1076006094224</v>
+        <v>148.8235702535947</v>
       </c>
       <c r="C12" t="n">
-        <v>153.1173096060279</v>
+        <v>148.9109956881993</v>
       </c>
       <c r="D12" t="n">
-        <v>151.5144506152748</v>
+        <v>146.65727826643</v>
       </c>
       <c r="E12" t="n">
-        <v>151.5824432373047</v>
+        <v>148.1435699462891</v>
       </c>
       <c r="F12" t="n">
-        <v>17224800</v>
+        <v>8853400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>151.6213360350316</v>
+        <v>147.7064313677511</v>
       </c>
       <c r="C13" t="n">
-        <v>151.6213360350316</v>
+        <v>149.2412977099777</v>
       </c>
       <c r="D13" t="n">
-        <v>148.6778938405679</v>
+        <v>147.4538492314116</v>
       </c>
       <c r="E13" t="n">
-        <v>148.6973266601562</v>
+        <v>148.0658569335938</v>
       </c>
       <c r="F13" t="n">
-        <v>8712900</v>
+        <v>6483300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>148.8235702535947</v>
+        <v>148.852723372033</v>
       </c>
       <c r="C14" t="n">
-        <v>148.9109956881993</v>
+        <v>149.4841639233416</v>
       </c>
       <c r="D14" t="n">
-        <v>146.65727826643</v>
+        <v>147.4441480235695</v>
       </c>
       <c r="E14" t="n">
-        <v>148.1435699462891</v>
+        <v>147.8035736083984</v>
       </c>
       <c r="F14" t="n">
-        <v>8853400</v>
+        <v>7511400</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>147.7064465894999</v>
+        <v>147.8812788195801</v>
       </c>
       <c r="C15" t="n">
-        <v>149.2413130899007</v>
+        <v>148.3184208154984</v>
       </c>
       <c r="D15" t="n">
-        <v>147.4538644271308</v>
+        <v>147.2012785122745</v>
       </c>
       <c r="E15" t="n">
-        <v>148.0658721923828</v>
+        <v>148.1435699462891</v>
       </c>
       <c r="F15" t="n">
-        <v>6483300</v>
+        <v>5721100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>148.8527387391331</v>
+        <v>148.0658733987316</v>
       </c>
       <c r="C16" t="n">
-        <v>149.4841793556296</v>
+        <v>149.3287397521754</v>
       </c>
       <c r="D16" t="n">
-        <v>147.4441632452525</v>
+        <v>147.4538656284933</v>
       </c>
       <c r="E16" t="n">
-        <v>147.8035888671875</v>
+        <v>149.1441650390625</v>
       </c>
       <c r="F16" t="n">
-        <v>7511400</v>
+        <v>8139700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>147.8812788195801</v>
+        <v>149.0761670451376</v>
       </c>
       <c r="C17" t="n">
-        <v>148.3184208154984</v>
+        <v>149.9698839401892</v>
       </c>
       <c r="D17" t="n">
-        <v>147.2012785122745</v>
+        <v>148.4738682940947</v>
       </c>
       <c r="E17" t="n">
-        <v>148.1435699462891</v>
+        <v>149.2607269287109</v>
       </c>
       <c r="F17" t="n">
-        <v>5721100</v>
+        <v>7762600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>148.0658733987316</v>
+        <v>149.3092876242202</v>
       </c>
       <c r="C18" t="n">
-        <v>149.3287397521754</v>
+        <v>149.4938623134623</v>
       </c>
       <c r="D18" t="n">
-        <v>147.4538656284933</v>
+        <v>147.0847120028435</v>
       </c>
       <c r="E18" t="n">
-        <v>149.1441650390625</v>
+        <v>148.8041381835938</v>
       </c>
       <c r="F18" t="n">
-        <v>8139700</v>
+        <v>7566000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>149.0761518052159</v>
+        <v>148.3572946891603</v>
       </c>
       <c r="C19" t="n">
-        <v>149.9698686089037</v>
+        <v>148.4350111318697</v>
       </c>
       <c r="D19" t="n">
-        <v>148.4738531157455</v>
+        <v>147.2984359501739</v>
       </c>
       <c r="E19" t="n">
-        <v>149.2607116699219</v>
+        <v>147.7064361572266</v>
       </c>
       <c r="F19" t="n">
-        <v>7762600</v>
+        <v>6892100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>149.3093029348087</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="C20" t="n">
-        <v>149.4938776429776</v>
+        <v>149.0470174793467</v>
       </c>
       <c r="D20" t="n">
-        <v>147.0847270853178</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="E20" t="n">
-        <v>148.8041534423828</v>
+        <v>147.920166015625</v>
       </c>
       <c r="F20" t="n">
-        <v>7566000</v>
+        <v>5212600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>148.3572946891603</v>
+        <v>147.1721399535571</v>
       </c>
       <c r="C21" t="n">
-        <v>148.4350111318697</v>
+        <v>147.9687223475034</v>
       </c>
       <c r="D21" t="n">
-        <v>147.2984359501739</v>
+        <v>146.1035574306768</v>
       </c>
       <c r="E21" t="n">
-        <v>147.7064361572266</v>
+        <v>146.11328125</v>
       </c>
       <c r="F21" t="n">
-        <v>6892100</v>
+        <v>6737000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>147.6578748506764</v>
+        <v>146.4532839352596</v>
       </c>
       <c r="C22" t="n">
-        <v>149.0470174793467</v>
+        <v>148.7944418250997</v>
       </c>
       <c r="D22" t="n">
-        <v>147.6578748506764</v>
+        <v>145.7635745697061</v>
       </c>
       <c r="E22" t="n">
-        <v>147.920166015625</v>
+        <v>148.1824340820312</v>
       </c>
       <c r="F22" t="n">
-        <v>5212600</v>
+        <v>6844400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>147.1721553229241</v>
+        <v>148.4252854332665</v>
       </c>
       <c r="C23" t="n">
-        <v>147.9687378000585</v>
+        <v>148.4252854332665</v>
       </c>
       <c r="D23" t="n">
-        <v>146.1035726884504</v>
+        <v>146.3270007982578</v>
       </c>
       <c r="E23" t="n">
-        <v>146.1132965087891</v>
+        <v>146.3852844238281</v>
       </c>
       <c r="F23" t="n">
-        <v>6737000</v>
+        <v>5254700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>146.4532839352596</v>
+        <v>146.4338600084891</v>
       </c>
       <c r="C24" t="n">
-        <v>148.7944418250997</v>
+        <v>146.5601362570837</v>
       </c>
       <c r="D24" t="n">
-        <v>145.7635745697061</v>
+        <v>145.3069938304567</v>
       </c>
       <c r="E24" t="n">
-        <v>148.1824340820312</v>
+        <v>146.2784271240234</v>
       </c>
       <c r="F24" t="n">
-        <v>6844400</v>
+        <v>6134500</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>148.4252854332665</v>
+        <v>146.6281558533259</v>
       </c>
       <c r="C25" t="n">
-        <v>148.4252854332665</v>
+        <v>147.1818651686376</v>
       </c>
       <c r="D25" t="n">
-        <v>146.3270007982578</v>
+        <v>145.1807147897232</v>
       </c>
       <c r="E25" t="n">
-        <v>146.3852844238281</v>
+        <v>145.4138641357422</v>
       </c>
       <c r="F25" t="n">
-        <v>5254700</v>
+        <v>7374000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>146.4338600084891</v>
+        <v>144.7435618289234</v>
       </c>
       <c r="C26" t="n">
-        <v>146.5601362570837</v>
+        <v>145.1612710333055</v>
       </c>
       <c r="D26" t="n">
-        <v>145.3069938304567</v>
+        <v>142.7715534139986</v>
       </c>
       <c r="E26" t="n">
-        <v>146.2784271240234</v>
+        <v>143.2767028808594</v>
       </c>
       <c r="F26" t="n">
-        <v>6134500</v>
+        <v>7511100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>146.6281404671169</v>
+        <v>143.3544266058526</v>
       </c>
       <c r="C27" t="n">
-        <v>147.181849724326</v>
+        <v>144.9864275192193</v>
       </c>
       <c r="D27" t="n">
-        <v>145.1806995553993</v>
+        <v>142.8784189280057</v>
       </c>
       <c r="E27" t="n">
-        <v>145.4138488769531</v>
+        <v>144.8990020751953</v>
       </c>
       <c r="F27" t="n">
-        <v>7374000</v>
+        <v>8585300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>144.7435618289234</v>
+        <v>144.2869860075292</v>
       </c>
       <c r="C28" t="n">
-        <v>145.1612710333055</v>
+        <v>145.1418520497865</v>
       </c>
       <c r="D28" t="n">
-        <v>142.7715534139986</v>
+        <v>143.0629853930302</v>
       </c>
       <c r="E28" t="n">
-        <v>143.2767028808594</v>
+        <v>143.2086944580078</v>
       </c>
       <c r="F28" t="n">
-        <v>7511100</v>
+        <v>10003100</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>143.3544266058526</v>
+        <v>143.7818410230574</v>
       </c>
       <c r="C29" t="n">
-        <v>144.9864275192193</v>
+        <v>146.1035660756974</v>
       </c>
       <c r="D29" t="n">
-        <v>142.8784189280057</v>
+        <v>143.6944155813474</v>
       </c>
       <c r="E29" t="n">
-        <v>144.8990020751953</v>
+        <v>145.3264312744141</v>
       </c>
       <c r="F29" t="n">
-        <v>8585300</v>
+        <v>8809700</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>144.2869860075292</v>
+        <v>146.2687203464973</v>
       </c>
       <c r="C30" t="n">
-        <v>145.1418520497865</v>
+        <v>147.6870046758011</v>
       </c>
       <c r="D30" t="n">
-        <v>143.0629853930302</v>
+        <v>146.1327054533545</v>
       </c>
       <c r="E30" t="n">
-        <v>143.2086944580078</v>
+        <v>147.0749969482422</v>
       </c>
       <c r="F30" t="n">
-        <v>10003100</v>
+        <v>8612900</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>143.7818410230574</v>
+        <v>147.2595781352121</v>
       </c>
       <c r="C31" t="n">
-        <v>146.1035660756974</v>
+        <v>148.0367277806686</v>
       </c>
       <c r="D31" t="n">
-        <v>143.6944155813474</v>
+        <v>146.9778689854687</v>
       </c>
       <c r="E31" t="n">
-        <v>145.3264312744141</v>
+        <v>147.6190185546875</v>
       </c>
       <c r="F31" t="n">
-        <v>8809700</v>
+        <v>5601300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>146.2687203464973</v>
+        <v>147.6190101337839</v>
       </c>
       <c r="C32" t="n">
-        <v>147.6870046758011</v>
+        <v>147.9298610804961</v>
       </c>
       <c r="D32" t="n">
-        <v>146.1327054533545</v>
+        <v>146.5601365760907</v>
       </c>
       <c r="E32" t="n">
-        <v>147.0749969482422</v>
+        <v>147.2887115478516</v>
       </c>
       <c r="F32" t="n">
-        <v>8612900</v>
+        <v>6013400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>147.2595781352121</v>
+        <v>146.9778734792147</v>
       </c>
       <c r="C33" t="n">
-        <v>148.0367277806686</v>
+        <v>149.0761731392322</v>
       </c>
       <c r="D33" t="n">
-        <v>146.9778689854687</v>
+        <v>146.4824329683539</v>
       </c>
       <c r="E33" t="n">
-        <v>147.6190185546875</v>
+        <v>147.8521575927734</v>
       </c>
       <c r="F33" t="n">
-        <v>5601300</v>
+        <v>6394400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>147.6190254267912</v>
+        <v>147.9978622453251</v>
       </c>
       <c r="C34" t="n">
-        <v>147.9298764057069</v>
+        <v>148.9207208724779</v>
       </c>
       <c r="D34" t="n">
-        <v>146.560151759401</v>
+        <v>146.2784212345297</v>
       </c>
       <c r="E34" t="n">
-        <v>147.2887268066406</v>
+        <v>147.8618621826172</v>
       </c>
       <c r="F34" t="n">
-        <v>6013400</v>
+        <v>8205400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,25 +1327,25 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>146.9778734792147</v>
+        <v>152.9946080342638</v>
       </c>
       <c r="C35" t="n">
-        <v>149.0761731392322</v>
+        <v>153.9728344665201</v>
       </c>
       <c r="D35" t="n">
-        <v>146.4824329683539</v>
+        <v>148.2306500856719</v>
       </c>
       <c r="E35" t="n">
-        <v>147.8521575927734</v>
+        <v>149.1697540283203</v>
       </c>
       <c r="F35" t="n">
-        <v>6394400</v>
+        <v>11968500</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>147.9978622453251</v>
+        <v>148.3089219684464</v>
       </c>
       <c r="C36" t="n">
-        <v>148.9207208724779</v>
+        <v>148.4556499745139</v>
       </c>
       <c r="D36" t="n">
-        <v>146.2784212345297</v>
+        <v>146.8611509112235</v>
       </c>
       <c r="E36" t="n">
-        <v>147.8618621826172</v>
+        <v>148.4360961914062</v>
       </c>
       <c r="F36" t="n">
-        <v>8205400</v>
+        <v>7775300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,25 +1379,25 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>152.9946080342638</v>
+        <v>147.8295858278712</v>
       </c>
       <c r="C37" t="n">
-        <v>153.9728344665201</v>
+        <v>149.8349531642864</v>
       </c>
       <c r="D37" t="n">
-        <v>148.2306500856719</v>
+        <v>147.3404725715042</v>
       </c>
       <c r="E37" t="n">
-        <v>149.1697540283203</v>
+        <v>148.0741424560547</v>
       </c>
       <c r="F37" t="n">
-        <v>11968500</v>
+        <v>5819300</v>
       </c>
       <c r="G37" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>148.3089067227305</v>
+        <v>147.3795937684592</v>
       </c>
       <c r="C38" t="n">
-        <v>148.4556347137148</v>
+        <v>147.6828415657792</v>
       </c>
       <c r="D38" t="n">
-        <v>146.8611358143341</v>
+        <v>145.2372755531334</v>
       </c>
       <c r="E38" t="n">
-        <v>148.4360809326172</v>
+        <v>145.5307464599609</v>
       </c>
       <c r="F38" t="n">
-        <v>7775300</v>
+        <v>7405500</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>147.8295858278712</v>
+        <v>146.2155146062609</v>
       </c>
       <c r="C39" t="n">
-        <v>149.8349531642864</v>
+        <v>147.5165576287185</v>
       </c>
       <c r="D39" t="n">
-        <v>147.3404725715042</v>
+        <v>146.0883403861062</v>
       </c>
       <c r="E39" t="n">
-        <v>148.0741424560547</v>
+        <v>146.3231201171875</v>
       </c>
       <c r="F39" t="n">
-        <v>5819300</v>
+        <v>6760700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>147.3795937684592</v>
+        <v>145.4720720722042</v>
       </c>
       <c r="C40" t="n">
-        <v>147.6828415657792</v>
+        <v>147.8100328533669</v>
       </c>
       <c r="D40" t="n">
-        <v>145.2372755531334</v>
+        <v>145.2959835371417</v>
       </c>
       <c r="E40" t="n">
-        <v>145.5307464599609</v>
+        <v>147.0959167480469</v>
       </c>
       <c r="F40" t="n">
-        <v>7405500</v>
+        <v>7930300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>146.2155146062609</v>
+        <v>146.8318015049148</v>
       </c>
       <c r="C41" t="n">
-        <v>147.5165576287185</v>
+        <v>146.9491839067269</v>
       </c>
       <c r="D41" t="n">
-        <v>146.0883403861062</v>
+        <v>144.5525320015707</v>
       </c>
       <c r="E41" t="n">
-        <v>146.3231201171875</v>
+        <v>144.7970886230469</v>
       </c>
       <c r="F41" t="n">
-        <v>6760700</v>
+        <v>8946400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>145.4720720722042</v>
+        <v>145.3644630798614</v>
       </c>
       <c r="C42" t="n">
-        <v>147.8100328533669</v>
+        <v>146.2448609544514</v>
       </c>
       <c r="D42" t="n">
-        <v>145.2959835371417</v>
+        <v>143.0656248467459</v>
       </c>
       <c r="E42" t="n">
-        <v>147.0959167480469</v>
+        <v>143.9655914306641</v>
       </c>
       <c r="F42" t="n">
-        <v>7930300</v>
+        <v>9295400</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>146.8318015049148</v>
+        <v>143.6721174868199</v>
       </c>
       <c r="C43" t="n">
-        <v>146.9491839067269</v>
+        <v>144.210145032931</v>
       </c>
       <c r="D43" t="n">
-        <v>144.5525320015707</v>
+        <v>142.478679994192</v>
       </c>
       <c r="E43" t="n">
-        <v>144.7970886230469</v>
+        <v>142.6156311035156</v>
       </c>
       <c r="F43" t="n">
-        <v>8946400</v>
+        <v>11199900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>145.3644630798614</v>
+        <v>142.703685564269</v>
       </c>
       <c r="C44" t="n">
-        <v>146.2448609544514</v>
+        <v>143.4862548173669</v>
       </c>
       <c r="D44" t="n">
-        <v>143.0656248467459</v>
+        <v>141.3146057355029</v>
       </c>
       <c r="E44" t="n">
-        <v>143.9655914306641</v>
+        <v>142.9482421875</v>
       </c>
       <c r="F44" t="n">
-        <v>9295400</v>
+        <v>10024500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>143.6721174868199</v>
+        <v>143.7503785207628</v>
       </c>
       <c r="C45" t="n">
-        <v>144.210145032931</v>
+        <v>144.7188281113408</v>
       </c>
       <c r="D45" t="n">
-        <v>142.478679994192</v>
+        <v>142.8210663483271</v>
       </c>
       <c r="E45" t="n">
-        <v>142.6156311035156</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F45" t="n">
-        <v>11199900</v>
+        <v>8500100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>142.703685564269</v>
+        <v>143.192783696673</v>
       </c>
       <c r="C46" t="n">
-        <v>143.4862548173669</v>
+        <v>143.4275484772021</v>
       </c>
       <c r="D46" t="n">
-        <v>141.3146057355029</v>
+        <v>140.9526369054562</v>
       </c>
       <c r="E46" t="n">
-        <v>142.9482421875</v>
+        <v>142.3319396972656</v>
       </c>
       <c r="F46" t="n">
-        <v>10024500</v>
+        <v>10208100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>143.750363265088</v>
+        <v>142.7819444175452</v>
       </c>
       <c r="C47" t="n">
-        <v>144.7188127528882</v>
+        <v>145.4133611257213</v>
       </c>
       <c r="D47" t="n">
-        <v>142.8210511912767</v>
+        <v>142.4982503778291</v>
       </c>
       <c r="E47" t="n">
-        <v>143.7797088623047</v>
+        <v>145.3057556152344</v>
       </c>
       <c r="F47" t="n">
-        <v>8500100</v>
+        <v>7332500</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>143.1927990477494</v>
+        <v>145.2959744173796</v>
       </c>
       <c r="C48" t="n">
-        <v>143.4275638534467</v>
+        <v>145.9024700440282</v>
       </c>
       <c r="D48" t="n">
-        <v>140.9526520163762</v>
+        <v>144.298179252126</v>
       </c>
       <c r="E48" t="n">
-        <v>142.3319549560547</v>
+        <v>144.7872924804688</v>
       </c>
       <c r="F48" t="n">
-        <v>10208100</v>
+        <v>7851100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>142.7819294237856</v>
+        <v>144.9535841420777</v>
       </c>
       <c r="C49" t="n">
-        <v>145.4133458556324</v>
+        <v>145.7557369733869</v>
       </c>
       <c r="D49" t="n">
-        <v>142.4982354138606</v>
+        <v>144.4253484415343</v>
       </c>
       <c r="E49" t="n">
-        <v>145.3057403564453</v>
+        <v>144.7383880615234</v>
       </c>
       <c r="F49" t="n">
-        <v>7332500</v>
+        <v>7566800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>145.2959744173796</v>
+        <v>145.8535682267802</v>
       </c>
       <c r="C50" t="n">
-        <v>145.9024700440282</v>
+        <v>146.1274704359541</v>
       </c>
       <c r="D50" t="n">
-        <v>144.298179252126</v>
+        <v>144.3960054571006</v>
       </c>
       <c r="E50" t="n">
-        <v>144.7872924804688</v>
+        <v>144.4546966552734</v>
       </c>
       <c r="F50" t="n">
-        <v>7851100</v>
+        <v>9150800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>144.9535841420777</v>
+        <v>144.5329589094707</v>
       </c>
       <c r="C51" t="n">
-        <v>145.7557369733869</v>
+        <v>144.7579468149716</v>
       </c>
       <c r="D51" t="n">
-        <v>144.4253484415343</v>
+        <v>141.8526130458145</v>
       </c>
       <c r="E51" t="n">
-        <v>144.7383880615234</v>
+        <v>142.6449890136719</v>
       </c>
       <c r="F51" t="n">
-        <v>7566800</v>
+        <v>9902300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>145.8535682267802</v>
+        <v>143.1438719935926</v>
       </c>
       <c r="C52" t="n">
-        <v>146.1274704359541</v>
+        <v>144.1807895972433</v>
       </c>
       <c r="D52" t="n">
-        <v>144.3960054571006</v>
+        <v>142.341719174738</v>
       </c>
       <c r="E52" t="n">
-        <v>144.4546966552734</v>
+        <v>143.7895050048828</v>
       </c>
       <c r="F52" t="n">
-        <v>9150800</v>
+        <v>10735200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>144.5329589094707</v>
+        <v>143.7601594067833</v>
       </c>
       <c r="C53" t="n">
-        <v>144.7579468149716</v>
+        <v>144.3275175877409</v>
       </c>
       <c r="D53" t="n">
-        <v>141.8526130458145</v>
+        <v>142.6841043879663</v>
       </c>
       <c r="E53" t="n">
-        <v>142.6449890136719</v>
+        <v>143.7895050048828</v>
       </c>
       <c r="F53" t="n">
-        <v>9902300</v>
+        <v>6367000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>143.1438871838678</v>
+        <v>143.4471249350237</v>
       </c>
       <c r="C54" t="n">
-        <v>144.1808048975551</v>
+        <v>145.4231465283615</v>
       </c>
       <c r="D54" t="n">
-        <v>142.3417342798896</v>
+        <v>142.9482348228936</v>
       </c>
       <c r="E54" t="n">
-        <v>143.7895202636719</v>
+        <v>144.96337890625</v>
       </c>
       <c r="F54" t="n">
-        <v>10735200</v>
+        <v>9021300</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>143.7601746624582</v>
+        <v>145.1492529070371</v>
       </c>
       <c r="C55" t="n">
-        <v>144.3275329036233</v>
+        <v>148.2013148118135</v>
       </c>
       <c r="D55" t="n">
-        <v>142.6841195294514</v>
+        <v>145.0709929958182</v>
       </c>
       <c r="E55" t="n">
-        <v>143.7895202636719</v>
+        <v>147.6339416503906</v>
       </c>
       <c r="F55" t="n">
-        <v>6367000</v>
+        <v>12018000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>143.4471249350237</v>
+        <v>146.8318008944829</v>
       </c>
       <c r="C56" t="n">
-        <v>145.4231465283615</v>
+        <v>147.1350487156044</v>
       </c>
       <c r="D56" t="n">
-        <v>142.9482348228936</v>
+        <v>143.3493020808368</v>
       </c>
       <c r="E56" t="n">
-        <v>144.96337890625</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F56" t="n">
-        <v>9021300</v>
+        <v>13846900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>145.1492529070371</v>
+        <v>144.1123129003486</v>
       </c>
       <c r="C57" t="n">
-        <v>148.2013148118135</v>
+        <v>145.4133408091634</v>
       </c>
       <c r="D57" t="n">
-        <v>145.0709929958182</v>
+        <v>144.0144842948282</v>
       </c>
       <c r="E57" t="n">
-        <v>147.6339416503906</v>
+        <v>145.2568359375</v>
       </c>
       <c r="F57" t="n">
-        <v>12018000</v>
+        <v>10477700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>146.8317853117887</v>
+        <v>144.6992477048879</v>
       </c>
       <c r="C58" t="n">
-        <v>147.1350331007276</v>
+        <v>145.7263884130947</v>
       </c>
       <c r="D58" t="n">
-        <v>143.3492868677268</v>
+        <v>144.3959999082808</v>
       </c>
       <c r="E58" t="n">
-        <v>143.7797088623047</v>
+        <v>145.0220642089844</v>
       </c>
       <c r="F58" t="n">
-        <v>13846900</v>
+        <v>9238500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>144.112328038909</v>
+        <v>144.5818741313487</v>
       </c>
       <c r="C59" t="n">
-        <v>145.4133560843928</v>
+        <v>145.4720637945254</v>
       </c>
       <c r="D59" t="n">
-        <v>144.0144994231119</v>
+        <v>143.9753635745919</v>
       </c>
       <c r="E59" t="n">
-        <v>145.2568511962891</v>
+        <v>144.9340362548828</v>
       </c>
       <c r="F59" t="n">
-        <v>10477700</v>
+        <v>4707200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>144.6992477048879</v>
+        <v>144.8753541574702</v>
       </c>
       <c r="C60" t="n">
-        <v>145.7263884130947</v>
+        <v>145.6481465436537</v>
       </c>
       <c r="D60" t="n">
-        <v>144.3959999082808</v>
+        <v>144.1416842645591</v>
       </c>
       <c r="E60" t="n">
-        <v>145.0220642089844</v>
+        <v>144.2297210693359</v>
       </c>
       <c r="F60" t="n">
-        <v>9238500</v>
+        <v>8240700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>144.5818741313487</v>
+        <v>142.1265162999446</v>
       </c>
       <c r="C61" t="n">
-        <v>145.4720637945254</v>
+        <v>143.0069290729368</v>
       </c>
       <c r="D61" t="n">
-        <v>143.9753635745919</v>
+        <v>139.4070479258121</v>
       </c>
       <c r="E61" t="n">
-        <v>144.9340362548828</v>
+        <v>142.6841125488281</v>
       </c>
       <c r="F61" t="n">
-        <v>4707200</v>
+        <v>16376800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8753541574702</v>
+        <v>142.7428024831051</v>
       </c>
       <c r="C62" t="n">
-        <v>145.6481465436537</v>
+        <v>145.0611944043203</v>
       </c>
       <c r="D62" t="n">
-        <v>144.1416842645591</v>
+        <v>142.6841112840695</v>
       </c>
       <c r="E62" t="n">
-        <v>144.2297210693359</v>
+        <v>143.5156097412109</v>
       </c>
       <c r="F62" t="n">
-        <v>8240700</v>
+        <v>9125300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>142.1265314991037</v>
+        <v>143.4764816751874</v>
       </c>
       <c r="C63" t="n">
-        <v>143.0069443662482</v>
+        <v>144.210151564052</v>
       </c>
       <c r="D63" t="n">
-        <v>139.4070628341484</v>
+        <v>141.3537319212585</v>
       </c>
       <c r="E63" t="n">
-        <v>142.6841278076172</v>
+        <v>142.1950073242188</v>
       </c>
       <c r="F63" t="n">
-        <v>16376800</v>
+        <v>10479300</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>142.7428176597282</v>
+        <v>141.999373131105</v>
       </c>
       <c r="C64" t="n">
-        <v>145.0612098274382</v>
+        <v>142.4591408152259</v>
       </c>
       <c r="D64" t="n">
-        <v>142.6841264544524</v>
+        <v>140.1309567915122</v>
       </c>
       <c r="E64" t="n">
-        <v>143.515625</v>
+        <v>140.3265991210938</v>
       </c>
       <c r="F64" t="n">
-        <v>9125300</v>
+        <v>12791700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>143.4764816751874</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="C65" t="n">
-        <v>144.210151564052</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="D65" t="n">
-        <v>141.3537319212585</v>
+        <v>135.1322080272313</v>
       </c>
       <c r="E65" t="n">
-        <v>142.1950073242188</v>
+        <v>135.3278503417969</v>
       </c>
       <c r="F65" t="n">
-        <v>10479300</v>
+        <v>17507500</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>141.9993576904224</v>
+        <v>136.1593454188843</v>
       </c>
       <c r="C66" t="n">
-        <v>142.4591253245491</v>
+        <v>137.8125505495836</v>
       </c>
       <c r="D66" t="n">
-        <v>140.1309415539968</v>
+        <v>135.9734800004196</v>
       </c>
       <c r="E66" t="n">
-        <v>140.3265838623047</v>
+        <v>136.5897674560547</v>
       </c>
       <c r="F66" t="n">
-        <v>12791700</v>
+        <v>10375700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>139.7983368458492</v>
+        <v>136.6093231272403</v>
       </c>
       <c r="C67" t="n">
-        <v>139.7983368458492</v>
+        <v>138.2038370797448</v>
       </c>
       <c r="D67" t="n">
-        <v>135.1321927905018</v>
+        <v>136.5017176164599</v>
       </c>
       <c r="E67" t="n">
-        <v>135.3278350830078</v>
+        <v>136.775634765625</v>
       </c>
       <c r="F67" t="n">
-        <v>17507500</v>
+        <v>13650400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>136.1593302081787</v>
+        <v>137.9299396510316</v>
       </c>
       <c r="C68" t="n">
-        <v>137.8125351541944</v>
+        <v>138.7516463474312</v>
       </c>
       <c r="D68" t="n">
-        <v>135.9734648104776</v>
+        <v>137.3038752737911</v>
       </c>
       <c r="E68" t="n">
-        <v>136.5897521972656</v>
+        <v>137.6951599121094</v>
       </c>
       <c r="F68" t="n">
-        <v>10375700</v>
+        <v>11798000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>136.6093231272403</v>
+        <v>137.929925366103</v>
       </c>
       <c r="C69" t="n">
-        <v>138.2038370797448</v>
+        <v>139.9939837115514</v>
       </c>
       <c r="D69" t="n">
-        <v>136.5017176164599</v>
+        <v>137.7734055563651</v>
       </c>
       <c r="E69" t="n">
-        <v>136.775634765625</v>
+        <v>139.7298583984375</v>
       </c>
       <c r="F69" t="n">
-        <v>13650400</v>
+        <v>10268800</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>137.9299396510316</v>
+        <v>140.1504995323008</v>
       </c>
       <c r="C70" t="n">
-        <v>138.7516463474312</v>
+        <v>142.155866623658</v>
       </c>
       <c r="D70" t="n">
-        <v>137.3038752737911</v>
+        <v>140.0820165200331</v>
       </c>
       <c r="E70" t="n">
-        <v>137.6951599121094</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F70" t="n">
-        <v>11798000</v>
+        <v>13877700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>137.9299404283357</v>
+        <v>142.918884457557</v>
       </c>
       <c r="C71" t="n">
-        <v>139.9939989991835</v>
+        <v>143.3492915396123</v>
       </c>
       <c r="D71" t="n">
-        <v>137.7734206015055</v>
+        <v>141.5004442219562</v>
       </c>
       <c r="E71" t="n">
-        <v>139.7298736572266</v>
+        <v>142.0482635498047</v>
       </c>
       <c r="F71" t="n">
-        <v>10268800</v>
+        <v>10251700</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>140.1504995323008</v>
+        <v>143.496050619897</v>
       </c>
       <c r="C72" t="n">
-        <v>142.155866623658</v>
+        <v>145.2177239216924</v>
       </c>
       <c r="D72" t="n">
-        <v>140.0820165200331</v>
+        <v>143.2612708815172</v>
       </c>
       <c r="E72" t="n">
-        <v>141.9700012207031</v>
+        <v>144.5916595458984</v>
       </c>
       <c r="F72" t="n">
-        <v>13877700</v>
+        <v>9833300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>142.918899809868</v>
+        <v>143.4275568592265</v>
       </c>
       <c r="C73" t="n">
-        <v>143.3493069381574</v>
+        <v>144.2884009089423</v>
       </c>
       <c r="D73" t="n">
-        <v>141.5004594218987</v>
+        <v>142.1852200188561</v>
       </c>
       <c r="E73" t="n">
-        <v>142.0482788085938</v>
+        <v>142.3515167236328</v>
       </c>
       <c r="F73" t="n">
-        <v>10251700</v>
+        <v>12239900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>143.496050619897</v>
+        <v>142.3417162193598</v>
       </c>
       <c r="C74" t="n">
-        <v>145.2177239216924</v>
+        <v>142.8699668272841</v>
       </c>
       <c r="D74" t="n">
-        <v>143.2612708815172</v>
+        <v>140.8059085533541</v>
       </c>
       <c r="E74" t="n">
-        <v>144.5916595458984</v>
+        <v>141.3145904541016</v>
       </c>
       <c r="F74" t="n">
-        <v>9833300</v>
+        <v>19345600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>143.4275568592265</v>
+        <v>140.5809250079643</v>
       </c>
       <c r="C75" t="n">
-        <v>144.2884009089423</v>
+        <v>141.2558886976474</v>
       </c>
       <c r="D75" t="n">
-        <v>142.1852200188561</v>
+        <v>139.3190045706883</v>
       </c>
       <c r="E75" t="n">
-        <v>142.3515167236328</v>
+        <v>139.5831298828125</v>
       </c>
       <c r="F75" t="n">
-        <v>12239900</v>
+        <v>11731400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>142.3417469587507</v>
+        <v>139.387490519737</v>
       </c>
       <c r="C76" t="n">
-        <v>142.8699976807533</v>
+        <v>140.6004817498258</v>
       </c>
       <c r="D76" t="n">
-        <v>140.8059389610799</v>
+        <v>138.9864140977976</v>
       </c>
       <c r="E76" t="n">
-        <v>141.3146209716797</v>
+        <v>140.0624542236328</v>
       </c>
       <c r="F76" t="n">
-        <v>19345600</v>
+        <v>9541600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>140.5809250079643</v>
+        <v>139.7885720199097</v>
       </c>
       <c r="C77" t="n">
-        <v>141.2558886976474</v>
+        <v>141.5885202675369</v>
       </c>
       <c r="D77" t="n">
-        <v>139.3190045706883</v>
+        <v>139.72010392126</v>
       </c>
       <c r="E77" t="n">
-        <v>139.5831298828125</v>
+        <v>141.3439636230469</v>
       </c>
       <c r="F77" t="n">
-        <v>11731400</v>
+        <v>3259200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>139.3875057049937</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="C78" t="n">
-        <v>140.6004970672291</v>
+        <v>142.4688988061542</v>
       </c>
       <c r="D78" t="n">
-        <v>138.9864292393599</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="E78" t="n">
-        <v>140.0624694824219</v>
+        <v>141.5885009765625</v>
       </c>
       <c r="F78" t="n">
-        <v>9541600</v>
+        <v>4711500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>139.7885569290329</v>
+        <v>141.6471833233528</v>
       </c>
       <c r="C79" t="n">
-        <v>141.5885049823468</v>
+        <v>141.9113086263453</v>
       </c>
       <c r="D79" t="n">
-        <v>139.7200888377747</v>
+        <v>140.8156849267153</v>
       </c>
       <c r="E79" t="n">
-        <v>141.3439483642578</v>
+        <v>141.4221954345703</v>
       </c>
       <c r="F79" t="n">
-        <v>3259200</v>
+        <v>7662100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>141.1678710570003</v>
+        <v>141.1482779620671</v>
       </c>
       <c r="C80" t="n">
-        <v>142.4689141598225</v>
+        <v>141.3145895822191</v>
       </c>
       <c r="D80" t="n">
-        <v>141.1678710570003</v>
+        <v>140.443968700097</v>
       </c>
       <c r="E80" t="n">
-        <v>141.5885162353516</v>
+        <v>140.9135131835938</v>
       </c>
       <c r="F80" t="n">
-        <v>4711500</v>
+        <v>6006400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>141.6472138894812</v>
+        <v>140.8646148984387</v>
       </c>
       <c r="C81" t="n">
-        <v>141.9113392494694</v>
+        <v>141.0015660103057</v>
       </c>
       <c r="D81" t="n">
-        <v>140.8157153134141</v>
+        <v>140.1113763198945</v>
       </c>
       <c r="E81" t="n">
-        <v>141.4222259521484</v>
+        <v>140.1896362304688</v>
       </c>
       <c r="F81" t="n">
-        <v>7662100</v>
+        <v>5293200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>141.1482932462777</v>
+        <v>139.9939944106823</v>
       </c>
       <c r="C82" t="n">
-        <v>141.3146048844386</v>
+        <v>140.2189823252813</v>
       </c>
       <c r="D82" t="n">
-        <v>140.4439839080415</v>
+        <v>138.164715640037</v>
       </c>
       <c r="E82" t="n">
-        <v>140.9135284423828</v>
+        <v>138.7027282714844</v>
       </c>
       <c r="F82" t="n">
-        <v>6006400</v>
+        <v>8946100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>140.8646148984387</v>
+        <v>138.0277758154179</v>
       </c>
       <c r="C83" t="n">
-        <v>141.0015660103057</v>
+        <v>138.2723324593669</v>
       </c>
       <c r="D83" t="n">
-        <v>140.1113763198945</v>
+        <v>136.5604359517241</v>
       </c>
       <c r="E83" t="n">
-        <v>140.1896362304688</v>
+        <v>137.3136596679688</v>
       </c>
       <c r="F83" t="n">
-        <v>5293200</v>
+        <v>12297300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>139.9939944106823</v>
+        <v>137.333222535484</v>
       </c>
       <c r="C84" t="n">
-        <v>140.2189823252813</v>
+        <v>138.340794671558</v>
       </c>
       <c r="D84" t="n">
-        <v>138.164715640037</v>
+        <v>136.472378408915</v>
       </c>
       <c r="E84" t="n">
-        <v>138.7027282714844</v>
+        <v>136.8636779785156</v>
       </c>
       <c r="F84" t="n">
-        <v>8946100</v>
+        <v>10421800</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>138.0277604772737</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="C85" t="n">
-        <v>138.2723170940466</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="D85" t="n">
-        <v>136.560420776636</v>
+        <v>134.6235247173271</v>
       </c>
       <c r="E85" t="n">
-        <v>137.3136444091797</v>
+        <v>135.0343780517578</v>
       </c>
       <c r="F85" t="n">
-        <v>12297300</v>
+        <v>14369100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>137.3332072243459</v>
+        <v>134.8876360609042</v>
       </c>
       <c r="C86" t="n">
-        <v>138.3407792480867</v>
+        <v>138.6929361136317</v>
       </c>
       <c r="D86" t="n">
-        <v>136.4723631937515</v>
+        <v>134.8191679755417</v>
       </c>
       <c r="E86" t="n">
-        <v>136.8636627197266</v>
+        <v>138.4483795166016</v>
       </c>
       <c r="F86" t="n">
-        <v>10421800</v>
+        <v>9297100</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>136.7560662263838</v>
+        <v>138.6146938845888</v>
       </c>
       <c r="C87" t="n">
-        <v>136.7560662263838</v>
+        <v>139.2309813641768</v>
       </c>
       <c r="D87" t="n">
-        <v>134.6235247173271</v>
+        <v>137.7636415949117</v>
       </c>
       <c r="E87" t="n">
-        <v>135.0343780517578</v>
+        <v>138.7809906005859</v>
       </c>
       <c r="F87" t="n">
-        <v>14369100</v>
+        <v>9528500</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>134.8876360609042</v>
+        <v>139.1820649751552</v>
       </c>
       <c r="C88" t="n">
-        <v>138.6929361136317</v>
+        <v>140.7472333429565</v>
       </c>
       <c r="D88" t="n">
-        <v>134.8191679755417</v>
+        <v>138.6244836329666</v>
       </c>
       <c r="E88" t="n">
-        <v>138.4483795166016</v>
+        <v>140.3363800048828</v>
       </c>
       <c r="F88" t="n">
-        <v>9297100</v>
+        <v>12812000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>138.6146786440839</v>
+        <v>140.8646007849644</v>
       </c>
       <c r="C89" t="n">
-        <v>139.2309660559118</v>
+        <v>141.1971941766679</v>
       </c>
       <c r="D89" t="n">
-        <v>137.7636264479789</v>
+        <v>139.8570287929182</v>
       </c>
       <c r="E89" t="n">
-        <v>138.7809753417969</v>
+        <v>141.0993804931641</v>
       </c>
       <c r="F89" t="n">
-        <v>9528500</v>
+        <v>15549200</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>139.1820801084355</v>
+        <v>141.5298158666727</v>
       </c>
       <c r="C90" t="n">
-        <v>140.7472486464177</v>
+        <v>143.7014800904468</v>
       </c>
       <c r="D90" t="n">
-        <v>138.624498705621</v>
+        <v>141.2265680120421</v>
       </c>
       <c r="E90" t="n">
-        <v>140.3363952636719</v>
+        <v>143.1634674072266</v>
       </c>
       <c r="F90" t="n">
-        <v>12812000</v>
+        <v>13475000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>140.8646160183639</v>
+        <v>142.5080218255822</v>
       </c>
       <c r="C91" t="n">
-        <v>141.1972094460348</v>
+        <v>143.1634466813173</v>
       </c>
       <c r="D91" t="n">
-        <v>139.8570439173567</v>
+        <v>141.20699378469</v>
       </c>
       <c r="E91" t="n">
-        <v>141.0993957519531</v>
+        <v>141.4808959960938</v>
       </c>
       <c r="F91" t="n">
-        <v>15549200</v>
+        <v>10102800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>141.5297856973334</v>
+        <v>140.6298333307039</v>
       </c>
       <c r="C92" t="n">
-        <v>143.7014494581827</v>
+        <v>141.5787142100195</v>
       </c>
       <c r="D92" t="n">
-        <v>141.226537907345</v>
+        <v>140.5320196386769</v>
       </c>
       <c r="E92" t="n">
-        <v>143.1634368896484</v>
+        <v>141.3830718994141</v>
       </c>
       <c r="F92" t="n">
-        <v>13475000</v>
+        <v>11729300</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>142.5080371951474</v>
+        <v>141.314612307562</v>
       </c>
       <c r="C93" t="n">
-        <v>143.1634621215703</v>
+        <v>143.7993011474609</v>
       </c>
       <c r="D93" t="n">
-        <v>141.2070090139386</v>
+        <v>140.98200394032</v>
       </c>
       <c r="E93" t="n">
-        <v>141.4809112548828</v>
+        <v>143.7993011474609</v>
       </c>
       <c r="F93" t="n">
-        <v>10102800</v>
+        <v>12901400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>140.6298333307039</v>
+        <v>143.8579872458876</v>
       </c>
       <c r="C94" t="n">
-        <v>141.5787142100195</v>
+        <v>144.1612350737863</v>
       </c>
       <c r="D94" t="n">
-        <v>140.5320196386769</v>
+        <v>141.8134974355268</v>
       </c>
       <c r="E94" t="n">
-        <v>141.3830718994141</v>
+        <v>142.8797607421875</v>
       </c>
       <c r="F94" t="n">
-        <v>11729300</v>
+        <v>14126800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>141.314612307562</v>
+        <v>144.8557716267987</v>
       </c>
       <c r="C95" t="n">
-        <v>143.7993011474609</v>
+        <v>147.6241542164368</v>
       </c>
       <c r="D95" t="n">
-        <v>140.98200394032</v>
+        <v>144.2883985058945</v>
       </c>
       <c r="E95" t="n">
-        <v>143.7993011474609</v>
+        <v>146.6654815673828</v>
       </c>
       <c r="F95" t="n">
-        <v>12901400</v>
+        <v>18501900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,25 +2913,25 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>143.8579718826292</v>
+        <v>148.6033244770038</v>
       </c>
       <c r="C96" t="n">
-        <v>144.1612196781427</v>
+        <v>149.401311303758</v>
       </c>
       <c r="D96" t="n">
-        <v>141.813482290609</v>
+        <v>147.5787523243573</v>
       </c>
       <c r="E96" t="n">
-        <v>142.8797454833984</v>
+        <v>147.9235534667969</v>
       </c>
       <c r="F96" t="n">
-        <v>14126800</v>
+        <v>14562600</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>144.8557716267987</v>
+        <v>147.8940093166009</v>
       </c>
       <c r="C97" t="n">
-        <v>147.6241542164368</v>
+        <v>148.642749624448</v>
       </c>
       <c r="D97" t="n">
-        <v>144.2883985058945</v>
+        <v>146.3177432055359</v>
       </c>
       <c r="E97" t="n">
-        <v>146.6654815673828</v>
+        <v>147.2733612060547</v>
       </c>
       <c r="F97" t="n">
-        <v>18501900</v>
+        <v>12655700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,25 +2965,25 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>148.6033244770038</v>
+        <v>145.8744105284403</v>
       </c>
       <c r="C98" t="n">
-        <v>149.401311303758</v>
+        <v>147.4211225953709</v>
       </c>
       <c r="D98" t="n">
-        <v>147.5787523243573</v>
+        <v>145.7364720311358</v>
       </c>
       <c r="E98" t="n">
-        <v>147.9235534667969</v>
+        <v>146.1403961181641</v>
       </c>
       <c r="F98" t="n">
-        <v>14562600</v>
+        <v>9546000</v>
       </c>
       <c r="G98" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>147.8939939935073</v>
+        <v>145.8054447387209</v>
       </c>
       <c r="C99" t="n">
-        <v>148.6427342237785</v>
+        <v>146.5049234190107</v>
       </c>
       <c r="D99" t="n">
-        <v>146.3177280457571</v>
+        <v>144.613380096476</v>
       </c>
       <c r="E99" t="n">
-        <v>147.2733459472656</v>
+        <v>145.1552276611328</v>
       </c>
       <c r="F99" t="n">
-        <v>12655700</v>
+        <v>7465800</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>145.8744105284403</v>
+        <v>145.1059620999764</v>
       </c>
       <c r="C100" t="n">
-        <v>147.4211225953709</v>
+        <v>147.9038617122788</v>
       </c>
       <c r="D100" t="n">
-        <v>145.7364720311358</v>
+        <v>144.9286383741246</v>
       </c>
       <c r="E100" t="n">
-        <v>146.1403961181641</v>
+        <v>147.6772613525391</v>
       </c>
       <c r="F100" t="n">
-        <v>9546000</v>
+        <v>11035600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>145.8054294115807</v>
+        <v>148.1994047112546</v>
       </c>
       <c r="C101" t="n">
-        <v>146.5049080183409</v>
+        <v>149.7165778862847</v>
       </c>
       <c r="D101" t="n">
-        <v>144.6133648946463</v>
+        <v>146.9383858562462</v>
       </c>
       <c r="E101" t="n">
-        <v>145.1552124023438</v>
+        <v>149.5195465087891</v>
       </c>
       <c r="F101" t="n">
-        <v>7465800</v>
+        <v>12651400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>145.1059620999764</v>
+        <v>150.1599009677594</v>
       </c>
       <c r="C102" t="n">
-        <v>147.9038617122788</v>
+        <v>151.4504737667986</v>
       </c>
       <c r="D102" t="n">
-        <v>144.9286383741246</v>
+        <v>149.0072516350481</v>
       </c>
       <c r="E102" t="n">
-        <v>147.6772613525391</v>
+        <v>150.9184875488281</v>
       </c>
       <c r="F102" t="n">
-        <v>11035600</v>
+        <v>10554900</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>148.1994047112546</v>
+        <v>150.3273766276017</v>
       </c>
       <c r="C103" t="n">
-        <v>149.7165778862847</v>
+        <v>154.2089563191786</v>
       </c>
       <c r="D103" t="n">
-        <v>146.9383858562462</v>
+        <v>149.9431601878661</v>
       </c>
       <c r="E103" t="n">
-        <v>149.5195465087891</v>
+        <v>153.0169067382812</v>
       </c>
       <c r="F103" t="n">
-        <v>12651400</v>
+        <v>12424700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>150.1599009677594</v>
+        <v>153.8148971925123</v>
       </c>
       <c r="C104" t="n">
-        <v>151.4504737667986</v>
+        <v>156.0216726798457</v>
       </c>
       <c r="D104" t="n">
-        <v>149.0072516350481</v>
+        <v>153.450373358777</v>
       </c>
       <c r="E104" t="n">
-        <v>150.9184875488281</v>
+        <v>154.5439147949219</v>
       </c>
       <c r="F104" t="n">
-        <v>10554900</v>
+        <v>12178500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>150.3273766276017</v>
+        <v>156.4847030065954</v>
       </c>
       <c r="C105" t="n">
-        <v>154.2089563191786</v>
+        <v>157.2826898506833</v>
       </c>
       <c r="D105" t="n">
-        <v>149.9431601878661</v>
+        <v>153.8050342014295</v>
       </c>
       <c r="E105" t="n">
-        <v>153.0169067382812</v>
+        <v>156.2581176757812</v>
       </c>
       <c r="F105" t="n">
-        <v>12424700</v>
+        <v>13077700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>153.8148971925123</v>
+        <v>155.8935966032756</v>
       </c>
       <c r="C106" t="n">
-        <v>156.0216726798457</v>
+        <v>157.6176473147596</v>
       </c>
       <c r="D106" t="n">
-        <v>153.450373358777</v>
+        <v>155.6669962577738</v>
       </c>
       <c r="E106" t="n">
-        <v>154.5439147949219</v>
+        <v>156.8097991943359</v>
       </c>
       <c r="F106" t="n">
-        <v>12178500</v>
+        <v>10441700</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>156.4847030065954</v>
+        <v>156.4058894678126</v>
       </c>
       <c r="C107" t="n">
-        <v>157.2826898506833</v>
+        <v>156.9181830781391</v>
       </c>
       <c r="D107" t="n">
-        <v>153.8050342014295</v>
+        <v>153.7065280129841</v>
       </c>
       <c r="E107" t="n">
-        <v>156.2581176757812</v>
+        <v>154.9971008300781</v>
       </c>
       <c r="F107" t="n">
-        <v>13077700</v>
+        <v>11439900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>155.8936117729111</v>
+        <v>155.1941261981174</v>
       </c>
       <c r="C108" t="n">
-        <v>157.6176626521585</v>
+        <v>157.7752717323398</v>
       </c>
       <c r="D108" t="n">
-        <v>155.6670114053594</v>
+        <v>154.3961393746382</v>
       </c>
       <c r="E108" t="n">
-        <v>156.809814453125</v>
+        <v>156.7211456298828</v>
       </c>
       <c r="F108" t="n">
-        <v>10441700</v>
+        <v>9910100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>156.4058894678126</v>
+        <v>156.2876680693531</v>
       </c>
       <c r="C109" t="n">
-        <v>156.9181830781391</v>
+        <v>158.7505977950001</v>
       </c>
       <c r="D109" t="n">
-        <v>153.7065280129841</v>
+        <v>155.8443437252427</v>
       </c>
       <c r="E109" t="n">
-        <v>154.9971008300781</v>
+        <v>157.6275024414062</v>
       </c>
       <c r="F109" t="n">
-        <v>11439900</v>
+        <v>10217300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>155.1941413082318</v>
+        <v>157.6472078811371</v>
       </c>
       <c r="C110" t="n">
-        <v>157.7752870937614</v>
+        <v>160.7209393253002</v>
       </c>
       <c r="D110" t="n">
-        <v>154.3961544070585</v>
+        <v>157.2826840647245</v>
       </c>
       <c r="E110" t="n">
-        <v>156.7211608886719</v>
+        <v>158.8195648193359</v>
       </c>
       <c r="F110" t="n">
-        <v>9910100</v>
+        <v>13512900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>156.2876831984424</v>
+        <v>159.3417228437737</v>
       </c>
       <c r="C111" t="n">
-        <v>158.7506131625079</v>
+        <v>160.1594173981944</v>
       </c>
       <c r="D111" t="n">
-        <v>155.8443588114169</v>
+        <v>157.3418249095697</v>
       </c>
       <c r="E111" t="n">
-        <v>157.6275177001953</v>
+        <v>157.6964874267578</v>
       </c>
       <c r="F111" t="n">
-        <v>10217300</v>
+        <v>13998900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>157.6472078811371</v>
+        <v>157.5782363157609</v>
       </c>
       <c r="C112" t="n">
-        <v>160.7209393253002</v>
+        <v>159.765319051939</v>
       </c>
       <c r="D112" t="n">
-        <v>157.2826840647245</v>
+        <v>156.5241102403673</v>
       </c>
       <c r="E112" t="n">
-        <v>158.8195648193359</v>
+        <v>157.1841735839844</v>
       </c>
       <c r="F112" t="n">
-        <v>13512900</v>
+        <v>13319100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>159.3417228437737</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="C113" t="n">
-        <v>160.1594173981944</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="D113" t="n">
-        <v>157.3418249095697</v>
+        <v>153.4602390569104</v>
       </c>
       <c r="E113" t="n">
-        <v>157.6964874267578</v>
+        <v>154.5340728759766</v>
       </c>
       <c r="F113" t="n">
-        <v>13998900</v>
+        <v>14434300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>157.5782363157609</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="C114" t="n">
-        <v>159.765319051939</v>
+        <v>157.588096663496</v>
       </c>
       <c r="D114" t="n">
-        <v>156.5241102403673</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="E114" t="n">
-        <v>157.1841735839844</v>
+        <v>156.2088470458984</v>
       </c>
       <c r="F114" t="n">
-        <v>13319100</v>
+        <v>10724600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>156.6226326022383</v>
+        <v>156.7704074552917</v>
       </c>
       <c r="C115" t="n">
-        <v>156.6226326022383</v>
+        <v>158.6717819848204</v>
       </c>
       <c r="D115" t="n">
-        <v>153.4602390569104</v>
+        <v>155.8147895206744</v>
       </c>
       <c r="E115" t="n">
-        <v>154.5340728759766</v>
+        <v>158.3959350585938</v>
       </c>
       <c r="F115" t="n">
-        <v>14434300</v>
+        <v>11508100</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>154.5045190368278</v>
+        <v>157.9427805830092</v>
       </c>
       <c r="C116" t="n">
-        <v>157.5881120570129</v>
+        <v>162.9080407961134</v>
       </c>
       <c r="D116" t="n">
-        <v>154.5045190368278</v>
+        <v>157.9230729341091</v>
       </c>
       <c r="E116" t="n">
-        <v>156.2088623046875</v>
+        <v>162.7208557128906</v>
       </c>
       <c r="F116" t="n">
-        <v>10724600</v>
+        <v>14772400</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>156.7704074552917</v>
+        <v>162.4548534700461</v>
       </c>
       <c r="C117" t="n">
-        <v>158.6717819848204</v>
+        <v>164.3956434730223</v>
       </c>
       <c r="D117" t="n">
-        <v>155.8147895206744</v>
+        <v>161.509096787574</v>
       </c>
       <c r="E117" t="n">
-        <v>158.3959350585938</v>
+        <v>162.8292236328125</v>
       </c>
       <c r="F117" t="n">
-        <v>11508100</v>
+        <v>9709500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>157.9427657722736</v>
+        <v>162.1001810746762</v>
       </c>
       <c r="C118" t="n">
-        <v>162.9080255197715</v>
+        <v>162.5533667721119</v>
       </c>
       <c r="D118" t="n">
-        <v>157.9230581252215</v>
+        <v>159.6963742176143</v>
       </c>
       <c r="E118" t="n">
-        <v>162.7208404541016</v>
+        <v>160.9672393798828</v>
       </c>
       <c r="F118" t="n">
-        <v>14772400</v>
+        <v>7878500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>162.4548534700461</v>
+        <v>161.7849314119297</v>
       </c>
       <c r="C119" t="n">
-        <v>164.3956434730223</v>
+        <v>162.0607783426765</v>
       </c>
       <c r="D119" t="n">
-        <v>161.509096787574</v>
+        <v>160.4450970200751</v>
       </c>
       <c r="E119" t="n">
-        <v>162.8292236328125</v>
+        <v>161.3218994140625</v>
       </c>
       <c r="F119" t="n">
-        <v>9709500</v>
+        <v>7028600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>162.1001810746762</v>
+        <v>161.6075869258529</v>
       </c>
       <c r="C120" t="n">
-        <v>162.5533667721119</v>
+        <v>164.7699952425796</v>
       </c>
       <c r="D120" t="n">
-        <v>159.6963742176143</v>
+        <v>161.262785790902</v>
       </c>
       <c r="E120" t="n">
-        <v>160.9672393798828</v>
+        <v>164.7207336425781</v>
       </c>
       <c r="F120" t="n">
-        <v>7878500</v>
+        <v>14878500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>161.7849314119297</v>
+        <v>162.8390693932343</v>
       </c>
       <c r="C121" t="n">
-        <v>162.0607783426765</v>
+        <v>164.0803957045348</v>
       </c>
       <c r="D121" t="n">
-        <v>160.4450970200751</v>
+        <v>161.0263565641498</v>
       </c>
       <c r="E121" t="n">
-        <v>161.3218994140625</v>
+        <v>161.0854644775391</v>
       </c>
       <c r="F121" t="n">
-        <v>7028600</v>
+        <v>9095500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>161.6075869258529</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="C122" t="n">
-        <v>164.7699952425796</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="D122" t="n">
-        <v>161.262785790902</v>
+        <v>156.2679589705066</v>
       </c>
       <c r="E122" t="n">
-        <v>164.7207336425781</v>
+        <v>157.3516540527344</v>
       </c>
       <c r="F122" t="n">
-        <v>14878500</v>
+        <v>10161000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>162.8390539683353</v>
+        <v>157.0758237333674</v>
       </c>
       <c r="C123" t="n">
-        <v>164.0803801620515</v>
+        <v>157.243301166956</v>
       </c>
       <c r="D123" t="n">
-        <v>161.0263413109597</v>
+        <v>154.9774025943761</v>
       </c>
       <c r="E123" t="n">
-        <v>161.08544921875</v>
+        <v>155.9527282714844</v>
       </c>
       <c r="F123" t="n">
-        <v>9095500</v>
+        <v>8752700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>159.7850452964264</v>
+        <v>154.6128887776175</v>
       </c>
       <c r="C124" t="n">
-        <v>159.7850452964264</v>
+        <v>154.7705198979749</v>
       </c>
       <c r="D124" t="n">
-        <v>156.267974124207</v>
+        <v>151.4898954891258</v>
       </c>
       <c r="E124" t="n">
-        <v>157.3516693115234</v>
+        <v>151.7066345214844</v>
       </c>
       <c r="F124" t="n">
-        <v>10161000</v>
+        <v>10060300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>157.075808364692</v>
+        <v>151.3815284437877</v>
       </c>
       <c r="C125" t="n">
-        <v>157.2432857818942</v>
+        <v>152.1401000368933</v>
       </c>
       <c r="D125" t="n">
-        <v>154.9773874310153</v>
+        <v>149.6377698486339</v>
       </c>
       <c r="E125" t="n">
-        <v>155.9527130126953</v>
+        <v>151.3519744873047</v>
       </c>
       <c r="F125" t="n">
-        <v>8752700</v>
+        <v>8187900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>154.6128732265148</v>
+        <v>150.8790677258081</v>
       </c>
       <c r="C126" t="n">
-        <v>154.7705043310175</v>
+        <v>153.9133989264833</v>
       </c>
       <c r="D126" t="n">
-        <v>151.4898802521365</v>
+        <v>150.6327747552909</v>
       </c>
       <c r="E126" t="n">
-        <v>151.7066192626953</v>
+        <v>152.9183807373047</v>
       </c>
       <c r="F126" t="n">
-        <v>10060300</v>
+        <v>12494900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>151.3815131820191</v>
+        <v>153.1843919415674</v>
       </c>
       <c r="C127" t="n">
-        <v>152.1400846986481</v>
+        <v>154.8197659541039</v>
       </c>
       <c r="D127" t="n">
-        <v>149.6377547626651</v>
+        <v>151.3224175570726</v>
       </c>
       <c r="E127" t="n">
-        <v>151.3519592285156</v>
+        <v>153.6966705322266</v>
       </c>
       <c r="F127" t="n">
-        <v>8187900</v>
+        <v>7756800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>150.8790677258081</v>
+        <v>152.9282368144603</v>
       </c>
       <c r="C128" t="n">
-        <v>153.9133989264833</v>
+        <v>153.07602162573</v>
       </c>
       <c r="D128" t="n">
-        <v>150.6327747552909</v>
+        <v>149.1845804169242</v>
       </c>
       <c r="E128" t="n">
-        <v>152.9183807373047</v>
+        <v>151.0465698242188</v>
       </c>
       <c r="F128" t="n">
-        <v>12494900</v>
+        <v>8855100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>153.1843767336366</v>
+        <v>149.9530221525258</v>
       </c>
       <c r="C129" t="n">
-        <v>154.8197505838155</v>
+        <v>150.7805629442461</v>
       </c>
       <c r="D129" t="n">
-        <v>151.322402533996</v>
+        <v>148.100894162221</v>
       </c>
       <c r="E129" t="n">
-        <v>153.6966552734375</v>
+        <v>148.2683715820312</v>
       </c>
       <c r="F129" t="n">
-        <v>7756800</v>
+        <v>8489300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>152.9282368144603</v>
+        <v>149.1254779831649</v>
       </c>
       <c r="C130" t="n">
-        <v>153.07602162573</v>
+        <v>150.2879887378921</v>
       </c>
       <c r="D130" t="n">
-        <v>149.1845804169242</v>
+        <v>147.9531209203371</v>
       </c>
       <c r="E130" t="n">
-        <v>151.0465698242188</v>
+        <v>148.4161529541016</v>
       </c>
       <c r="F130" t="n">
-        <v>8855100</v>
+        <v>7298900</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>149.9530221525258</v>
+        <v>149.6082100748309</v>
       </c>
       <c r="C131" t="n">
-        <v>150.7805629442461</v>
+        <v>150.3766429785721</v>
       </c>
       <c r="D131" t="n">
-        <v>148.100894162221</v>
+        <v>148.4161454237534</v>
       </c>
       <c r="E131" t="n">
-        <v>148.2683715820312</v>
+        <v>149.8643493652344</v>
       </c>
       <c r="F131" t="n">
-        <v>8489300</v>
+        <v>6944000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>149.1254626514495</v>
+        <v>150.7411528047512</v>
       </c>
       <c r="C132" t="n">
-        <v>150.287973286658</v>
+        <v>151.184492202826</v>
       </c>
       <c r="D132" t="n">
-        <v>147.9531057091528</v>
+        <v>148.9579940023762</v>
       </c>
       <c r="E132" t="n">
-        <v>148.4161376953125</v>
+        <v>149.2338409423828</v>
       </c>
       <c r="F132" t="n">
-        <v>7298900</v>
+        <v>6147700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>149.6082100748309</v>
+        <v>147.0960143427481</v>
       </c>
       <c r="C133" t="n">
-        <v>150.3766429785721</v>
+        <v>147.4014152272885</v>
       </c>
       <c r="D133" t="n">
-        <v>148.4161454237534</v>
+        <v>144.2882834404146</v>
       </c>
       <c r="E133" t="n">
-        <v>149.8643493652344</v>
+        <v>144.5345764160156</v>
       </c>
       <c r="F133" t="n">
-        <v>6944000</v>
+        <v>10059300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>150.7411528047512</v>
+        <v>144.0518332623683</v>
       </c>
       <c r="C134" t="n">
-        <v>151.184492202826</v>
+        <v>145.1946362491204</v>
       </c>
       <c r="D134" t="n">
-        <v>148.9579940023762</v>
+        <v>142.6430296593396</v>
       </c>
       <c r="E134" t="n">
-        <v>149.2338409423828</v>
+        <v>142.6922912597656</v>
       </c>
       <c r="F134" t="n">
-        <v>6147700</v>
+        <v>10340300</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>147.0960143427481</v>
+        <v>142.8400884498559</v>
       </c>
       <c r="C135" t="n">
-        <v>147.4014152272885</v>
+        <v>143.6577829837524</v>
       </c>
       <c r="D135" t="n">
-        <v>144.2882834404146</v>
+        <v>142.111055784898</v>
       </c>
       <c r="E135" t="n">
-        <v>144.5345764160156</v>
+        <v>142.1406097412109</v>
       </c>
       <c r="F135" t="n">
-        <v>10059300</v>
+        <v>60620900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>144.0518332623683</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="C136" t="n">
-        <v>145.1946362491204</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="D136" t="n">
-        <v>142.6430296593396</v>
+        <v>141.3524721007716</v>
       </c>
       <c r="E136" t="n">
-        <v>142.6922912597656</v>
+        <v>141.8549194335938</v>
       </c>
       <c r="F136" t="n">
-        <v>10340300</v>
+        <v>10315600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>142.8400731159778</v>
+        <v>141.2046936096272</v>
       </c>
       <c r="C137" t="n">
-        <v>143.6577675620949</v>
+        <v>143.0765142514037</v>
       </c>
       <c r="D137" t="n">
-        <v>142.1110405292816</v>
+        <v>140.1209984806846</v>
       </c>
       <c r="E137" t="n">
-        <v>142.1405944824219</v>
+        <v>141.0372161865234</v>
       </c>
       <c r="F137" t="n">
-        <v>60620900</v>
+        <v>8567600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>143.9828640073101</v>
+        <v>141.6086259660596</v>
       </c>
       <c r="C138" t="n">
-        <v>143.9828640073101</v>
+        <v>141.9632884805344</v>
       </c>
       <c r="D138" t="n">
-        <v>141.3524568960289</v>
+        <v>140.1210066538726</v>
       </c>
       <c r="E138" t="n">
-        <v>141.8549041748047</v>
+        <v>141.7859497070312</v>
       </c>
       <c r="F138" t="n">
-        <v>10315600</v>
+        <v>8418100</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>141.2046936096272</v>
+        <v>141.559369693648</v>
       </c>
       <c r="C139" t="n">
-        <v>143.0765142514037</v>
+        <v>142.4263258800331</v>
       </c>
       <c r="D139" t="n">
-        <v>140.1209984806846</v>
+        <v>140.1308732738322</v>
       </c>
       <c r="E139" t="n">
-        <v>141.0372161865234</v>
+        <v>140.3081970214844</v>
       </c>
       <c r="F139" t="n">
-        <v>8567600</v>
+        <v>6443200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>141.6086107263538</v>
+        <v>140.603748896169</v>
       </c>
       <c r="C140" t="n">
-        <v>141.9632732026604</v>
+        <v>141.9435834160748</v>
       </c>
       <c r="D140" t="n">
-        <v>140.1209915742622</v>
+        <v>139.9042701625835</v>
       </c>
       <c r="E140" t="n">
-        <v>141.7859344482422</v>
+        <v>140.5939025878906</v>
       </c>
       <c r="F140" t="n">
-        <v>8418100</v>
+        <v>11558300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>141.5593542987915</v>
+        <v>140.9189847788946</v>
       </c>
       <c r="C141" t="n">
-        <v>142.4263103908934</v>
+        <v>143.4114835656516</v>
       </c>
       <c r="D141" t="n">
-        <v>140.1308580343274</v>
+        <v>140.4559678065659</v>
       </c>
       <c r="E141" t="n">
-        <v>140.3081817626953</v>
+        <v>142.5740814208984</v>
       </c>
       <c r="F141" t="n">
-        <v>6443200</v>
+        <v>11616300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>140.6037336363113</v>
+        <v>142.6726031682958</v>
       </c>
       <c r="C142" t="n">
-        <v>141.9435680108036</v>
+        <v>142.7711113397407</v>
       </c>
       <c r="D142" t="n">
-        <v>139.9042549786409</v>
+        <v>140.1702580996175</v>
       </c>
       <c r="E142" t="n">
-        <v>140.5938873291016</v>
+        <v>142.2982330322266</v>
       </c>
       <c r="F142" t="n">
-        <v>11558300</v>
+        <v>10407500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>140.9189847788946</v>
+        <v>141.7859527393269</v>
       </c>
       <c r="C143" t="n">
-        <v>143.4114835656516</v>
+        <v>142.8203863480455</v>
       </c>
       <c r="D143" t="n">
-        <v>140.4559678065659</v>
+        <v>141.0864890360487</v>
       </c>
       <c r="E143" t="n">
-        <v>142.5740814208984</v>
+        <v>141.9534301757812</v>
       </c>
       <c r="F143" t="n">
-        <v>11616300</v>
+        <v>8061700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>142.6726031682958</v>
+        <v>141.9534207153344</v>
       </c>
       <c r="C144" t="n">
-        <v>142.7711113397407</v>
+        <v>142.0716515698294</v>
       </c>
       <c r="D144" t="n">
-        <v>140.1702580996175</v>
+        <v>140.4658165030053</v>
       </c>
       <c r="E144" t="n">
-        <v>142.2982330322266</v>
+        <v>140.997802734375</v>
       </c>
       <c r="F144" t="n">
-        <v>10407500</v>
+        <v>5941700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>141.7859527393269</v>
+        <v>140.8894315190035</v>
       </c>
       <c r="C145" t="n">
-        <v>142.8203863480455</v>
+        <v>141.5396485970176</v>
       </c>
       <c r="D145" t="n">
-        <v>141.0864890360487</v>
+        <v>139.8155977290451</v>
       </c>
       <c r="E145" t="n">
-        <v>141.9534301757812</v>
+        <v>140.6529998779297</v>
       </c>
       <c r="F145" t="n">
-        <v>8061700</v>
+        <v>6823100</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>141.9534207153344</v>
+        <v>140.4066990917555</v>
       </c>
       <c r="C146" t="n">
-        <v>142.0716515698294</v>
+        <v>140.6529920592033</v>
       </c>
       <c r="D146" t="n">
-        <v>140.4658165030053</v>
+        <v>138.6530943661295</v>
       </c>
       <c r="E146" t="n">
-        <v>140.997802734375</v>
+        <v>139.2047882080078</v>
       </c>
       <c r="F146" t="n">
-        <v>5941700</v>
+        <v>7207500</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>140.8894315190035</v>
+        <v>141.0273529653376</v>
       </c>
       <c r="C147" t="n">
-        <v>141.5396485970176</v>
+        <v>142.9582965240978</v>
       </c>
       <c r="D147" t="n">
-        <v>139.8155977290451</v>
+        <v>139.766334122587</v>
       </c>
       <c r="E147" t="n">
-        <v>140.6529998779297</v>
+        <v>142.7514038085938</v>
       </c>
       <c r="F147" t="n">
-        <v>6823100</v>
+        <v>10849700</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>140.4066990917555</v>
+        <v>142.2489765209199</v>
       </c>
       <c r="C148" t="n">
-        <v>140.6529920592033</v>
+        <v>144.7611679868877</v>
       </c>
       <c r="D148" t="n">
-        <v>138.6530943661295</v>
+        <v>140.8795881188284</v>
       </c>
       <c r="E148" t="n">
-        <v>139.2047882080078</v>
+        <v>144.4853210449219</v>
       </c>
       <c r="F148" t="n">
-        <v>7207500</v>
+        <v>6794800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>141.0273529653376</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="C149" t="n">
-        <v>142.9582965240978</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="D149" t="n">
-        <v>139.766334122587</v>
+        <v>142.6134905474848</v>
       </c>
       <c r="E149" t="n">
-        <v>142.7514038085938</v>
+        <v>143.007568359375</v>
       </c>
       <c r="F149" t="n">
-        <v>10849700</v>
+        <v>9790300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>142.2489765209199</v>
+        <v>142.8499157089539</v>
       </c>
       <c r="C150" t="n">
-        <v>144.7611679868877</v>
+        <v>142.9385775660697</v>
       </c>
       <c r="D150" t="n">
-        <v>140.8795881188284</v>
+        <v>140.5150632763963</v>
       </c>
       <c r="E150" t="n">
-        <v>144.4853210449219</v>
+        <v>141.4509735107422</v>
       </c>
       <c r="F150" t="n">
-        <v>6794800</v>
+        <v>7121400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>144.7118962366312</v>
+        <v>141.1160402826616</v>
       </c>
       <c r="C151" t="n">
-        <v>144.7118962366312</v>
+        <v>142.5740906086617</v>
       </c>
       <c r="D151" t="n">
-        <v>142.6134753307435</v>
+        <v>140.6530082479637</v>
       </c>
       <c r="E151" t="n">
-        <v>143.0075531005859</v>
+        <v>142.2391357421875</v>
       </c>
       <c r="F151" t="n">
-        <v>9790300</v>
+        <v>6621600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>142.8499157089539</v>
+        <v>142.2194162805844</v>
       </c>
       <c r="C152" t="n">
-        <v>142.9385775660697</v>
+        <v>142.2588165423252</v>
       </c>
       <c r="D152" t="n">
-        <v>140.5150632763963</v>
+        <v>140.1505492747316</v>
       </c>
       <c r="E152" t="n">
-        <v>141.4509735107422</v>
+        <v>141.2539520263672</v>
       </c>
       <c r="F152" t="n">
-        <v>7121400</v>
+        <v>7698200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>141.1160402826616</v>
+        <v>141.0766226846627</v>
       </c>
       <c r="C153" t="n">
-        <v>142.5740906086617</v>
+        <v>142.1504565210129</v>
       </c>
       <c r="D153" t="n">
-        <v>140.6530082479637</v>
+        <v>140.5446364367332</v>
       </c>
       <c r="E153" t="n">
-        <v>142.2391357421875</v>
+        <v>140.9879608154297</v>
       </c>
       <c r="F153" t="n">
-        <v>6621600</v>
+        <v>6947100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>142.2194162805844</v>
+        <v>141.2835176988996</v>
       </c>
       <c r="C154" t="n">
-        <v>142.2588165423252</v>
+        <v>145.4015293724886</v>
       </c>
       <c r="D154" t="n">
-        <v>140.1505492747316</v>
+        <v>141.0372247031338</v>
       </c>
       <c r="E154" t="n">
-        <v>141.2539520263672</v>
+        <v>144.7513122558594</v>
       </c>
       <c r="F154" t="n">
-        <v>7698200</v>
+        <v>10886000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>141.0766226846627</v>
+        <v>143.8942158414082</v>
       </c>
       <c r="C155" t="n">
-        <v>142.1504565210129</v>
+        <v>144.4853250376877</v>
       </c>
       <c r="D155" t="n">
-        <v>140.5446364367332</v>
+        <v>141.4608398676902</v>
       </c>
       <c r="E155" t="n">
-        <v>140.9879608154297</v>
+        <v>142.3475036621094</v>
       </c>
       <c r="F155" t="n">
-        <v>6947100</v>
+        <v>8084700</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>141.2835176988996</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="C156" t="n">
-        <v>145.4015293724886</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="D156" t="n">
-        <v>141.0372247031338</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="E156" t="n">
-        <v>144.7513122558594</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="F156" t="n">
-        <v>10886000</v>
+        <v>11197200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>143.894200416821</v>
+        <v>140.3869953464167</v>
       </c>
       <c r="C157" t="n">
-        <v>144.4853095497371</v>
+        <v>141.175135870657</v>
       </c>
       <c r="D157" t="n">
-        <v>141.4608247039461</v>
+        <v>140.1111484178121</v>
       </c>
       <c r="E157" t="n">
-        <v>142.3474884033203</v>
+        <v>140.7318115234375</v>
       </c>
       <c r="F157" t="n">
-        <v>8084700</v>
+        <v>7236300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>142.4755543482728</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="C158" t="n">
-        <v>142.4755543482728</v>
+        <v>144.0616865371081</v>
       </c>
       <c r="D158" t="n">
-        <v>140.2096710205078</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="E158" t="n">
-        <v>140.2096710205078</v>
+        <v>143.5494079589844</v>
       </c>
       <c r="F158" t="n">
-        <v>11197200</v>
+        <v>11288800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,25 +4551,25 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>140.3869953464167</v>
+        <v>150.8836541197979</v>
       </c>
       <c r="C159" t="n">
-        <v>141.175135870657</v>
+        <v>151.2906197995367</v>
       </c>
       <c r="D159" t="n">
-        <v>140.1111484178121</v>
+        <v>146.5261830755894</v>
       </c>
       <c r="E159" t="n">
-        <v>140.7318115234375</v>
+        <v>147.08203125</v>
       </c>
       <c r="F159" t="n">
-        <v>7236300</v>
+        <v>13786200</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>141.2736481824844</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="C160" t="n">
-        <v>144.0616865371081</v>
+        <v>148.59077024601</v>
       </c>
       <c r="D160" t="n">
-        <v>141.2736481824844</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="E160" t="n">
-        <v>143.5494079589844</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F160" t="n">
-        <v>11288800</v>
+        <v>9166400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,25 +4603,25 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>150.8836541197979</v>
+        <v>148.9183255527001</v>
       </c>
       <c r="C161" t="n">
-        <v>151.2906197995367</v>
+        <v>150.0697339670296</v>
       </c>
       <c r="D161" t="n">
-        <v>146.5261830755894</v>
+        <v>147.3301749711611</v>
       </c>
       <c r="E161" t="n">
-        <v>147.08203125</v>
+        <v>148.064697265625</v>
       </c>
       <c r="F161" t="n">
-        <v>13786200</v>
+        <v>7965700</v>
       </c>
       <c r="G161" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>146.3276654919543</v>
+        <v>147.2011489489405</v>
       </c>
       <c r="C162" t="n">
-        <v>148.59077024601</v>
+        <v>147.6478115682369</v>
       </c>
       <c r="D162" t="n">
-        <v>146.3276654919543</v>
+        <v>144.8090026189782</v>
       </c>
       <c r="E162" t="n">
-        <v>147.3003997802734</v>
+        <v>145.3747863769531</v>
       </c>
       <c r="F162" t="n">
-        <v>9166400</v>
+        <v>9002400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>148.9183255527001</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="C163" t="n">
-        <v>150.0697339670296</v>
+        <v>146.6254435609453</v>
       </c>
       <c r="D163" t="n">
-        <v>147.3301749711611</v>
+        <v>144.8685544504002</v>
       </c>
       <c r="E163" t="n">
-        <v>148.064697265625</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="F163" t="n">
-        <v>7965700</v>
+        <v>9491700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>147.2011489489405</v>
+        <v>146.7743191747914</v>
       </c>
       <c r="C164" t="n">
-        <v>147.6478115682369</v>
+        <v>148.1738750980608</v>
       </c>
       <c r="D164" t="n">
-        <v>144.8090026189782</v>
+        <v>145.3747783972478</v>
       </c>
       <c r="E164" t="n">
-        <v>145.3747863769531</v>
+        <v>146.1688385009766</v>
       </c>
       <c r="F164" t="n">
-        <v>9002400</v>
+        <v>6814800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>146.0001068115234</v>
+        <v>144.977737605514</v>
       </c>
       <c r="C165" t="n">
-        <v>146.6254435609453</v>
+        <v>144.977737605514</v>
       </c>
       <c r="D165" t="n">
-        <v>144.8685544504002</v>
+        <v>142.2084173171452</v>
       </c>
       <c r="E165" t="n">
-        <v>146.0001068115234</v>
+        <v>142.3572998046875</v>
       </c>
       <c r="F165" t="n">
-        <v>9491700</v>
+        <v>9642800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>146.7743191747914</v>
+        <v>142.3175981532361</v>
       </c>
       <c r="C166" t="n">
-        <v>148.1738750980608</v>
+        <v>144.8189147356386</v>
       </c>
       <c r="D166" t="n">
-        <v>145.3747783972478</v>
+        <v>141.1264777093581</v>
       </c>
       <c r="E166" t="n">
-        <v>146.1688385009766</v>
+        <v>143.8263244628906</v>
       </c>
       <c r="F166" t="n">
-        <v>6814800</v>
+        <v>7664300</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>144.977737605514</v>
+        <v>145.3152221312864</v>
       </c>
       <c r="C167" t="n">
-        <v>144.977737605514</v>
+        <v>147.8463305694715</v>
       </c>
       <c r="D167" t="n">
-        <v>142.2084173171452</v>
+        <v>144.8586390489098</v>
       </c>
       <c r="E167" t="n">
-        <v>142.3572998046875</v>
+        <v>146.8041076660156</v>
       </c>
       <c r="F167" t="n">
-        <v>9642800</v>
+        <v>9399500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>142.3175981532361</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="C168" t="n">
-        <v>144.8189147356386</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="D168" t="n">
-        <v>141.1264777093581</v>
+        <v>144.9380404787042</v>
       </c>
       <c r="E168" t="n">
-        <v>143.8263244628906</v>
+        <v>144.9777374267578</v>
       </c>
       <c r="F168" t="n">
-        <v>7664300</v>
+        <v>9545800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>145.3152221312864</v>
+        <v>145.4641093327384</v>
       </c>
       <c r="C169" t="n">
-        <v>147.8463305694715</v>
+        <v>146.4269231210903</v>
       </c>
       <c r="D169" t="n">
-        <v>144.8586390489098</v>
+        <v>145.1266322707271</v>
       </c>
       <c r="E169" t="n">
-        <v>146.8041076660156</v>
+        <v>145.3350677490234</v>
       </c>
       <c r="F169" t="n">
-        <v>9399500</v>
+        <v>5741000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>146.8934445898874</v>
+        <v>144.7097318886224</v>
       </c>
       <c r="C170" t="n">
-        <v>146.8934445898874</v>
+        <v>144.8685499701872</v>
       </c>
       <c r="D170" t="n">
-        <v>144.9380404787042</v>
+        <v>140.9180448520501</v>
       </c>
       <c r="E170" t="n">
-        <v>144.9777374267578</v>
+        <v>142.2977447509766</v>
       </c>
       <c r="F170" t="n">
-        <v>9545800</v>
+        <v>7489500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>145.4641093327384</v>
+        <v>143.280415861365</v>
       </c>
       <c r="C171" t="n">
-        <v>146.4269231210903</v>
+        <v>144.7792217618835</v>
       </c>
       <c r="D171" t="n">
-        <v>145.1266322707271</v>
+        <v>141.8014508619235</v>
       </c>
       <c r="E171" t="n">
-        <v>145.3350677490234</v>
+        <v>142.8436737060547</v>
       </c>
       <c r="F171" t="n">
-        <v>5741000</v>
+        <v>9051200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>144.7097318886224</v>
+        <v>142.0892960817053</v>
       </c>
       <c r="C172" t="n">
-        <v>144.8685499701872</v>
+        <v>143.5980375858882</v>
       </c>
       <c r="D172" t="n">
-        <v>140.9180448520501</v>
+        <v>140.610346220736</v>
       </c>
       <c r="E172" t="n">
-        <v>142.2977447509766</v>
+        <v>141.1860504150391</v>
       </c>
       <c r="F172" t="n">
-        <v>7489500</v>
+        <v>6685900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>143.280415861365</v>
+        <v>142.1190761527801</v>
       </c>
       <c r="C173" t="n">
-        <v>144.7792217618835</v>
+        <v>143.2109315738657</v>
       </c>
       <c r="D173" t="n">
-        <v>141.8014508619235</v>
+        <v>141.5731635879637</v>
       </c>
       <c r="E173" t="n">
-        <v>142.8436737060547</v>
+        <v>141.6525726318359</v>
       </c>
       <c r="F173" t="n">
-        <v>9051200</v>
+        <v>9636200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>142.0892960817053</v>
+        <v>142.337438212696</v>
       </c>
       <c r="C174" t="n">
-        <v>143.5980375858882</v>
+        <v>142.337438212696</v>
       </c>
       <c r="D174" t="n">
-        <v>140.610346220736</v>
+        <v>140.1537426546991</v>
       </c>
       <c r="E174" t="n">
-        <v>141.1860504150391</v>
+        <v>140.5210113525391</v>
       </c>
       <c r="F174" t="n">
-        <v>6685900</v>
+        <v>6989400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>142.1190761527801</v>
+        <v>141.0470859006894</v>
       </c>
       <c r="C175" t="n">
-        <v>143.2109315738657</v>
+        <v>143.3598079421396</v>
       </c>
       <c r="D175" t="n">
-        <v>141.5731635879637</v>
+        <v>140.5805672539439</v>
       </c>
       <c r="E175" t="n">
-        <v>141.6525726318359</v>
+        <v>141.3349304199219</v>
       </c>
       <c r="F175" t="n">
-        <v>9636200</v>
+        <v>7731200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>142.337438212696</v>
+        <v>141.4143347616525</v>
       </c>
       <c r="C176" t="n">
-        <v>142.337438212696</v>
+        <v>142.6451521296186</v>
       </c>
       <c r="D176" t="n">
-        <v>140.1537426546991</v>
+        <v>139.8063433960926</v>
       </c>
       <c r="E176" t="n">
-        <v>140.5210113525391</v>
+        <v>140.2530059814453</v>
       </c>
       <c r="F176" t="n">
-        <v>6989400</v>
+        <v>8355800</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>141.0470859006894</v>
+        <v>140.4018973938673</v>
       </c>
       <c r="C177" t="n">
-        <v>143.3598079421396</v>
+        <v>142.1587864968038</v>
       </c>
       <c r="D177" t="n">
-        <v>140.5805672539439</v>
+        <v>139.578045612781</v>
       </c>
       <c r="E177" t="n">
-        <v>141.3349304199219</v>
+        <v>141.3845672607422</v>
       </c>
       <c r="F177" t="n">
-        <v>7731200</v>
+        <v>8375600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>141.4143347616525</v>
+        <v>140.8287217143626</v>
       </c>
       <c r="C178" t="n">
-        <v>142.6451521296186</v>
+        <v>142.655084297577</v>
       </c>
       <c r="D178" t="n">
-        <v>139.8063433960926</v>
+        <v>139.0519765313656</v>
       </c>
       <c r="E178" t="n">
-        <v>140.2530059814453</v>
+        <v>142.3374481201172</v>
       </c>
       <c r="F178" t="n">
-        <v>8355800</v>
+        <v>6297300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>140.4018973938673</v>
+        <v>142.8039672134308</v>
       </c>
       <c r="C179" t="n">
-        <v>142.1587864968038</v>
+        <v>143.5682660152007</v>
       </c>
       <c r="D179" t="n">
-        <v>139.578045612781</v>
+        <v>142.4664901331732</v>
       </c>
       <c r="E179" t="n">
-        <v>141.3845672607422</v>
+        <v>143.3697509765625</v>
       </c>
       <c r="F179" t="n">
-        <v>8375600</v>
+        <v>4616700</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>140.8287217143626</v>
+        <v>143.439213854944</v>
       </c>
       <c r="C180" t="n">
-        <v>142.655084297577</v>
+        <v>144.5310692055886</v>
       </c>
       <c r="D180" t="n">
-        <v>139.0519765313656</v>
+        <v>141.473889369509</v>
       </c>
       <c r="E180" t="n">
-        <v>142.3374481201172</v>
+        <v>141.9007110595703</v>
       </c>
       <c r="F180" t="n">
-        <v>6297300</v>
+        <v>8157200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>142.8039672134308</v>
+        <v>142.397017874141</v>
       </c>
       <c r="C181" t="n">
-        <v>143.5682660152007</v>
+        <v>147.4393635097026</v>
       </c>
       <c r="D181" t="n">
-        <v>142.4664901331732</v>
+        <v>142.397017874141</v>
       </c>
       <c r="E181" t="n">
-        <v>143.3697509765625</v>
+        <v>146.3971557617188</v>
       </c>
       <c r="F181" t="n">
-        <v>4616700</v>
+        <v>10048900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>143.439213854944</v>
+        <v>145.612997111615</v>
       </c>
       <c r="C182" t="n">
-        <v>144.5310692055886</v>
+        <v>145.612997111615</v>
       </c>
       <c r="D182" t="n">
-        <v>141.473889369509</v>
+        <v>143.9355170452321</v>
       </c>
       <c r="E182" t="n">
-        <v>141.9007110595703</v>
+        <v>144.828857421875</v>
       </c>
       <c r="F182" t="n">
-        <v>8157200</v>
+        <v>10196700</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>142.397017874141</v>
+        <v>144.4417452563355</v>
       </c>
       <c r="C183" t="n">
-        <v>147.4393635097026</v>
+        <v>144.5608512461645</v>
       </c>
       <c r="D183" t="n">
-        <v>142.397017874141</v>
+        <v>142.1389284814664</v>
       </c>
       <c r="E183" t="n">
-        <v>146.3971557617188</v>
+        <v>142.4962615966797</v>
       </c>
       <c r="F183" t="n">
-        <v>10048900</v>
+        <v>12355800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>145.612997111615</v>
+        <v>140.4713875281435</v>
       </c>
       <c r="C184" t="n">
-        <v>145.612997111615</v>
+        <v>140.7691676558347</v>
       </c>
       <c r="D184" t="n">
-        <v>143.9355170452321</v>
+        <v>137.8310936193964</v>
       </c>
       <c r="E184" t="n">
-        <v>144.828857421875</v>
+        <v>139.2405700683594</v>
       </c>
       <c r="F184" t="n">
-        <v>10196700</v>
+        <v>11093800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>144.4417452563355</v>
+        <v>139.0817554467106</v>
       </c>
       <c r="C185" t="n">
-        <v>144.5608512461645</v>
+        <v>140.0743457999317</v>
       </c>
       <c r="D185" t="n">
-        <v>142.1389284814664</v>
+        <v>137.999835596674</v>
       </c>
       <c r="E185" t="n">
-        <v>142.4962615966797</v>
+        <v>139.7765808105469</v>
       </c>
       <c r="F185" t="n">
-        <v>12355800</v>
+        <v>9599500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>140.4713875281435</v>
+        <v>139.8857522909846</v>
       </c>
       <c r="C186" t="n">
-        <v>140.7691676558347</v>
+        <v>141.3944938803485</v>
       </c>
       <c r="D186" t="n">
-        <v>137.8310936193964</v>
+        <v>138.9626505253011</v>
       </c>
       <c r="E186" t="n">
-        <v>139.2405700683594</v>
+        <v>139.1512451171875</v>
       </c>
       <c r="F186" t="n">
-        <v>11093800</v>
+        <v>9351000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>139.0817554467106</v>
+        <v>141.6426337542266</v>
       </c>
       <c r="C187" t="n">
-        <v>140.0743457999317</v>
+        <v>142.079375912544</v>
       </c>
       <c r="D187" t="n">
-        <v>137.999835596674</v>
+        <v>138.8534574153755</v>
       </c>
       <c r="E187" t="n">
-        <v>139.7765808105469</v>
+        <v>139.7368621826172</v>
       </c>
       <c r="F187" t="n">
-        <v>9599500</v>
+        <v>8194000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>139.8857522909846</v>
+        <v>141.1661955784844</v>
       </c>
       <c r="C188" t="n">
-        <v>141.3944938803485</v>
+        <v>147.131657909349</v>
       </c>
       <c r="D188" t="n">
-        <v>138.9626505253011</v>
+        <v>140.7493094643581</v>
       </c>
       <c r="E188" t="n">
-        <v>139.1512451171875</v>
+        <v>145.4541778564453</v>
       </c>
       <c r="F188" t="n">
-        <v>9351000</v>
+        <v>10963200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>141.6426337542266</v>
+        <v>144.709731142363</v>
       </c>
       <c r="C189" t="n">
-        <v>142.079375912544</v>
+        <v>145.4641094530425</v>
       </c>
       <c r="D189" t="n">
-        <v>138.8534574153755</v>
+        <v>143.9454475270099</v>
       </c>
       <c r="E189" t="n">
-        <v>139.7368621826172</v>
+        <v>144.0248565673828</v>
       </c>
       <c r="F189" t="n">
-        <v>8194000</v>
+        <v>7200700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>141.1661955784844</v>
+        <v>143.598043761205</v>
       </c>
       <c r="C190" t="n">
-        <v>147.131657909349</v>
+        <v>148.3724009095588</v>
       </c>
       <c r="D190" t="n">
-        <v>140.7493094643581</v>
+        <v>143.4590817183783</v>
       </c>
       <c r="E190" t="n">
-        <v>145.4541778564453</v>
+        <v>147.5684051513672</v>
       </c>
       <c r="F190" t="n">
-        <v>10963200</v>
+        <v>8259300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>144.709731142363</v>
+        <v>148.7992154215363</v>
       </c>
       <c r="C191" t="n">
-        <v>145.4641094530425</v>
+        <v>149.3153514723138</v>
       </c>
       <c r="D191" t="n">
-        <v>143.9454475270099</v>
+        <v>147.2805534750766</v>
       </c>
       <c r="E191" t="n">
-        <v>144.0248565673828</v>
+        <v>147.9455871582031</v>
       </c>
       <c r="F191" t="n">
-        <v>7200700</v>
+        <v>7345900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>143.598043761205</v>
+        <v>147.598177848302</v>
       </c>
       <c r="C192" t="n">
-        <v>148.3724009095588</v>
+        <v>148.5113591270304</v>
       </c>
       <c r="D192" t="n">
-        <v>143.4590817183783</v>
+        <v>146.6750761188154</v>
       </c>
       <c r="E192" t="n">
-        <v>147.5684051513672</v>
+        <v>147.2408447265625</v>
       </c>
       <c r="F192" t="n">
-        <v>8259300</v>
+        <v>6684700</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>148.7992154215363</v>
+        <v>148.2731427996088</v>
       </c>
       <c r="C193" t="n">
-        <v>149.3153514723138</v>
+        <v>149.087058964007</v>
       </c>
       <c r="D193" t="n">
-        <v>147.2805534750766</v>
+        <v>147.2011434657927</v>
       </c>
       <c r="E193" t="n">
-        <v>147.9455871582031</v>
+        <v>148.5014343261719</v>
       </c>
       <c r="F193" t="n">
-        <v>7345900</v>
+        <v>6832000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>147.598177848302</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="C194" t="n">
-        <v>148.5113591270304</v>
+        <v>150.377425765528</v>
       </c>
       <c r="D194" t="n">
-        <v>146.6750761188154</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="E194" t="n">
-        <v>147.2408447265625</v>
+        <v>149.3451385498047</v>
       </c>
       <c r="F194" t="n">
-        <v>6684700</v>
+        <v>9158900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>148.2731427996088</v>
+        <v>150.3873579771785</v>
       </c>
       <c r="C195" t="n">
-        <v>149.087058964007</v>
+        <v>151.8861790939718</v>
       </c>
       <c r="D195" t="n">
-        <v>147.2011434657927</v>
+        <v>149.4344797259463</v>
       </c>
       <c r="E195" t="n">
-        <v>148.5014343261719</v>
+        <v>151.360107421875</v>
       </c>
       <c r="F195" t="n">
-        <v>6832000</v>
+        <v>8518900</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>147.6577229757893</v>
+        <v>151.2509186348782</v>
       </c>
       <c r="C196" t="n">
-        <v>150.377425765528</v>
+        <v>151.8067667938</v>
       </c>
       <c r="D196" t="n">
-        <v>147.6577229757893</v>
+        <v>148.6602572796902</v>
       </c>
       <c r="E196" t="n">
-        <v>149.3451385498047</v>
+        <v>149.4443969726562</v>
       </c>
       <c r="F196" t="n">
-        <v>9158900</v>
+        <v>7055800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>150.3873579771785</v>
+        <v>149.7520913576046</v>
       </c>
       <c r="C197" t="n">
-        <v>151.8861790939718</v>
+        <v>151.1615677439354</v>
       </c>
       <c r="D197" t="n">
-        <v>149.4344797259463</v>
+        <v>149.067201638067</v>
       </c>
       <c r="E197" t="n">
-        <v>151.360107421875</v>
+        <v>149.2657318115234</v>
       </c>
       <c r="F197" t="n">
-        <v>8518900</v>
+        <v>17076100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>151.2509186348782</v>
+        <v>148.9977261100366</v>
       </c>
       <c r="C198" t="n">
-        <v>151.8067667938</v>
+        <v>149.7719453093657</v>
       </c>
       <c r="D198" t="n">
-        <v>148.6602572796902</v>
+        <v>146.4765534870951</v>
       </c>
       <c r="E198" t="n">
-        <v>149.4443969726562</v>
+        <v>146.5857238769531</v>
       </c>
       <c r="F198" t="n">
-        <v>7055800</v>
+        <v>10533000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>149.7520913576046</v>
+        <v>148.5510669184904</v>
       </c>
       <c r="C199" t="n">
-        <v>151.1615677439354</v>
+        <v>150.2483878382925</v>
       </c>
       <c r="D199" t="n">
-        <v>149.067201638067</v>
+        <v>148.2632072518497</v>
       </c>
       <c r="E199" t="n">
-        <v>149.2657318115234</v>
+        <v>149.7421722412109</v>
       </c>
       <c r="F199" t="n">
-        <v>17076100</v>
+        <v>7259600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>148.9977261100366</v>
+        <v>150.8638042327417</v>
       </c>
       <c r="C200" t="n">
-        <v>149.7719453093657</v>
+        <v>152.213727638368</v>
       </c>
       <c r="D200" t="n">
-        <v>146.4765534870951</v>
+        <v>149.8017253482469</v>
       </c>
       <c r="E200" t="n">
-        <v>146.5857238769531</v>
+        <v>150.9134216308594</v>
       </c>
       <c r="F200" t="n">
-        <v>10533000</v>
+        <v>8618500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>148.5510669184904</v>
+        <v>150.446917666229</v>
       </c>
       <c r="C201" t="n">
-        <v>150.2483878382925</v>
+        <v>151.1615687416308</v>
       </c>
       <c r="D201" t="n">
-        <v>148.2632072518497</v>
+        <v>146.7247040752409</v>
       </c>
       <c r="E201" t="n">
-        <v>149.7421722412109</v>
+        <v>147.399658203125</v>
       </c>
       <c r="F201" t="n">
-        <v>7259600</v>
+        <v>11197200</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>150.8638042327417</v>
+        <v>149.226028638664</v>
       </c>
       <c r="C202" t="n">
-        <v>152.213727638368</v>
+        <v>149.7620359058753</v>
       </c>
       <c r="D202" t="n">
-        <v>149.8017253482469</v>
+        <v>147.3202569962244</v>
       </c>
       <c r="E202" t="n">
-        <v>150.9134216308594</v>
+        <v>147.9158172607422</v>
       </c>
       <c r="F202" t="n">
-        <v>8618500</v>
+        <v>16724600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>150.446917666229</v>
+        <v>147.627945424002</v>
       </c>
       <c r="C203" t="n">
-        <v>151.1615687416308</v>
+        <v>147.945581577785</v>
       </c>
       <c r="D203" t="n">
-        <v>146.7247040752409</v>
+        <v>145.9504654579339</v>
       </c>
       <c r="E203" t="n">
-        <v>147.399658203125</v>
+        <v>147.3500213623047</v>
       </c>
       <c r="F203" t="n">
-        <v>11197200</v>
+        <v>10387700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>149.226028638664</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="C204" t="n">
-        <v>149.7620359058753</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="D204" t="n">
-        <v>147.3202569962244</v>
+        <v>143.1017371059213</v>
       </c>
       <c r="E204" t="n">
-        <v>147.9158172607422</v>
+        <v>145.5534362792969</v>
       </c>
       <c r="F204" t="n">
-        <v>16724600</v>
+        <v>9353800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>147.627945424002</v>
+        <v>145.4442602082673</v>
       </c>
       <c r="C205" t="n">
-        <v>147.945581577785</v>
+        <v>146.4070740424418</v>
       </c>
       <c r="D205" t="n">
-        <v>145.9504654579339</v>
+        <v>144.4715259232294</v>
       </c>
       <c r="E205" t="n">
-        <v>147.3500213623047</v>
+        <v>146.3375854492188</v>
       </c>
       <c r="F205" t="n">
-        <v>10387700</v>
+        <v>9571700</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>146.4368410119005</v>
+        <v>147.4790688253476</v>
       </c>
       <c r="C206" t="n">
-        <v>146.4368410119005</v>
+        <v>150.5461692222369</v>
       </c>
       <c r="D206" t="n">
-        <v>143.1017371059213</v>
+        <v>146.6452966069997</v>
       </c>
       <c r="E206" t="n">
-        <v>145.5534362792969</v>
+        <v>150.2881011962891</v>
       </c>
       <c r="F206" t="n">
-        <v>9353800</v>
+        <v>9256000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>145.4442602082673</v>
+        <v>149.5635029567411</v>
       </c>
       <c r="C207" t="n">
-        <v>146.4070740424418</v>
+        <v>150.0995102140475</v>
       </c>
       <c r="D207" t="n">
-        <v>144.4715259232294</v>
+        <v>145.8710808804345</v>
       </c>
       <c r="E207" t="n">
-        <v>146.3375854492188</v>
+        <v>148.2036590576172</v>
       </c>
       <c r="F207" t="n">
-        <v>9571700</v>
+        <v>8323100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>147.4790688253476</v>
+        <v>151.5288345729856</v>
       </c>
       <c r="C208" t="n">
-        <v>150.5461692222369</v>
+        <v>152.3526863163115</v>
       </c>
       <c r="D208" t="n">
-        <v>146.6452966069997</v>
+        <v>149.4940214860459</v>
       </c>
       <c r="E208" t="n">
-        <v>150.2881011962891</v>
+        <v>151.6181640625</v>
       </c>
       <c r="F208" t="n">
-        <v>9256000</v>
+        <v>8061400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>149.5635029567411</v>
+        <v>149.8414437624326</v>
       </c>
       <c r="C209" t="n">
-        <v>150.0995102140475</v>
+        <v>149.950629305204</v>
       </c>
       <c r="D209" t="n">
-        <v>145.8710808804345</v>
+        <v>147.2507823800627</v>
       </c>
       <c r="E209" t="n">
-        <v>148.2036590576172</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F209" t="n">
-        <v>8323100</v>
+        <v>14272300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>151.5288345729856</v>
+        <v>145.6824775579256</v>
       </c>
       <c r="C210" t="n">
-        <v>152.3526863163115</v>
+        <v>146.5658822886928</v>
       </c>
       <c r="D210" t="n">
-        <v>149.4940214860459</v>
+        <v>144.5211487643815</v>
       </c>
       <c r="E210" t="n">
-        <v>151.6181640625</v>
+        <v>145.7618865966797</v>
       </c>
       <c r="F210" t="n">
-        <v>8061400</v>
+        <v>7748000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>149.8414437624326</v>
+        <v>146.0100381106733</v>
       </c>
       <c r="C211" t="n">
-        <v>149.950629305204</v>
+        <v>147.4889879534934</v>
       </c>
       <c r="D211" t="n">
-        <v>147.2507823800627</v>
+        <v>145.6229285023594</v>
       </c>
       <c r="E211" t="n">
-        <v>147.3003997802734</v>
+        <v>145.9504699707031</v>
       </c>
       <c r="F211" t="n">
-        <v>14272300</v>
+        <v>12473000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>145.6824775579256</v>
+        <v>146.9827701076717</v>
       </c>
       <c r="C212" t="n">
-        <v>146.5658822886928</v>
+        <v>148.9381741659779</v>
       </c>
       <c r="D212" t="n">
-        <v>144.5211487643815</v>
+        <v>146.0199563268518</v>
       </c>
       <c r="E212" t="n">
-        <v>145.7618865966797</v>
+        <v>147.2706146240234</v>
       </c>
       <c r="F212" t="n">
-        <v>7748000</v>
+        <v>7816100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>146.0100381106733</v>
+        <v>147.2706141757336</v>
       </c>
       <c r="C213" t="n">
-        <v>147.4889879534934</v>
+        <v>147.6478033266625</v>
       </c>
       <c r="D213" t="n">
-        <v>145.6229285023594</v>
+        <v>144.5112144243791</v>
       </c>
       <c r="E213" t="n">
-        <v>145.9504699707031</v>
+        <v>144.9975891113281</v>
       </c>
       <c r="F213" t="n">
-        <v>12473000</v>
+        <v>7668100</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>146.9827701076717</v>
+        <v>144.2035234458952</v>
       </c>
       <c r="C214" t="n">
-        <v>148.9381741659779</v>
+        <v>147.4889950493996</v>
       </c>
       <c r="D214" t="n">
-        <v>146.0199563268518</v>
+        <v>143.5881222814616</v>
       </c>
       <c r="E214" t="n">
-        <v>147.2706146240234</v>
+        <v>146.9530029296875</v>
       </c>
       <c r="F214" t="n">
-        <v>7816100</v>
+        <v>6180000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>147.2706141757336</v>
+        <v>148.3823251540053</v>
       </c>
       <c r="C215" t="n">
-        <v>147.6478033266625</v>
+        <v>150.3972821936961</v>
       </c>
       <c r="D215" t="n">
-        <v>144.5112144243791</v>
+        <v>147.0820191757993</v>
       </c>
       <c r="E215" t="n">
-        <v>144.9975891113281</v>
+        <v>150.3774261474609</v>
       </c>
       <c r="F215" t="n">
-        <v>7668100</v>
+        <v>6485400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>144.2035234458952</v>
+        <v>151.7273476549808</v>
       </c>
       <c r="C216" t="n">
-        <v>147.4889950493996</v>
+        <v>153.1765360977979</v>
       </c>
       <c r="D216" t="n">
-        <v>143.5881222814616</v>
+        <v>148.2036492050291</v>
       </c>
       <c r="E216" t="n">
-        <v>146.9530029296875</v>
+        <v>148.8686828613281</v>
       </c>
       <c r="F216" t="n">
-        <v>6180000</v>
+        <v>8917400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>148.3823251540053</v>
+        <v>148.4518004486472</v>
       </c>
       <c r="C217" t="n">
-        <v>150.3972821936961</v>
+        <v>148.9878076836025</v>
       </c>
       <c r="D217" t="n">
-        <v>147.0820191757993</v>
+        <v>147.3301685811182</v>
       </c>
       <c r="E217" t="n">
-        <v>150.3774261474609</v>
+        <v>148.0249938964844</v>
       </c>
       <c r="F217" t="n">
-        <v>6485400</v>
+        <v>5788300</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>151.7273476549808</v>
+        <v>146.7643973953222</v>
       </c>
       <c r="C218" t="n">
-        <v>153.1765360977979</v>
+        <v>147.3103250709858</v>
       </c>
       <c r="D218" t="n">
-        <v>148.2036492050291</v>
+        <v>145.7916631750561</v>
       </c>
       <c r="E218" t="n">
-        <v>148.8686828613281</v>
+        <v>147.0026245117188</v>
       </c>
       <c r="F218" t="n">
-        <v>8917400</v>
+        <v>7027600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>148.4518004486472</v>
+        <v>148.3922474549245</v>
       </c>
       <c r="C219" t="n">
-        <v>148.9878076836025</v>
+        <v>149.3451407916641</v>
       </c>
       <c r="D219" t="n">
-        <v>147.3301685811182</v>
+        <v>147.7172933317669</v>
       </c>
       <c r="E219" t="n">
         <v>148.0249938964844</v>
       </c>
       <c r="F219" t="n">
-        <v>5788300</v>
+        <v>5371200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>146.7643973953222</v>
+        <v>145.057144942689</v>
       </c>
       <c r="C220" t="n">
-        <v>147.3103250709858</v>
+        <v>146.5162538863596</v>
       </c>
       <c r="D220" t="n">
-        <v>145.7916631750561</v>
+        <v>144.5112172519064</v>
       </c>
       <c r="E220" t="n">
-        <v>147.0026245117188</v>
+        <v>145.8809967041016</v>
       </c>
       <c r="F220" t="n">
-        <v>7027600</v>
+        <v>6499200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,25 +6163,25 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>148.3922474549245</v>
+        <v>146.4499969482422</v>
       </c>
       <c r="C221" t="n">
-        <v>149.3451407916641</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="D221" t="n">
-        <v>147.7172933317669</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E221" t="n">
-        <v>148.0249938964844</v>
+        <v>147.4100036621094</v>
       </c>
       <c r="F221" t="n">
-        <v>5371200</v>
+        <v>6620700</v>
       </c>
       <c r="G221" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>145.057144942689</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C222" t="n">
-        <v>146.5162538863596</v>
+        <v>150.25</v>
       </c>
       <c r="D222" t="n">
-        <v>144.5112172519064</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="E222" t="n">
-        <v>145.8809967041016</v>
+        <v>148.6300048828125</v>
       </c>
       <c r="F222" t="n">
-        <v>6499200</v>
+        <v>7301800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,25 +6215,25 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>146.4499969482422</v>
+        <v>151.5</v>
       </c>
       <c r="C223" t="n">
-        <v>147.9900054931641</v>
+        <v>153.6799926757812</v>
       </c>
       <c r="D223" t="n">
-        <v>145.3999938964844</v>
+        <v>148.5200042724609</v>
       </c>
       <c r="E223" t="n">
-        <v>147.4100036621094</v>
+        <v>148.8800048828125</v>
       </c>
       <c r="F223" t="n">
-        <v>6620700</v>
+        <v>12848800</v>
       </c>
       <c r="G223" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>147.8500061035156</v>
+        <v>141.3800048828125</v>
       </c>
       <c r="C224" t="n">
-        <v>150.25</v>
+        <v>146.3800048828125</v>
       </c>
       <c r="D224" t="n">
-        <v>147.8500061035156</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="E224" t="n">
-        <v>148.6300048828125</v>
+        <v>146.1000061035156</v>
       </c>
       <c r="F224" t="n">
-        <v>7301800</v>
+        <v>14616800</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>151.5</v>
+        <v>143.7599945068359</v>
       </c>
       <c r="C225" t="n">
-        <v>153.6799926757812</v>
+        <v>144.4499969482422</v>
       </c>
       <c r="D225" t="n">
-        <v>148.5200042724609</v>
+        <v>142.25</v>
       </c>
       <c r="E225" t="n">
-        <v>148.8800048828125</v>
+        <v>143.9600067138672</v>
       </c>
       <c r="F225" t="n">
-        <v>12848800</v>
+        <v>9571100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>141.3800048828125</v>
+        <v>143.5099945068359</v>
       </c>
       <c r="C226" t="n">
-        <v>146.3800048828125</v>
+        <v>144.6999969482422</v>
       </c>
       <c r="D226" t="n">
-        <v>140.1999969482422</v>
+        <v>141.4600067138672</v>
       </c>
       <c r="E226" t="n">
-        <v>146.1000061035156</v>
+        <v>144.4900054931641</v>
       </c>
       <c r="F226" t="n">
-        <v>14616800</v>
+        <v>9152600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>143.7599945068359</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C227" t="n">
-        <v>144.4499969482422</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D227" t="n">
-        <v>142.25</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="E227" t="n">
-        <v>143.9600067138672</v>
+        <v>144.9700012207031</v>
       </c>
       <c r="F227" t="n">
-        <v>9571100</v>
+        <v>8843600</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>143.5099945068359</v>
+        <v>144.0399932861328</v>
       </c>
       <c r="C228" t="n">
-        <v>144.6999969482422</v>
+        <v>148.25</v>
       </c>
       <c r="D228" t="n">
-        <v>141.4600067138672</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E228" t="n">
-        <v>144.4900054931641</v>
+        <v>148.0099945068359</v>
       </c>
       <c r="F228" t="n">
-        <v>9152600</v>
+        <v>7362300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>145.8500061035156</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C229" t="n">
-        <v>147.1499938964844</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="D229" t="n">
-        <v>144.2599945068359</v>
+        <v>144.6600036621094</v>
       </c>
       <c r="E229" t="n">
-        <v>144.9700012207031</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="F229" t="n">
-        <v>8843600</v>
+        <v>9753300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>144.0399932861328</v>
+        <v>147.8200073242188</v>
       </c>
       <c r="C230" t="n">
-        <v>148.25</v>
+        <v>148.5</v>
       </c>
       <c r="D230" t="n">
-        <v>143.7899932861328</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="E230" t="n">
-        <v>148.0099945068359</v>
+        <v>146.9700012207031</v>
       </c>
       <c r="F230" t="n">
-        <v>7362300</v>
+        <v>8766700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>147.8500061035156</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C231" t="n">
-        <v>147.8500061035156</v>
+        <v>146</v>
       </c>
       <c r="D231" t="n">
-        <v>144.6600036621094</v>
+        <v>143.8800048828125</v>
       </c>
       <c r="E231" t="n">
-        <v>146.8000030517578</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="F231" t="n">
-        <v>9753300</v>
+        <v>7565500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>147.8200073242188</v>
+        <v>144.7299957275391</v>
       </c>
       <c r="C232" t="n">
-        <v>148.5</v>
+        <v>146.4600067138672</v>
       </c>
       <c r="D232" t="n">
-        <v>145.4499969482422</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="E232" t="n">
-        <v>146.9700012207031</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F232" t="n">
-        <v>8766700</v>
+        <v>7386500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>144.8999938964844</v>
+        <v>145.4100036621094</v>
       </c>
       <c r="C233" t="n">
-        <v>146</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="D233" t="n">
-        <v>143.8800048828125</v>
+        <v>143.9299926757812</v>
       </c>
       <c r="E233" t="n">
-        <v>145.7899932861328</v>
+        <v>145.2100067138672</v>
       </c>
       <c r="F233" t="n">
-        <v>7565500</v>
+        <v>7936700</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>144.7299957275391</v>
+        <v>144.0500030517578</v>
       </c>
       <c r="C234" t="n">
-        <v>146.4600067138672</v>
+        <v>144.9400024414062</v>
       </c>
       <c r="D234" t="n">
-        <v>144.1499938964844</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E234" t="n">
-        <v>146.4400024414062</v>
+        <v>144.0800018310547</v>
       </c>
       <c r="F234" t="n">
-        <v>7386500</v>
+        <v>7195000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>145.4100036621094</v>
+        <v>144.5899963378906</v>
       </c>
       <c r="C235" t="n">
-        <v>145.7100067138672</v>
+        <v>145.8000030517578</v>
       </c>
       <c r="D235" t="n">
-        <v>143.9299926757812</v>
+        <v>144</v>
       </c>
       <c r="E235" t="n">
-        <v>145.2100067138672</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="F235" t="n">
-        <v>7936700</v>
+        <v>7491300</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>144.0500030517578</v>
+        <v>144.3300018310547</v>
       </c>
       <c r="C236" t="n">
-        <v>144.9400024414062</v>
+        <v>144.9100036621094</v>
       </c>
       <c r="D236" t="n">
-        <v>143.7899932861328</v>
+        <v>143.4199981689453</v>
       </c>
       <c r="E236" t="n">
-        <v>144.0800018310547</v>
+        <v>144.5500030517578</v>
       </c>
       <c r="F236" t="n">
-        <v>7195000</v>
+        <v>7249600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>144.5899963378906</v>
+        <v>143.6399993896484</v>
       </c>
       <c r="C237" t="n">
-        <v>145.8000030517578</v>
+        <v>143.9700012207031</v>
       </c>
       <c r="D237" t="n">
-        <v>144</v>
+        <v>142.4799957275391</v>
       </c>
       <c r="E237" t="n">
-        <v>144.2599945068359</v>
+        <v>143.1199951171875</v>
       </c>
       <c r="F237" t="n">
-        <v>7491300</v>
+        <v>9867500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>144.3300018310547</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="C238" t="n">
-        <v>144.9100036621094</v>
+        <v>144.4199981689453</v>
       </c>
       <c r="D238" t="n">
-        <v>143.4199981689453</v>
+        <v>142.6799926757812</v>
       </c>
       <c r="E238" t="n">
-        <v>144.5500030517578</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F238" t="n">
-        <v>7249600</v>
+        <v>12746100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>143.6399993896484</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="C239" t="n">
-        <v>143.9700012207031</v>
+        <v>146.2299957275391</v>
       </c>
       <c r="D239" t="n">
-        <v>142.4799957275391</v>
+        <v>143.6199951171875</v>
       </c>
       <c r="E239" t="n">
-        <v>143.1199951171875</v>
+        <v>144.3800048828125</v>
       </c>
       <c r="F239" t="n">
-        <v>9867500</v>
+        <v>13948500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>143.2799987792969</v>
+        <v>144.4700012207031</v>
       </c>
       <c r="C240" t="n">
-        <v>144.4199981689453</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="D240" t="n">
-        <v>142.6799926757812</v>
+        <v>142.5599975585938</v>
       </c>
       <c r="E240" t="n">
-        <v>143.4499969482422</v>
+        <v>142.9700012207031</v>
       </c>
       <c r="F240" t="n">
-        <v>12746100</v>
+        <v>15794100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>144.3000030517578</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C241" t="n">
-        <v>146.2299957275391</v>
+        <v>145.2700042724609</v>
       </c>
       <c r="D241" t="n">
-        <v>143.6199951171875</v>
+        <v>142.1399993896484</v>
       </c>
       <c r="E241" t="n">
-        <v>144.3800048828125</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="F241" t="n">
-        <v>13948500</v>
+        <v>9785200</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>144.4700012207031</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="C242" t="n">
-        <v>144.9199981689453</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="D242" t="n">
-        <v>142.5599975585938</v>
+        <v>145</v>
       </c>
       <c r="E242" t="n">
-        <v>142.9700012207031</v>
+        <v>146.6000061035156</v>
       </c>
       <c r="F242" t="n">
-        <v>15794100</v>
+        <v>7061800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>143.0200042724609</v>
+        <v>145.7299957275391</v>
       </c>
       <c r="C243" t="n">
-        <v>145.2700042724609</v>
+        <v>146.1199951171875</v>
       </c>
       <c r="D243" t="n">
-        <v>142.1399993896484</v>
+        <v>144.9499969482422</v>
       </c>
       <c r="E243" t="n">
-        <v>144.6799926757812</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F243" t="n">
-        <v>9785200</v>
+        <v>9125700</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>145.2400054931641</v>
+        <v>145.2799987792969</v>
       </c>
       <c r="C244" t="n">
-        <v>146.8000030517578</v>
+        <v>145.9299926757812</v>
       </c>
       <c r="D244" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="E244" t="n">
         <v>145</v>
       </c>
-      <c r="E244" t="n">
-        <v>146.6000061035156</v>
-      </c>
       <c r="F244" t="n">
-        <v>7061800</v>
+        <v>8249100</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>145.7299957275391</v>
+        <v>143.6999969482422</v>
       </c>
       <c r="C245" t="n">
-        <v>146.1199951171875</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="D245" t="n">
-        <v>144.9499969482422</v>
+        <v>142.7100067138672</v>
       </c>
       <c r="E245" t="n">
-        <v>145.3999938964844</v>
+        <v>143.1399993896484</v>
       </c>
       <c r="F245" t="n">
-        <v>9125700</v>
+        <v>7817200</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>145.2799987792969</v>
+        <v>143.25</v>
       </c>
       <c r="C246" t="n">
-        <v>145.9299926757812</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D246" t="n">
-        <v>144.5</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="E246" t="n">
-        <v>145</v>
+        <v>143.7799987792969</v>
       </c>
       <c r="F246" t="n">
-        <v>8249100</v>
+        <v>5868900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>143.6999969482422</v>
+        <v>143.4400024414062</v>
       </c>
       <c r="C247" t="n">
-        <v>144.1499938964844</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D247" t="n">
-        <v>142.7100067138672</v>
+        <v>142.5</v>
       </c>
       <c r="E247" t="n">
-        <v>143.1399993896484</v>
+        <v>145.1199951171875</v>
       </c>
       <c r="F247" t="n">
-        <v>7817200</v>
+        <v>12097900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>143.25</v>
+        <v>145.7599945068359</v>
       </c>
       <c r="C248" t="n">
-        <v>144.3999938964844</v>
+        <v>148.3600006103516</v>
       </c>
       <c r="D248" t="n">
-        <v>143.0099945068359</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E248" t="n">
-        <v>143.7799987792969</v>
+        <v>146.2100067138672</v>
       </c>
       <c r="F248" t="n">
-        <v>5868900</v>
+        <v>8503800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>143.4400024414062</v>
+        <v>146.4199981689453</v>
       </c>
       <c r="C249" t="n">
-        <v>145.8999938964844</v>
+        <v>148.3200073242188</v>
       </c>
       <c r="D249" t="n">
-        <v>142.5</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="E249" t="n">
-        <v>145.1199951171875</v>
+        <v>147.6399993896484</v>
       </c>
       <c r="F249" t="n">
-        <v>12097900</v>
+        <v>7431100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>145.7599945068359</v>
+        <v>147.6799926757812</v>
       </c>
       <c r="C250" t="n">
-        <v>148.3600006103516</v>
+        <v>148.2200012207031</v>
       </c>
       <c r="D250" t="n">
-        <v>145.0899963378906</v>
+        <v>146.5</v>
       </c>
       <c r="E250" t="n">
-        <v>146.2100067138672</v>
+        <v>146.9199981689453</v>
       </c>
       <c r="F250" t="n">
-        <v>8503800</v>
+        <v>6105800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>146.4199981689453</v>
+        <v>146.4700012207031</v>
       </c>
       <c r="C251" t="n">
-        <v>148.3200073242188</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D251" t="n">
-        <v>145.7899932861328</v>
+        <v>145.8200073242188</v>
       </c>
       <c r="E251" t="n">
-        <v>147.6399993896484</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F251" t="n">
-        <v>7431100</v>
+        <v>5588200</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>147.6799926757812</v>
-      </c>
-      <c r="C252" t="n">
-        <v>148.2200012207031</v>
-      </c>
-      <c r="D252" t="n">
-        <v>146.5</v>
-      </c>
-      <c r="E252" t="n">
-        <v>146.9199981689453</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>6105800</v>
+        <v>8315492</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>146.4700012207031</v>
-      </c>
-      <c r="C253" t="n">
-        <v>147.1499938964844</v>
-      </c>
-      <c r="D253" t="n">
-        <v>145.8200073242188</v>
-      </c>
-      <c r="E253" t="n">
-        <v>146.4400024414062</v>
-      </c>
-      <c r="F253" t="n">
-        <v>5588200</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10832,34 +10798,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>145.58</v>
+      </c>
+      <c r="D2" t="n">
         <v>146.44</v>
       </c>
-      <c r="D2" t="n">
-        <v>146.92</v>
-      </c>
       <c r="E2" t="n">
-        <v>146.47</v>
+        <v>145.595</v>
       </c>
       <c r="F2" t="n">
-        <v>147.15</v>
+        <v>146.15</v>
       </c>
       <c r="G2" t="n">
-        <v>145.82</v>
+        <v>144.305</v>
       </c>
       <c r="H2" t="n">
-        <v>5552427</v>
+        <v>8315492</v>
       </c>
       <c r="I2" t="n">
-        <v>8941566</v>
+        <v>8969645</v>
       </c>
       <c r="J2" t="n">
-        <v>340132134912</v>
+        <v>338134663168</v>
       </c>
       <c r="K2" t="n">
-        <v>22.120846</v>
+        <v>21.990936</v>
       </c>
       <c r="L2" t="n">
-        <v>19.789724</v>
+        <v>19.673506</v>
       </c>
       <c r="M2" t="n">
         <v>6.62</v>
@@ -10898,7 +10864,7 @@
         <v>22.947</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.381662</v>
+        <v>6.3441844</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.155</v>
@@ -10910,7 +10876,7 @@
         <v>87031996416</v>
       </c>
       <c r="AC2" t="n">
-        <v>366458961920</v>
+        <v>364459950080</v>
       </c>
       <c r="AD2" t="n">
         <v>24752001024</v>
@@ -10937,7 +10903,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:28</t>
+          <t>2026-09-09 09:15:25</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>154.0790304359711</v>
+        <v>154.0693331751388</v>
       </c>
       <c r="C2" t="n">
-        <v>155.3030310110979</v>
+        <v>154.3996169522188</v>
       </c>
       <c r="D2" t="n">
-        <v>153.6807392406498</v>
+        <v>151.4367423098323</v>
       </c>
       <c r="E2" t="n">
-        <v>154.9047546386719</v>
+        <v>152.8550415039062</v>
       </c>
       <c r="F2" t="n">
-        <v>4984900</v>
+        <v>6205500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>154.0693177951327</v>
+        <v>153.2144723004245</v>
       </c>
       <c r="C3" t="n">
-        <v>154.3996015392422</v>
+        <v>154.7979134368329</v>
       </c>
       <c r="D3" t="n">
-        <v>151.4367271926253</v>
+        <v>152.8938975095807</v>
       </c>
       <c r="E3" t="n">
-        <v>152.8550262451172</v>
+        <v>154.0984802246094</v>
       </c>
       <c r="F3" t="n">
-        <v>6205500</v>
+        <v>5819500</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>153.2144723004245</v>
+        <v>153.4184698191116</v>
       </c>
       <c r="C4" t="n">
-        <v>154.7979134368329</v>
+        <v>154.5842017579773</v>
       </c>
       <c r="D4" t="n">
-        <v>152.8938975095807</v>
+        <v>153.272760738202</v>
       </c>
       <c r="E4" t="n">
-        <v>154.0984802246094</v>
+        <v>153.3893280029297</v>
       </c>
       <c r="F4" t="n">
-        <v>5819500</v>
+        <v>5957000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>153.4184545574236</v>
+        <v>153.3699073091056</v>
       </c>
       <c r="C5" t="n">
-        <v>154.5841863803252</v>
+        <v>153.9916240815438</v>
       </c>
       <c r="D5" t="n">
-        <v>153.2727454910088</v>
+        <v>151.7378915171447</v>
       </c>
       <c r="E5" t="n">
-        <v>153.3893127441406</v>
+        <v>152.3498992919922</v>
       </c>
       <c r="F5" t="n">
-        <v>5957000</v>
+        <v>5995000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>153.3698919481564</v>
+        <v>152.6510263298436</v>
       </c>
       <c r="C6" t="n">
-        <v>153.9916086583258</v>
+        <v>153.865317940213</v>
       </c>
       <c r="D6" t="n">
-        <v>151.7378763196521</v>
+        <v>152.4081680077697</v>
       </c>
       <c r="E6" t="n">
-        <v>152.3498840332031</v>
+        <v>153.5350341796875</v>
       </c>
       <c r="F6" t="n">
-        <v>5995000</v>
+        <v>6559600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>152.6510415007772</v>
+        <v>153.9041762162224</v>
       </c>
       <c r="C7" t="n">
-        <v>153.8653332318267</v>
+        <v>157.0516255592386</v>
       </c>
       <c r="D7" t="n">
-        <v>152.4081831545673</v>
+        <v>153.9041762162224</v>
       </c>
       <c r="E7" t="n">
-        <v>153.5350494384766</v>
+        <v>155.7499084472656</v>
       </c>
       <c r="F7" t="n">
-        <v>6559600</v>
+        <v>6764200</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>153.9041611382593</v>
+        <v>153.6321891685915</v>
       </c>
       <c r="C8" t="n">
-        <v>157.0516101729205</v>
+        <v>154.4773463220477</v>
       </c>
       <c r="D8" t="n">
-        <v>153.9041611382593</v>
+        <v>152.670479571169</v>
       </c>
       <c r="E8" t="n">
-        <v>155.7498931884766</v>
+        <v>152.8259124755859</v>
       </c>
       <c r="F8" t="n">
-        <v>6764200</v>
+        <v>7651500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>153.6321891685915</v>
+        <v>153.1076006094224</v>
       </c>
       <c r="C9" t="n">
-        <v>154.4773463220477</v>
+        <v>153.1173096060279</v>
       </c>
       <c r="D9" t="n">
-        <v>152.670479571169</v>
+        <v>151.5144506152748</v>
       </c>
       <c r="E9" t="n">
-        <v>152.8259124755859</v>
+        <v>151.5824432373047</v>
       </c>
       <c r="F9" t="n">
-        <v>7651500</v>
+        <v>17224800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>153.1076006094224</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="C10" t="n">
-        <v>153.1173096060279</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="D10" t="n">
-        <v>151.5144506152748</v>
+        <v>148.677863326978</v>
       </c>
       <c r="E10" t="n">
-        <v>151.5824432373047</v>
+        <v>148.6972961425781</v>
       </c>
       <c r="F10" t="n">
-        <v>17224800</v>
+        <v>8712900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>151.6213049173507</v>
+        <v>148.8235855824238</v>
       </c>
       <c r="C11" t="n">
-        <v>151.6213049173507</v>
+        <v>148.9110110260332</v>
       </c>
       <c r="D11" t="n">
-        <v>148.677863326978</v>
+        <v>146.657293372131</v>
       </c>
       <c r="E11" t="n">
-        <v>148.6972961425781</v>
+        <v>148.1435852050781</v>
       </c>
       <c r="F11" t="n">
-        <v>8712900</v>
+        <v>8853400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>148.8235702535947</v>
+        <v>147.7064465894999</v>
       </c>
       <c r="C12" t="n">
-        <v>148.9109956881993</v>
+        <v>149.2413130899007</v>
       </c>
       <c r="D12" t="n">
-        <v>146.65727826643</v>
+        <v>147.4538644271308</v>
       </c>
       <c r="E12" t="n">
-        <v>148.1435699462891</v>
+        <v>148.0658721923828</v>
       </c>
       <c r="F12" t="n">
-        <v>8853400</v>
+        <v>6483300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>147.7064313677511</v>
+        <v>148.852723372033</v>
       </c>
       <c r="C13" t="n">
-        <v>149.2412977099777</v>
+        <v>149.4841639233416</v>
       </c>
       <c r="D13" t="n">
-        <v>147.4538492314116</v>
+        <v>147.4441480235695</v>
       </c>
       <c r="E13" t="n">
-        <v>148.0658569335938</v>
+        <v>147.8035736083984</v>
       </c>
       <c r="F13" t="n">
-        <v>6483300</v>
+        <v>7511400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>148.852723372033</v>
+        <v>147.8812940513532</v>
       </c>
       <c r="C14" t="n">
-        <v>149.4841639233416</v>
+        <v>148.3184360922971</v>
       </c>
       <c r="D14" t="n">
-        <v>147.4441480235695</v>
+        <v>147.2012936740075</v>
       </c>
       <c r="E14" t="n">
-        <v>147.8035736083984</v>
+        <v>148.1435852050781</v>
       </c>
       <c r="F14" t="n">
-        <v>7511400</v>
+        <v>5721100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>147.8812788195801</v>
+        <v>148.0658733987316</v>
       </c>
       <c r="C15" t="n">
-        <v>148.3184208154984</v>
+        <v>149.3287397521754</v>
       </c>
       <c r="D15" t="n">
-        <v>147.2012785122745</v>
+        <v>147.4538656284933</v>
       </c>
       <c r="E15" t="n">
-        <v>148.1435699462891</v>
+        <v>149.1441650390625</v>
       </c>
       <c r="F15" t="n">
-        <v>5721100</v>
+        <v>8139700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>148.0658733987316</v>
+        <v>149.0761670451376</v>
       </c>
       <c r="C16" t="n">
-        <v>149.3287397521754</v>
+        <v>149.9698839401892</v>
       </c>
       <c r="D16" t="n">
-        <v>147.4538656284933</v>
+        <v>148.4738682940947</v>
       </c>
       <c r="E16" t="n">
-        <v>149.1441650390625</v>
+        <v>149.2607269287109</v>
       </c>
       <c r="F16" t="n">
-        <v>8139700</v>
+        <v>7762600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>149.0761670451376</v>
+        <v>149.3092876242202</v>
       </c>
       <c r="C17" t="n">
-        <v>149.9698839401892</v>
+        <v>149.4938623134623</v>
       </c>
       <c r="D17" t="n">
-        <v>148.4738682940947</v>
+        <v>147.0847120028435</v>
       </c>
       <c r="E17" t="n">
-        <v>149.2607269287109</v>
+        <v>148.8041381835938</v>
       </c>
       <c r="F17" t="n">
-        <v>7762600</v>
+        <v>7566000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>149.3092876242202</v>
+        <v>148.3572946891603</v>
       </c>
       <c r="C18" t="n">
-        <v>149.4938623134623</v>
+        <v>148.4350111318697</v>
       </c>
       <c r="D18" t="n">
-        <v>147.0847120028435</v>
+        <v>147.2984359501739</v>
       </c>
       <c r="E18" t="n">
-        <v>148.8041381835938</v>
+        <v>147.7064361572266</v>
       </c>
       <c r="F18" t="n">
-        <v>7566000</v>
+        <v>6892100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>148.3572946891603</v>
+        <v>147.6578596189441</v>
       </c>
       <c r="C19" t="n">
-        <v>148.4350111318697</v>
+        <v>149.0470021043167</v>
       </c>
       <c r="D19" t="n">
-        <v>147.2984359501739</v>
+        <v>147.6578596189441</v>
       </c>
       <c r="E19" t="n">
-        <v>147.7064361572266</v>
+        <v>147.9201507568359</v>
       </c>
       <c r="F19" t="n">
-        <v>6892100</v>
+        <v>5212600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>147.6578748506764</v>
+        <v>147.1721553229241</v>
       </c>
       <c r="C20" t="n">
-        <v>149.0470174793467</v>
+        <v>147.9687378000585</v>
       </c>
       <c r="D20" t="n">
-        <v>147.6578748506764</v>
+        <v>146.1035726884504</v>
       </c>
       <c r="E20" t="n">
-        <v>147.920166015625</v>
+        <v>146.1132965087891</v>
       </c>
       <c r="F20" t="n">
-        <v>5212600</v>
+        <v>6737000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>147.1721399535571</v>
+        <v>146.4532839352596</v>
       </c>
       <c r="C21" t="n">
-        <v>147.9687223475034</v>
+        <v>148.7944418250997</v>
       </c>
       <c r="D21" t="n">
-        <v>146.1035574306768</v>
+        <v>145.7635745697061</v>
       </c>
       <c r="E21" t="n">
-        <v>146.11328125</v>
+        <v>148.1824340820312</v>
       </c>
       <c r="F21" t="n">
-        <v>6737000</v>
+        <v>6844400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>146.4532839352596</v>
+        <v>148.4252854332665</v>
       </c>
       <c r="C22" t="n">
-        <v>148.7944418250997</v>
+        <v>148.4252854332665</v>
       </c>
       <c r="D22" t="n">
-        <v>145.7635745697061</v>
+        <v>146.3270007982578</v>
       </c>
       <c r="E22" t="n">
-        <v>148.1824340820312</v>
+        <v>146.3852844238281</v>
       </c>
       <c r="F22" t="n">
-        <v>6844400</v>
+        <v>5254700</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>148.4252854332665</v>
+        <v>146.4338752834919</v>
       </c>
       <c r="C23" t="n">
-        <v>148.4252854332665</v>
+        <v>146.5601515452587</v>
       </c>
       <c r="D23" t="n">
-        <v>146.3270007982578</v>
+        <v>145.3070089879124</v>
       </c>
       <c r="E23" t="n">
-        <v>146.3852844238281</v>
+        <v>146.2784423828125</v>
       </c>
       <c r="F23" t="n">
-        <v>5254700</v>
+        <v>6134500</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>146.4338600084891</v>
+        <v>146.6281712395348</v>
       </c>
       <c r="C24" t="n">
-        <v>146.5601362570837</v>
+        <v>147.1818806129492</v>
       </c>
       <c r="D24" t="n">
-        <v>145.3069938304567</v>
+        <v>145.1807300240471</v>
       </c>
       <c r="E24" t="n">
-        <v>146.2784271240234</v>
+        <v>145.4138793945312</v>
       </c>
       <c r="F24" t="n">
-        <v>6134500</v>
+        <v>7374000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>146.6281558533259</v>
+        <v>144.7435618289234</v>
       </c>
       <c r="C25" t="n">
-        <v>147.1818651686376</v>
+        <v>145.1612710333055</v>
       </c>
       <c r="D25" t="n">
-        <v>145.1807147897232</v>
+        <v>142.7715534139986</v>
       </c>
       <c r="E25" t="n">
-        <v>145.4138641357422</v>
+        <v>143.2767028808594</v>
       </c>
       <c r="F25" t="n">
-        <v>7374000</v>
+        <v>7511100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>144.7435618289234</v>
+        <v>143.3544266058526</v>
       </c>
       <c r="C26" t="n">
-        <v>145.1612710333055</v>
+        <v>144.9864275192193</v>
       </c>
       <c r="D26" t="n">
-        <v>142.7715534139986</v>
+        <v>142.8784189280057</v>
       </c>
       <c r="E26" t="n">
-        <v>143.2767028808594</v>
+        <v>144.8990020751953</v>
       </c>
       <c r="F26" t="n">
-        <v>7511100</v>
+        <v>8585300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>143.3544266058526</v>
+        <v>144.2870013812095</v>
       </c>
       <c r="C27" t="n">
-        <v>144.9864275192193</v>
+        <v>145.1418675145521</v>
       </c>
       <c r="D27" t="n">
-        <v>142.8784189280057</v>
+        <v>143.0630006362941</v>
       </c>
       <c r="E27" t="n">
-        <v>144.8990020751953</v>
+        <v>143.2087097167969</v>
       </c>
       <c r="F27" t="n">
-        <v>8585300</v>
+        <v>10003100</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>144.2869860075292</v>
+        <v>143.7818561196696</v>
       </c>
       <c r="C28" t="n">
-        <v>145.1418520497865</v>
+        <v>146.103581416083</v>
       </c>
       <c r="D28" t="n">
-        <v>143.0629853930302</v>
+        <v>143.6944306687803</v>
       </c>
       <c r="E28" t="n">
-        <v>143.2086944580078</v>
+        <v>145.3264465332031</v>
       </c>
       <c r="F28" t="n">
-        <v>10003100</v>
+        <v>8809700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>143.7818410230574</v>
+        <v>146.2687051713582</v>
       </c>
       <c r="C29" t="n">
-        <v>146.1035660756974</v>
+        <v>147.6869893535173</v>
       </c>
       <c r="D29" t="n">
-        <v>143.6944155813474</v>
+        <v>146.1326902923267</v>
       </c>
       <c r="E29" t="n">
-        <v>145.3264312744141</v>
+        <v>147.0749816894531</v>
       </c>
       <c r="F29" t="n">
-        <v>8809700</v>
+        <v>8612900</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>146.2687203464973</v>
+        <v>147.259562913577</v>
       </c>
       <c r="C30" t="n">
-        <v>147.6870046758011</v>
+        <v>148.0367124787026</v>
       </c>
       <c r="D30" t="n">
-        <v>146.1327054533545</v>
+        <v>146.9778537929527</v>
       </c>
       <c r="E30" t="n">
-        <v>147.0749969482422</v>
+        <v>147.6190032958984</v>
       </c>
       <c r="F30" t="n">
-        <v>8612900</v>
+        <v>5601300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>147.2595781352121</v>
+        <v>147.6189948407767</v>
       </c>
       <c r="C31" t="n">
-        <v>148.0367277806686</v>
+        <v>147.9298457552854</v>
       </c>
       <c r="D31" t="n">
-        <v>146.9778689854687</v>
+        <v>146.5601213927804</v>
       </c>
       <c r="E31" t="n">
-        <v>147.6190185546875</v>
+        <v>147.2886962890625</v>
       </c>
       <c r="F31" t="n">
-        <v>5601300</v>
+        <v>6013400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>147.6190101337839</v>
+        <v>146.9778583106544</v>
       </c>
       <c r="C32" t="n">
-        <v>147.9298610804961</v>
+        <v>149.076157754121</v>
       </c>
       <c r="D32" t="n">
-        <v>146.5601365760907</v>
+        <v>146.4824178509246</v>
       </c>
       <c r="E32" t="n">
-        <v>147.2887115478516</v>
+        <v>147.8521423339844</v>
       </c>
       <c r="F32" t="n">
-        <v>6013400</v>
+        <v>6394400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>146.9778734792147</v>
+        <v>147.9978775181488</v>
       </c>
       <c r="C33" t="n">
-        <v>149.0761731392322</v>
+        <v>148.9207362405373</v>
       </c>
       <c r="D33" t="n">
-        <v>146.4824329683539</v>
+        <v>146.2784363299136</v>
       </c>
       <c r="E33" t="n">
-        <v>147.8521575927734</v>
+        <v>147.8618774414062</v>
       </c>
       <c r="F33" t="n">
-        <v>6394400</v>
+        <v>8205400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,25 +1301,25 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>147.9978622453251</v>
+        <v>152.9946080342638</v>
       </c>
       <c r="C34" t="n">
-        <v>148.9207208724779</v>
+        <v>153.9728344665201</v>
       </c>
       <c r="D34" t="n">
-        <v>146.2784212345297</v>
+        <v>148.2306500856719</v>
       </c>
       <c r="E34" t="n">
-        <v>147.8618621826172</v>
+        <v>149.1697540283203</v>
       </c>
       <c r="F34" t="n">
-        <v>8205400</v>
+        <v>11968500</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1327,25 +1327,25 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>152.9946080342638</v>
+        <v>148.3089372141624</v>
       </c>
       <c r="C35" t="n">
-        <v>153.9728344665201</v>
+        <v>148.4556652353131</v>
       </c>
       <c r="D35" t="n">
-        <v>148.2306500856719</v>
+        <v>146.8611660081129</v>
       </c>
       <c r="E35" t="n">
-        <v>149.1697540283203</v>
+        <v>148.4361114501953</v>
       </c>
       <c r="F35" t="n">
-        <v>11968500</v>
+        <v>7775300</v>
       </c>
       <c r="G35" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>148.3089219684464</v>
+        <v>147.8295858278712</v>
       </c>
       <c r="C36" t="n">
-        <v>148.4556499745139</v>
+        <v>149.8349531642864</v>
       </c>
       <c r="D36" t="n">
-        <v>146.8611509112235</v>
+        <v>147.3404725715042</v>
       </c>
       <c r="E36" t="n">
-        <v>148.4360961914062</v>
+        <v>148.0741424560547</v>
       </c>
       <c r="F36" t="n">
-        <v>7775300</v>
+        <v>5819300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>147.8295858278712</v>
+        <v>147.3795937684592</v>
       </c>
       <c r="C37" t="n">
-        <v>149.8349531642864</v>
+        <v>147.6828415657792</v>
       </c>
       <c r="D37" t="n">
-        <v>147.3404725715042</v>
+        <v>145.2372755531334</v>
       </c>
       <c r="E37" t="n">
-        <v>148.0741424560547</v>
+        <v>145.5307464599609</v>
       </c>
       <c r="F37" t="n">
-        <v>5819300</v>
+        <v>7405500</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>147.3795937684592</v>
+        <v>146.2155298538287</v>
       </c>
       <c r="C38" t="n">
-        <v>147.6828415657792</v>
+        <v>147.516573011961</v>
       </c>
       <c r="D38" t="n">
-        <v>145.2372755531334</v>
+        <v>146.0883556204121</v>
       </c>
       <c r="E38" t="n">
-        <v>145.5307464599609</v>
+        <v>146.3231353759766</v>
       </c>
       <c r="F38" t="n">
-        <v>7405500</v>
+        <v>6760700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>146.2155146062609</v>
+        <v>145.4720720722042</v>
       </c>
       <c r="C39" t="n">
-        <v>147.5165576287185</v>
+        <v>147.8100328533669</v>
       </c>
       <c r="D39" t="n">
-        <v>146.0883403861062</v>
+        <v>145.2959835371417</v>
       </c>
       <c r="E39" t="n">
-        <v>146.3231201171875</v>
+        <v>147.0959167480469</v>
       </c>
       <c r="F39" t="n">
-        <v>6760700</v>
+        <v>7930300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>145.4720720722042</v>
+        <v>146.8318015049148</v>
       </c>
       <c r="C40" t="n">
-        <v>147.8100328533669</v>
+        <v>146.9491839067269</v>
       </c>
       <c r="D40" t="n">
-        <v>145.2959835371417</v>
+        <v>144.5525320015707</v>
       </c>
       <c r="E40" t="n">
-        <v>147.0959167480469</v>
+        <v>144.7970886230469</v>
       </c>
       <c r="F40" t="n">
-        <v>7930300</v>
+        <v>8946400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>146.8318015049148</v>
+        <v>145.3644630798614</v>
       </c>
       <c r="C41" t="n">
-        <v>146.9491839067269</v>
+        <v>146.2448609544514</v>
       </c>
       <c r="D41" t="n">
-        <v>144.5525320015707</v>
+        <v>143.0656248467459</v>
       </c>
       <c r="E41" t="n">
-        <v>144.7970886230469</v>
+        <v>143.9655914306641</v>
       </c>
       <c r="F41" t="n">
-        <v>8946400</v>
+        <v>9295400</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>145.3644630798614</v>
+        <v>143.6721174868199</v>
       </c>
       <c r="C42" t="n">
-        <v>146.2448609544514</v>
+        <v>144.210145032931</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0656248467459</v>
+        <v>142.478679994192</v>
       </c>
       <c r="E42" t="n">
-        <v>143.9655914306641</v>
+        <v>142.6156311035156</v>
       </c>
       <c r="F42" t="n">
-        <v>9295400</v>
+        <v>11199900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>143.6721174868199</v>
+        <v>142.7036703315847</v>
       </c>
       <c r="C43" t="n">
-        <v>144.210145032931</v>
+        <v>143.4862395011485</v>
       </c>
       <c r="D43" t="n">
-        <v>142.478679994192</v>
+        <v>141.3145906510938</v>
       </c>
       <c r="E43" t="n">
-        <v>142.6156311035156</v>
+        <v>142.9482269287109</v>
       </c>
       <c r="F43" t="n">
-        <v>11199900</v>
+        <v>10024500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>142.703685564269</v>
+        <v>143.7503785207628</v>
       </c>
       <c r="C44" t="n">
-        <v>143.4862548173669</v>
+        <v>144.7188281113408</v>
       </c>
       <c r="D44" t="n">
-        <v>141.3146057355029</v>
+        <v>142.8210663483271</v>
       </c>
       <c r="E44" t="n">
-        <v>142.9482421875</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F44" t="n">
-        <v>10024500</v>
+        <v>8500100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>143.7503785207628</v>
+        <v>143.1927990477494</v>
       </c>
       <c r="C45" t="n">
-        <v>144.7188281113408</v>
+        <v>143.4275638534467</v>
       </c>
       <c r="D45" t="n">
-        <v>142.8210663483271</v>
+        <v>140.9526520163762</v>
       </c>
       <c r="E45" t="n">
-        <v>143.7797241210938</v>
+        <v>142.3319549560547</v>
       </c>
       <c r="F45" t="n">
-        <v>8500100</v>
+        <v>10208100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>143.192783696673</v>
+        <v>142.7819444175452</v>
       </c>
       <c r="C46" t="n">
-        <v>143.4275484772021</v>
+        <v>145.4133611257213</v>
       </c>
       <c r="D46" t="n">
-        <v>140.9526369054562</v>
+        <v>142.4982503778291</v>
       </c>
       <c r="E46" t="n">
-        <v>142.3319396972656</v>
+        <v>145.3057556152344</v>
       </c>
       <c r="F46" t="n">
-        <v>10208100</v>
+        <v>7332500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>142.7819444175452</v>
+        <v>145.2959744173796</v>
       </c>
       <c r="C47" t="n">
-        <v>145.4133611257213</v>
+        <v>145.9024700440282</v>
       </c>
       <c r="D47" t="n">
-        <v>142.4982503778291</v>
+        <v>144.298179252126</v>
       </c>
       <c r="E47" t="n">
-        <v>145.3057556152344</v>
+        <v>144.7872924804688</v>
       </c>
       <c r="F47" t="n">
-        <v>7332500</v>
+        <v>7851100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>145.2959744173796</v>
+        <v>144.9535841420777</v>
       </c>
       <c r="C48" t="n">
-        <v>145.9024700440282</v>
+        <v>145.7557369733869</v>
       </c>
       <c r="D48" t="n">
-        <v>144.298179252126</v>
+        <v>144.4253484415343</v>
       </c>
       <c r="E48" t="n">
-        <v>144.7872924804688</v>
+        <v>144.7383880615234</v>
       </c>
       <c r="F48" t="n">
-        <v>7851100</v>
+        <v>7566800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>144.9535841420777</v>
+        <v>145.8535682267802</v>
       </c>
       <c r="C49" t="n">
-        <v>145.7557369733869</v>
+        <v>146.1274704359541</v>
       </c>
       <c r="D49" t="n">
-        <v>144.4253484415343</v>
+        <v>144.3960054571006</v>
       </c>
       <c r="E49" t="n">
-        <v>144.7383880615234</v>
+        <v>144.4546966552734</v>
       </c>
       <c r="F49" t="n">
-        <v>7566800</v>
+        <v>9150800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>145.8535682267802</v>
+        <v>144.5329589094707</v>
       </c>
       <c r="C50" t="n">
-        <v>146.1274704359541</v>
+        <v>144.7579468149716</v>
       </c>
       <c r="D50" t="n">
-        <v>144.3960054571006</v>
+        <v>141.8526130458145</v>
       </c>
       <c r="E50" t="n">
-        <v>144.4546966552734</v>
+        <v>142.6449890136719</v>
       </c>
       <c r="F50" t="n">
-        <v>9150800</v>
+        <v>9902300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>144.5329589094707</v>
+        <v>143.1438871838678</v>
       </c>
       <c r="C51" t="n">
-        <v>144.7579468149716</v>
+        <v>144.1808048975551</v>
       </c>
       <c r="D51" t="n">
-        <v>141.8526130458145</v>
+        <v>142.3417342798896</v>
       </c>
       <c r="E51" t="n">
-        <v>142.6449890136719</v>
+        <v>143.7895202636719</v>
       </c>
       <c r="F51" t="n">
-        <v>9902300</v>
+        <v>10735200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>143.1438719935926</v>
+        <v>143.7601746624582</v>
       </c>
       <c r="C52" t="n">
-        <v>144.1807895972433</v>
+        <v>144.3275329036233</v>
       </c>
       <c r="D52" t="n">
-        <v>142.341719174738</v>
+        <v>142.6841195294514</v>
       </c>
       <c r="E52" t="n">
-        <v>143.7895050048828</v>
+        <v>143.7895202636719</v>
       </c>
       <c r="F52" t="n">
-        <v>10735200</v>
+        <v>6367000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>143.7601594067833</v>
+        <v>143.4471249350237</v>
       </c>
       <c r="C53" t="n">
-        <v>144.3275175877409</v>
+        <v>145.4231465283615</v>
       </c>
       <c r="D53" t="n">
-        <v>142.6841043879663</v>
+        <v>142.9482348228936</v>
       </c>
       <c r="E53" t="n">
-        <v>143.7895050048828</v>
+        <v>144.96337890625</v>
       </c>
       <c r="F53" t="n">
-        <v>6367000</v>
+        <v>9021300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>143.4471249350237</v>
+        <v>145.1492529070371</v>
       </c>
       <c r="C54" t="n">
-        <v>145.4231465283615</v>
+        <v>148.2013148118135</v>
       </c>
       <c r="D54" t="n">
-        <v>142.9482348228936</v>
+        <v>145.0709929958182</v>
       </c>
       <c r="E54" t="n">
-        <v>144.96337890625</v>
+        <v>147.6339416503906</v>
       </c>
       <c r="F54" t="n">
-        <v>9021300</v>
+        <v>12018000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>145.1492529070371</v>
+        <v>146.8318008944829</v>
       </c>
       <c r="C55" t="n">
-        <v>148.2013148118135</v>
+        <v>147.1350487156044</v>
       </c>
       <c r="D55" t="n">
-        <v>145.0709929958182</v>
+        <v>143.3493020808368</v>
       </c>
       <c r="E55" t="n">
-        <v>147.6339416503906</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F55" t="n">
-        <v>12018000</v>
+        <v>13846900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>146.8318008944829</v>
+        <v>144.112328038909</v>
       </c>
       <c r="C56" t="n">
-        <v>147.1350487156044</v>
+        <v>145.4133560843928</v>
       </c>
       <c r="D56" t="n">
-        <v>143.3493020808368</v>
+        <v>144.0144994231119</v>
       </c>
       <c r="E56" t="n">
-        <v>143.7797241210938</v>
+        <v>145.2568511962891</v>
       </c>
       <c r="F56" t="n">
-        <v>13846900</v>
+        <v>10477700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>144.1123129003486</v>
+        <v>144.6992629297112</v>
       </c>
       <c r="C57" t="n">
-        <v>145.4133408091634</v>
+        <v>145.7264037459907</v>
       </c>
       <c r="D57" t="n">
-        <v>144.0144842948282</v>
+        <v>144.3960151011972</v>
       </c>
       <c r="E57" t="n">
-        <v>145.2568359375</v>
+        <v>145.0220794677734</v>
       </c>
       <c r="F57" t="n">
-        <v>10477700</v>
+        <v>9238500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>144.6992477048879</v>
+        <v>144.5818741313487</v>
       </c>
       <c r="C58" t="n">
-        <v>145.7263884130947</v>
+        <v>145.4720637945254</v>
       </c>
       <c r="D58" t="n">
-        <v>144.3959999082808</v>
+        <v>143.9753635745919</v>
       </c>
       <c r="E58" t="n">
-        <v>145.0220642089844</v>
+        <v>144.9340362548828</v>
       </c>
       <c r="F58" t="n">
-        <v>9238500</v>
+        <v>4707200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>144.5818741313487</v>
+        <v>144.8753541574702</v>
       </c>
       <c r="C59" t="n">
-        <v>145.4720637945254</v>
+        <v>145.6481465436537</v>
       </c>
       <c r="D59" t="n">
-        <v>143.9753635745919</v>
+        <v>144.1416842645591</v>
       </c>
       <c r="E59" t="n">
-        <v>144.9340362548828</v>
+        <v>144.2297210693359</v>
       </c>
       <c r="F59" t="n">
-        <v>4707200</v>
+        <v>8240700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>144.8753541574702</v>
+        <v>142.1265314991037</v>
       </c>
       <c r="C60" t="n">
-        <v>145.6481465436537</v>
+        <v>143.0069443662482</v>
       </c>
       <c r="D60" t="n">
-        <v>144.1416842645591</v>
+        <v>139.4070628341484</v>
       </c>
       <c r="E60" t="n">
-        <v>144.2297210693359</v>
+        <v>142.6841278076172</v>
       </c>
       <c r="F60" t="n">
-        <v>8240700</v>
+        <v>16376800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>142.1265162999446</v>
+        <v>142.7428024831051</v>
       </c>
       <c r="C61" t="n">
-        <v>143.0069290729368</v>
+        <v>145.0611944043203</v>
       </c>
       <c r="D61" t="n">
-        <v>139.4070479258121</v>
+        <v>142.6841112840695</v>
       </c>
       <c r="E61" t="n">
-        <v>142.6841125488281</v>
+        <v>143.5156097412109</v>
       </c>
       <c r="F61" t="n">
-        <v>16376800</v>
+        <v>9125300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>142.7428024831051</v>
+        <v>143.47649707149</v>
       </c>
       <c r="C62" t="n">
-        <v>145.0611944043203</v>
+        <v>144.210167039084</v>
       </c>
       <c r="D62" t="n">
-        <v>142.6841112840695</v>
+        <v>141.3537470897712</v>
       </c>
       <c r="E62" t="n">
-        <v>143.5156097412109</v>
+        <v>142.1950225830078</v>
       </c>
       <c r="F62" t="n">
-        <v>9125300</v>
+        <v>10479300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>143.4764816751874</v>
+        <v>141.9993576904224</v>
       </c>
       <c r="C63" t="n">
-        <v>144.210151564052</v>
+        <v>142.4591253245491</v>
       </c>
       <c r="D63" t="n">
-        <v>141.3537319212585</v>
+        <v>140.1309415539968</v>
       </c>
       <c r="E63" t="n">
-        <v>142.1950073242188</v>
+        <v>140.3265838623047</v>
       </c>
       <c r="F63" t="n">
-        <v>10479300</v>
+        <v>12791700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>141.999373131105</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="C64" t="n">
-        <v>142.4591408152259</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="D64" t="n">
-        <v>140.1309567915122</v>
+        <v>135.1322080272313</v>
       </c>
       <c r="E64" t="n">
-        <v>140.3265991210938</v>
+        <v>135.3278503417969</v>
       </c>
       <c r="F64" t="n">
-        <v>12791700</v>
+        <v>17507500</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>139.7983526087064</v>
+        <v>136.1593454188843</v>
       </c>
       <c r="C65" t="n">
-        <v>139.7983526087064</v>
+        <v>137.8125505495836</v>
       </c>
       <c r="D65" t="n">
-        <v>135.1322080272313</v>
+        <v>135.9734800004196</v>
       </c>
       <c r="E65" t="n">
-        <v>135.3278503417969</v>
+        <v>136.5897674560547</v>
       </c>
       <c r="F65" t="n">
-        <v>17507500</v>
+        <v>10375700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>136.1593454188843</v>
+        <v>136.6093231272403</v>
       </c>
       <c r="C66" t="n">
-        <v>137.8125505495836</v>
+        <v>138.2038370797448</v>
       </c>
       <c r="D66" t="n">
-        <v>135.9734800004196</v>
+        <v>136.5017176164599</v>
       </c>
       <c r="E66" t="n">
-        <v>136.5897674560547</v>
+        <v>136.775634765625</v>
       </c>
       <c r="F66" t="n">
-        <v>10375700</v>
+        <v>13650400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>136.6093231272403</v>
+        <v>137.9299396510316</v>
       </c>
       <c r="C67" t="n">
-        <v>138.2038370797448</v>
+        <v>138.7516463474312</v>
       </c>
       <c r="D67" t="n">
-        <v>136.5017176164599</v>
+        <v>137.3038752737911</v>
       </c>
       <c r="E67" t="n">
-        <v>136.775634765625</v>
+        <v>137.6951599121094</v>
       </c>
       <c r="F67" t="n">
-        <v>13650400</v>
+        <v>11798000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>137.9299396510316</v>
+        <v>137.9299404283357</v>
       </c>
       <c r="C68" t="n">
-        <v>138.7516463474312</v>
+        <v>139.9939989991835</v>
       </c>
       <c r="D68" t="n">
-        <v>137.3038752737911</v>
+        <v>137.7734206015055</v>
       </c>
       <c r="E68" t="n">
-        <v>137.6951599121094</v>
+        <v>139.7298736572266</v>
       </c>
       <c r="F68" t="n">
-        <v>11798000</v>
+        <v>10268800</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>137.929925366103</v>
+        <v>140.1504995323008</v>
       </c>
       <c r="C69" t="n">
-        <v>139.9939837115514</v>
+        <v>142.155866623658</v>
       </c>
       <c r="D69" t="n">
-        <v>137.7734055563651</v>
+        <v>140.0820165200331</v>
       </c>
       <c r="E69" t="n">
-        <v>139.7298583984375</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F69" t="n">
-        <v>10268800</v>
+        <v>13877700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>140.1504995323008</v>
+        <v>142.918899809868</v>
       </c>
       <c r="C70" t="n">
-        <v>142.155866623658</v>
+        <v>143.3493069381574</v>
       </c>
       <c r="D70" t="n">
-        <v>140.0820165200331</v>
+        <v>141.5004594218987</v>
       </c>
       <c r="E70" t="n">
-        <v>141.9700012207031</v>
+        <v>142.0482788085938</v>
       </c>
       <c r="F70" t="n">
-        <v>13877700</v>
+        <v>10251700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>142.918884457557</v>
+        <v>143.496050619897</v>
       </c>
       <c r="C71" t="n">
-        <v>143.3492915396123</v>
+        <v>145.2177239216924</v>
       </c>
       <c r="D71" t="n">
-        <v>141.5004442219562</v>
+        <v>143.2612708815172</v>
       </c>
       <c r="E71" t="n">
-        <v>142.0482635498047</v>
+        <v>144.5916595458984</v>
       </c>
       <c r="F71" t="n">
-        <v>10251700</v>
+        <v>9833300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>143.496050619897</v>
+        <v>143.4275568592265</v>
       </c>
       <c r="C72" t="n">
-        <v>145.2177239216924</v>
+        <v>144.2884009089423</v>
       </c>
       <c r="D72" t="n">
-        <v>143.2612708815172</v>
+        <v>142.1852200188561</v>
       </c>
       <c r="E72" t="n">
-        <v>144.5916595458984</v>
+        <v>142.3515167236328</v>
       </c>
       <c r="F72" t="n">
-        <v>9833300</v>
+        <v>12239900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>143.4275568592265</v>
+        <v>142.3417162193598</v>
       </c>
       <c r="C73" t="n">
-        <v>144.2884009089423</v>
+        <v>142.8699668272841</v>
       </c>
       <c r="D73" t="n">
-        <v>142.1852200188561</v>
+        <v>140.8059085533541</v>
       </c>
       <c r="E73" t="n">
-        <v>142.3515167236328</v>
+        <v>141.3145904541016</v>
       </c>
       <c r="F73" t="n">
-        <v>12239900</v>
+        <v>19345600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>142.3417162193598</v>
+        <v>140.5809250079643</v>
       </c>
       <c r="C74" t="n">
-        <v>142.8699668272841</v>
+        <v>141.2558886976474</v>
       </c>
       <c r="D74" t="n">
-        <v>140.8059085533541</v>
+        <v>139.3190045706883</v>
       </c>
       <c r="E74" t="n">
-        <v>141.3145904541016</v>
+        <v>139.5831298828125</v>
       </c>
       <c r="F74" t="n">
-        <v>19345600</v>
+        <v>11731400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>140.5809250079643</v>
+        <v>139.387490519737</v>
       </c>
       <c r="C75" t="n">
-        <v>141.2558886976474</v>
+        <v>140.6004817498258</v>
       </c>
       <c r="D75" t="n">
-        <v>139.3190045706883</v>
+        <v>138.9864140977976</v>
       </c>
       <c r="E75" t="n">
-        <v>139.5831298828125</v>
+        <v>140.0624542236328</v>
       </c>
       <c r="F75" t="n">
-        <v>11731400</v>
+        <v>9541600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>139.387490519737</v>
+        <v>139.7885720199097</v>
       </c>
       <c r="C76" t="n">
-        <v>140.6004817498258</v>
+        <v>141.5885202675369</v>
       </c>
       <c r="D76" t="n">
-        <v>138.9864140977976</v>
+        <v>139.72010392126</v>
       </c>
       <c r="E76" t="n">
-        <v>140.0624542236328</v>
+        <v>141.3439636230469</v>
       </c>
       <c r="F76" t="n">
-        <v>9541600</v>
+        <v>3259200</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>139.7885720199097</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="C77" t="n">
-        <v>141.5885202675369</v>
+        <v>142.4688988061542</v>
       </c>
       <c r="D77" t="n">
-        <v>139.72010392126</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="E77" t="n">
-        <v>141.3439636230469</v>
+        <v>141.5885009765625</v>
       </c>
       <c r="F77" t="n">
-        <v>3259200</v>
+        <v>4711500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>141.1678558435435</v>
+        <v>141.6471833233528</v>
       </c>
       <c r="C78" t="n">
-        <v>142.4688988061542</v>
+        <v>141.9113086263453</v>
       </c>
       <c r="D78" t="n">
-        <v>141.1678558435435</v>
+        <v>140.8156849267153</v>
       </c>
       <c r="E78" t="n">
-        <v>141.5885009765625</v>
+        <v>141.4221954345703</v>
       </c>
       <c r="F78" t="n">
-        <v>4711500</v>
+        <v>7662100</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>141.6471833233528</v>
+        <v>141.1482932462777</v>
       </c>
       <c r="C79" t="n">
-        <v>141.9113086263453</v>
+        <v>141.3146048844386</v>
       </c>
       <c r="D79" t="n">
-        <v>140.8156849267153</v>
+        <v>140.4439839080415</v>
       </c>
       <c r="E79" t="n">
-        <v>141.4221954345703</v>
+        <v>140.9135284423828</v>
       </c>
       <c r="F79" t="n">
-        <v>7662100</v>
+        <v>6006400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>141.1482779620671</v>
+        <v>140.8646302306951</v>
       </c>
       <c r="C80" t="n">
-        <v>141.3145895822191</v>
+        <v>141.0015813574684</v>
       </c>
       <c r="D80" t="n">
-        <v>140.443968700097</v>
+        <v>140.1113915701655</v>
       </c>
       <c r="E80" t="n">
-        <v>140.9135131835938</v>
+        <v>140.1896514892578</v>
       </c>
       <c r="F80" t="n">
-        <v>6006400</v>
+        <v>5293200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>140.8646148984387</v>
+        <v>139.9939944106823</v>
       </c>
       <c r="C81" t="n">
-        <v>141.0015660103057</v>
+        <v>140.2189823252813</v>
       </c>
       <c r="D81" t="n">
-        <v>140.1113763198945</v>
+        <v>138.164715640037</v>
       </c>
       <c r="E81" t="n">
-        <v>140.1896362304688</v>
+        <v>138.7027282714844</v>
       </c>
       <c r="F81" t="n">
-        <v>5293200</v>
+        <v>8946100</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>139.9939944106823</v>
+        <v>138.0277758154179</v>
       </c>
       <c r="C82" t="n">
-        <v>140.2189823252813</v>
+        <v>138.2723324593669</v>
       </c>
       <c r="D82" t="n">
-        <v>138.164715640037</v>
+        <v>136.5604359517241</v>
       </c>
       <c r="E82" t="n">
-        <v>138.7027282714844</v>
+        <v>137.3136596679688</v>
       </c>
       <c r="F82" t="n">
-        <v>8946100</v>
+        <v>12297300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>138.0277758154179</v>
+        <v>137.3332072243459</v>
       </c>
       <c r="C83" t="n">
-        <v>138.2723324593669</v>
+        <v>138.3407792480867</v>
       </c>
       <c r="D83" t="n">
-        <v>136.5604359517241</v>
+        <v>136.4723631937515</v>
       </c>
       <c r="E83" t="n">
-        <v>137.3136596679688</v>
+        <v>136.8636627197266</v>
       </c>
       <c r="F83" t="n">
-        <v>12297300</v>
+        <v>10421800</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>137.333222535484</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="C84" t="n">
-        <v>138.340794671558</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="D84" t="n">
-        <v>136.472378408915</v>
+        <v>134.6235247173271</v>
       </c>
       <c r="E84" t="n">
-        <v>136.8636779785156</v>
+        <v>135.0343780517578</v>
       </c>
       <c r="F84" t="n">
-        <v>10421800</v>
+        <v>14369100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>136.7560662263838</v>
+        <v>134.8876360609042</v>
       </c>
       <c r="C85" t="n">
-        <v>136.7560662263838</v>
+        <v>138.6929361136317</v>
       </c>
       <c r="D85" t="n">
-        <v>134.6235247173271</v>
+        <v>134.8191679755417</v>
       </c>
       <c r="E85" t="n">
-        <v>135.0343780517578</v>
+        <v>138.4483795166016</v>
       </c>
       <c r="F85" t="n">
-        <v>14369100</v>
+        <v>9297100</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>134.8876360609042</v>
+        <v>138.6146938845888</v>
       </c>
       <c r="C86" t="n">
-        <v>138.6929361136317</v>
+        <v>139.2309813641768</v>
       </c>
       <c r="D86" t="n">
-        <v>134.8191679755417</v>
+        <v>137.7636415949117</v>
       </c>
       <c r="E86" t="n">
-        <v>138.4483795166016</v>
+        <v>138.7809906005859</v>
       </c>
       <c r="F86" t="n">
-        <v>9297100</v>
+        <v>9528500</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>138.6146938845888</v>
+        <v>139.1820498418749</v>
       </c>
       <c r="C87" t="n">
-        <v>139.2309813641768</v>
+        <v>140.7472180394953</v>
       </c>
       <c r="D87" t="n">
-        <v>137.7636415949117</v>
+        <v>138.6244685603122</v>
       </c>
       <c r="E87" t="n">
-        <v>138.7809906005859</v>
+        <v>140.3363647460938</v>
       </c>
       <c r="F87" t="n">
-        <v>9528500</v>
+        <v>12812000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>139.1820649751552</v>
+        <v>140.8646007849644</v>
       </c>
       <c r="C88" t="n">
-        <v>140.7472333429565</v>
+        <v>141.1971941766679</v>
       </c>
       <c r="D88" t="n">
-        <v>138.6244836329666</v>
+        <v>139.8570287929182</v>
       </c>
       <c r="E88" t="n">
-        <v>140.3363800048828</v>
+        <v>141.0993804931641</v>
       </c>
       <c r="F88" t="n">
-        <v>12812000</v>
+        <v>15549200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>140.8646007849644</v>
+        <v>141.529800782003</v>
       </c>
       <c r="C89" t="n">
-        <v>141.1971941766679</v>
+        <v>143.7014647743148</v>
       </c>
       <c r="D89" t="n">
-        <v>139.8570287929182</v>
+        <v>141.2265529596936</v>
       </c>
       <c r="E89" t="n">
-        <v>141.0993804931641</v>
+        <v>143.1634521484375</v>
       </c>
       <c r="F89" t="n">
-        <v>15549200</v>
+        <v>13475000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>141.5298158666727</v>
+        <v>142.5080218255822</v>
       </c>
       <c r="C90" t="n">
-        <v>143.7014800904468</v>
+        <v>143.1634466813173</v>
       </c>
       <c r="D90" t="n">
-        <v>141.2265680120421</v>
+        <v>141.20699378469</v>
       </c>
       <c r="E90" t="n">
-        <v>143.1634674072266</v>
+        <v>141.4808959960938</v>
       </c>
       <c r="F90" t="n">
-        <v>13475000</v>
+        <v>10102800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>142.5080218255822</v>
+        <v>140.6298333307039</v>
       </c>
       <c r="C91" t="n">
-        <v>143.1634466813173</v>
+        <v>141.5787142100195</v>
       </c>
       <c r="D91" t="n">
-        <v>141.20699378469</v>
+        <v>140.5320196386769</v>
       </c>
       <c r="E91" t="n">
-        <v>141.4808959960938</v>
+        <v>141.3830718994141</v>
       </c>
       <c r="F91" t="n">
-        <v>10102800</v>
+        <v>11729300</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>140.6298333307039</v>
+        <v>141.3145973124275</v>
       </c>
       <c r="C92" t="n">
-        <v>141.5787142100195</v>
+        <v>143.7992858886719</v>
       </c>
       <c r="D92" t="n">
-        <v>140.5320196386769</v>
+        <v>140.9819889804792</v>
       </c>
       <c r="E92" t="n">
-        <v>141.3830718994141</v>
+        <v>143.7992858886719</v>
       </c>
       <c r="F92" t="n">
-        <v>11729300</v>
+        <v>12901400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>141.314612307562</v>
+        <v>143.8579872458876</v>
       </c>
       <c r="C93" t="n">
-        <v>143.7993011474609</v>
+        <v>144.1612350737863</v>
       </c>
       <c r="D93" t="n">
-        <v>140.98200394032</v>
+        <v>141.8134974355268</v>
       </c>
       <c r="E93" t="n">
-        <v>143.7993011474609</v>
+        <v>142.8797607421875</v>
       </c>
       <c r="F93" t="n">
-        <v>12901400</v>
+        <v>14126800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>143.8579872458876</v>
+        <v>144.8557716267987</v>
       </c>
       <c r="C94" t="n">
-        <v>144.1612350737863</v>
+        <v>147.6241542164368</v>
       </c>
       <c r="D94" t="n">
-        <v>141.8134974355268</v>
+        <v>144.2883985058945</v>
       </c>
       <c r="E94" t="n">
-        <v>142.8797607421875</v>
+        <v>146.6654815673828</v>
       </c>
       <c r="F94" t="n">
-        <v>14126800</v>
+        <v>18501900</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,25 +2887,25 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>144.8557716267987</v>
+        <v>148.6033244770038</v>
       </c>
       <c r="C95" t="n">
-        <v>147.6241542164368</v>
+        <v>149.401311303758</v>
       </c>
       <c r="D95" t="n">
-        <v>144.2883985058945</v>
+        <v>147.5787523243573</v>
       </c>
       <c r="E95" t="n">
-        <v>146.6654815673828</v>
+        <v>147.9235534667969</v>
       </c>
       <c r="F95" t="n">
-        <v>18501900</v>
+        <v>14562600</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -2913,25 +2913,25 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>148.6033244770038</v>
+        <v>147.8940093166009</v>
       </c>
       <c r="C96" t="n">
-        <v>149.401311303758</v>
+        <v>148.642749624448</v>
       </c>
       <c r="D96" t="n">
-        <v>147.5787523243573</v>
+        <v>146.3177432055359</v>
       </c>
       <c r="E96" t="n">
-        <v>147.9235534667969</v>
+        <v>147.2733612060547</v>
       </c>
       <c r="F96" t="n">
-        <v>14562600</v>
+        <v>12655700</v>
       </c>
       <c r="G96" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>147.8940093166009</v>
+        <v>145.8744105284403</v>
       </c>
       <c r="C97" t="n">
-        <v>148.642749624448</v>
+        <v>147.4211225953709</v>
       </c>
       <c r="D97" t="n">
-        <v>146.3177432055359</v>
+        <v>145.7364720311358</v>
       </c>
       <c r="E97" t="n">
-        <v>147.2733612060547</v>
+        <v>146.1403961181641</v>
       </c>
       <c r="F97" t="n">
-        <v>12655700</v>
+        <v>9546000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>145.8744105284403</v>
+        <v>145.8054447387209</v>
       </c>
       <c r="C98" t="n">
-        <v>147.4211225953709</v>
+        <v>146.5049234190107</v>
       </c>
       <c r="D98" t="n">
-        <v>145.7364720311358</v>
+        <v>144.613380096476</v>
       </c>
       <c r="E98" t="n">
-        <v>146.1403961181641</v>
+        <v>145.1552276611328</v>
       </c>
       <c r="F98" t="n">
-        <v>9546000</v>
+        <v>7465800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>145.8054447387209</v>
+        <v>145.1059620999764</v>
       </c>
       <c r="C99" t="n">
-        <v>146.5049234190107</v>
+        <v>147.9038617122788</v>
       </c>
       <c r="D99" t="n">
-        <v>144.613380096476</v>
+        <v>144.9286383741246</v>
       </c>
       <c r="E99" t="n">
-        <v>145.1552276611328</v>
+        <v>147.6772613525391</v>
       </c>
       <c r="F99" t="n">
-        <v>7465800</v>
+        <v>11035600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>145.1059620999764</v>
+        <v>148.1994047112546</v>
       </c>
       <c r="C100" t="n">
-        <v>147.9038617122788</v>
+        <v>149.7165778862847</v>
       </c>
       <c r="D100" t="n">
-        <v>144.9286383741246</v>
+        <v>146.9383858562462</v>
       </c>
       <c r="E100" t="n">
-        <v>147.6772613525391</v>
+        <v>149.5195465087891</v>
       </c>
       <c r="F100" t="n">
-        <v>11035600</v>
+        <v>12651400</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>148.1994047112546</v>
+        <v>150.1599009677594</v>
       </c>
       <c r="C101" t="n">
-        <v>149.7165778862847</v>
+        <v>151.4504737667986</v>
       </c>
       <c r="D101" t="n">
-        <v>146.9383858562462</v>
+        <v>149.0072516350481</v>
       </c>
       <c r="E101" t="n">
-        <v>149.5195465087891</v>
+        <v>150.9184875488281</v>
       </c>
       <c r="F101" t="n">
-        <v>12651400</v>
+        <v>10554900</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>150.1599009677594</v>
+        <v>150.3273766276017</v>
       </c>
       <c r="C102" t="n">
-        <v>151.4504737667986</v>
+        <v>154.2089563191786</v>
       </c>
       <c r="D102" t="n">
-        <v>149.0072516350481</v>
+        <v>149.9431601878661</v>
       </c>
       <c r="E102" t="n">
-        <v>150.9184875488281</v>
+        <v>153.0169067382812</v>
       </c>
       <c r="F102" t="n">
-        <v>10554900</v>
+        <v>12424700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>150.3273766276017</v>
+        <v>153.8148971925123</v>
       </c>
       <c r="C103" t="n">
-        <v>154.2089563191786</v>
+        <v>156.0216726798457</v>
       </c>
       <c r="D103" t="n">
-        <v>149.9431601878661</v>
+        <v>153.450373358777</v>
       </c>
       <c r="E103" t="n">
-        <v>153.0169067382812</v>
+        <v>154.5439147949219</v>
       </c>
       <c r="F103" t="n">
-        <v>12424700</v>
+        <v>12178500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>153.8148971925123</v>
+        <v>156.4847030065954</v>
       </c>
       <c r="C104" t="n">
-        <v>156.0216726798457</v>
+        <v>157.2826898506833</v>
       </c>
       <c r="D104" t="n">
-        <v>153.450373358777</v>
+        <v>153.8050342014295</v>
       </c>
       <c r="E104" t="n">
-        <v>154.5439147949219</v>
+        <v>156.2581176757812</v>
       </c>
       <c r="F104" t="n">
-        <v>12178500</v>
+        <v>13077700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>156.4847030065954</v>
+        <v>155.8935966032756</v>
       </c>
       <c r="C105" t="n">
-        <v>157.2826898506833</v>
+        <v>157.6176473147596</v>
       </c>
       <c r="D105" t="n">
-        <v>153.8050342014295</v>
+        <v>155.6669962577738</v>
       </c>
       <c r="E105" t="n">
-        <v>156.2581176757812</v>
+        <v>156.8097991943359</v>
       </c>
       <c r="F105" t="n">
-        <v>13077700</v>
+        <v>10441700</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>155.8935966032756</v>
+        <v>156.4058894678126</v>
       </c>
       <c r="C106" t="n">
-        <v>157.6176473147596</v>
+        <v>156.9181830781391</v>
       </c>
       <c r="D106" t="n">
-        <v>155.6669962577738</v>
+        <v>153.7065280129841</v>
       </c>
       <c r="E106" t="n">
-        <v>156.8097991943359</v>
+        <v>154.9971008300781</v>
       </c>
       <c r="F106" t="n">
-        <v>10441700</v>
+        <v>11439900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>156.4058894678126</v>
+        <v>155.1941261981174</v>
       </c>
       <c r="C107" t="n">
-        <v>156.9181830781391</v>
+        <v>157.7752717323398</v>
       </c>
       <c r="D107" t="n">
-        <v>153.7065280129841</v>
+        <v>154.3961393746382</v>
       </c>
       <c r="E107" t="n">
-        <v>154.9971008300781</v>
+        <v>156.7211456298828</v>
       </c>
       <c r="F107" t="n">
-        <v>11439900</v>
+        <v>9910100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>155.1941261981174</v>
+        <v>156.2876680693531</v>
       </c>
       <c r="C108" t="n">
-        <v>157.7752717323398</v>
+        <v>158.7505977950001</v>
       </c>
       <c r="D108" t="n">
-        <v>154.3961393746382</v>
+        <v>155.8443437252427</v>
       </c>
       <c r="E108" t="n">
-        <v>156.7211456298828</v>
+        <v>157.6275024414062</v>
       </c>
       <c r="F108" t="n">
-        <v>9910100</v>
+        <v>10217300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>156.2876680693531</v>
+        <v>157.6472078811371</v>
       </c>
       <c r="C109" t="n">
-        <v>158.7505977950001</v>
+        <v>160.7209393253002</v>
       </c>
       <c r="D109" t="n">
-        <v>155.8443437252427</v>
+        <v>157.2826840647245</v>
       </c>
       <c r="E109" t="n">
-        <v>157.6275024414062</v>
+        <v>158.8195648193359</v>
       </c>
       <c r="F109" t="n">
-        <v>10217300</v>
+        <v>13512900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>157.6472078811371</v>
+        <v>159.3417228437737</v>
       </c>
       <c r="C110" t="n">
-        <v>160.7209393253002</v>
+        <v>160.1594173981944</v>
       </c>
       <c r="D110" t="n">
-        <v>157.2826840647245</v>
+        <v>157.3418249095697</v>
       </c>
       <c r="E110" t="n">
-        <v>158.8195648193359</v>
+        <v>157.6964874267578</v>
       </c>
       <c r="F110" t="n">
-        <v>13512900</v>
+        <v>13998900</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>159.3417228437737</v>
+        <v>157.5782363157609</v>
       </c>
       <c r="C111" t="n">
-        <v>160.1594173981944</v>
+        <v>159.765319051939</v>
       </c>
       <c r="D111" t="n">
-        <v>157.3418249095697</v>
+        <v>156.5241102403673</v>
       </c>
       <c r="E111" t="n">
-        <v>157.6964874267578</v>
+        <v>157.1841735839844</v>
       </c>
       <c r="F111" t="n">
-        <v>13998900</v>
+        <v>13319100</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>157.5782363157609</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="C112" t="n">
-        <v>159.765319051939</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="D112" t="n">
-        <v>156.5241102403673</v>
+        <v>153.4602390569104</v>
       </c>
       <c r="E112" t="n">
-        <v>157.1841735839844</v>
+        <v>154.5340728759766</v>
       </c>
       <c r="F112" t="n">
-        <v>13319100</v>
+        <v>14434300</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>156.6226326022383</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="C113" t="n">
-        <v>156.6226326022383</v>
+        <v>157.588096663496</v>
       </c>
       <c r="D113" t="n">
-        <v>153.4602390569104</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="E113" t="n">
-        <v>154.5340728759766</v>
+        <v>156.2088470458984</v>
       </c>
       <c r="F113" t="n">
-        <v>14434300</v>
+        <v>10724600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>154.5045039445223</v>
+        <v>156.7704074552917</v>
       </c>
       <c r="C114" t="n">
-        <v>157.588096663496</v>
+        <v>158.6717819848204</v>
       </c>
       <c r="D114" t="n">
-        <v>154.5045039445223</v>
+        <v>155.8147895206744</v>
       </c>
       <c r="E114" t="n">
-        <v>156.2088470458984</v>
+        <v>158.3959350585938</v>
       </c>
       <c r="F114" t="n">
-        <v>10724600</v>
+        <v>11508100</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>156.7704074552917</v>
+        <v>157.9427805830092</v>
       </c>
       <c r="C115" t="n">
-        <v>158.6717819848204</v>
+        <v>162.9080407961134</v>
       </c>
       <c r="D115" t="n">
-        <v>155.8147895206744</v>
+        <v>157.9230729341091</v>
       </c>
       <c r="E115" t="n">
-        <v>158.3959350585938</v>
+        <v>162.7208557128906</v>
       </c>
       <c r="F115" t="n">
-        <v>11508100</v>
+        <v>14772400</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>157.9427805830092</v>
+        <v>162.4548534700461</v>
       </c>
       <c r="C116" t="n">
-        <v>162.9080407961134</v>
+        <v>164.3956434730223</v>
       </c>
       <c r="D116" t="n">
-        <v>157.9230729341091</v>
+        <v>161.509096787574</v>
       </c>
       <c r="E116" t="n">
-        <v>162.7208557128906</v>
+        <v>162.8292236328125</v>
       </c>
       <c r="F116" t="n">
-        <v>14772400</v>
+        <v>9709500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>162.4548534700461</v>
+        <v>162.1001810746762</v>
       </c>
       <c r="C117" t="n">
-        <v>164.3956434730223</v>
+        <v>162.5533667721119</v>
       </c>
       <c r="D117" t="n">
-        <v>161.509096787574</v>
+        <v>159.6963742176143</v>
       </c>
       <c r="E117" t="n">
-        <v>162.8292236328125</v>
+        <v>160.9672393798828</v>
       </c>
       <c r="F117" t="n">
-        <v>9709500</v>
+        <v>7878500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>162.1001810746762</v>
+        <v>161.7849314119297</v>
       </c>
       <c r="C118" t="n">
-        <v>162.5533667721119</v>
+        <v>162.0607783426765</v>
       </c>
       <c r="D118" t="n">
-        <v>159.6963742176143</v>
+        <v>160.4450970200751</v>
       </c>
       <c r="E118" t="n">
-        <v>160.9672393798828</v>
+        <v>161.3218994140625</v>
       </c>
       <c r="F118" t="n">
-        <v>7878500</v>
+        <v>7028600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>161.7849314119297</v>
+        <v>161.6075869258529</v>
       </c>
       <c r="C119" t="n">
-        <v>162.0607783426765</v>
+        <v>164.7699952425796</v>
       </c>
       <c r="D119" t="n">
-        <v>160.4450970200751</v>
+        <v>161.262785790902</v>
       </c>
       <c r="E119" t="n">
-        <v>161.3218994140625</v>
+        <v>164.7207336425781</v>
       </c>
       <c r="F119" t="n">
-        <v>7028600</v>
+        <v>14878500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>161.6075869258529</v>
+        <v>162.8390693932343</v>
       </c>
       <c r="C120" t="n">
-        <v>164.7699952425796</v>
+        <v>164.0803957045348</v>
       </c>
       <c r="D120" t="n">
-        <v>161.262785790902</v>
+        <v>161.0263565641498</v>
       </c>
       <c r="E120" t="n">
-        <v>164.7207336425781</v>
+        <v>161.0854644775391</v>
       </c>
       <c r="F120" t="n">
-        <v>14878500</v>
+        <v>9095500</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>162.8390693932343</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="C121" t="n">
-        <v>164.0803957045348</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="D121" t="n">
-        <v>161.0263565641498</v>
+        <v>156.2679589705066</v>
       </c>
       <c r="E121" t="n">
-        <v>161.0854644775391</v>
+        <v>157.3516540527344</v>
       </c>
       <c r="F121" t="n">
-        <v>9095500</v>
+        <v>10161000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>159.7850298016668</v>
+        <v>157.0758237333674</v>
       </c>
       <c r="C122" t="n">
-        <v>159.7850298016668</v>
+        <v>157.243301166956</v>
       </c>
       <c r="D122" t="n">
-        <v>156.2679589705066</v>
+        <v>154.9774025943761</v>
       </c>
       <c r="E122" t="n">
-        <v>157.3516540527344</v>
+        <v>155.9527282714844</v>
       </c>
       <c r="F122" t="n">
-        <v>10161000</v>
+        <v>8752700</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>157.0758237333674</v>
+        <v>154.6128887776175</v>
       </c>
       <c r="C123" t="n">
-        <v>157.243301166956</v>
+        <v>154.7705198979749</v>
       </c>
       <c r="D123" t="n">
-        <v>154.9774025943761</v>
+        <v>151.4898954891258</v>
       </c>
       <c r="E123" t="n">
-        <v>155.9527282714844</v>
+        <v>151.7066345214844</v>
       </c>
       <c r="F123" t="n">
-        <v>8752700</v>
+        <v>10060300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>154.6128887776175</v>
+        <v>151.3815284437877</v>
       </c>
       <c r="C124" t="n">
-        <v>154.7705198979749</v>
+        <v>152.1401000368933</v>
       </c>
       <c r="D124" t="n">
-        <v>151.4898954891258</v>
+        <v>149.6377698486339</v>
       </c>
       <c r="E124" t="n">
-        <v>151.7066345214844</v>
+        <v>151.3519744873047</v>
       </c>
       <c r="F124" t="n">
-        <v>10060300</v>
+        <v>8187900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>151.3815284437877</v>
+        <v>150.8790677258081</v>
       </c>
       <c r="C125" t="n">
-        <v>152.1401000368933</v>
+        <v>153.9133989264833</v>
       </c>
       <c r="D125" t="n">
-        <v>149.6377698486339</v>
+        <v>150.6327747552909</v>
       </c>
       <c r="E125" t="n">
-        <v>151.3519744873047</v>
+        <v>152.9183807373047</v>
       </c>
       <c r="F125" t="n">
-        <v>8187900</v>
+        <v>12494900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>150.8790677258081</v>
+        <v>153.1843919415674</v>
       </c>
       <c r="C126" t="n">
-        <v>153.9133989264833</v>
+        <v>154.8197659541039</v>
       </c>
       <c r="D126" t="n">
-        <v>150.6327747552909</v>
+        <v>151.3224175570726</v>
       </c>
       <c r="E126" t="n">
-        <v>152.9183807373047</v>
+        <v>153.6966705322266</v>
       </c>
       <c r="F126" t="n">
-        <v>12494900</v>
+        <v>7756800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>153.1843919415674</v>
+        <v>152.9282368144603</v>
       </c>
       <c r="C127" t="n">
-        <v>154.8197659541039</v>
+        <v>153.07602162573</v>
       </c>
       <c r="D127" t="n">
-        <v>151.3224175570726</v>
+        <v>149.1845804169242</v>
       </c>
       <c r="E127" t="n">
-        <v>153.6966705322266</v>
+        <v>151.0465698242188</v>
       </c>
       <c r="F127" t="n">
-        <v>7756800</v>
+        <v>8855100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>152.9282368144603</v>
+        <v>149.9530221525258</v>
       </c>
       <c r="C128" t="n">
-        <v>153.07602162573</v>
+        <v>150.7805629442461</v>
       </c>
       <c r="D128" t="n">
-        <v>149.1845804169242</v>
+        <v>148.100894162221</v>
       </c>
       <c r="E128" t="n">
-        <v>151.0465698242188</v>
+        <v>148.2683715820312</v>
       </c>
       <c r="F128" t="n">
-        <v>8855100</v>
+        <v>8489300</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>149.9530221525258</v>
+        <v>149.1254779831649</v>
       </c>
       <c r="C129" t="n">
-        <v>150.7805629442461</v>
+        <v>150.2879887378921</v>
       </c>
       <c r="D129" t="n">
-        <v>148.100894162221</v>
+        <v>147.9531209203371</v>
       </c>
       <c r="E129" t="n">
-        <v>148.2683715820312</v>
+        <v>148.4161529541016</v>
       </c>
       <c r="F129" t="n">
-        <v>8489300</v>
+        <v>7298900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>149.1254779831649</v>
+        <v>149.6082100748309</v>
       </c>
       <c r="C130" t="n">
-        <v>150.2879887378921</v>
+        <v>150.3766429785721</v>
       </c>
       <c r="D130" t="n">
-        <v>147.9531209203371</v>
+        <v>148.4161454237534</v>
       </c>
       <c r="E130" t="n">
-        <v>148.4161529541016</v>
+        <v>149.8643493652344</v>
       </c>
       <c r="F130" t="n">
-        <v>7298900</v>
+        <v>6944000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>149.6082100748309</v>
+        <v>150.7411528047512</v>
       </c>
       <c r="C131" t="n">
-        <v>150.3766429785721</v>
+        <v>151.184492202826</v>
       </c>
       <c r="D131" t="n">
-        <v>148.4161454237534</v>
+        <v>148.9579940023762</v>
       </c>
       <c r="E131" t="n">
-        <v>149.8643493652344</v>
+        <v>149.2338409423828</v>
       </c>
       <c r="F131" t="n">
-        <v>6944000</v>
+        <v>6147700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>150.7411528047512</v>
+        <v>147.0960143427481</v>
       </c>
       <c r="C132" t="n">
-        <v>151.184492202826</v>
+        <v>147.4014152272885</v>
       </c>
       <c r="D132" t="n">
-        <v>148.9579940023762</v>
+        <v>144.2882834404146</v>
       </c>
       <c r="E132" t="n">
-        <v>149.2338409423828</v>
+        <v>144.5345764160156</v>
       </c>
       <c r="F132" t="n">
-        <v>6147700</v>
+        <v>10059300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>147.0960143427481</v>
+        <v>144.0518332623683</v>
       </c>
       <c r="C133" t="n">
-        <v>147.4014152272885</v>
+        <v>145.1946362491204</v>
       </c>
       <c r="D133" t="n">
-        <v>144.2882834404146</v>
+        <v>142.6430296593396</v>
       </c>
       <c r="E133" t="n">
-        <v>144.5345764160156</v>
+        <v>142.6922912597656</v>
       </c>
       <c r="F133" t="n">
-        <v>10059300</v>
+        <v>10340300</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>144.0518332623683</v>
+        <v>142.8400884498559</v>
       </c>
       <c r="C134" t="n">
-        <v>145.1946362491204</v>
+        <v>143.6577829837524</v>
       </c>
       <c r="D134" t="n">
-        <v>142.6430296593396</v>
+        <v>142.111055784898</v>
       </c>
       <c r="E134" t="n">
-        <v>142.6922912597656</v>
+        <v>142.1406097412109</v>
       </c>
       <c r="F134" t="n">
-        <v>10340300</v>
+        <v>60620900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>142.8400884498559</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="C135" t="n">
-        <v>143.6577829837524</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="D135" t="n">
-        <v>142.111055784898</v>
+        <v>141.3524721007716</v>
       </c>
       <c r="E135" t="n">
-        <v>142.1406097412109</v>
+        <v>141.8549194335938</v>
       </c>
       <c r="F135" t="n">
-        <v>60620900</v>
+        <v>10315600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>143.9828794949957</v>
+        <v>141.2046936096272</v>
       </c>
       <c r="C136" t="n">
-        <v>143.9828794949957</v>
+        <v>143.0765142514037</v>
       </c>
       <c r="D136" t="n">
-        <v>141.3524721007716</v>
+        <v>140.1209984806846</v>
       </c>
       <c r="E136" t="n">
-        <v>141.8549194335938</v>
+        <v>141.0372161865234</v>
       </c>
       <c r="F136" t="n">
-        <v>10315600</v>
+        <v>8567600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>141.2046936096272</v>
+        <v>141.6086259660596</v>
       </c>
       <c r="C137" t="n">
-        <v>143.0765142514037</v>
+        <v>141.9632884805344</v>
       </c>
       <c r="D137" t="n">
-        <v>140.1209984806846</v>
+        <v>140.1210066538726</v>
       </c>
       <c r="E137" t="n">
-        <v>141.0372161865234</v>
+        <v>141.7859497070312</v>
       </c>
       <c r="F137" t="n">
-        <v>8567600</v>
+        <v>8418100</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>141.6086259660596</v>
+        <v>141.559369693648</v>
       </c>
       <c r="C138" t="n">
-        <v>141.9632884805344</v>
+        <v>142.4263258800331</v>
       </c>
       <c r="D138" t="n">
-        <v>140.1210066538726</v>
+        <v>140.1308732738322</v>
       </c>
       <c r="E138" t="n">
-        <v>141.7859497070312</v>
+        <v>140.3081970214844</v>
       </c>
       <c r="F138" t="n">
-        <v>8418100</v>
+        <v>6443200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>141.559369693648</v>
+        <v>140.603748896169</v>
       </c>
       <c r="C139" t="n">
-        <v>142.4263258800331</v>
+        <v>141.9435834160748</v>
       </c>
       <c r="D139" t="n">
-        <v>140.1308732738322</v>
+        <v>139.9042701625835</v>
       </c>
       <c r="E139" t="n">
-        <v>140.3081970214844</v>
+        <v>140.5939025878906</v>
       </c>
       <c r="F139" t="n">
-        <v>6443200</v>
+        <v>11558300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>140.603748896169</v>
+        <v>140.9189847788946</v>
       </c>
       <c r="C140" t="n">
-        <v>141.9435834160748</v>
+        <v>143.4114835656516</v>
       </c>
       <c r="D140" t="n">
-        <v>139.9042701625835</v>
+        <v>140.4559678065659</v>
       </c>
       <c r="E140" t="n">
-        <v>140.5939025878906</v>
+        <v>142.5740814208984</v>
       </c>
       <c r="F140" t="n">
-        <v>11558300</v>
+        <v>11616300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>140.9189847788946</v>
+        <v>142.6726031682958</v>
       </c>
       <c r="C141" t="n">
-        <v>143.4114835656516</v>
+        <v>142.7711113397407</v>
       </c>
       <c r="D141" t="n">
-        <v>140.4559678065659</v>
+        <v>140.1702580996175</v>
       </c>
       <c r="E141" t="n">
-        <v>142.5740814208984</v>
+        <v>142.2982330322266</v>
       </c>
       <c r="F141" t="n">
-        <v>11616300</v>
+        <v>10407500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>142.6726031682958</v>
+        <v>141.7859527393269</v>
       </c>
       <c r="C142" t="n">
-        <v>142.7711113397407</v>
+        <v>142.8203863480455</v>
       </c>
       <c r="D142" t="n">
-        <v>140.1702580996175</v>
+        <v>141.0864890360487</v>
       </c>
       <c r="E142" t="n">
-        <v>142.2982330322266</v>
+        <v>141.9534301757812</v>
       </c>
       <c r="F142" t="n">
-        <v>10407500</v>
+        <v>8061700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>141.7859527393269</v>
+        <v>141.9534207153344</v>
       </c>
       <c r="C143" t="n">
-        <v>142.8203863480455</v>
+        <v>142.0716515698294</v>
       </c>
       <c r="D143" t="n">
-        <v>141.0864890360487</v>
+        <v>140.4658165030053</v>
       </c>
       <c r="E143" t="n">
-        <v>141.9534301757812</v>
+        <v>140.997802734375</v>
       </c>
       <c r="F143" t="n">
-        <v>8061700</v>
+        <v>5941700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>141.9534207153344</v>
+        <v>140.8894315190035</v>
       </c>
       <c r="C144" t="n">
-        <v>142.0716515698294</v>
+        <v>141.5396485970176</v>
       </c>
       <c r="D144" t="n">
-        <v>140.4658165030053</v>
+        <v>139.8155977290451</v>
       </c>
       <c r="E144" t="n">
-        <v>140.997802734375</v>
+        <v>140.6529998779297</v>
       </c>
       <c r="F144" t="n">
-        <v>5941700</v>
+        <v>6823100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>140.8894315190035</v>
+        <v>140.4066990917555</v>
       </c>
       <c r="C145" t="n">
-        <v>141.5396485970176</v>
+        <v>140.6529920592033</v>
       </c>
       <c r="D145" t="n">
-        <v>139.8155977290451</v>
+        <v>138.6530943661295</v>
       </c>
       <c r="E145" t="n">
-        <v>140.6529998779297</v>
+        <v>139.2047882080078</v>
       </c>
       <c r="F145" t="n">
-        <v>6823100</v>
+        <v>7207500</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>140.4066990917555</v>
+        <v>141.0273529653376</v>
       </c>
       <c r="C146" t="n">
-        <v>140.6529920592033</v>
+        <v>142.9582965240978</v>
       </c>
       <c r="D146" t="n">
-        <v>138.6530943661295</v>
+        <v>139.766334122587</v>
       </c>
       <c r="E146" t="n">
-        <v>139.2047882080078</v>
+        <v>142.7514038085938</v>
       </c>
       <c r="F146" t="n">
-        <v>7207500</v>
+        <v>10849700</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>141.0273529653376</v>
+        <v>142.2489765209199</v>
       </c>
       <c r="C147" t="n">
-        <v>142.9582965240978</v>
+        <v>144.7611679868877</v>
       </c>
       <c r="D147" t="n">
-        <v>139.766334122587</v>
+        <v>140.8795881188284</v>
       </c>
       <c r="E147" t="n">
-        <v>142.7514038085938</v>
+        <v>144.4853210449219</v>
       </c>
       <c r="F147" t="n">
-        <v>10849700</v>
+        <v>6794800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>142.2489765209199</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="C148" t="n">
-        <v>144.7611679868877</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="D148" t="n">
-        <v>140.8795881188284</v>
+        <v>142.6134905474848</v>
       </c>
       <c r="E148" t="n">
-        <v>144.4853210449219</v>
+        <v>143.007568359375</v>
       </c>
       <c r="F148" t="n">
-        <v>6794800</v>
+        <v>9790300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>144.7119116772724</v>
+        <v>142.8499157089539</v>
       </c>
       <c r="C149" t="n">
-        <v>144.7119116772724</v>
+        <v>142.9385775660697</v>
       </c>
       <c r="D149" t="n">
-        <v>142.6134905474848</v>
+        <v>140.5150632763963</v>
       </c>
       <c r="E149" t="n">
-        <v>143.007568359375</v>
+        <v>141.4509735107422</v>
       </c>
       <c r="F149" t="n">
-        <v>9790300</v>
+        <v>7121400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>142.8499157089539</v>
+        <v>141.1160402826616</v>
       </c>
       <c r="C150" t="n">
-        <v>142.9385775660697</v>
+        <v>142.5740906086617</v>
       </c>
       <c r="D150" t="n">
-        <v>140.5150632763963</v>
+        <v>140.6530082479637</v>
       </c>
       <c r="E150" t="n">
-        <v>141.4509735107422</v>
+        <v>142.2391357421875</v>
       </c>
       <c r="F150" t="n">
-        <v>7121400</v>
+        <v>6621600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>141.1160402826616</v>
+        <v>142.2194162805844</v>
       </c>
       <c r="C151" t="n">
-        <v>142.5740906086617</v>
+        <v>142.2588165423252</v>
       </c>
       <c r="D151" t="n">
-        <v>140.6530082479637</v>
+        <v>140.1505492747316</v>
       </c>
       <c r="E151" t="n">
-        <v>142.2391357421875</v>
+        <v>141.2539520263672</v>
       </c>
       <c r="F151" t="n">
-        <v>6621600</v>
+        <v>7698200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>142.2194162805844</v>
+        <v>141.0766226846627</v>
       </c>
       <c r="C152" t="n">
-        <v>142.2588165423252</v>
+        <v>142.1504565210129</v>
       </c>
       <c r="D152" t="n">
-        <v>140.1505492747316</v>
+        <v>140.5446364367332</v>
       </c>
       <c r="E152" t="n">
-        <v>141.2539520263672</v>
+        <v>140.9879608154297</v>
       </c>
       <c r="F152" t="n">
-        <v>7698200</v>
+        <v>6947100</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>141.0766226846627</v>
+        <v>141.2835176988996</v>
       </c>
       <c r="C153" t="n">
-        <v>142.1504565210129</v>
+        <v>145.4015293724886</v>
       </c>
       <c r="D153" t="n">
-        <v>140.5446364367332</v>
+        <v>141.0372247031338</v>
       </c>
       <c r="E153" t="n">
-        <v>140.9879608154297</v>
+        <v>144.7513122558594</v>
       </c>
       <c r="F153" t="n">
-        <v>6947100</v>
+        <v>10886000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>141.2835176988996</v>
+        <v>143.8942158414082</v>
       </c>
       <c r="C154" t="n">
-        <v>145.4015293724886</v>
+        <v>144.4853250376877</v>
       </c>
       <c r="D154" t="n">
-        <v>141.0372247031338</v>
+        <v>141.4608398676902</v>
       </c>
       <c r="E154" t="n">
-        <v>144.7513122558594</v>
+        <v>142.3475036621094</v>
       </c>
       <c r="F154" t="n">
-        <v>10886000</v>
+        <v>8084700</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>143.8942158414082</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="C155" t="n">
-        <v>144.4853250376877</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="D155" t="n">
-        <v>141.4608398676902</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="E155" t="n">
-        <v>142.3475036621094</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="F155" t="n">
-        <v>8084700</v>
+        <v>11197200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>142.4755698536542</v>
+        <v>140.3869953464167</v>
       </c>
       <c r="C156" t="n">
-        <v>142.4755698536542</v>
+        <v>141.175135870657</v>
       </c>
       <c r="D156" t="n">
-        <v>140.2096862792969</v>
+        <v>140.1111484178121</v>
       </c>
       <c r="E156" t="n">
-        <v>140.2096862792969</v>
+        <v>140.7318115234375</v>
       </c>
       <c r="F156" t="n">
-        <v>11197200</v>
+        <v>7236300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>140.3869953464167</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="C157" t="n">
-        <v>141.175135870657</v>
+        <v>144.0616865371081</v>
       </c>
       <c r="D157" t="n">
-        <v>140.1111484178121</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="E157" t="n">
-        <v>140.7318115234375</v>
+        <v>143.5494079589844</v>
       </c>
       <c r="F157" t="n">
-        <v>7236300</v>
+        <v>11288800</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,25 +4525,25 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>141.2736481824844</v>
+        <v>150.8836541197979</v>
       </c>
       <c r="C158" t="n">
-        <v>144.0616865371081</v>
+        <v>151.2906197995367</v>
       </c>
       <c r="D158" t="n">
-        <v>141.2736481824844</v>
+        <v>146.5261830755894</v>
       </c>
       <c r="E158" t="n">
-        <v>143.5494079589844</v>
+        <v>147.08203125</v>
       </c>
       <c r="F158" t="n">
-        <v>11288800</v>
+        <v>13786200</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4551,25 +4551,25 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>150.8836541197979</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="C159" t="n">
-        <v>151.2906197995367</v>
+        <v>148.59077024601</v>
       </c>
       <c r="D159" t="n">
-        <v>146.5261830755894</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="E159" t="n">
-        <v>147.08203125</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F159" t="n">
-        <v>13786200</v>
+        <v>9166400</v>
       </c>
       <c r="G159" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>146.3276654919543</v>
+        <v>148.9183255527001</v>
       </c>
       <c r="C160" t="n">
-        <v>148.59077024601</v>
+        <v>150.0697339670296</v>
       </c>
       <c r="D160" t="n">
-        <v>146.3276654919543</v>
+        <v>147.3301749711611</v>
       </c>
       <c r="E160" t="n">
-        <v>147.3003997802734</v>
+        <v>148.064697265625</v>
       </c>
       <c r="F160" t="n">
-        <v>9166400</v>
+        <v>7965700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>148.9183255527001</v>
+        <v>147.2011489489405</v>
       </c>
       <c r="C161" t="n">
-        <v>150.0697339670296</v>
+        <v>147.6478115682369</v>
       </c>
       <c r="D161" t="n">
-        <v>147.3301749711611</v>
+        <v>144.8090026189782</v>
       </c>
       <c r="E161" t="n">
-        <v>148.064697265625</v>
+        <v>145.3747863769531</v>
       </c>
       <c r="F161" t="n">
-        <v>7965700</v>
+        <v>9002400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>147.2011489489405</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="C162" t="n">
-        <v>147.6478115682369</v>
+        <v>146.6254435609453</v>
       </c>
       <c r="D162" t="n">
-        <v>144.8090026189782</v>
+        <v>144.8685544504002</v>
       </c>
       <c r="E162" t="n">
-        <v>145.3747863769531</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="F162" t="n">
-        <v>9002400</v>
+        <v>9491700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>146.0001068115234</v>
+        <v>146.7743191747914</v>
       </c>
       <c r="C163" t="n">
-        <v>146.6254435609453</v>
+        <v>148.1738750980608</v>
       </c>
       <c r="D163" t="n">
-        <v>144.8685544504002</v>
+        <v>145.3747783972478</v>
       </c>
       <c r="E163" t="n">
-        <v>146.0001068115234</v>
+        <v>146.1688385009766</v>
       </c>
       <c r="F163" t="n">
-        <v>9491700</v>
+        <v>6814800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>146.7743191747914</v>
+        <v>144.977737605514</v>
       </c>
       <c r="C164" t="n">
-        <v>148.1738750980608</v>
+        <v>144.977737605514</v>
       </c>
       <c r="D164" t="n">
-        <v>145.3747783972478</v>
+        <v>142.2084173171452</v>
       </c>
       <c r="E164" t="n">
-        <v>146.1688385009766</v>
+        <v>142.3572998046875</v>
       </c>
       <c r="F164" t="n">
-        <v>6814800</v>
+        <v>9642800</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>144.977737605514</v>
+        <v>142.3175981532361</v>
       </c>
       <c r="C165" t="n">
-        <v>144.977737605514</v>
+        <v>144.8189147356386</v>
       </c>
       <c r="D165" t="n">
-        <v>142.2084173171452</v>
+        <v>141.1264777093581</v>
       </c>
       <c r="E165" t="n">
-        <v>142.3572998046875</v>
+        <v>143.8263244628906</v>
       </c>
       <c r="F165" t="n">
-        <v>9642800</v>
+        <v>7664300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>142.3175981532361</v>
+        <v>145.3152221312864</v>
       </c>
       <c r="C166" t="n">
-        <v>144.8189147356386</v>
+        <v>147.8463305694715</v>
       </c>
       <c r="D166" t="n">
-        <v>141.1264777093581</v>
+        <v>144.8586390489098</v>
       </c>
       <c r="E166" t="n">
-        <v>143.8263244628906</v>
+        <v>146.8041076660156</v>
       </c>
       <c r="F166" t="n">
-        <v>7664300</v>
+        <v>9399500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>145.3152221312864</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="C167" t="n">
-        <v>147.8463305694715</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="D167" t="n">
-        <v>144.8586390489098</v>
+        <v>144.9380404787042</v>
       </c>
       <c r="E167" t="n">
-        <v>146.8041076660156</v>
+        <v>144.9777374267578</v>
       </c>
       <c r="F167" t="n">
-        <v>9399500</v>
+        <v>9545800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>146.8934445898874</v>
+        <v>145.4641093327384</v>
       </c>
       <c r="C168" t="n">
-        <v>146.8934445898874</v>
+        <v>146.4269231210903</v>
       </c>
       <c r="D168" t="n">
-        <v>144.9380404787042</v>
+        <v>145.1266322707271</v>
       </c>
       <c r="E168" t="n">
-        <v>144.9777374267578</v>
+        <v>145.3350677490234</v>
       </c>
       <c r="F168" t="n">
-        <v>9545800</v>
+        <v>5741000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>145.4641093327384</v>
+        <v>144.7097318886224</v>
       </c>
       <c r="C169" t="n">
-        <v>146.4269231210903</v>
+        <v>144.8685499701872</v>
       </c>
       <c r="D169" t="n">
-        <v>145.1266322707271</v>
+        <v>140.9180448520501</v>
       </c>
       <c r="E169" t="n">
-        <v>145.3350677490234</v>
+        <v>142.2977447509766</v>
       </c>
       <c r="F169" t="n">
-        <v>5741000</v>
+        <v>7489500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>144.7097318886224</v>
+        <v>143.280415861365</v>
       </c>
       <c r="C170" t="n">
-        <v>144.8685499701872</v>
+        <v>144.7792217618835</v>
       </c>
       <c r="D170" t="n">
-        <v>140.9180448520501</v>
+        <v>141.8014508619235</v>
       </c>
       <c r="E170" t="n">
-        <v>142.2977447509766</v>
+        <v>142.8436737060547</v>
       </c>
       <c r="F170" t="n">
-        <v>7489500</v>
+        <v>9051200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>143.280415861365</v>
+        <v>142.0892960817053</v>
       </c>
       <c r="C171" t="n">
-        <v>144.7792217618835</v>
+        <v>143.5980375858882</v>
       </c>
       <c r="D171" t="n">
-        <v>141.8014508619235</v>
+        <v>140.610346220736</v>
       </c>
       <c r="E171" t="n">
-        <v>142.8436737060547</v>
+        <v>141.1860504150391</v>
       </c>
       <c r="F171" t="n">
-        <v>9051200</v>
+        <v>6685900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>142.0892960817053</v>
+        <v>142.1190761527801</v>
       </c>
       <c r="C172" t="n">
-        <v>143.5980375858882</v>
+        <v>143.2109315738657</v>
       </c>
       <c r="D172" t="n">
-        <v>140.610346220736</v>
+        <v>141.5731635879637</v>
       </c>
       <c r="E172" t="n">
-        <v>141.1860504150391</v>
+        <v>141.6525726318359</v>
       </c>
       <c r="F172" t="n">
-        <v>6685900</v>
+        <v>9636200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>142.1190761527801</v>
+        <v>142.337438212696</v>
       </c>
       <c r="C173" t="n">
-        <v>143.2109315738657</v>
+        <v>142.337438212696</v>
       </c>
       <c r="D173" t="n">
-        <v>141.5731635879637</v>
+        <v>140.1537426546991</v>
       </c>
       <c r="E173" t="n">
-        <v>141.6525726318359</v>
+        <v>140.5210113525391</v>
       </c>
       <c r="F173" t="n">
-        <v>9636200</v>
+        <v>6989400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>142.337438212696</v>
+        <v>141.0470859006894</v>
       </c>
       <c r="C174" t="n">
-        <v>142.337438212696</v>
+        <v>143.3598079421396</v>
       </c>
       <c r="D174" t="n">
-        <v>140.1537426546991</v>
+        <v>140.5805672539439</v>
       </c>
       <c r="E174" t="n">
-        <v>140.5210113525391</v>
+        <v>141.3349304199219</v>
       </c>
       <c r="F174" t="n">
-        <v>6989400</v>
+        <v>7731200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>141.0470859006894</v>
+        <v>141.4143347616525</v>
       </c>
       <c r="C175" t="n">
-        <v>143.3598079421396</v>
+        <v>142.6451521296186</v>
       </c>
       <c r="D175" t="n">
-        <v>140.5805672539439</v>
+        <v>139.8063433960926</v>
       </c>
       <c r="E175" t="n">
-        <v>141.3349304199219</v>
+        <v>140.2530059814453</v>
       </c>
       <c r="F175" t="n">
-        <v>7731200</v>
+        <v>8355800</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>141.4143347616525</v>
+        <v>140.4018973938673</v>
       </c>
       <c r="C176" t="n">
-        <v>142.6451521296186</v>
+        <v>142.1587864968038</v>
       </c>
       <c r="D176" t="n">
-        <v>139.8063433960926</v>
+        <v>139.578045612781</v>
       </c>
       <c r="E176" t="n">
-        <v>140.2530059814453</v>
+        <v>141.3845672607422</v>
       </c>
       <c r="F176" t="n">
-        <v>8355800</v>
+        <v>8375600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>140.4018973938673</v>
+        <v>140.8287217143626</v>
       </c>
       <c r="C177" t="n">
-        <v>142.1587864968038</v>
+        <v>142.655084297577</v>
       </c>
       <c r="D177" t="n">
-        <v>139.578045612781</v>
+        <v>139.0519765313656</v>
       </c>
       <c r="E177" t="n">
-        <v>141.3845672607422</v>
+        <v>142.3374481201172</v>
       </c>
       <c r="F177" t="n">
-        <v>8375600</v>
+        <v>6297300</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>140.8287217143626</v>
+        <v>142.8039672134308</v>
       </c>
       <c r="C178" t="n">
-        <v>142.655084297577</v>
+        <v>143.5682660152007</v>
       </c>
       <c r="D178" t="n">
-        <v>139.0519765313656</v>
+        <v>142.4664901331732</v>
       </c>
       <c r="E178" t="n">
-        <v>142.3374481201172</v>
+        <v>143.3697509765625</v>
       </c>
       <c r="F178" t="n">
-        <v>6297300</v>
+        <v>4616700</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>142.8039672134308</v>
+        <v>143.439213854944</v>
       </c>
       <c r="C179" t="n">
-        <v>143.5682660152007</v>
+        <v>144.5310692055886</v>
       </c>
       <c r="D179" t="n">
-        <v>142.4664901331732</v>
+        <v>141.473889369509</v>
       </c>
       <c r="E179" t="n">
-        <v>143.3697509765625</v>
+        <v>141.9007110595703</v>
       </c>
       <c r="F179" t="n">
-        <v>4616700</v>
+        <v>8157200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>143.439213854944</v>
+        <v>142.397017874141</v>
       </c>
       <c r="C180" t="n">
-        <v>144.5310692055886</v>
+        <v>147.4393635097026</v>
       </c>
       <c r="D180" t="n">
-        <v>141.473889369509</v>
+        <v>142.397017874141</v>
       </c>
       <c r="E180" t="n">
-        <v>141.9007110595703</v>
+        <v>146.3971557617188</v>
       </c>
       <c r="F180" t="n">
-        <v>8157200</v>
+        <v>10048900</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>142.397017874141</v>
+        <v>145.612997111615</v>
       </c>
       <c r="C181" t="n">
-        <v>147.4393635097026</v>
+        <v>145.612997111615</v>
       </c>
       <c r="D181" t="n">
-        <v>142.397017874141</v>
+        <v>143.9355170452321</v>
       </c>
       <c r="E181" t="n">
-        <v>146.3971557617188</v>
+        <v>144.828857421875</v>
       </c>
       <c r="F181" t="n">
-        <v>10048900</v>
+        <v>10196700</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>145.612997111615</v>
+        <v>144.4417452563355</v>
       </c>
       <c r="C182" t="n">
-        <v>145.612997111615</v>
+        <v>144.5608512461645</v>
       </c>
       <c r="D182" t="n">
-        <v>143.9355170452321</v>
+        <v>142.1389284814664</v>
       </c>
       <c r="E182" t="n">
-        <v>144.828857421875</v>
+        <v>142.4962615966797</v>
       </c>
       <c r="F182" t="n">
-        <v>10196700</v>
+        <v>12355800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>144.4417452563355</v>
+        <v>140.4713875281435</v>
       </c>
       <c r="C183" t="n">
-        <v>144.5608512461645</v>
+        <v>140.7691676558347</v>
       </c>
       <c r="D183" t="n">
-        <v>142.1389284814664</v>
+        <v>137.8310936193964</v>
       </c>
       <c r="E183" t="n">
-        <v>142.4962615966797</v>
+        <v>139.2405700683594</v>
       </c>
       <c r="F183" t="n">
-        <v>12355800</v>
+        <v>11093800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>140.4713875281435</v>
+        <v>139.0817554467106</v>
       </c>
       <c r="C184" t="n">
-        <v>140.7691676558347</v>
+        <v>140.0743457999317</v>
       </c>
       <c r="D184" t="n">
-        <v>137.8310936193964</v>
+        <v>137.999835596674</v>
       </c>
       <c r="E184" t="n">
-        <v>139.2405700683594</v>
+        <v>139.7765808105469</v>
       </c>
       <c r="F184" t="n">
-        <v>11093800</v>
+        <v>9599500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>139.0817554467106</v>
+        <v>139.8857522909846</v>
       </c>
       <c r="C185" t="n">
-        <v>140.0743457999317</v>
+        <v>141.3944938803485</v>
       </c>
       <c r="D185" t="n">
-        <v>137.999835596674</v>
+        <v>138.9626505253011</v>
       </c>
       <c r="E185" t="n">
-        <v>139.7765808105469</v>
+        <v>139.1512451171875</v>
       </c>
       <c r="F185" t="n">
-        <v>9599500</v>
+        <v>9351000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>139.8857522909846</v>
+        <v>141.6426337542266</v>
       </c>
       <c r="C186" t="n">
-        <v>141.3944938803485</v>
+        <v>142.079375912544</v>
       </c>
       <c r="D186" t="n">
-        <v>138.9626505253011</v>
+        <v>138.8534574153755</v>
       </c>
       <c r="E186" t="n">
-        <v>139.1512451171875</v>
+        <v>139.7368621826172</v>
       </c>
       <c r="F186" t="n">
-        <v>9351000</v>
+        <v>8194000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>141.6426337542266</v>
+        <v>141.1661955784844</v>
       </c>
       <c r="C187" t="n">
-        <v>142.079375912544</v>
+        <v>147.131657909349</v>
       </c>
       <c r="D187" t="n">
-        <v>138.8534574153755</v>
+        <v>140.7493094643581</v>
       </c>
       <c r="E187" t="n">
-        <v>139.7368621826172</v>
+        <v>145.4541778564453</v>
       </c>
       <c r="F187" t="n">
-        <v>8194000</v>
+        <v>10963200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>141.1661955784844</v>
+        <v>144.709731142363</v>
       </c>
       <c r="C188" t="n">
-        <v>147.131657909349</v>
+        <v>145.4641094530425</v>
       </c>
       <c r="D188" t="n">
-        <v>140.7493094643581</v>
+        <v>143.9454475270099</v>
       </c>
       <c r="E188" t="n">
-        <v>145.4541778564453</v>
+        <v>144.0248565673828</v>
       </c>
       <c r="F188" t="n">
-        <v>10963200</v>
+        <v>7200700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>144.709731142363</v>
+        <v>143.598043761205</v>
       </c>
       <c r="C189" t="n">
-        <v>145.4641094530425</v>
+        <v>148.3724009095588</v>
       </c>
       <c r="D189" t="n">
-        <v>143.9454475270099</v>
+        <v>143.4590817183783</v>
       </c>
       <c r="E189" t="n">
-        <v>144.0248565673828</v>
+        <v>147.5684051513672</v>
       </c>
       <c r="F189" t="n">
-        <v>7200700</v>
+        <v>8259300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>143.598043761205</v>
+        <v>148.7992154215363</v>
       </c>
       <c r="C190" t="n">
-        <v>148.3724009095588</v>
+        <v>149.3153514723138</v>
       </c>
       <c r="D190" t="n">
-        <v>143.4590817183783</v>
+        <v>147.2805534750766</v>
       </c>
       <c r="E190" t="n">
-        <v>147.5684051513672</v>
+        <v>147.9455871582031</v>
       </c>
       <c r="F190" t="n">
-        <v>8259300</v>
+        <v>7345900</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>148.7992154215363</v>
+        <v>147.598177848302</v>
       </c>
       <c r="C191" t="n">
-        <v>149.3153514723138</v>
+        <v>148.5113591270304</v>
       </c>
       <c r="D191" t="n">
-        <v>147.2805534750766</v>
+        <v>146.6750761188154</v>
       </c>
       <c r="E191" t="n">
-        <v>147.9455871582031</v>
+        <v>147.2408447265625</v>
       </c>
       <c r="F191" t="n">
-        <v>7345900</v>
+        <v>6684700</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>147.598177848302</v>
+        <v>148.2731427996088</v>
       </c>
       <c r="C192" t="n">
-        <v>148.5113591270304</v>
+        <v>149.087058964007</v>
       </c>
       <c r="D192" t="n">
-        <v>146.6750761188154</v>
+        <v>147.2011434657927</v>
       </c>
       <c r="E192" t="n">
-        <v>147.2408447265625</v>
+        <v>148.5014343261719</v>
       </c>
       <c r="F192" t="n">
-        <v>6684700</v>
+        <v>6832000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>148.2731427996088</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="C193" t="n">
-        <v>149.087058964007</v>
+        <v>150.377425765528</v>
       </c>
       <c r="D193" t="n">
-        <v>147.2011434657927</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="E193" t="n">
-        <v>148.5014343261719</v>
+        <v>149.3451385498047</v>
       </c>
       <c r="F193" t="n">
-        <v>6832000</v>
+        <v>9158900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>147.6577229757893</v>
+        <v>150.3873579771785</v>
       </c>
       <c r="C194" t="n">
-        <v>150.377425765528</v>
+        <v>151.8861790939718</v>
       </c>
       <c r="D194" t="n">
-        <v>147.6577229757893</v>
+        <v>149.4344797259463</v>
       </c>
       <c r="E194" t="n">
-        <v>149.3451385498047</v>
+        <v>151.360107421875</v>
       </c>
       <c r="F194" t="n">
-        <v>9158900</v>
+        <v>8518900</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>150.3873579771785</v>
+        <v>151.2509186348782</v>
       </c>
       <c r="C195" t="n">
-        <v>151.8861790939718</v>
+        <v>151.8067667938</v>
       </c>
       <c r="D195" t="n">
-        <v>149.4344797259463</v>
+        <v>148.6602572796902</v>
       </c>
       <c r="E195" t="n">
-        <v>151.360107421875</v>
+        <v>149.4443969726562</v>
       </c>
       <c r="F195" t="n">
-        <v>8518900</v>
+        <v>7055800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>151.2509186348782</v>
+        <v>149.7520913576046</v>
       </c>
       <c r="C196" t="n">
-        <v>151.8067667938</v>
+        <v>151.1615677439354</v>
       </c>
       <c r="D196" t="n">
-        <v>148.6602572796902</v>
+        <v>149.067201638067</v>
       </c>
       <c r="E196" t="n">
-        <v>149.4443969726562</v>
+        <v>149.2657318115234</v>
       </c>
       <c r="F196" t="n">
-        <v>7055800</v>
+        <v>17076100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>149.7520913576046</v>
+        <v>148.9977261100366</v>
       </c>
       <c r="C197" t="n">
-        <v>151.1615677439354</v>
+        <v>149.7719453093657</v>
       </c>
       <c r="D197" t="n">
-        <v>149.067201638067</v>
+        <v>146.4765534870951</v>
       </c>
       <c r="E197" t="n">
-        <v>149.2657318115234</v>
+        <v>146.5857238769531</v>
       </c>
       <c r="F197" t="n">
-        <v>17076100</v>
+        <v>10533000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>148.9977261100366</v>
+        <v>148.5510669184904</v>
       </c>
       <c r="C198" t="n">
-        <v>149.7719453093657</v>
+        <v>150.2483878382925</v>
       </c>
       <c r="D198" t="n">
-        <v>146.4765534870951</v>
+        <v>148.2632072518497</v>
       </c>
       <c r="E198" t="n">
-        <v>146.5857238769531</v>
+        <v>149.7421722412109</v>
       </c>
       <c r="F198" t="n">
-        <v>10533000</v>
+        <v>7259600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>148.5510669184904</v>
+        <v>150.8638042327417</v>
       </c>
       <c r="C199" t="n">
-        <v>150.2483878382925</v>
+        <v>152.213727638368</v>
       </c>
       <c r="D199" t="n">
-        <v>148.2632072518497</v>
+        <v>149.8017253482469</v>
       </c>
       <c r="E199" t="n">
-        <v>149.7421722412109</v>
+        <v>150.9134216308594</v>
       </c>
       <c r="F199" t="n">
-        <v>7259600</v>
+        <v>8618500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>150.8638042327417</v>
+        <v>150.446917666229</v>
       </c>
       <c r="C200" t="n">
-        <v>152.213727638368</v>
+        <v>151.1615687416308</v>
       </c>
       <c r="D200" t="n">
-        <v>149.8017253482469</v>
+        <v>146.7247040752409</v>
       </c>
       <c r="E200" t="n">
-        <v>150.9134216308594</v>
+        <v>147.399658203125</v>
       </c>
       <c r="F200" t="n">
-        <v>8618500</v>
+        <v>11197200</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>150.446917666229</v>
+        <v>149.226028638664</v>
       </c>
       <c r="C201" t="n">
-        <v>151.1615687416308</v>
+        <v>149.7620359058753</v>
       </c>
       <c r="D201" t="n">
-        <v>146.7247040752409</v>
+        <v>147.3202569962244</v>
       </c>
       <c r="E201" t="n">
-        <v>147.399658203125</v>
+        <v>147.9158172607422</v>
       </c>
       <c r="F201" t="n">
-        <v>11197200</v>
+        <v>16724600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>149.226028638664</v>
+        <v>147.627945424002</v>
       </c>
       <c r="C202" t="n">
-        <v>149.7620359058753</v>
+        <v>147.945581577785</v>
       </c>
       <c r="D202" t="n">
-        <v>147.3202569962244</v>
+        <v>145.9504654579339</v>
       </c>
       <c r="E202" t="n">
-        <v>147.9158172607422</v>
+        <v>147.3500213623047</v>
       </c>
       <c r="F202" t="n">
-        <v>16724600</v>
+        <v>10387700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>147.627945424002</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="C203" t="n">
-        <v>147.945581577785</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="D203" t="n">
-        <v>145.9504654579339</v>
+        <v>143.1017371059213</v>
       </c>
       <c r="E203" t="n">
-        <v>147.3500213623047</v>
+        <v>145.5534362792969</v>
       </c>
       <c r="F203" t="n">
-        <v>10387700</v>
+        <v>9353800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>146.4368410119005</v>
+        <v>145.4442602082673</v>
       </c>
       <c r="C204" t="n">
-        <v>146.4368410119005</v>
+        <v>146.4070740424418</v>
       </c>
       <c r="D204" t="n">
-        <v>143.1017371059213</v>
+        <v>144.4715259232294</v>
       </c>
       <c r="E204" t="n">
-        <v>145.5534362792969</v>
+        <v>146.3375854492188</v>
       </c>
       <c r="F204" t="n">
-        <v>9353800</v>
+        <v>9571700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>145.4442602082673</v>
+        <v>147.4790688253476</v>
       </c>
       <c r="C205" t="n">
-        <v>146.4070740424418</v>
+        <v>150.5461692222369</v>
       </c>
       <c r="D205" t="n">
-        <v>144.4715259232294</v>
+        <v>146.6452966069997</v>
       </c>
       <c r="E205" t="n">
-        <v>146.3375854492188</v>
+        <v>150.2881011962891</v>
       </c>
       <c r="F205" t="n">
-        <v>9571700</v>
+        <v>9256000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>147.4790688253476</v>
+        <v>149.5635029567411</v>
       </c>
       <c r="C206" t="n">
-        <v>150.5461692222369</v>
+        <v>150.0995102140475</v>
       </c>
       <c r="D206" t="n">
-        <v>146.6452966069997</v>
+        <v>145.8710808804345</v>
       </c>
       <c r="E206" t="n">
-        <v>150.2881011962891</v>
+        <v>148.2036590576172</v>
       </c>
       <c r="F206" t="n">
-        <v>9256000</v>
+        <v>8323100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>149.5635029567411</v>
+        <v>151.5288345729856</v>
       </c>
       <c r="C207" t="n">
-        <v>150.0995102140475</v>
+        <v>152.3526863163115</v>
       </c>
       <c r="D207" t="n">
-        <v>145.8710808804345</v>
+        <v>149.4940214860459</v>
       </c>
       <c r="E207" t="n">
-        <v>148.2036590576172</v>
+        <v>151.6181640625</v>
       </c>
       <c r="F207" t="n">
-        <v>8323100</v>
+        <v>8061400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>151.5288345729856</v>
+        <v>149.8414437624326</v>
       </c>
       <c r="C208" t="n">
-        <v>152.3526863163115</v>
+        <v>149.950629305204</v>
       </c>
       <c r="D208" t="n">
-        <v>149.4940214860459</v>
+        <v>147.2507823800627</v>
       </c>
       <c r="E208" t="n">
-        <v>151.6181640625</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F208" t="n">
-        <v>8061400</v>
+        <v>14272300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>149.8414437624326</v>
+        <v>145.6824775579256</v>
       </c>
       <c r="C209" t="n">
-        <v>149.950629305204</v>
+        <v>146.5658822886928</v>
       </c>
       <c r="D209" t="n">
-        <v>147.2507823800627</v>
+        <v>144.5211487643815</v>
       </c>
       <c r="E209" t="n">
-        <v>147.3003997802734</v>
+        <v>145.7618865966797</v>
       </c>
       <c r="F209" t="n">
-        <v>14272300</v>
+        <v>7748000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>145.6824775579256</v>
+        <v>146.0100381106733</v>
       </c>
       <c r="C210" t="n">
-        <v>146.5658822886928</v>
+        <v>147.4889879534934</v>
       </c>
       <c r="D210" t="n">
-        <v>144.5211487643815</v>
+        <v>145.6229285023594</v>
       </c>
       <c r="E210" t="n">
-        <v>145.7618865966797</v>
+        <v>145.9504699707031</v>
       </c>
       <c r="F210" t="n">
-        <v>7748000</v>
+        <v>12473000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>146.0100381106733</v>
+        <v>146.9827701076717</v>
       </c>
       <c r="C211" t="n">
-        <v>147.4889879534934</v>
+        <v>148.9381741659779</v>
       </c>
       <c r="D211" t="n">
-        <v>145.6229285023594</v>
+        <v>146.0199563268518</v>
       </c>
       <c r="E211" t="n">
-        <v>145.9504699707031</v>
+        <v>147.2706146240234</v>
       </c>
       <c r="F211" t="n">
-        <v>12473000</v>
+        <v>7816100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>146.9827701076717</v>
+        <v>147.2706141757336</v>
       </c>
       <c r="C212" t="n">
-        <v>148.9381741659779</v>
+        <v>147.6478033266625</v>
       </c>
       <c r="D212" t="n">
-        <v>146.0199563268518</v>
+        <v>144.5112144243791</v>
       </c>
       <c r="E212" t="n">
-        <v>147.2706146240234</v>
+        <v>144.9975891113281</v>
       </c>
       <c r="F212" t="n">
-        <v>7816100</v>
+        <v>7668100</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>147.2706141757336</v>
+        <v>144.2035234458952</v>
       </c>
       <c r="C213" t="n">
-        <v>147.6478033266625</v>
+        <v>147.4889950493996</v>
       </c>
       <c r="D213" t="n">
-        <v>144.5112144243791</v>
+        <v>143.5881222814616</v>
       </c>
       <c r="E213" t="n">
-        <v>144.9975891113281</v>
+        <v>146.9530029296875</v>
       </c>
       <c r="F213" t="n">
-        <v>7668100</v>
+        <v>6180000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>144.2035234458952</v>
+        <v>148.3823251540053</v>
       </c>
       <c r="C214" t="n">
-        <v>147.4889950493996</v>
+        <v>150.3972821936961</v>
       </c>
       <c r="D214" t="n">
-        <v>143.5881222814616</v>
+        <v>147.0820191757993</v>
       </c>
       <c r="E214" t="n">
-        <v>146.9530029296875</v>
+        <v>150.3774261474609</v>
       </c>
       <c r="F214" t="n">
-        <v>6180000</v>
+        <v>6485400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>148.3823251540053</v>
+        <v>151.7273476549808</v>
       </c>
       <c r="C215" t="n">
-        <v>150.3972821936961</v>
+        <v>153.1765360977979</v>
       </c>
       <c r="D215" t="n">
-        <v>147.0820191757993</v>
+        <v>148.2036492050291</v>
       </c>
       <c r="E215" t="n">
-        <v>150.3774261474609</v>
+        <v>148.8686828613281</v>
       </c>
       <c r="F215" t="n">
-        <v>6485400</v>
+        <v>8917400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>151.7273476549808</v>
+        <v>148.4518004486472</v>
       </c>
       <c r="C216" t="n">
-        <v>153.1765360977979</v>
+        <v>148.9878076836025</v>
       </c>
       <c r="D216" t="n">
-        <v>148.2036492050291</v>
+        <v>147.3301685811182</v>
       </c>
       <c r="E216" t="n">
-        <v>148.8686828613281</v>
+        <v>148.0249938964844</v>
       </c>
       <c r="F216" t="n">
-        <v>8917400</v>
+        <v>5788300</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>148.4518004486472</v>
+        <v>146.7643973953222</v>
       </c>
       <c r="C217" t="n">
-        <v>148.9878076836025</v>
+        <v>147.3103250709858</v>
       </c>
       <c r="D217" t="n">
-        <v>147.3301685811182</v>
+        <v>145.7916631750561</v>
       </c>
       <c r="E217" t="n">
-        <v>148.0249938964844</v>
+        <v>147.0026245117188</v>
       </c>
       <c r="F217" t="n">
-        <v>5788300</v>
+        <v>7027600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>146.7643973953222</v>
+        <v>148.3922474549245</v>
       </c>
       <c r="C218" t="n">
-        <v>147.3103250709858</v>
+        <v>149.3451407916641</v>
       </c>
       <c r="D218" t="n">
-        <v>145.7916631750561</v>
+        <v>147.7172933317669</v>
       </c>
       <c r="E218" t="n">
-        <v>147.0026245117188</v>
+        <v>148.0249938964844</v>
       </c>
       <c r="F218" t="n">
-        <v>7027600</v>
+        <v>5371200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>148.3922474549245</v>
+        <v>145.057144942689</v>
       </c>
       <c r="C219" t="n">
-        <v>149.3451407916641</v>
+        <v>146.5162538863596</v>
       </c>
       <c r="D219" t="n">
-        <v>147.7172933317669</v>
+        <v>144.5112172519064</v>
       </c>
       <c r="E219" t="n">
-        <v>148.0249938964844</v>
+        <v>145.8809967041016</v>
       </c>
       <c r="F219" t="n">
-        <v>5371200</v>
+        <v>6499200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,25 +6137,25 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>145.057144942689</v>
+        <v>146.4499969482422</v>
       </c>
       <c r="C220" t="n">
-        <v>146.5162538863596</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="D220" t="n">
-        <v>144.5112172519064</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E220" t="n">
-        <v>145.8809967041016</v>
+        <v>147.4100036621094</v>
       </c>
       <c r="F220" t="n">
-        <v>6499200</v>
+        <v>6620700</v>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6163,25 +6163,25 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>146.4499969482422</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C221" t="n">
-        <v>147.9900054931641</v>
+        <v>150.25</v>
       </c>
       <c r="D221" t="n">
-        <v>145.3999938964844</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="E221" t="n">
-        <v>147.4100036621094</v>
+        <v>148.6300048828125</v>
       </c>
       <c r="F221" t="n">
-        <v>6620700</v>
+        <v>7301800</v>
       </c>
       <c r="G221" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>147.8500061035156</v>
+        <v>151.5</v>
       </c>
       <c r="C222" t="n">
-        <v>150.25</v>
+        <v>153.6799926757812</v>
       </c>
       <c r="D222" t="n">
-        <v>147.8500061035156</v>
+        <v>148.5200042724609</v>
       </c>
       <c r="E222" t="n">
-        <v>148.6300048828125</v>
+        <v>148.8800048828125</v>
       </c>
       <c r="F222" t="n">
-        <v>7301800</v>
+        <v>12848800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>151.5</v>
+        <v>141.3800048828125</v>
       </c>
       <c r="C223" t="n">
-        <v>153.6799926757812</v>
+        <v>146.3800048828125</v>
       </c>
       <c r="D223" t="n">
-        <v>148.5200042724609</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="E223" t="n">
-        <v>148.8800048828125</v>
+        <v>146.1000061035156</v>
       </c>
       <c r="F223" t="n">
-        <v>12848800</v>
+        <v>14616800</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>141.3800048828125</v>
+        <v>143.7599945068359</v>
       </c>
       <c r="C224" t="n">
-        <v>146.3800048828125</v>
+        <v>144.4499969482422</v>
       </c>
       <c r="D224" t="n">
-        <v>140.1999969482422</v>
+        <v>142.25</v>
       </c>
       <c r="E224" t="n">
-        <v>146.1000061035156</v>
+        <v>143.9600067138672</v>
       </c>
       <c r="F224" t="n">
-        <v>14616800</v>
+        <v>9571100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>143.7599945068359</v>
+        <v>143.5099945068359</v>
       </c>
       <c r="C225" t="n">
-        <v>144.4499969482422</v>
+        <v>144.6999969482422</v>
       </c>
       <c r="D225" t="n">
-        <v>142.25</v>
+        <v>141.4600067138672</v>
       </c>
       <c r="E225" t="n">
-        <v>143.9600067138672</v>
+        <v>144.4900054931641</v>
       </c>
       <c r="F225" t="n">
-        <v>9571100</v>
+        <v>9152600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>143.5099945068359</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C226" t="n">
-        <v>144.6999969482422</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D226" t="n">
-        <v>141.4600067138672</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="E226" t="n">
-        <v>144.4900054931641</v>
+        <v>144.9700012207031</v>
       </c>
       <c r="F226" t="n">
-        <v>9152600</v>
+        <v>8843600</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>145.8500061035156</v>
+        <v>144.0399932861328</v>
       </c>
       <c r="C227" t="n">
-        <v>147.1499938964844</v>
+        <v>148.25</v>
       </c>
       <c r="D227" t="n">
-        <v>144.2599945068359</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E227" t="n">
-        <v>144.9700012207031</v>
+        <v>148.0099945068359</v>
       </c>
       <c r="F227" t="n">
-        <v>8843600</v>
+        <v>7362300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>144.0399932861328</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C228" t="n">
-        <v>148.25</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="D228" t="n">
-        <v>143.7899932861328</v>
+        <v>144.6600036621094</v>
       </c>
       <c r="E228" t="n">
-        <v>148.0099945068359</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="F228" t="n">
-        <v>7362300</v>
+        <v>9753300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>147.8500061035156</v>
+        <v>147.8200073242188</v>
       </c>
       <c r="C229" t="n">
-        <v>147.8500061035156</v>
+        <v>148.5</v>
       </c>
       <c r="D229" t="n">
-        <v>144.6600036621094</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="E229" t="n">
-        <v>146.8000030517578</v>
+        <v>146.9700012207031</v>
       </c>
       <c r="F229" t="n">
-        <v>9753300</v>
+        <v>8766700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>147.8200073242188</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C230" t="n">
-        <v>148.5</v>
+        <v>146</v>
       </c>
       <c r="D230" t="n">
-        <v>145.4499969482422</v>
+        <v>143.8800048828125</v>
       </c>
       <c r="E230" t="n">
-        <v>146.9700012207031</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="F230" t="n">
-        <v>8766700</v>
+        <v>7565500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>144.8999938964844</v>
+        <v>144.7299957275391</v>
       </c>
       <c r="C231" t="n">
-        <v>146</v>
+        <v>146.4600067138672</v>
       </c>
       <c r="D231" t="n">
-        <v>143.8800048828125</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="E231" t="n">
-        <v>145.7899932861328</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F231" t="n">
-        <v>7565500</v>
+        <v>7386500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>144.7299957275391</v>
+        <v>145.4100036621094</v>
       </c>
       <c r="C232" t="n">
-        <v>146.4600067138672</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="D232" t="n">
-        <v>144.1499938964844</v>
+        <v>143.9299926757812</v>
       </c>
       <c r="E232" t="n">
-        <v>146.4400024414062</v>
+        <v>145.2100067138672</v>
       </c>
       <c r="F232" t="n">
-        <v>7386500</v>
+        <v>7936700</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>145.4100036621094</v>
+        <v>144.0500030517578</v>
       </c>
       <c r="C233" t="n">
-        <v>145.7100067138672</v>
+        <v>144.9400024414062</v>
       </c>
       <c r="D233" t="n">
-        <v>143.9299926757812</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E233" t="n">
-        <v>145.2100067138672</v>
+        <v>144.0800018310547</v>
       </c>
       <c r="F233" t="n">
-        <v>7936700</v>
+        <v>7195000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>144.0500030517578</v>
+        <v>144.5899963378906</v>
       </c>
       <c r="C234" t="n">
-        <v>144.9400024414062</v>
+        <v>145.8000030517578</v>
       </c>
       <c r="D234" t="n">
-        <v>143.7899932861328</v>
+        <v>144</v>
       </c>
       <c r="E234" t="n">
-        <v>144.0800018310547</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="F234" t="n">
-        <v>7195000</v>
+        <v>7491300</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>144.5899963378906</v>
+        <v>144.3300018310547</v>
       </c>
       <c r="C235" t="n">
-        <v>145.8000030517578</v>
+        <v>144.9100036621094</v>
       </c>
       <c r="D235" t="n">
-        <v>144</v>
+        <v>143.4199981689453</v>
       </c>
       <c r="E235" t="n">
-        <v>144.2599945068359</v>
+        <v>144.5500030517578</v>
       </c>
       <c r="F235" t="n">
-        <v>7491300</v>
+        <v>7249600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>144.3300018310547</v>
+        <v>143.6399993896484</v>
       </c>
       <c r="C236" t="n">
-        <v>144.9100036621094</v>
+        <v>143.9700012207031</v>
       </c>
       <c r="D236" t="n">
-        <v>143.4199981689453</v>
+        <v>142.4799957275391</v>
       </c>
       <c r="E236" t="n">
-        <v>144.5500030517578</v>
+        <v>143.1199951171875</v>
       </c>
       <c r="F236" t="n">
-        <v>7249600</v>
+        <v>9867500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>143.6399993896484</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="C237" t="n">
-        <v>143.9700012207031</v>
+        <v>144.4199981689453</v>
       </c>
       <c r="D237" t="n">
-        <v>142.4799957275391</v>
+        <v>142.6799926757812</v>
       </c>
       <c r="E237" t="n">
-        <v>143.1199951171875</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F237" t="n">
-        <v>9867500</v>
+        <v>12746100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>143.2799987792969</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="C238" t="n">
-        <v>144.4199981689453</v>
+        <v>146.2299957275391</v>
       </c>
       <c r="D238" t="n">
-        <v>142.6799926757812</v>
+        <v>143.6199951171875</v>
       </c>
       <c r="E238" t="n">
-        <v>143.4499969482422</v>
+        <v>144.3800048828125</v>
       </c>
       <c r="F238" t="n">
-        <v>12746100</v>
+        <v>13948500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>144.3000030517578</v>
+        <v>144.4700012207031</v>
       </c>
       <c r="C239" t="n">
-        <v>146.2299957275391</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="D239" t="n">
-        <v>143.6199951171875</v>
+        <v>142.5599975585938</v>
       </c>
       <c r="E239" t="n">
-        <v>144.3800048828125</v>
+        <v>142.9700012207031</v>
       </c>
       <c r="F239" t="n">
-        <v>13948500</v>
+        <v>15794100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>144.4700012207031</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C240" t="n">
-        <v>144.9199981689453</v>
+        <v>145.2700042724609</v>
       </c>
       <c r="D240" t="n">
-        <v>142.5599975585938</v>
+        <v>142.1399993896484</v>
       </c>
       <c r="E240" t="n">
-        <v>142.9700012207031</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="F240" t="n">
-        <v>15794100</v>
+        <v>9785200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>143.0200042724609</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="C241" t="n">
-        <v>145.2700042724609</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="D241" t="n">
-        <v>142.1399993896484</v>
+        <v>145</v>
       </c>
       <c r="E241" t="n">
-        <v>144.6799926757812</v>
+        <v>146.6000061035156</v>
       </c>
       <c r="F241" t="n">
-        <v>9785200</v>
+        <v>7061800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>145.2400054931641</v>
+        <v>145.7299957275391</v>
       </c>
       <c r="C242" t="n">
-        <v>146.8000030517578</v>
+        <v>146.1199951171875</v>
       </c>
       <c r="D242" t="n">
-        <v>145</v>
+        <v>144.9499969482422</v>
       </c>
       <c r="E242" t="n">
-        <v>146.6000061035156</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F242" t="n">
-        <v>7061800</v>
+        <v>9125700</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>145.7299957275391</v>
+        <v>145.2799987792969</v>
       </c>
       <c r="C243" t="n">
-        <v>146.1199951171875</v>
+        <v>145.9299926757812</v>
       </c>
       <c r="D243" t="n">
-        <v>144.9499969482422</v>
+        <v>144.5</v>
       </c>
       <c r="E243" t="n">
-        <v>145.3999938964844</v>
+        <v>145</v>
       </c>
       <c r="F243" t="n">
-        <v>9125700</v>
+        <v>8249100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>145.2799987792969</v>
+        <v>143.6999969482422</v>
       </c>
       <c r="C244" t="n">
-        <v>145.9299926757812</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="D244" t="n">
-        <v>144.5</v>
+        <v>142.7100067138672</v>
       </c>
       <c r="E244" t="n">
-        <v>145</v>
+        <v>143.1399993896484</v>
       </c>
       <c r="F244" t="n">
-        <v>8249100</v>
+        <v>7817200</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>143.6999969482422</v>
+        <v>143.25</v>
       </c>
       <c r="C245" t="n">
-        <v>144.1499938964844</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D245" t="n">
-        <v>142.7100067138672</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="E245" t="n">
-        <v>143.1399993896484</v>
+        <v>143.7799987792969</v>
       </c>
       <c r="F245" t="n">
-        <v>7817200</v>
+        <v>5868900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>143.25</v>
+        <v>143.4400024414062</v>
       </c>
       <c r="C246" t="n">
-        <v>144.3999938964844</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D246" t="n">
-        <v>143.0099945068359</v>
+        <v>142.5</v>
       </c>
       <c r="E246" t="n">
-        <v>143.7799987792969</v>
+        <v>145.1199951171875</v>
       </c>
       <c r="F246" t="n">
-        <v>5868900</v>
+        <v>12097900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>143.4400024414062</v>
+        <v>145.7599945068359</v>
       </c>
       <c r="C247" t="n">
-        <v>145.8999938964844</v>
+        <v>148.3600006103516</v>
       </c>
       <c r="D247" t="n">
-        <v>142.5</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E247" t="n">
-        <v>145.1199951171875</v>
+        <v>146.2100067138672</v>
       </c>
       <c r="F247" t="n">
-        <v>12097900</v>
+        <v>8503800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>145.7599945068359</v>
+        <v>146.4199981689453</v>
       </c>
       <c r="C248" t="n">
-        <v>148.3600006103516</v>
+        <v>148.3200073242188</v>
       </c>
       <c r="D248" t="n">
-        <v>145.0899963378906</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="E248" t="n">
-        <v>146.2100067138672</v>
+        <v>147.6399993896484</v>
       </c>
       <c r="F248" t="n">
-        <v>8503800</v>
+        <v>7431100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>146.4199981689453</v>
+        <v>147.6799926757812</v>
       </c>
       <c r="C249" t="n">
-        <v>148.3200073242188</v>
+        <v>148.2200012207031</v>
       </c>
       <c r="D249" t="n">
-        <v>145.7899932861328</v>
+        <v>146.5</v>
       </c>
       <c r="E249" t="n">
-        <v>147.6399993896484</v>
+        <v>146.9199981689453</v>
       </c>
       <c r="F249" t="n">
-        <v>7431100</v>
+        <v>6105800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>147.6799926757812</v>
+        <v>146.4700012207031</v>
       </c>
       <c r="C250" t="n">
-        <v>148.2200012207031</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>146.5</v>
+        <v>145.8200073242188</v>
       </c>
       <c r="E250" t="n">
-        <v>146.9199981689453</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F250" t="n">
-        <v>6105800</v>
+        <v>5588200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>146.4700012207031</v>
+        <v>145.6000061035156</v>
       </c>
       <c r="C251" t="n">
-        <v>147.1499938964844</v>
+        <v>146.1600036621094</v>
       </c>
       <c r="D251" t="n">
-        <v>145.8200073242188</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="E251" t="n">
-        <v>146.4400024414062</v>
+        <v>145.5800018310547</v>
       </c>
       <c r="F251" t="n">
-        <v>5588200</v>
+        <v>8325100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>144.1600036621094</v>
+      </c>
+      <c r="C252" t="n">
+        <v>144.4700012207031</v>
+      </c>
+      <c r="D252" t="n">
+        <v>142.3399963378906</v>
+      </c>
+      <c r="E252" t="n">
+        <v>142.6399993896484</v>
+      </c>
       <c r="F252" t="n">
-        <v>8315492</v>
+        <v>9270000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10798,37 +10806,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>142.64</v>
+      </c>
+      <c r="D2" t="n">
         <v>145.58</v>
       </c>
-      <c r="D2" t="n">
-        <v>146.44</v>
-      </c>
       <c r="E2" t="n">
-        <v>145.595</v>
+        <v>144.16</v>
       </c>
       <c r="F2" t="n">
-        <v>146.15</v>
+        <v>144.16</v>
       </c>
       <c r="G2" t="n">
-        <v>144.305</v>
+        <v>142.34</v>
       </c>
       <c r="H2" t="n">
-        <v>8315492</v>
+        <v>9260540</v>
       </c>
       <c r="I2" t="n">
-        <v>8969645</v>
+        <v>8970706</v>
       </c>
       <c r="J2" t="n">
-        <v>338134663168</v>
+        <v>331305975808</v>
       </c>
       <c r="K2" t="n">
-        <v>21.990936</v>
+        <v>21.97843</v>
       </c>
       <c r="L2" t="n">
-        <v>19.673506</v>
+        <v>19.276197</v>
       </c>
       <c r="M2" t="n">
-        <v>6.62</v>
+        <v>6.49</v>
       </c>
       <c r="N2" t="n">
         <v>167.25</v>
@@ -10840,7 +10848,7 @@
         <v>0.377</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="R2" t="n">
         <v>0.18437</v>
@@ -10864,7 +10872,7 @@
         <v>22.947</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.3441844</v>
+        <v>6.216063</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.155</v>
@@ -10876,7 +10884,7 @@
         <v>87031996416</v>
       </c>
       <c r="AC2" t="n">
-        <v>364459950080</v>
+        <v>357626118144</v>
       </c>
       <c r="AD2" t="n">
         <v>24752001024</v>
@@ -10903,7 +10911,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:25</t>
+          <t>2026-09-10 18:59:42</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>154.0693331751388</v>
+        <v>153.2144571291697</v>
       </c>
       <c r="C2" t="n">
-        <v>154.3996169522188</v>
+        <v>154.7978981087861</v>
       </c>
       <c r="D2" t="n">
-        <v>151.4367423098323</v>
+        <v>152.8938823700691</v>
       </c>
       <c r="E2" t="n">
-        <v>152.8550415039062</v>
+        <v>154.0984649658203</v>
       </c>
       <c r="F2" t="n">
-        <v>6205500</v>
+        <v>5819500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>153.2144723004245</v>
+        <v>153.4184545574236</v>
       </c>
       <c r="C3" t="n">
-        <v>154.7979134368329</v>
+        <v>154.5841863803252</v>
       </c>
       <c r="D3" t="n">
-        <v>152.8938975095807</v>
+        <v>153.2727454910088</v>
       </c>
       <c r="E3" t="n">
-        <v>154.0984802246094</v>
+        <v>153.3893127441406</v>
       </c>
       <c r="F3" t="n">
-        <v>5819500</v>
+        <v>5957000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>153.4184698191116</v>
+        <v>153.3699073091056</v>
       </c>
       <c r="C4" t="n">
-        <v>154.5842017579773</v>
+        <v>153.9916240815438</v>
       </c>
       <c r="D4" t="n">
-        <v>153.272760738202</v>
+        <v>151.7378915171447</v>
       </c>
       <c r="E4" t="n">
-        <v>153.3893280029297</v>
+        <v>152.3498992919922</v>
       </c>
       <c r="F4" t="n">
-        <v>5957000</v>
+        <v>5995000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>153.3699073091056</v>
+        <v>152.6510263298436</v>
       </c>
       <c r="C5" t="n">
-        <v>153.9916240815438</v>
+        <v>153.865317940213</v>
       </c>
       <c r="D5" t="n">
-        <v>151.7378915171447</v>
+        <v>152.4081680077697</v>
       </c>
       <c r="E5" t="n">
-        <v>152.3498992919922</v>
+        <v>153.5350341796875</v>
       </c>
       <c r="F5" t="n">
-        <v>5995000</v>
+        <v>6559600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>152.6510263298436</v>
+        <v>153.9041762162224</v>
       </c>
       <c r="C6" t="n">
-        <v>153.865317940213</v>
+        <v>157.0516255592386</v>
       </c>
       <c r="D6" t="n">
-        <v>152.4081680077697</v>
+        <v>153.9041762162224</v>
       </c>
       <c r="E6" t="n">
-        <v>153.5350341796875</v>
+        <v>155.7499084472656</v>
       </c>
       <c r="F6" t="n">
-        <v>6559600</v>
+        <v>6764200</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>153.9041762162224</v>
+        <v>153.6321891685915</v>
       </c>
       <c r="C7" t="n">
-        <v>157.0516255592386</v>
+        <v>154.4773463220477</v>
       </c>
       <c r="D7" t="n">
-        <v>153.9041762162224</v>
+        <v>152.670479571169</v>
       </c>
       <c r="E7" t="n">
-        <v>155.7499084472656</v>
+        <v>152.8259124755859</v>
       </c>
       <c r="F7" t="n">
-        <v>6764200</v>
+        <v>7651500</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>153.6321891685915</v>
+        <v>153.1076006094224</v>
       </c>
       <c r="C8" t="n">
-        <v>154.4773463220477</v>
+        <v>153.1173096060279</v>
       </c>
       <c r="D8" t="n">
-        <v>152.670479571169</v>
+        <v>151.5144506152748</v>
       </c>
       <c r="E8" t="n">
-        <v>152.8259124755859</v>
+        <v>151.5824432373047</v>
       </c>
       <c r="F8" t="n">
-        <v>7651500</v>
+        <v>17224800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>153.1076006094224</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="C9" t="n">
-        <v>153.1173096060279</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="D9" t="n">
-        <v>151.5144506152748</v>
+        <v>148.677863326978</v>
       </c>
       <c r="E9" t="n">
-        <v>151.5824432373047</v>
+        <v>148.6972961425781</v>
       </c>
       <c r="F9" t="n">
-        <v>17224800</v>
+        <v>8712900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>151.6213049173507</v>
+        <v>148.8235702535947</v>
       </c>
       <c r="C10" t="n">
-        <v>151.6213049173507</v>
+        <v>148.9109956881993</v>
       </c>
       <c r="D10" t="n">
-        <v>148.677863326978</v>
+        <v>146.65727826643</v>
       </c>
       <c r="E10" t="n">
-        <v>148.6972961425781</v>
+        <v>148.1435699462891</v>
       </c>
       <c r="F10" t="n">
-        <v>8712900</v>
+        <v>8853400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>148.8235855824238</v>
+        <v>147.7064465894999</v>
       </c>
       <c r="C11" t="n">
-        <v>148.9110110260332</v>
+        <v>149.2413130899007</v>
       </c>
       <c r="D11" t="n">
-        <v>146.657293372131</v>
+        <v>147.4538644271308</v>
       </c>
       <c r="E11" t="n">
-        <v>148.1435852050781</v>
+        <v>148.0658721923828</v>
       </c>
       <c r="F11" t="n">
-        <v>8853400</v>
+        <v>6483300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>147.7064465894999</v>
+        <v>148.8527387391331</v>
       </c>
       <c r="C12" t="n">
-        <v>149.2413130899007</v>
+        <v>149.4841793556296</v>
       </c>
       <c r="D12" t="n">
-        <v>147.4538644271308</v>
+        <v>147.4441632452525</v>
       </c>
       <c r="E12" t="n">
-        <v>148.0658721923828</v>
+        <v>147.8035888671875</v>
       </c>
       <c r="F12" t="n">
-        <v>6483300</v>
+        <v>7511400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>148.852723372033</v>
+        <v>147.8812788195801</v>
       </c>
       <c r="C13" t="n">
-        <v>149.4841639233416</v>
+        <v>148.3184208154984</v>
       </c>
       <c r="D13" t="n">
-        <v>147.4441480235695</v>
+        <v>147.2012785122745</v>
       </c>
       <c r="E13" t="n">
-        <v>147.8035736083984</v>
+        <v>148.1435699462891</v>
       </c>
       <c r="F13" t="n">
-        <v>7511400</v>
+        <v>5721100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>147.8812940513532</v>
+        <v>148.0658733987316</v>
       </c>
       <c r="C14" t="n">
-        <v>148.3184360922971</v>
+        <v>149.3287397521754</v>
       </c>
       <c r="D14" t="n">
-        <v>147.2012936740075</v>
+        <v>147.4538656284933</v>
       </c>
       <c r="E14" t="n">
-        <v>148.1435852050781</v>
+        <v>149.1441650390625</v>
       </c>
       <c r="F14" t="n">
-        <v>5721100</v>
+        <v>8139700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>148.0658733987316</v>
+        <v>149.0761670451376</v>
       </c>
       <c r="C15" t="n">
-        <v>149.3287397521754</v>
+        <v>149.9698839401892</v>
       </c>
       <c r="D15" t="n">
-        <v>147.4538656284933</v>
+        <v>148.4738682940947</v>
       </c>
       <c r="E15" t="n">
-        <v>149.1441650390625</v>
+        <v>149.2607269287109</v>
       </c>
       <c r="F15" t="n">
-        <v>8139700</v>
+        <v>7762600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>149.0761670451376</v>
+        <v>149.3093029348087</v>
       </c>
       <c r="C16" t="n">
-        <v>149.9698839401892</v>
+        <v>149.4938776429776</v>
       </c>
       <c r="D16" t="n">
-        <v>148.4738682940947</v>
+        <v>147.0847270853178</v>
       </c>
       <c r="E16" t="n">
-        <v>149.2607269287109</v>
+        <v>148.8041534423828</v>
       </c>
       <c r="F16" t="n">
-        <v>7762600</v>
+        <v>7566000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>149.3092876242202</v>
+        <v>148.3573100151862</v>
       </c>
       <c r="C17" t="n">
-        <v>149.4938623134623</v>
+        <v>148.4350264659241</v>
       </c>
       <c r="D17" t="n">
-        <v>147.0847120028435</v>
+        <v>147.2984511668146</v>
       </c>
       <c r="E17" t="n">
-        <v>148.8041381835938</v>
+        <v>147.7064514160156</v>
       </c>
       <c r="F17" t="n">
-        <v>7566000</v>
+        <v>6892100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>148.3572946891603</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="C18" t="n">
-        <v>148.4350111318697</v>
+        <v>149.0470174793467</v>
       </c>
       <c r="D18" t="n">
-        <v>147.2984359501739</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="E18" t="n">
-        <v>147.7064361572266</v>
+        <v>147.920166015625</v>
       </c>
       <c r="F18" t="n">
-        <v>6892100</v>
+        <v>5212600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>147.6578596189441</v>
+        <v>147.1721399535571</v>
       </c>
       <c r="C19" t="n">
-        <v>149.0470021043167</v>
+        <v>147.9687223475034</v>
       </c>
       <c r="D19" t="n">
-        <v>147.6578596189441</v>
+        <v>146.1035574306768</v>
       </c>
       <c r="E19" t="n">
-        <v>147.9201507568359</v>
+        <v>146.11328125</v>
       </c>
       <c r="F19" t="n">
-        <v>5212600</v>
+        <v>6737000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>147.1721553229241</v>
+        <v>146.4532839352596</v>
       </c>
       <c r="C20" t="n">
-        <v>147.9687378000585</v>
+        <v>148.7944418250997</v>
       </c>
       <c r="D20" t="n">
-        <v>146.1035726884504</v>
+        <v>145.7635745697061</v>
       </c>
       <c r="E20" t="n">
-        <v>146.1132965087891</v>
+        <v>148.1824340820312</v>
       </c>
       <c r="F20" t="n">
-        <v>6737000</v>
+        <v>6844400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>146.4532839352596</v>
+        <v>148.4252854332665</v>
       </c>
       <c r="C21" t="n">
-        <v>148.7944418250997</v>
+        <v>148.4252854332665</v>
       </c>
       <c r="D21" t="n">
-        <v>145.7635745697061</v>
+        <v>146.3270007982578</v>
       </c>
       <c r="E21" t="n">
-        <v>148.1824340820312</v>
+        <v>146.3852844238281</v>
       </c>
       <c r="F21" t="n">
-        <v>6844400</v>
+        <v>5254700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>148.4252854332665</v>
+        <v>146.4338752834919</v>
       </c>
       <c r="C22" t="n">
-        <v>148.4252854332665</v>
+        <v>146.5601515452587</v>
       </c>
       <c r="D22" t="n">
-        <v>146.3270007982578</v>
+        <v>145.3070089879124</v>
       </c>
       <c r="E22" t="n">
-        <v>146.3852844238281</v>
+        <v>146.2784423828125</v>
       </c>
       <c r="F22" t="n">
-        <v>5254700</v>
+        <v>6134500</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>146.4338752834919</v>
+        <v>146.6281558533259</v>
       </c>
       <c r="C23" t="n">
-        <v>146.5601515452587</v>
+        <v>147.1818651686376</v>
       </c>
       <c r="D23" t="n">
-        <v>145.3070089879124</v>
+        <v>145.1807147897232</v>
       </c>
       <c r="E23" t="n">
-        <v>146.2784423828125</v>
+        <v>145.4138641357422</v>
       </c>
       <c r="F23" t="n">
-        <v>6134500</v>
+        <v>7374000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>146.6281712395348</v>
+        <v>144.7435618289234</v>
       </c>
       <c r="C24" t="n">
-        <v>147.1818806129492</v>
+        <v>145.1612710333055</v>
       </c>
       <c r="D24" t="n">
-        <v>145.1807300240471</v>
+        <v>142.7715534139986</v>
       </c>
       <c r="E24" t="n">
-        <v>145.4138793945312</v>
+        <v>143.2767028808594</v>
       </c>
       <c r="F24" t="n">
-        <v>7374000</v>
+        <v>7511100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>144.7435618289234</v>
+        <v>143.3544266058526</v>
       </c>
       <c r="C25" t="n">
-        <v>145.1612710333055</v>
+        <v>144.9864275192193</v>
       </c>
       <c r="D25" t="n">
-        <v>142.7715534139986</v>
+        <v>142.8784189280057</v>
       </c>
       <c r="E25" t="n">
-        <v>143.2767028808594</v>
+        <v>144.8990020751953</v>
       </c>
       <c r="F25" t="n">
-        <v>7511100</v>
+        <v>8585300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>143.3544266058526</v>
+        <v>144.2869860075292</v>
       </c>
       <c r="C26" t="n">
-        <v>144.9864275192193</v>
+        <v>145.1418520497865</v>
       </c>
       <c r="D26" t="n">
-        <v>142.8784189280057</v>
+        <v>143.0629853930302</v>
       </c>
       <c r="E26" t="n">
-        <v>144.8990020751953</v>
+        <v>143.2086944580078</v>
       </c>
       <c r="F26" t="n">
-        <v>8585300</v>
+        <v>10003100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>144.2870013812095</v>
+        <v>143.7818259264451</v>
       </c>
       <c r="C27" t="n">
-        <v>145.1418675145521</v>
+        <v>146.1035507353118</v>
       </c>
       <c r="D27" t="n">
-        <v>143.0630006362941</v>
+        <v>143.6944004939145</v>
       </c>
       <c r="E27" t="n">
-        <v>143.2087097167969</v>
+        <v>145.326416015625</v>
       </c>
       <c r="F27" t="n">
-        <v>10003100</v>
+        <v>8809700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>143.7818561196696</v>
+        <v>146.2687203464973</v>
       </c>
       <c r="C28" t="n">
-        <v>146.103581416083</v>
+        <v>147.6870046758011</v>
       </c>
       <c r="D28" t="n">
-        <v>143.6944306687803</v>
+        <v>146.1327054533545</v>
       </c>
       <c r="E28" t="n">
-        <v>145.3264465332031</v>
+        <v>147.0749969482422</v>
       </c>
       <c r="F28" t="n">
-        <v>8809700</v>
+        <v>8612900</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>146.2687051713582</v>
+        <v>147.2595781352121</v>
       </c>
       <c r="C29" t="n">
-        <v>147.6869893535173</v>
+        <v>148.0367277806686</v>
       </c>
       <c r="D29" t="n">
-        <v>146.1326902923267</v>
+        <v>146.9778689854687</v>
       </c>
       <c r="E29" t="n">
-        <v>147.0749816894531</v>
+        <v>147.6190185546875</v>
       </c>
       <c r="F29" t="n">
-        <v>8612900</v>
+        <v>5601300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>147.259562913577</v>
+        <v>147.6189948407767</v>
       </c>
       <c r="C30" t="n">
-        <v>148.0367124787026</v>
+        <v>147.9298457552854</v>
       </c>
       <c r="D30" t="n">
-        <v>146.9778537929527</v>
+        <v>146.5601213927804</v>
       </c>
       <c r="E30" t="n">
-        <v>147.6190032958984</v>
+        <v>147.2886962890625</v>
       </c>
       <c r="F30" t="n">
-        <v>5601300</v>
+        <v>6013400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>147.6189948407767</v>
+        <v>146.9778583106544</v>
       </c>
       <c r="C31" t="n">
-        <v>147.9298457552854</v>
+        <v>149.076157754121</v>
       </c>
       <c r="D31" t="n">
-        <v>146.5601213927804</v>
+        <v>146.4824178509246</v>
       </c>
       <c r="E31" t="n">
-        <v>147.2886962890625</v>
+        <v>147.8521423339844</v>
       </c>
       <c r="F31" t="n">
-        <v>6013400</v>
+        <v>6394400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>146.9778583106544</v>
+        <v>147.9978622453251</v>
       </c>
       <c r="C32" t="n">
-        <v>149.076157754121</v>
+        <v>148.9207208724779</v>
       </c>
       <c r="D32" t="n">
-        <v>146.4824178509246</v>
+        <v>146.2784212345297</v>
       </c>
       <c r="E32" t="n">
-        <v>147.8521423339844</v>
+        <v>147.8618621826172</v>
       </c>
       <c r="F32" t="n">
-        <v>6394400</v>
+        <v>8205400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,25 +1275,25 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>147.9978775181488</v>
+        <v>152.9946080342638</v>
       </c>
       <c r="C33" t="n">
-        <v>148.9207362405373</v>
+        <v>153.9728344665201</v>
       </c>
       <c r="D33" t="n">
-        <v>146.2784363299136</v>
+        <v>148.2306500856719</v>
       </c>
       <c r="E33" t="n">
-        <v>147.8618774414062</v>
+        <v>149.1697540283203</v>
       </c>
       <c r="F33" t="n">
-        <v>8205400</v>
+        <v>11968500</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1301,25 +1301,25 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>152.9946080342638</v>
+        <v>148.3089219684464</v>
       </c>
       <c r="C34" t="n">
-        <v>153.9728344665201</v>
+        <v>148.4556499745139</v>
       </c>
       <c r="D34" t="n">
-        <v>148.2306500856719</v>
+        <v>146.8611509112235</v>
       </c>
       <c r="E34" t="n">
-        <v>149.1697540283203</v>
+        <v>148.4360961914062</v>
       </c>
       <c r="F34" t="n">
-        <v>11968500</v>
+        <v>7775300</v>
       </c>
       <c r="G34" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>148.3089372141624</v>
+        <v>147.8295858278712</v>
       </c>
       <c r="C35" t="n">
-        <v>148.4556652353131</v>
+        <v>149.8349531642864</v>
       </c>
       <c r="D35" t="n">
-        <v>146.8611660081129</v>
+        <v>147.3404725715042</v>
       </c>
       <c r="E35" t="n">
-        <v>148.4361114501953</v>
+        <v>148.0741424560547</v>
       </c>
       <c r="F35" t="n">
-        <v>7775300</v>
+        <v>5819300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>147.8295858278712</v>
+        <v>147.3795937684592</v>
       </c>
       <c r="C36" t="n">
-        <v>149.8349531642864</v>
+        <v>147.6828415657792</v>
       </c>
       <c r="D36" t="n">
-        <v>147.3404725715042</v>
+        <v>145.2372755531334</v>
       </c>
       <c r="E36" t="n">
-        <v>148.0741424560547</v>
+        <v>145.5307464599609</v>
       </c>
       <c r="F36" t="n">
-        <v>5819300</v>
+        <v>7405500</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>147.3795937684592</v>
+        <v>146.2155146062609</v>
       </c>
       <c r="C37" t="n">
-        <v>147.6828415657792</v>
+        <v>147.5165576287185</v>
       </c>
       <c r="D37" t="n">
-        <v>145.2372755531334</v>
+        <v>146.0883403861062</v>
       </c>
       <c r="E37" t="n">
-        <v>145.5307464599609</v>
+        <v>146.3231201171875</v>
       </c>
       <c r="F37" t="n">
-        <v>7405500</v>
+        <v>6760700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>146.2155298538287</v>
+        <v>145.4720720722042</v>
       </c>
       <c r="C38" t="n">
-        <v>147.516573011961</v>
+        <v>147.8100328533669</v>
       </c>
       <c r="D38" t="n">
-        <v>146.0883556204121</v>
+        <v>145.2959835371417</v>
       </c>
       <c r="E38" t="n">
-        <v>146.3231353759766</v>
+        <v>147.0959167480469</v>
       </c>
       <c r="F38" t="n">
-        <v>6760700</v>
+        <v>7930300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>145.4720720722042</v>
+        <v>146.8318015049148</v>
       </c>
       <c r="C39" t="n">
-        <v>147.8100328533669</v>
+        <v>146.9491839067269</v>
       </c>
       <c r="D39" t="n">
-        <v>145.2959835371417</v>
+        <v>144.5525320015707</v>
       </c>
       <c r="E39" t="n">
-        <v>147.0959167480469</v>
+        <v>144.7970886230469</v>
       </c>
       <c r="F39" t="n">
-        <v>7930300</v>
+        <v>8946400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>146.8318015049148</v>
+        <v>145.3644630798614</v>
       </c>
       <c r="C40" t="n">
-        <v>146.9491839067269</v>
+        <v>146.2448609544514</v>
       </c>
       <c r="D40" t="n">
-        <v>144.5525320015707</v>
+        <v>143.0656248467459</v>
       </c>
       <c r="E40" t="n">
-        <v>144.7970886230469</v>
+        <v>143.9655914306641</v>
       </c>
       <c r="F40" t="n">
-        <v>8946400</v>
+        <v>9295400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>145.3644630798614</v>
+        <v>143.6721174868199</v>
       </c>
       <c r="C41" t="n">
-        <v>146.2448609544514</v>
+        <v>144.210145032931</v>
       </c>
       <c r="D41" t="n">
-        <v>143.0656248467459</v>
+        <v>142.478679994192</v>
       </c>
       <c r="E41" t="n">
-        <v>143.9655914306641</v>
+        <v>142.6156311035156</v>
       </c>
       <c r="F41" t="n">
-        <v>9295400</v>
+        <v>11199900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>143.6721174868199</v>
+        <v>142.703685564269</v>
       </c>
       <c r="C42" t="n">
-        <v>144.210145032931</v>
+        <v>143.4862548173669</v>
       </c>
       <c r="D42" t="n">
-        <v>142.478679994192</v>
+        <v>141.3146057355029</v>
       </c>
       <c r="E42" t="n">
-        <v>142.6156311035156</v>
+        <v>142.9482421875</v>
       </c>
       <c r="F42" t="n">
-        <v>11199900</v>
+        <v>10024500</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>142.7036703315847</v>
+        <v>143.7503785207628</v>
       </c>
       <c r="C43" t="n">
-        <v>143.4862395011485</v>
+        <v>144.7188281113408</v>
       </c>
       <c r="D43" t="n">
-        <v>141.3145906510938</v>
+        <v>142.8210663483271</v>
       </c>
       <c r="E43" t="n">
-        <v>142.9482269287109</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F43" t="n">
-        <v>10024500</v>
+        <v>8500100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>143.7503785207628</v>
+        <v>143.192783696673</v>
       </c>
       <c r="C44" t="n">
-        <v>144.7188281113408</v>
+        <v>143.4275484772021</v>
       </c>
       <c r="D44" t="n">
-        <v>142.8210663483271</v>
+        <v>140.9526369054562</v>
       </c>
       <c r="E44" t="n">
-        <v>143.7797241210938</v>
+        <v>142.3319396972656</v>
       </c>
       <c r="F44" t="n">
-        <v>8500100</v>
+        <v>10208100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>143.1927990477494</v>
+        <v>142.7819444175452</v>
       </c>
       <c r="C45" t="n">
-        <v>143.4275638534467</v>
+        <v>145.4133611257213</v>
       </c>
       <c r="D45" t="n">
-        <v>140.9526520163762</v>
+        <v>142.4982503778291</v>
       </c>
       <c r="E45" t="n">
-        <v>142.3319549560547</v>
+        <v>145.3057556152344</v>
       </c>
       <c r="F45" t="n">
-        <v>10208100</v>
+        <v>7332500</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>142.7819444175452</v>
+        <v>145.2959744173796</v>
       </c>
       <c r="C46" t="n">
-        <v>145.4133611257213</v>
+        <v>145.9024700440282</v>
       </c>
       <c r="D46" t="n">
-        <v>142.4982503778291</v>
+        <v>144.298179252126</v>
       </c>
       <c r="E46" t="n">
-        <v>145.3057556152344</v>
+        <v>144.7872924804688</v>
       </c>
       <c r="F46" t="n">
-        <v>7332500</v>
+        <v>7851100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>145.2959744173796</v>
+        <v>144.9535841420777</v>
       </c>
       <c r="C47" t="n">
-        <v>145.9024700440282</v>
+        <v>145.7557369733869</v>
       </c>
       <c r="D47" t="n">
-        <v>144.298179252126</v>
+        <v>144.4253484415343</v>
       </c>
       <c r="E47" t="n">
-        <v>144.7872924804688</v>
+        <v>144.7383880615234</v>
       </c>
       <c r="F47" t="n">
-        <v>7851100</v>
+        <v>7566800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>144.9535841420777</v>
+        <v>145.8535682267802</v>
       </c>
       <c r="C48" t="n">
-        <v>145.7557369733869</v>
+        <v>146.1274704359541</v>
       </c>
       <c r="D48" t="n">
-        <v>144.4253484415343</v>
+        <v>144.3960054571006</v>
       </c>
       <c r="E48" t="n">
-        <v>144.7383880615234</v>
+        <v>144.4546966552734</v>
       </c>
       <c r="F48" t="n">
-        <v>7566800</v>
+        <v>9150800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>145.8535682267802</v>
+        <v>144.5329589094707</v>
       </c>
       <c r="C49" t="n">
-        <v>146.1274704359541</v>
+        <v>144.7579468149716</v>
       </c>
       <c r="D49" t="n">
-        <v>144.3960054571006</v>
+        <v>141.8526130458145</v>
       </c>
       <c r="E49" t="n">
-        <v>144.4546966552734</v>
+        <v>142.6449890136719</v>
       </c>
       <c r="F49" t="n">
-        <v>9150800</v>
+        <v>9902300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>144.5329589094707</v>
+        <v>143.1438719935926</v>
       </c>
       <c r="C50" t="n">
-        <v>144.7579468149716</v>
+        <v>144.1807895972433</v>
       </c>
       <c r="D50" t="n">
-        <v>141.8526130458145</v>
+        <v>142.341719174738</v>
       </c>
       <c r="E50" t="n">
-        <v>142.6449890136719</v>
+        <v>143.7895050048828</v>
       </c>
       <c r="F50" t="n">
-        <v>9902300</v>
+        <v>10735200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>143.1438871838678</v>
+        <v>143.7601594067833</v>
       </c>
       <c r="C51" t="n">
-        <v>144.1808048975551</v>
+        <v>144.3275175877409</v>
       </c>
       <c r="D51" t="n">
-        <v>142.3417342798896</v>
+        <v>142.6841043879663</v>
       </c>
       <c r="E51" t="n">
-        <v>143.7895202636719</v>
+        <v>143.7895050048828</v>
       </c>
       <c r="F51" t="n">
-        <v>10735200</v>
+        <v>6367000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>143.7601746624582</v>
+        <v>143.4471249350237</v>
       </c>
       <c r="C52" t="n">
-        <v>144.3275329036233</v>
+        <v>145.4231465283615</v>
       </c>
       <c r="D52" t="n">
-        <v>142.6841195294514</v>
+        <v>142.9482348228936</v>
       </c>
       <c r="E52" t="n">
-        <v>143.7895202636719</v>
+        <v>144.96337890625</v>
       </c>
       <c r="F52" t="n">
-        <v>6367000</v>
+        <v>9021300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>143.4471249350237</v>
+        <v>145.1492529070371</v>
       </c>
       <c r="C53" t="n">
-        <v>145.4231465283615</v>
+        <v>148.2013148118135</v>
       </c>
       <c r="D53" t="n">
-        <v>142.9482348228936</v>
+        <v>145.0709929958182</v>
       </c>
       <c r="E53" t="n">
-        <v>144.96337890625</v>
+        <v>147.6339416503906</v>
       </c>
       <c r="F53" t="n">
-        <v>9021300</v>
+        <v>12018000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>145.1492529070371</v>
+        <v>146.8318008944829</v>
       </c>
       <c r="C54" t="n">
-        <v>148.2013148118135</v>
+        <v>147.1350487156044</v>
       </c>
       <c r="D54" t="n">
-        <v>145.0709929958182</v>
+        <v>143.3493020808368</v>
       </c>
       <c r="E54" t="n">
-        <v>147.6339416503906</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F54" t="n">
-        <v>12018000</v>
+        <v>13846900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>146.8318008944829</v>
+        <v>144.1123129003486</v>
       </c>
       <c r="C55" t="n">
-        <v>147.1350487156044</v>
+        <v>145.4133408091634</v>
       </c>
       <c r="D55" t="n">
-        <v>143.3493020808368</v>
+        <v>144.0144842948282</v>
       </c>
       <c r="E55" t="n">
-        <v>143.7797241210938</v>
+        <v>145.2568359375</v>
       </c>
       <c r="F55" t="n">
-        <v>13846900</v>
+        <v>10477700</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>144.112328038909</v>
+        <v>144.6992477048879</v>
       </c>
       <c r="C56" t="n">
-        <v>145.4133560843928</v>
+        <v>145.7263884130947</v>
       </c>
       <c r="D56" t="n">
-        <v>144.0144994231119</v>
+        <v>144.3959999082808</v>
       </c>
       <c r="E56" t="n">
-        <v>145.2568511962891</v>
+        <v>145.0220642089844</v>
       </c>
       <c r="F56" t="n">
-        <v>10477700</v>
+        <v>9238500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>144.6992629297112</v>
+        <v>144.5818741313487</v>
       </c>
       <c r="C57" t="n">
-        <v>145.7264037459907</v>
+        <v>145.4720637945254</v>
       </c>
       <c r="D57" t="n">
-        <v>144.3960151011972</v>
+        <v>143.9753635745919</v>
       </c>
       <c r="E57" t="n">
-        <v>145.0220794677734</v>
+        <v>144.9340362548828</v>
       </c>
       <c r="F57" t="n">
-        <v>9238500</v>
+        <v>4707200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>144.5818741313487</v>
+        <v>144.8753541574702</v>
       </c>
       <c r="C58" t="n">
-        <v>145.4720637945254</v>
+        <v>145.6481465436537</v>
       </c>
       <c r="D58" t="n">
-        <v>143.9753635745919</v>
+        <v>144.1416842645591</v>
       </c>
       <c r="E58" t="n">
-        <v>144.9340362548828</v>
+        <v>144.2297210693359</v>
       </c>
       <c r="F58" t="n">
-        <v>4707200</v>
+        <v>8240700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>144.8753541574702</v>
+        <v>142.1265162999446</v>
       </c>
       <c r="C59" t="n">
-        <v>145.6481465436537</v>
+        <v>143.0069290729368</v>
       </c>
       <c r="D59" t="n">
-        <v>144.1416842645591</v>
+        <v>139.4070479258121</v>
       </c>
       <c r="E59" t="n">
-        <v>144.2297210693359</v>
+        <v>142.6841125488281</v>
       </c>
       <c r="F59" t="n">
-        <v>8240700</v>
+        <v>16376800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>142.1265314991037</v>
+        <v>142.7428024831051</v>
       </c>
       <c r="C60" t="n">
-        <v>143.0069443662482</v>
+        <v>145.0611944043203</v>
       </c>
       <c r="D60" t="n">
-        <v>139.4070628341484</v>
+        <v>142.6841112840695</v>
       </c>
       <c r="E60" t="n">
-        <v>142.6841278076172</v>
+        <v>143.5156097412109</v>
       </c>
       <c r="F60" t="n">
-        <v>16376800</v>
+        <v>9125300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>142.7428024831051</v>
+        <v>143.4764816751874</v>
       </c>
       <c r="C61" t="n">
-        <v>145.0611944043203</v>
+        <v>144.210151564052</v>
       </c>
       <c r="D61" t="n">
-        <v>142.6841112840695</v>
+        <v>141.3537319212585</v>
       </c>
       <c r="E61" t="n">
-        <v>143.5156097412109</v>
+        <v>142.1950073242188</v>
       </c>
       <c r="F61" t="n">
-        <v>9125300</v>
+        <v>10479300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>143.47649707149</v>
+        <v>141.999373131105</v>
       </c>
       <c r="C62" t="n">
-        <v>144.210167039084</v>
+        <v>142.4591408152259</v>
       </c>
       <c r="D62" t="n">
-        <v>141.3537470897712</v>
+        <v>140.1309567915122</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1950225830078</v>
+        <v>140.3265991210938</v>
       </c>
       <c r="F62" t="n">
-        <v>10479300</v>
+        <v>12791700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>141.9993576904224</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="C63" t="n">
-        <v>142.4591253245491</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="D63" t="n">
-        <v>140.1309415539968</v>
+        <v>135.1322080272313</v>
       </c>
       <c r="E63" t="n">
-        <v>140.3265838623047</v>
+        <v>135.3278503417969</v>
       </c>
       <c r="F63" t="n">
-        <v>12791700</v>
+        <v>17507500</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>139.7983526087064</v>
+        <v>136.1593454188843</v>
       </c>
       <c r="C64" t="n">
-        <v>139.7983526087064</v>
+        <v>137.8125505495836</v>
       </c>
       <c r="D64" t="n">
-        <v>135.1322080272313</v>
+        <v>135.9734800004196</v>
       </c>
       <c r="E64" t="n">
-        <v>135.3278503417969</v>
+        <v>136.5897674560547</v>
       </c>
       <c r="F64" t="n">
-        <v>17507500</v>
+        <v>10375700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>136.1593454188843</v>
+        <v>136.6093231272403</v>
       </c>
       <c r="C65" t="n">
-        <v>137.8125505495836</v>
+        <v>138.2038370797448</v>
       </c>
       <c r="D65" t="n">
-        <v>135.9734800004196</v>
+        <v>136.5017176164599</v>
       </c>
       <c r="E65" t="n">
-        <v>136.5897674560547</v>
+        <v>136.775634765625</v>
       </c>
       <c r="F65" t="n">
-        <v>10375700</v>
+        <v>13650400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>136.6093231272403</v>
+        <v>137.9299396510316</v>
       </c>
       <c r="C66" t="n">
-        <v>138.2038370797448</v>
+        <v>138.7516463474312</v>
       </c>
       <c r="D66" t="n">
-        <v>136.5017176164599</v>
+        <v>137.3038752737911</v>
       </c>
       <c r="E66" t="n">
-        <v>136.775634765625</v>
+        <v>137.6951599121094</v>
       </c>
       <c r="F66" t="n">
-        <v>13650400</v>
+        <v>11798000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>137.9299396510316</v>
+        <v>137.929925366103</v>
       </c>
       <c r="C67" t="n">
-        <v>138.7516463474312</v>
+        <v>139.9939837115514</v>
       </c>
       <c r="D67" t="n">
-        <v>137.3038752737911</v>
+        <v>137.7734055563651</v>
       </c>
       <c r="E67" t="n">
-        <v>137.6951599121094</v>
+        <v>139.7298583984375</v>
       </c>
       <c r="F67" t="n">
-        <v>11798000</v>
+        <v>10268800</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>137.9299404283357</v>
+        <v>140.1504995323008</v>
       </c>
       <c r="C68" t="n">
-        <v>139.9939989991835</v>
+        <v>142.155866623658</v>
       </c>
       <c r="D68" t="n">
-        <v>137.7734206015055</v>
+        <v>140.0820165200331</v>
       </c>
       <c r="E68" t="n">
-        <v>139.7298736572266</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F68" t="n">
-        <v>10268800</v>
+        <v>13877700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>140.1504995323008</v>
+        <v>142.918884457557</v>
       </c>
       <c r="C69" t="n">
-        <v>142.155866623658</v>
+        <v>143.3492915396123</v>
       </c>
       <c r="D69" t="n">
-        <v>140.0820165200331</v>
+        <v>141.5004442219562</v>
       </c>
       <c r="E69" t="n">
-        <v>141.9700012207031</v>
+        <v>142.0482635498047</v>
       </c>
       <c r="F69" t="n">
-        <v>13877700</v>
+        <v>10251700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>142.918899809868</v>
+        <v>143.496050619897</v>
       </c>
       <c r="C70" t="n">
-        <v>143.3493069381574</v>
+        <v>145.2177239216924</v>
       </c>
       <c r="D70" t="n">
-        <v>141.5004594218987</v>
+        <v>143.2612708815172</v>
       </c>
       <c r="E70" t="n">
-        <v>142.0482788085938</v>
+        <v>144.5916595458984</v>
       </c>
       <c r="F70" t="n">
-        <v>10251700</v>
+        <v>9833300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>143.496050619897</v>
+        <v>143.4275568592265</v>
       </c>
       <c r="C71" t="n">
-        <v>145.2177239216924</v>
+        <v>144.2884009089423</v>
       </c>
       <c r="D71" t="n">
-        <v>143.2612708815172</v>
+        <v>142.1852200188561</v>
       </c>
       <c r="E71" t="n">
-        <v>144.5916595458984</v>
+        <v>142.3515167236328</v>
       </c>
       <c r="F71" t="n">
-        <v>9833300</v>
+        <v>12239900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>143.4275568592265</v>
+        <v>142.3417162193598</v>
       </c>
       <c r="C72" t="n">
-        <v>144.2884009089423</v>
+        <v>142.8699668272841</v>
       </c>
       <c r="D72" t="n">
-        <v>142.1852200188561</v>
+        <v>140.8059085533541</v>
       </c>
       <c r="E72" t="n">
-        <v>142.3515167236328</v>
+        <v>141.3145904541016</v>
       </c>
       <c r="F72" t="n">
-        <v>12239900</v>
+        <v>19345600</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>142.3417162193598</v>
+        <v>140.5809250079643</v>
       </c>
       <c r="C73" t="n">
-        <v>142.8699668272841</v>
+        <v>141.2558886976474</v>
       </c>
       <c r="D73" t="n">
-        <v>140.8059085533541</v>
+        <v>139.3190045706883</v>
       </c>
       <c r="E73" t="n">
-        <v>141.3145904541016</v>
+        <v>139.5831298828125</v>
       </c>
       <c r="F73" t="n">
-        <v>19345600</v>
+        <v>11731400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>140.5809250079643</v>
+        <v>139.387490519737</v>
       </c>
       <c r="C74" t="n">
-        <v>141.2558886976474</v>
+        <v>140.6004817498258</v>
       </c>
       <c r="D74" t="n">
-        <v>139.3190045706883</v>
+        <v>138.9864140977976</v>
       </c>
       <c r="E74" t="n">
-        <v>139.5831298828125</v>
+        <v>140.0624542236328</v>
       </c>
       <c r="F74" t="n">
-        <v>11731400</v>
+        <v>9541600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>139.387490519737</v>
+        <v>139.7885720199097</v>
       </c>
       <c r="C75" t="n">
-        <v>140.6004817498258</v>
+        <v>141.5885202675369</v>
       </c>
       <c r="D75" t="n">
-        <v>138.9864140977976</v>
+        <v>139.72010392126</v>
       </c>
       <c r="E75" t="n">
-        <v>140.0624542236328</v>
+        <v>141.3439636230469</v>
       </c>
       <c r="F75" t="n">
-        <v>9541600</v>
+        <v>3259200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>139.7885720199097</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="C76" t="n">
-        <v>141.5885202675369</v>
+        <v>142.4688988061542</v>
       </c>
       <c r="D76" t="n">
-        <v>139.72010392126</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="E76" t="n">
-        <v>141.3439636230469</v>
+        <v>141.5885009765625</v>
       </c>
       <c r="F76" t="n">
-        <v>3259200</v>
+        <v>4711500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>141.1678558435435</v>
+        <v>141.6471833233528</v>
       </c>
       <c r="C77" t="n">
-        <v>142.4688988061542</v>
+        <v>141.9113086263453</v>
       </c>
       <c r="D77" t="n">
-        <v>141.1678558435435</v>
+        <v>140.8156849267153</v>
       </c>
       <c r="E77" t="n">
-        <v>141.5885009765625</v>
+        <v>141.4221954345703</v>
       </c>
       <c r="F77" t="n">
-        <v>4711500</v>
+        <v>7662100</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>141.6471833233528</v>
+        <v>141.1482779620671</v>
       </c>
       <c r="C78" t="n">
-        <v>141.9113086263453</v>
+        <v>141.3145895822191</v>
       </c>
       <c r="D78" t="n">
-        <v>140.8156849267153</v>
+        <v>140.443968700097</v>
       </c>
       <c r="E78" t="n">
-        <v>141.4221954345703</v>
+        <v>140.9135131835938</v>
       </c>
       <c r="F78" t="n">
-        <v>7662100</v>
+        <v>6006400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>141.1482932462777</v>
+        <v>140.8646148984387</v>
       </c>
       <c r="C79" t="n">
-        <v>141.3146048844386</v>
+        <v>141.0015660103057</v>
       </c>
       <c r="D79" t="n">
-        <v>140.4439839080415</v>
+        <v>140.1113763198945</v>
       </c>
       <c r="E79" t="n">
-        <v>140.9135284423828</v>
+        <v>140.1896362304688</v>
       </c>
       <c r="F79" t="n">
-        <v>6006400</v>
+        <v>5293200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>140.8646302306951</v>
+        <v>139.9939944106823</v>
       </c>
       <c r="C80" t="n">
-        <v>141.0015813574684</v>
+        <v>140.2189823252813</v>
       </c>
       <c r="D80" t="n">
-        <v>140.1113915701655</v>
+        <v>138.164715640037</v>
       </c>
       <c r="E80" t="n">
-        <v>140.1896514892578</v>
+        <v>138.7027282714844</v>
       </c>
       <c r="F80" t="n">
-        <v>5293200</v>
+        <v>8946100</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>139.9939944106823</v>
+        <v>138.0277758154179</v>
       </c>
       <c r="C81" t="n">
-        <v>140.2189823252813</v>
+        <v>138.2723324593669</v>
       </c>
       <c r="D81" t="n">
-        <v>138.164715640037</v>
+        <v>136.5604359517241</v>
       </c>
       <c r="E81" t="n">
-        <v>138.7027282714844</v>
+        <v>137.3136596679688</v>
       </c>
       <c r="F81" t="n">
-        <v>8946100</v>
+        <v>12297300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>138.0277758154179</v>
+        <v>137.333222535484</v>
       </c>
       <c r="C82" t="n">
-        <v>138.2723324593669</v>
+        <v>138.340794671558</v>
       </c>
       <c r="D82" t="n">
-        <v>136.5604359517241</v>
+        <v>136.472378408915</v>
       </c>
       <c r="E82" t="n">
-        <v>137.3136596679688</v>
+        <v>136.8636779785156</v>
       </c>
       <c r="F82" t="n">
-        <v>12297300</v>
+        <v>10421800</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>137.3332072243459</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="C83" t="n">
-        <v>138.3407792480867</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="D83" t="n">
-        <v>136.4723631937515</v>
+        <v>134.6235247173271</v>
       </c>
       <c r="E83" t="n">
-        <v>136.8636627197266</v>
+        <v>135.0343780517578</v>
       </c>
       <c r="F83" t="n">
-        <v>10421800</v>
+        <v>14369100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>136.7560662263838</v>
+        <v>134.8876360609042</v>
       </c>
       <c r="C84" t="n">
-        <v>136.7560662263838</v>
+        <v>138.6929361136317</v>
       </c>
       <c r="D84" t="n">
-        <v>134.6235247173271</v>
+        <v>134.8191679755417</v>
       </c>
       <c r="E84" t="n">
-        <v>135.0343780517578</v>
+        <v>138.4483795166016</v>
       </c>
       <c r="F84" t="n">
-        <v>14369100</v>
+        <v>9297100</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>134.8876360609042</v>
+        <v>138.6146938845888</v>
       </c>
       <c r="C85" t="n">
-        <v>138.6929361136317</v>
+        <v>139.2309813641768</v>
       </c>
       <c r="D85" t="n">
-        <v>134.8191679755417</v>
+        <v>137.7636415949117</v>
       </c>
       <c r="E85" t="n">
-        <v>138.4483795166016</v>
+        <v>138.7809906005859</v>
       </c>
       <c r="F85" t="n">
-        <v>9297100</v>
+        <v>9528500</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>138.6146938845888</v>
+        <v>139.1820649751552</v>
       </c>
       <c r="C86" t="n">
-        <v>139.2309813641768</v>
+        <v>140.7472333429565</v>
       </c>
       <c r="D86" t="n">
-        <v>137.7636415949117</v>
+        <v>138.6244836329666</v>
       </c>
       <c r="E86" t="n">
-        <v>138.7809906005859</v>
+        <v>140.3363800048828</v>
       </c>
       <c r="F86" t="n">
-        <v>9528500</v>
+        <v>12812000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>139.1820498418749</v>
+        <v>140.8646007849644</v>
       </c>
       <c r="C87" t="n">
-        <v>140.7472180394953</v>
+        <v>141.1971941766679</v>
       </c>
       <c r="D87" t="n">
-        <v>138.6244685603122</v>
+        <v>139.8570287929182</v>
       </c>
       <c r="E87" t="n">
-        <v>140.3363647460938</v>
+        <v>141.0993804931641</v>
       </c>
       <c r="F87" t="n">
-        <v>12812000</v>
+        <v>15549200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>140.8646007849644</v>
+        <v>141.5298158666727</v>
       </c>
       <c r="C88" t="n">
-        <v>141.1971941766679</v>
+        <v>143.7014800904468</v>
       </c>
       <c r="D88" t="n">
-        <v>139.8570287929182</v>
+        <v>141.2265680120421</v>
       </c>
       <c r="E88" t="n">
-        <v>141.0993804931641</v>
+        <v>143.1634674072266</v>
       </c>
       <c r="F88" t="n">
-        <v>15549200</v>
+        <v>13475000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>141.529800782003</v>
+        <v>142.5080218255822</v>
       </c>
       <c r="C89" t="n">
-        <v>143.7014647743148</v>
+        <v>143.1634466813173</v>
       </c>
       <c r="D89" t="n">
-        <v>141.2265529596936</v>
+        <v>141.20699378469</v>
       </c>
       <c r="E89" t="n">
-        <v>143.1634521484375</v>
+        <v>141.4808959960938</v>
       </c>
       <c r="F89" t="n">
-        <v>13475000</v>
+        <v>10102800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>142.5080218255822</v>
+        <v>140.6298333307039</v>
       </c>
       <c r="C90" t="n">
-        <v>143.1634466813173</v>
+        <v>141.5787142100195</v>
       </c>
       <c r="D90" t="n">
-        <v>141.20699378469</v>
+        <v>140.5320196386769</v>
       </c>
       <c r="E90" t="n">
-        <v>141.4808959960938</v>
+        <v>141.3830718994141</v>
       </c>
       <c r="F90" t="n">
-        <v>10102800</v>
+        <v>11729300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>140.6298333307039</v>
+        <v>141.314612307562</v>
       </c>
       <c r="C91" t="n">
-        <v>141.5787142100195</v>
+        <v>143.7993011474609</v>
       </c>
       <c r="D91" t="n">
-        <v>140.5320196386769</v>
+        <v>140.98200394032</v>
       </c>
       <c r="E91" t="n">
-        <v>141.3830718994141</v>
+        <v>143.7993011474609</v>
       </c>
       <c r="F91" t="n">
-        <v>11729300</v>
+        <v>12901400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>141.3145973124275</v>
+        <v>143.8579872458876</v>
       </c>
       <c r="C92" t="n">
-        <v>143.7992858886719</v>
+        <v>144.1612350737863</v>
       </c>
       <c r="D92" t="n">
-        <v>140.9819889804792</v>
+        <v>141.8134974355268</v>
       </c>
       <c r="E92" t="n">
-        <v>143.7992858886719</v>
+        <v>142.8797607421875</v>
       </c>
       <c r="F92" t="n">
-        <v>12901400</v>
+        <v>14126800</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>143.8579872458876</v>
+        <v>144.8557716267987</v>
       </c>
       <c r="C93" t="n">
-        <v>144.1612350737863</v>
+        <v>147.6241542164368</v>
       </c>
       <c r="D93" t="n">
-        <v>141.8134974355268</v>
+        <v>144.2883985058945</v>
       </c>
       <c r="E93" t="n">
-        <v>142.8797607421875</v>
+        <v>146.6654815673828</v>
       </c>
       <c r="F93" t="n">
-        <v>14126800</v>
+        <v>18501900</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,25 +2861,25 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>144.8557716267987</v>
+        <v>148.6033244770038</v>
       </c>
       <c r="C94" t="n">
-        <v>147.6241542164368</v>
+        <v>149.401311303758</v>
       </c>
       <c r="D94" t="n">
-        <v>144.2883985058945</v>
+        <v>147.5787523243573</v>
       </c>
       <c r="E94" t="n">
-        <v>146.6654815673828</v>
+        <v>147.9235534667969</v>
       </c>
       <c r="F94" t="n">
-        <v>18501900</v>
+        <v>14562600</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -2887,25 +2887,25 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>148.6033244770038</v>
+        <v>147.8940093166009</v>
       </c>
       <c r="C95" t="n">
-        <v>149.401311303758</v>
+        <v>148.642749624448</v>
       </c>
       <c r="D95" t="n">
-        <v>147.5787523243573</v>
+        <v>146.3177432055359</v>
       </c>
       <c r="E95" t="n">
-        <v>147.9235534667969</v>
+        <v>147.2733612060547</v>
       </c>
       <c r="F95" t="n">
-        <v>14562600</v>
+        <v>12655700</v>
       </c>
       <c r="G95" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>147.8940093166009</v>
+        <v>145.8744105284403</v>
       </c>
       <c r="C96" t="n">
-        <v>148.642749624448</v>
+        <v>147.4211225953709</v>
       </c>
       <c r="D96" t="n">
-        <v>146.3177432055359</v>
+        <v>145.7364720311358</v>
       </c>
       <c r="E96" t="n">
-        <v>147.2733612060547</v>
+        <v>146.1403961181641</v>
       </c>
       <c r="F96" t="n">
-        <v>12655700</v>
+        <v>9546000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>145.8744105284403</v>
+        <v>145.8054447387209</v>
       </c>
       <c r="C97" t="n">
-        <v>147.4211225953709</v>
+        <v>146.5049234190107</v>
       </c>
       <c r="D97" t="n">
-        <v>145.7364720311358</v>
+        <v>144.613380096476</v>
       </c>
       <c r="E97" t="n">
-        <v>146.1403961181641</v>
+        <v>145.1552276611328</v>
       </c>
       <c r="F97" t="n">
-        <v>9546000</v>
+        <v>7465800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>145.8054447387209</v>
+        <v>145.1059620999764</v>
       </c>
       <c r="C98" t="n">
-        <v>146.5049234190107</v>
+        <v>147.9038617122788</v>
       </c>
       <c r="D98" t="n">
-        <v>144.613380096476</v>
+        <v>144.9286383741246</v>
       </c>
       <c r="E98" t="n">
-        <v>145.1552276611328</v>
+        <v>147.6772613525391</v>
       </c>
       <c r="F98" t="n">
-        <v>7465800</v>
+        <v>11035600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>145.1059620999764</v>
+        <v>148.1994047112546</v>
       </c>
       <c r="C99" t="n">
-        <v>147.9038617122788</v>
+        <v>149.7165778862847</v>
       </c>
       <c r="D99" t="n">
-        <v>144.9286383741246</v>
+        <v>146.9383858562462</v>
       </c>
       <c r="E99" t="n">
-        <v>147.6772613525391</v>
+        <v>149.5195465087891</v>
       </c>
       <c r="F99" t="n">
-        <v>11035600</v>
+        <v>12651400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1994047112546</v>
+        <v>150.1599009677594</v>
       </c>
       <c r="C100" t="n">
-        <v>149.7165778862847</v>
+        <v>151.4504737667986</v>
       </c>
       <c r="D100" t="n">
-        <v>146.9383858562462</v>
+        <v>149.0072516350481</v>
       </c>
       <c r="E100" t="n">
-        <v>149.5195465087891</v>
+        <v>150.9184875488281</v>
       </c>
       <c r="F100" t="n">
-        <v>12651400</v>
+        <v>10554900</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>150.1599009677594</v>
+        <v>150.3273766276017</v>
       </c>
       <c r="C101" t="n">
-        <v>151.4504737667986</v>
+        <v>154.2089563191786</v>
       </c>
       <c r="D101" t="n">
-        <v>149.0072516350481</v>
+        <v>149.9431601878661</v>
       </c>
       <c r="E101" t="n">
-        <v>150.9184875488281</v>
+        <v>153.0169067382812</v>
       </c>
       <c r="F101" t="n">
-        <v>10554900</v>
+        <v>12424700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>150.3273766276017</v>
+        <v>153.8148971925123</v>
       </c>
       <c r="C102" t="n">
-        <v>154.2089563191786</v>
+        <v>156.0216726798457</v>
       </c>
       <c r="D102" t="n">
-        <v>149.9431601878661</v>
+        <v>153.450373358777</v>
       </c>
       <c r="E102" t="n">
-        <v>153.0169067382812</v>
+        <v>154.5439147949219</v>
       </c>
       <c r="F102" t="n">
-        <v>12424700</v>
+        <v>12178500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>153.8148971925123</v>
+        <v>156.4847030065954</v>
       </c>
       <c r="C103" t="n">
-        <v>156.0216726798457</v>
+        <v>157.2826898506833</v>
       </c>
       <c r="D103" t="n">
-        <v>153.450373358777</v>
+        <v>153.8050342014295</v>
       </c>
       <c r="E103" t="n">
-        <v>154.5439147949219</v>
+        <v>156.2581176757812</v>
       </c>
       <c r="F103" t="n">
-        <v>12178500</v>
+        <v>13077700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>156.4847030065954</v>
+        <v>155.8935966032756</v>
       </c>
       <c r="C104" t="n">
-        <v>157.2826898506833</v>
+        <v>157.6176473147596</v>
       </c>
       <c r="D104" t="n">
-        <v>153.8050342014295</v>
+        <v>155.6669962577738</v>
       </c>
       <c r="E104" t="n">
-        <v>156.2581176757812</v>
+        <v>156.8097991943359</v>
       </c>
       <c r="F104" t="n">
-        <v>13077700</v>
+        <v>10441700</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>155.8935966032756</v>
+        <v>156.4058894678126</v>
       </c>
       <c r="C105" t="n">
-        <v>157.6176473147596</v>
+        <v>156.9181830781391</v>
       </c>
       <c r="D105" t="n">
-        <v>155.6669962577738</v>
+        <v>153.7065280129841</v>
       </c>
       <c r="E105" t="n">
-        <v>156.8097991943359</v>
+        <v>154.9971008300781</v>
       </c>
       <c r="F105" t="n">
-        <v>10441700</v>
+        <v>11439900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>156.4058894678126</v>
+        <v>155.1941261981174</v>
       </c>
       <c r="C106" t="n">
-        <v>156.9181830781391</v>
+        <v>157.7752717323398</v>
       </c>
       <c r="D106" t="n">
-        <v>153.7065280129841</v>
+        <v>154.3961393746382</v>
       </c>
       <c r="E106" t="n">
-        <v>154.9971008300781</v>
+        <v>156.7211456298828</v>
       </c>
       <c r="F106" t="n">
-        <v>11439900</v>
+        <v>9910100</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>155.1941261981174</v>
+        <v>156.2876680693531</v>
       </c>
       <c r="C107" t="n">
-        <v>157.7752717323398</v>
+        <v>158.7505977950001</v>
       </c>
       <c r="D107" t="n">
-        <v>154.3961393746382</v>
+        <v>155.8443437252427</v>
       </c>
       <c r="E107" t="n">
-        <v>156.7211456298828</v>
+        <v>157.6275024414062</v>
       </c>
       <c r="F107" t="n">
-        <v>9910100</v>
+        <v>10217300</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>156.2876680693531</v>
+        <v>157.6472078811371</v>
       </c>
       <c r="C108" t="n">
-        <v>158.7505977950001</v>
+        <v>160.7209393253002</v>
       </c>
       <c r="D108" t="n">
-        <v>155.8443437252427</v>
+        <v>157.2826840647245</v>
       </c>
       <c r="E108" t="n">
-        <v>157.6275024414062</v>
+        <v>158.8195648193359</v>
       </c>
       <c r="F108" t="n">
-        <v>10217300</v>
+        <v>13512900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>157.6472078811371</v>
+        <v>159.3417228437737</v>
       </c>
       <c r="C109" t="n">
-        <v>160.7209393253002</v>
+        <v>160.1594173981944</v>
       </c>
       <c r="D109" t="n">
-        <v>157.2826840647245</v>
+        <v>157.3418249095697</v>
       </c>
       <c r="E109" t="n">
-        <v>158.8195648193359</v>
+        <v>157.6964874267578</v>
       </c>
       <c r="F109" t="n">
-        <v>13512900</v>
+        <v>13998900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>159.3417228437737</v>
+        <v>157.5782363157609</v>
       </c>
       <c r="C110" t="n">
-        <v>160.1594173981944</v>
+        <v>159.765319051939</v>
       </c>
       <c r="D110" t="n">
-        <v>157.3418249095697</v>
+        <v>156.5241102403673</v>
       </c>
       <c r="E110" t="n">
-        <v>157.6964874267578</v>
+        <v>157.1841735839844</v>
       </c>
       <c r="F110" t="n">
-        <v>13998900</v>
+        <v>13319100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>157.5782363157609</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="C111" t="n">
-        <v>159.765319051939</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="D111" t="n">
-        <v>156.5241102403673</v>
+        <v>153.4602390569104</v>
       </c>
       <c r="E111" t="n">
-        <v>157.1841735839844</v>
+        <v>154.5340728759766</v>
       </c>
       <c r="F111" t="n">
-        <v>13319100</v>
+        <v>14434300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>156.6226326022383</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="C112" t="n">
-        <v>156.6226326022383</v>
+        <v>157.588096663496</v>
       </c>
       <c r="D112" t="n">
-        <v>153.4602390569104</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="E112" t="n">
-        <v>154.5340728759766</v>
+        <v>156.2088470458984</v>
       </c>
       <c r="F112" t="n">
-        <v>14434300</v>
+        <v>10724600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>154.5045039445223</v>
+        <v>156.7704074552917</v>
       </c>
       <c r="C113" t="n">
-        <v>157.588096663496</v>
+        <v>158.6717819848204</v>
       </c>
       <c r="D113" t="n">
-        <v>154.5045039445223</v>
+        <v>155.8147895206744</v>
       </c>
       <c r="E113" t="n">
-        <v>156.2088470458984</v>
+        <v>158.3959350585938</v>
       </c>
       <c r="F113" t="n">
-        <v>10724600</v>
+        <v>11508100</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>156.7704074552917</v>
+        <v>157.9427805830092</v>
       </c>
       <c r="C114" t="n">
-        <v>158.6717819848204</v>
+        <v>162.9080407961134</v>
       </c>
       <c r="D114" t="n">
-        <v>155.8147895206744</v>
+        <v>157.9230729341091</v>
       </c>
       <c r="E114" t="n">
-        <v>158.3959350585938</v>
+        <v>162.7208557128906</v>
       </c>
       <c r="F114" t="n">
-        <v>11508100</v>
+        <v>14772400</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>157.9427805830092</v>
+        <v>162.4548534700461</v>
       </c>
       <c r="C115" t="n">
-        <v>162.9080407961134</v>
+        <v>164.3956434730223</v>
       </c>
       <c r="D115" t="n">
-        <v>157.9230729341091</v>
+        <v>161.509096787574</v>
       </c>
       <c r="E115" t="n">
-        <v>162.7208557128906</v>
+        <v>162.8292236328125</v>
       </c>
       <c r="F115" t="n">
-        <v>14772400</v>
+        <v>9709500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>162.4548534700461</v>
+        <v>162.1001810746762</v>
       </c>
       <c r="C116" t="n">
-        <v>164.3956434730223</v>
+        <v>162.5533667721119</v>
       </c>
       <c r="D116" t="n">
-        <v>161.509096787574</v>
+        <v>159.6963742176143</v>
       </c>
       <c r="E116" t="n">
-        <v>162.8292236328125</v>
+        <v>160.9672393798828</v>
       </c>
       <c r="F116" t="n">
-        <v>9709500</v>
+        <v>7878500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>162.1001810746762</v>
+        <v>161.7849314119297</v>
       </c>
       <c r="C117" t="n">
-        <v>162.5533667721119</v>
+        <v>162.0607783426765</v>
       </c>
       <c r="D117" t="n">
-        <v>159.6963742176143</v>
+        <v>160.4450970200751</v>
       </c>
       <c r="E117" t="n">
-        <v>160.9672393798828</v>
+        <v>161.3218994140625</v>
       </c>
       <c r="F117" t="n">
-        <v>7878500</v>
+        <v>7028600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>161.7849314119297</v>
+        <v>161.6075869258529</v>
       </c>
       <c r="C118" t="n">
-        <v>162.0607783426765</v>
+        <v>164.7699952425796</v>
       </c>
       <c r="D118" t="n">
-        <v>160.4450970200751</v>
+        <v>161.262785790902</v>
       </c>
       <c r="E118" t="n">
-        <v>161.3218994140625</v>
+        <v>164.7207336425781</v>
       </c>
       <c r="F118" t="n">
-        <v>7028600</v>
+        <v>14878500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>161.6075869258529</v>
+        <v>162.8390693932343</v>
       </c>
       <c r="C119" t="n">
-        <v>164.7699952425796</v>
+        <v>164.0803957045348</v>
       </c>
       <c r="D119" t="n">
-        <v>161.262785790902</v>
+        <v>161.0263565641498</v>
       </c>
       <c r="E119" t="n">
-        <v>164.7207336425781</v>
+        <v>161.0854644775391</v>
       </c>
       <c r="F119" t="n">
-        <v>14878500</v>
+        <v>9095500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>162.8390693932343</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="C120" t="n">
-        <v>164.0803957045348</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="D120" t="n">
-        <v>161.0263565641498</v>
+        <v>156.2679589705066</v>
       </c>
       <c r="E120" t="n">
-        <v>161.0854644775391</v>
+        <v>157.3516540527344</v>
       </c>
       <c r="F120" t="n">
-        <v>9095500</v>
+        <v>10161000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>159.7850298016668</v>
+        <v>157.0758237333674</v>
       </c>
       <c r="C121" t="n">
-        <v>159.7850298016668</v>
+        <v>157.243301166956</v>
       </c>
       <c r="D121" t="n">
-        <v>156.2679589705066</v>
+        <v>154.9774025943761</v>
       </c>
       <c r="E121" t="n">
-        <v>157.3516540527344</v>
+        <v>155.9527282714844</v>
       </c>
       <c r="F121" t="n">
-        <v>10161000</v>
+        <v>8752700</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>157.0758237333674</v>
+        <v>154.6128887776175</v>
       </c>
       <c r="C122" t="n">
-        <v>157.243301166956</v>
+        <v>154.7705198979749</v>
       </c>
       <c r="D122" t="n">
-        <v>154.9774025943761</v>
+        <v>151.4898954891258</v>
       </c>
       <c r="E122" t="n">
-        <v>155.9527282714844</v>
+        <v>151.7066345214844</v>
       </c>
       <c r="F122" t="n">
-        <v>8752700</v>
+        <v>10060300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>154.6128887776175</v>
+        <v>151.3815284437877</v>
       </c>
       <c r="C123" t="n">
-        <v>154.7705198979749</v>
+        <v>152.1401000368933</v>
       </c>
       <c r="D123" t="n">
-        <v>151.4898954891258</v>
+        <v>149.6377698486339</v>
       </c>
       <c r="E123" t="n">
-        <v>151.7066345214844</v>
+        <v>151.3519744873047</v>
       </c>
       <c r="F123" t="n">
-        <v>10060300</v>
+        <v>8187900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>151.3815284437877</v>
+        <v>150.8790677258081</v>
       </c>
       <c r="C124" t="n">
-        <v>152.1401000368933</v>
+        <v>153.9133989264833</v>
       </c>
       <c r="D124" t="n">
-        <v>149.6377698486339</v>
+        <v>150.6327747552909</v>
       </c>
       <c r="E124" t="n">
-        <v>151.3519744873047</v>
+        <v>152.9183807373047</v>
       </c>
       <c r="F124" t="n">
-        <v>8187900</v>
+        <v>12494900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>150.8790677258081</v>
+        <v>153.1843919415674</v>
       </c>
       <c r="C125" t="n">
-        <v>153.9133989264833</v>
+        <v>154.8197659541039</v>
       </c>
       <c r="D125" t="n">
-        <v>150.6327747552909</v>
+        <v>151.3224175570726</v>
       </c>
       <c r="E125" t="n">
-        <v>152.9183807373047</v>
+        <v>153.6966705322266</v>
       </c>
       <c r="F125" t="n">
-        <v>12494900</v>
+        <v>7756800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>153.1843919415674</v>
+        <v>152.9282368144603</v>
       </c>
       <c r="C126" t="n">
-        <v>154.8197659541039</v>
+        <v>153.07602162573</v>
       </c>
       <c r="D126" t="n">
-        <v>151.3224175570726</v>
+        <v>149.1845804169242</v>
       </c>
       <c r="E126" t="n">
-        <v>153.6966705322266</v>
+        <v>151.0465698242188</v>
       </c>
       <c r="F126" t="n">
-        <v>7756800</v>
+        <v>8855100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>152.9282368144603</v>
+        <v>149.9530221525258</v>
       </c>
       <c r="C127" t="n">
-        <v>153.07602162573</v>
+        <v>150.7805629442461</v>
       </c>
       <c r="D127" t="n">
-        <v>149.1845804169242</v>
+        <v>148.100894162221</v>
       </c>
       <c r="E127" t="n">
-        <v>151.0465698242188</v>
+        <v>148.2683715820312</v>
       </c>
       <c r="F127" t="n">
-        <v>8855100</v>
+        <v>8489300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>149.9530221525258</v>
+        <v>149.1254779831649</v>
       </c>
       <c r="C128" t="n">
-        <v>150.7805629442461</v>
+        <v>150.2879887378921</v>
       </c>
       <c r="D128" t="n">
-        <v>148.100894162221</v>
+        <v>147.9531209203371</v>
       </c>
       <c r="E128" t="n">
-        <v>148.2683715820312</v>
+        <v>148.4161529541016</v>
       </c>
       <c r="F128" t="n">
-        <v>8489300</v>
+        <v>7298900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>149.1254779831649</v>
+        <v>149.6082100748309</v>
       </c>
       <c r="C129" t="n">
-        <v>150.2879887378921</v>
+        <v>150.3766429785721</v>
       </c>
       <c r="D129" t="n">
-        <v>147.9531209203371</v>
+        <v>148.4161454237534</v>
       </c>
       <c r="E129" t="n">
-        <v>148.4161529541016</v>
+        <v>149.8643493652344</v>
       </c>
       <c r="F129" t="n">
-        <v>7298900</v>
+        <v>6944000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>149.6082100748309</v>
+        <v>150.7411528047512</v>
       </c>
       <c r="C130" t="n">
-        <v>150.3766429785721</v>
+        <v>151.184492202826</v>
       </c>
       <c r="D130" t="n">
-        <v>148.4161454237534</v>
+        <v>148.9579940023762</v>
       </c>
       <c r="E130" t="n">
-        <v>149.8643493652344</v>
+        <v>149.2338409423828</v>
       </c>
       <c r="F130" t="n">
-        <v>6944000</v>
+        <v>6147700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>150.7411528047512</v>
+        <v>147.0960143427481</v>
       </c>
       <c r="C131" t="n">
-        <v>151.184492202826</v>
+        <v>147.4014152272885</v>
       </c>
       <c r="D131" t="n">
-        <v>148.9579940023762</v>
+        <v>144.2882834404146</v>
       </c>
       <c r="E131" t="n">
-        <v>149.2338409423828</v>
+        <v>144.5345764160156</v>
       </c>
       <c r="F131" t="n">
-        <v>6147700</v>
+        <v>10059300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>147.0960143427481</v>
+        <v>144.0518332623683</v>
       </c>
       <c r="C132" t="n">
-        <v>147.4014152272885</v>
+        <v>145.1946362491204</v>
       </c>
       <c r="D132" t="n">
-        <v>144.2882834404146</v>
+        <v>142.6430296593396</v>
       </c>
       <c r="E132" t="n">
-        <v>144.5345764160156</v>
+        <v>142.6922912597656</v>
       </c>
       <c r="F132" t="n">
-        <v>10059300</v>
+        <v>10340300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>144.0518332623683</v>
+        <v>142.8400884498559</v>
       </c>
       <c r="C133" t="n">
-        <v>145.1946362491204</v>
+        <v>143.6577829837524</v>
       </c>
       <c r="D133" t="n">
-        <v>142.6430296593396</v>
+        <v>142.111055784898</v>
       </c>
       <c r="E133" t="n">
-        <v>142.6922912597656</v>
+        <v>142.1406097412109</v>
       </c>
       <c r="F133" t="n">
-        <v>10340300</v>
+        <v>60620900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>142.8400884498559</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="C134" t="n">
-        <v>143.6577829837524</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="D134" t="n">
-        <v>142.111055784898</v>
+        <v>141.3524721007716</v>
       </c>
       <c r="E134" t="n">
-        <v>142.1406097412109</v>
+        <v>141.8549194335938</v>
       </c>
       <c r="F134" t="n">
-        <v>60620900</v>
+        <v>10315600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>143.9828794949957</v>
+        <v>141.2046936096272</v>
       </c>
       <c r="C135" t="n">
-        <v>143.9828794949957</v>
+        <v>143.0765142514037</v>
       </c>
       <c r="D135" t="n">
-        <v>141.3524721007716</v>
+        <v>140.1209984806846</v>
       </c>
       <c r="E135" t="n">
-        <v>141.8549194335938</v>
+        <v>141.0372161865234</v>
       </c>
       <c r="F135" t="n">
-        <v>10315600</v>
+        <v>8567600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>141.2046936096272</v>
+        <v>141.6086259660596</v>
       </c>
       <c r="C136" t="n">
-        <v>143.0765142514037</v>
+        <v>141.9632884805344</v>
       </c>
       <c r="D136" t="n">
-        <v>140.1209984806846</v>
+        <v>140.1210066538726</v>
       </c>
       <c r="E136" t="n">
-        <v>141.0372161865234</v>
+        <v>141.7859497070312</v>
       </c>
       <c r="F136" t="n">
-        <v>8567600</v>
+        <v>8418100</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>141.6086259660596</v>
+        <v>141.559369693648</v>
       </c>
       <c r="C137" t="n">
-        <v>141.9632884805344</v>
+        <v>142.4263258800331</v>
       </c>
       <c r="D137" t="n">
-        <v>140.1210066538726</v>
+        <v>140.1308732738322</v>
       </c>
       <c r="E137" t="n">
-        <v>141.7859497070312</v>
+        <v>140.3081970214844</v>
       </c>
       <c r="F137" t="n">
-        <v>8418100</v>
+        <v>6443200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>141.559369693648</v>
+        <v>140.603748896169</v>
       </c>
       <c r="C138" t="n">
-        <v>142.4263258800331</v>
+        <v>141.9435834160748</v>
       </c>
       <c r="D138" t="n">
-        <v>140.1308732738322</v>
+        <v>139.9042701625835</v>
       </c>
       <c r="E138" t="n">
-        <v>140.3081970214844</v>
+        <v>140.5939025878906</v>
       </c>
       <c r="F138" t="n">
-        <v>6443200</v>
+        <v>11558300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>140.603748896169</v>
+        <v>140.9189847788946</v>
       </c>
       <c r="C139" t="n">
-        <v>141.9435834160748</v>
+        <v>143.4114835656516</v>
       </c>
       <c r="D139" t="n">
-        <v>139.9042701625835</v>
+        <v>140.4559678065659</v>
       </c>
       <c r="E139" t="n">
-        <v>140.5939025878906</v>
+        <v>142.5740814208984</v>
       </c>
       <c r="F139" t="n">
-        <v>11558300</v>
+        <v>11616300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>140.9189847788946</v>
+        <v>142.6726031682958</v>
       </c>
       <c r="C140" t="n">
-        <v>143.4114835656516</v>
+        <v>142.7711113397407</v>
       </c>
       <c r="D140" t="n">
-        <v>140.4559678065659</v>
+        <v>140.1702580996175</v>
       </c>
       <c r="E140" t="n">
-        <v>142.5740814208984</v>
+        <v>142.2982330322266</v>
       </c>
       <c r="F140" t="n">
-        <v>11616300</v>
+        <v>10407500</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>142.6726031682958</v>
+        <v>141.7859527393269</v>
       </c>
       <c r="C141" t="n">
-        <v>142.7711113397407</v>
+        <v>142.8203863480455</v>
       </c>
       <c r="D141" t="n">
-        <v>140.1702580996175</v>
+        <v>141.0864890360487</v>
       </c>
       <c r="E141" t="n">
-        <v>142.2982330322266</v>
+        <v>141.9534301757812</v>
       </c>
       <c r="F141" t="n">
-        <v>10407500</v>
+        <v>8061700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>141.7859527393269</v>
+        <v>141.9534207153344</v>
       </c>
       <c r="C142" t="n">
-        <v>142.8203863480455</v>
+        <v>142.0716515698294</v>
       </c>
       <c r="D142" t="n">
-        <v>141.0864890360487</v>
+        <v>140.4658165030053</v>
       </c>
       <c r="E142" t="n">
-        <v>141.9534301757812</v>
+        <v>140.997802734375</v>
       </c>
       <c r="F142" t="n">
-        <v>8061700</v>
+        <v>5941700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>141.9534207153344</v>
+        <v>140.8894315190035</v>
       </c>
       <c r="C143" t="n">
-        <v>142.0716515698294</v>
+        <v>141.5396485970176</v>
       </c>
       <c r="D143" t="n">
-        <v>140.4658165030053</v>
+        <v>139.8155977290451</v>
       </c>
       <c r="E143" t="n">
-        <v>140.997802734375</v>
+        <v>140.6529998779297</v>
       </c>
       <c r="F143" t="n">
-        <v>5941700</v>
+        <v>6823100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>140.8894315190035</v>
+        <v>140.4066990917555</v>
       </c>
       <c r="C144" t="n">
-        <v>141.5396485970176</v>
+        <v>140.6529920592033</v>
       </c>
       <c r="D144" t="n">
-        <v>139.8155977290451</v>
+        <v>138.6530943661295</v>
       </c>
       <c r="E144" t="n">
-        <v>140.6529998779297</v>
+        <v>139.2047882080078</v>
       </c>
       <c r="F144" t="n">
-        <v>6823100</v>
+        <v>7207500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>140.4066990917555</v>
+        <v>141.0273529653376</v>
       </c>
       <c r="C145" t="n">
-        <v>140.6529920592033</v>
+        <v>142.9582965240978</v>
       </c>
       <c r="D145" t="n">
-        <v>138.6530943661295</v>
+        <v>139.766334122587</v>
       </c>
       <c r="E145" t="n">
-        <v>139.2047882080078</v>
+        <v>142.7514038085938</v>
       </c>
       <c r="F145" t="n">
-        <v>7207500</v>
+        <v>10849700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>141.0273529653376</v>
+        <v>142.2489765209199</v>
       </c>
       <c r="C146" t="n">
-        <v>142.9582965240978</v>
+        <v>144.7611679868877</v>
       </c>
       <c r="D146" t="n">
-        <v>139.766334122587</v>
+        <v>140.8795881188284</v>
       </c>
       <c r="E146" t="n">
-        <v>142.7514038085938</v>
+        <v>144.4853210449219</v>
       </c>
       <c r="F146" t="n">
-        <v>10849700</v>
+        <v>6794800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>142.2489765209199</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="C147" t="n">
-        <v>144.7611679868877</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="D147" t="n">
-        <v>140.8795881188284</v>
+        <v>142.6134905474848</v>
       </c>
       <c r="E147" t="n">
-        <v>144.4853210449219</v>
+        <v>143.007568359375</v>
       </c>
       <c r="F147" t="n">
-        <v>6794800</v>
+        <v>9790300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>144.7119116772724</v>
+        <v>142.8499157089539</v>
       </c>
       <c r="C148" t="n">
-        <v>144.7119116772724</v>
+        <v>142.9385775660697</v>
       </c>
       <c r="D148" t="n">
-        <v>142.6134905474848</v>
+        <v>140.5150632763963</v>
       </c>
       <c r="E148" t="n">
-        <v>143.007568359375</v>
+        <v>141.4509735107422</v>
       </c>
       <c r="F148" t="n">
-        <v>9790300</v>
+        <v>7121400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>142.8499157089539</v>
+        <v>141.1160402826616</v>
       </c>
       <c r="C149" t="n">
-        <v>142.9385775660697</v>
+        <v>142.5740906086617</v>
       </c>
       <c r="D149" t="n">
-        <v>140.5150632763963</v>
+        <v>140.6530082479637</v>
       </c>
       <c r="E149" t="n">
-        <v>141.4509735107422</v>
+        <v>142.2391357421875</v>
       </c>
       <c r="F149" t="n">
-        <v>7121400</v>
+        <v>6621600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>141.1160402826616</v>
+        <v>142.2194162805844</v>
       </c>
       <c r="C150" t="n">
-        <v>142.5740906086617</v>
+        <v>142.2588165423252</v>
       </c>
       <c r="D150" t="n">
-        <v>140.6530082479637</v>
+        <v>140.1505492747316</v>
       </c>
       <c r="E150" t="n">
-        <v>142.2391357421875</v>
+        <v>141.2539520263672</v>
       </c>
       <c r="F150" t="n">
-        <v>6621600</v>
+        <v>7698200</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>142.2194162805844</v>
+        <v>141.0766226846627</v>
       </c>
       <c r="C151" t="n">
-        <v>142.2588165423252</v>
+        <v>142.1504565210129</v>
       </c>
       <c r="D151" t="n">
-        <v>140.1505492747316</v>
+        <v>140.5446364367332</v>
       </c>
       <c r="E151" t="n">
-        <v>141.2539520263672</v>
+        <v>140.9879608154297</v>
       </c>
       <c r="F151" t="n">
-        <v>7698200</v>
+        <v>6947100</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>141.0766226846627</v>
+        <v>141.2835176988996</v>
       </c>
       <c r="C152" t="n">
-        <v>142.1504565210129</v>
+        <v>145.4015293724886</v>
       </c>
       <c r="D152" t="n">
-        <v>140.5446364367332</v>
+        <v>141.0372247031338</v>
       </c>
       <c r="E152" t="n">
-        <v>140.9879608154297</v>
+        <v>144.7513122558594</v>
       </c>
       <c r="F152" t="n">
-        <v>6947100</v>
+        <v>10886000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>141.2835176988996</v>
+        <v>143.8942158414082</v>
       </c>
       <c r="C153" t="n">
-        <v>145.4015293724886</v>
+        <v>144.4853250376877</v>
       </c>
       <c r="D153" t="n">
-        <v>141.0372247031338</v>
+        <v>141.4608398676902</v>
       </c>
       <c r="E153" t="n">
-        <v>144.7513122558594</v>
+        <v>142.3475036621094</v>
       </c>
       <c r="F153" t="n">
-        <v>10886000</v>
+        <v>8084700</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>143.8942158414082</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="C154" t="n">
-        <v>144.4853250376877</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="D154" t="n">
-        <v>141.4608398676902</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="E154" t="n">
-        <v>142.3475036621094</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="F154" t="n">
-        <v>8084700</v>
+        <v>11197200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>142.4755698536542</v>
+        <v>140.3869953464167</v>
       </c>
       <c r="C155" t="n">
-        <v>142.4755698536542</v>
+        <v>141.175135870657</v>
       </c>
       <c r="D155" t="n">
-        <v>140.2096862792969</v>
+        <v>140.1111484178121</v>
       </c>
       <c r="E155" t="n">
-        <v>140.2096862792969</v>
+        <v>140.7318115234375</v>
       </c>
       <c r="F155" t="n">
-        <v>11197200</v>
+        <v>7236300</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>140.3869953464167</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="C156" t="n">
-        <v>141.175135870657</v>
+        <v>144.0616865371081</v>
       </c>
       <c r="D156" t="n">
-        <v>140.1111484178121</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="E156" t="n">
-        <v>140.7318115234375</v>
+        <v>143.5494079589844</v>
       </c>
       <c r="F156" t="n">
-        <v>7236300</v>
+        <v>11288800</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,25 +4499,25 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>141.2736481824844</v>
+        <v>150.8836541197979</v>
       </c>
       <c r="C157" t="n">
-        <v>144.0616865371081</v>
+        <v>151.2906197995367</v>
       </c>
       <c r="D157" t="n">
-        <v>141.2736481824844</v>
+        <v>146.5261830755894</v>
       </c>
       <c r="E157" t="n">
-        <v>143.5494079589844</v>
+        <v>147.08203125</v>
       </c>
       <c r="F157" t="n">
-        <v>11288800</v>
+        <v>13786200</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4525,25 +4525,25 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>150.8836541197979</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="C158" t="n">
-        <v>151.2906197995367</v>
+        <v>148.59077024601</v>
       </c>
       <c r="D158" t="n">
-        <v>146.5261830755894</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="E158" t="n">
-        <v>147.08203125</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F158" t="n">
-        <v>13786200</v>
+        <v>9166400</v>
       </c>
       <c r="G158" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>146.3276654919543</v>
+        <v>148.9183255527001</v>
       </c>
       <c r="C159" t="n">
-        <v>148.59077024601</v>
+        <v>150.0697339670296</v>
       </c>
       <c r="D159" t="n">
-        <v>146.3276654919543</v>
+        <v>147.3301749711611</v>
       </c>
       <c r="E159" t="n">
-        <v>147.3003997802734</v>
+        <v>148.064697265625</v>
       </c>
       <c r="F159" t="n">
-        <v>9166400</v>
+        <v>7965700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>148.9183255527001</v>
+        <v>147.2011489489405</v>
       </c>
       <c r="C160" t="n">
-        <v>150.0697339670296</v>
+        <v>147.6478115682369</v>
       </c>
       <c r="D160" t="n">
-        <v>147.3301749711611</v>
+        <v>144.8090026189782</v>
       </c>
       <c r="E160" t="n">
-        <v>148.064697265625</v>
+        <v>145.3747863769531</v>
       </c>
       <c r="F160" t="n">
-        <v>7965700</v>
+        <v>9002400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>147.2011489489405</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="C161" t="n">
-        <v>147.6478115682369</v>
+        <v>146.6254435609453</v>
       </c>
       <c r="D161" t="n">
-        <v>144.8090026189782</v>
+        <v>144.8685544504002</v>
       </c>
       <c r="E161" t="n">
-        <v>145.3747863769531</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="F161" t="n">
-        <v>9002400</v>
+        <v>9491700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>146.0001068115234</v>
+        <v>146.7743191747914</v>
       </c>
       <c r="C162" t="n">
-        <v>146.6254435609453</v>
+        <v>148.1738750980608</v>
       </c>
       <c r="D162" t="n">
-        <v>144.8685544504002</v>
+        <v>145.3747783972478</v>
       </c>
       <c r="E162" t="n">
-        <v>146.0001068115234</v>
+        <v>146.1688385009766</v>
       </c>
       <c r="F162" t="n">
-        <v>9491700</v>
+        <v>6814800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>146.7743191747914</v>
+        <v>144.977737605514</v>
       </c>
       <c r="C163" t="n">
-        <v>148.1738750980608</v>
+        <v>144.977737605514</v>
       </c>
       <c r="D163" t="n">
-        <v>145.3747783972478</v>
+        <v>142.2084173171452</v>
       </c>
       <c r="E163" t="n">
-        <v>146.1688385009766</v>
+        <v>142.3572998046875</v>
       </c>
       <c r="F163" t="n">
-        <v>6814800</v>
+        <v>9642800</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>144.977737605514</v>
+        <v>142.3175981532361</v>
       </c>
       <c r="C164" t="n">
-        <v>144.977737605514</v>
+        <v>144.8189147356386</v>
       </c>
       <c r="D164" t="n">
-        <v>142.2084173171452</v>
+        <v>141.1264777093581</v>
       </c>
       <c r="E164" t="n">
-        <v>142.3572998046875</v>
+        <v>143.8263244628906</v>
       </c>
       <c r="F164" t="n">
-        <v>9642800</v>
+        <v>7664300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>142.3175981532361</v>
+        <v>145.3152221312864</v>
       </c>
       <c r="C165" t="n">
-        <v>144.8189147356386</v>
+        <v>147.8463305694715</v>
       </c>
       <c r="D165" t="n">
-        <v>141.1264777093581</v>
+        <v>144.8586390489098</v>
       </c>
       <c r="E165" t="n">
-        <v>143.8263244628906</v>
+        <v>146.8041076660156</v>
       </c>
       <c r="F165" t="n">
-        <v>7664300</v>
+        <v>9399500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>145.3152221312864</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="C166" t="n">
-        <v>147.8463305694715</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="D166" t="n">
-        <v>144.8586390489098</v>
+        <v>144.9380404787042</v>
       </c>
       <c r="E166" t="n">
-        <v>146.8041076660156</v>
+        <v>144.9777374267578</v>
       </c>
       <c r="F166" t="n">
-        <v>9399500</v>
+        <v>9545800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>146.8934445898874</v>
+        <v>145.4641093327384</v>
       </c>
       <c r="C167" t="n">
-        <v>146.8934445898874</v>
+        <v>146.4269231210903</v>
       </c>
       <c r="D167" t="n">
-        <v>144.9380404787042</v>
+        <v>145.1266322707271</v>
       </c>
       <c r="E167" t="n">
-        <v>144.9777374267578</v>
+        <v>145.3350677490234</v>
       </c>
       <c r="F167" t="n">
-        <v>9545800</v>
+        <v>5741000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>145.4641093327384</v>
+        <v>144.7097318886224</v>
       </c>
       <c r="C168" t="n">
-        <v>146.4269231210903</v>
+        <v>144.8685499701872</v>
       </c>
       <c r="D168" t="n">
-        <v>145.1266322707271</v>
+        <v>140.9180448520501</v>
       </c>
       <c r="E168" t="n">
-        <v>145.3350677490234</v>
+        <v>142.2977447509766</v>
       </c>
       <c r="F168" t="n">
-        <v>5741000</v>
+        <v>7489500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>144.7097318886224</v>
+        <v>143.280415861365</v>
       </c>
       <c r="C169" t="n">
-        <v>144.8685499701872</v>
+        <v>144.7792217618835</v>
       </c>
       <c r="D169" t="n">
-        <v>140.9180448520501</v>
+        <v>141.8014508619235</v>
       </c>
       <c r="E169" t="n">
-        <v>142.2977447509766</v>
+        <v>142.8436737060547</v>
       </c>
       <c r="F169" t="n">
-        <v>7489500</v>
+        <v>9051200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>143.280415861365</v>
+        <v>142.0892960817053</v>
       </c>
       <c r="C170" t="n">
-        <v>144.7792217618835</v>
+        <v>143.5980375858882</v>
       </c>
       <c r="D170" t="n">
-        <v>141.8014508619235</v>
+        <v>140.610346220736</v>
       </c>
       <c r="E170" t="n">
-        <v>142.8436737060547</v>
+        <v>141.1860504150391</v>
       </c>
       <c r="F170" t="n">
-        <v>9051200</v>
+        <v>6685900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>142.0892960817053</v>
+        <v>142.1190761527801</v>
       </c>
       <c r="C171" t="n">
-        <v>143.5980375858882</v>
+        <v>143.2109315738657</v>
       </c>
       <c r="D171" t="n">
-        <v>140.610346220736</v>
+        <v>141.5731635879637</v>
       </c>
       <c r="E171" t="n">
-        <v>141.1860504150391</v>
+        <v>141.6525726318359</v>
       </c>
       <c r="F171" t="n">
-        <v>6685900</v>
+        <v>9636200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>142.1190761527801</v>
+        <v>142.337438212696</v>
       </c>
       <c r="C172" t="n">
-        <v>143.2109315738657</v>
+        <v>142.337438212696</v>
       </c>
       <c r="D172" t="n">
-        <v>141.5731635879637</v>
+        <v>140.1537426546991</v>
       </c>
       <c r="E172" t="n">
-        <v>141.6525726318359</v>
+        <v>140.5210113525391</v>
       </c>
       <c r="F172" t="n">
-        <v>9636200</v>
+        <v>6989400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>142.337438212696</v>
+        <v>141.0470859006894</v>
       </c>
       <c r="C173" t="n">
-        <v>142.337438212696</v>
+        <v>143.3598079421396</v>
       </c>
       <c r="D173" t="n">
-        <v>140.1537426546991</v>
+        <v>140.5805672539439</v>
       </c>
       <c r="E173" t="n">
-        <v>140.5210113525391</v>
+        <v>141.3349304199219</v>
       </c>
       <c r="F173" t="n">
-        <v>6989400</v>
+        <v>7731200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>141.0470859006894</v>
+        <v>141.4143347616525</v>
       </c>
       <c r="C174" t="n">
-        <v>143.3598079421396</v>
+        <v>142.6451521296186</v>
       </c>
       <c r="D174" t="n">
-        <v>140.5805672539439</v>
+        <v>139.8063433960926</v>
       </c>
       <c r="E174" t="n">
-        <v>141.3349304199219</v>
+        <v>140.2530059814453</v>
       </c>
       <c r="F174" t="n">
-        <v>7731200</v>
+        <v>8355800</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>141.4143347616525</v>
+        <v>140.4018973938673</v>
       </c>
       <c r="C175" t="n">
-        <v>142.6451521296186</v>
+        <v>142.1587864968038</v>
       </c>
       <c r="D175" t="n">
-        <v>139.8063433960926</v>
+        <v>139.578045612781</v>
       </c>
       <c r="E175" t="n">
-        <v>140.2530059814453</v>
+        <v>141.3845672607422</v>
       </c>
       <c r="F175" t="n">
-        <v>8355800</v>
+        <v>8375600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>140.4018973938673</v>
+        <v>140.8287217143626</v>
       </c>
       <c r="C176" t="n">
-        <v>142.1587864968038</v>
+        <v>142.655084297577</v>
       </c>
       <c r="D176" t="n">
-        <v>139.578045612781</v>
+        <v>139.0519765313656</v>
       </c>
       <c r="E176" t="n">
-        <v>141.3845672607422</v>
+        <v>142.3374481201172</v>
       </c>
       <c r="F176" t="n">
-        <v>8375600</v>
+        <v>6297300</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>140.8287217143626</v>
+        <v>142.8039672134308</v>
       </c>
       <c r="C177" t="n">
-        <v>142.655084297577</v>
+        <v>143.5682660152007</v>
       </c>
       <c r="D177" t="n">
-        <v>139.0519765313656</v>
+        <v>142.4664901331732</v>
       </c>
       <c r="E177" t="n">
-        <v>142.3374481201172</v>
+        <v>143.3697509765625</v>
       </c>
       <c r="F177" t="n">
-        <v>6297300</v>
+        <v>4616700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>142.8039672134308</v>
+        <v>143.439213854944</v>
       </c>
       <c r="C178" t="n">
-        <v>143.5682660152007</v>
+        <v>144.5310692055886</v>
       </c>
       <c r="D178" t="n">
-        <v>142.4664901331732</v>
+        <v>141.473889369509</v>
       </c>
       <c r="E178" t="n">
-        <v>143.3697509765625</v>
+        <v>141.9007110595703</v>
       </c>
       <c r="F178" t="n">
-        <v>4616700</v>
+        <v>8157200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>143.439213854944</v>
+        <v>142.397017874141</v>
       </c>
       <c r="C179" t="n">
-        <v>144.5310692055886</v>
+        <v>147.4393635097026</v>
       </c>
       <c r="D179" t="n">
-        <v>141.473889369509</v>
+        <v>142.397017874141</v>
       </c>
       <c r="E179" t="n">
-        <v>141.9007110595703</v>
+        <v>146.3971557617188</v>
       </c>
       <c r="F179" t="n">
-        <v>8157200</v>
+        <v>10048900</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>142.397017874141</v>
+        <v>145.612997111615</v>
       </c>
       <c r="C180" t="n">
-        <v>147.4393635097026</v>
+        <v>145.612997111615</v>
       </c>
       <c r="D180" t="n">
-        <v>142.397017874141</v>
+        <v>143.9355170452321</v>
       </c>
       <c r="E180" t="n">
-        <v>146.3971557617188</v>
+        <v>144.828857421875</v>
       </c>
       <c r="F180" t="n">
-        <v>10048900</v>
+        <v>10196700</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>145.612997111615</v>
+        <v>144.4417452563355</v>
       </c>
       <c r="C181" t="n">
-        <v>145.612997111615</v>
+        <v>144.5608512461645</v>
       </c>
       <c r="D181" t="n">
-        <v>143.9355170452321</v>
+        <v>142.1389284814664</v>
       </c>
       <c r="E181" t="n">
-        <v>144.828857421875</v>
+        <v>142.4962615966797</v>
       </c>
       <c r="F181" t="n">
-        <v>10196700</v>
+        <v>12355800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>144.4417452563355</v>
+        <v>140.4713875281435</v>
       </c>
       <c r="C182" t="n">
-        <v>144.5608512461645</v>
+        <v>140.7691676558347</v>
       </c>
       <c r="D182" t="n">
-        <v>142.1389284814664</v>
+        <v>137.8310936193964</v>
       </c>
       <c r="E182" t="n">
-        <v>142.4962615966797</v>
+        <v>139.2405700683594</v>
       </c>
       <c r="F182" t="n">
-        <v>12355800</v>
+        <v>11093800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>140.4713875281435</v>
+        <v>139.0817554467106</v>
       </c>
       <c r="C183" t="n">
-        <v>140.7691676558347</v>
+        <v>140.0743457999317</v>
       </c>
       <c r="D183" t="n">
-        <v>137.8310936193964</v>
+        <v>137.999835596674</v>
       </c>
       <c r="E183" t="n">
-        <v>139.2405700683594</v>
+        <v>139.7765808105469</v>
       </c>
       <c r="F183" t="n">
-        <v>11093800</v>
+        <v>9599500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>139.0817554467106</v>
+        <v>139.8857522909846</v>
       </c>
       <c r="C184" t="n">
-        <v>140.0743457999317</v>
+        <v>141.3944938803485</v>
       </c>
       <c r="D184" t="n">
-        <v>137.999835596674</v>
+        <v>138.9626505253011</v>
       </c>
       <c r="E184" t="n">
-        <v>139.7765808105469</v>
+        <v>139.1512451171875</v>
       </c>
       <c r="F184" t="n">
-        <v>9599500</v>
+        <v>9351000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>139.8857522909846</v>
+        <v>141.6426337542266</v>
       </c>
       <c r="C185" t="n">
-        <v>141.3944938803485</v>
+        <v>142.079375912544</v>
       </c>
       <c r="D185" t="n">
-        <v>138.9626505253011</v>
+        <v>138.8534574153755</v>
       </c>
       <c r="E185" t="n">
-        <v>139.1512451171875</v>
+        <v>139.7368621826172</v>
       </c>
       <c r="F185" t="n">
-        <v>9351000</v>
+        <v>8194000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>141.6426337542266</v>
+        <v>141.1661955784844</v>
       </c>
       <c r="C186" t="n">
-        <v>142.079375912544</v>
+        <v>147.131657909349</v>
       </c>
       <c r="D186" t="n">
-        <v>138.8534574153755</v>
+        <v>140.7493094643581</v>
       </c>
       <c r="E186" t="n">
-        <v>139.7368621826172</v>
+        <v>145.4541778564453</v>
       </c>
       <c r="F186" t="n">
-        <v>8194000</v>
+        <v>10963200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>141.1661955784844</v>
+        <v>144.709731142363</v>
       </c>
       <c r="C187" t="n">
-        <v>147.131657909349</v>
+        <v>145.4641094530425</v>
       </c>
       <c r="D187" t="n">
-        <v>140.7493094643581</v>
+        <v>143.9454475270099</v>
       </c>
       <c r="E187" t="n">
-        <v>145.4541778564453</v>
+        <v>144.0248565673828</v>
       </c>
       <c r="F187" t="n">
-        <v>10963200</v>
+        <v>7200700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>144.709731142363</v>
+        <v>143.598043761205</v>
       </c>
       <c r="C188" t="n">
-        <v>145.4641094530425</v>
+        <v>148.3724009095588</v>
       </c>
       <c r="D188" t="n">
-        <v>143.9454475270099</v>
+        <v>143.4590817183783</v>
       </c>
       <c r="E188" t="n">
-        <v>144.0248565673828</v>
+        <v>147.5684051513672</v>
       </c>
       <c r="F188" t="n">
-        <v>7200700</v>
+        <v>8259300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>143.598043761205</v>
+        <v>148.7992154215363</v>
       </c>
       <c r="C189" t="n">
-        <v>148.3724009095588</v>
+        <v>149.3153514723138</v>
       </c>
       <c r="D189" t="n">
-        <v>143.4590817183783</v>
+        <v>147.2805534750766</v>
       </c>
       <c r="E189" t="n">
-        <v>147.5684051513672</v>
+        <v>147.9455871582031</v>
       </c>
       <c r="F189" t="n">
-        <v>8259300</v>
+        <v>7345900</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>148.7992154215363</v>
+        <v>147.598177848302</v>
       </c>
       <c r="C190" t="n">
-        <v>149.3153514723138</v>
+        <v>148.5113591270304</v>
       </c>
       <c r="D190" t="n">
-        <v>147.2805534750766</v>
+        <v>146.6750761188154</v>
       </c>
       <c r="E190" t="n">
-        <v>147.9455871582031</v>
+        <v>147.2408447265625</v>
       </c>
       <c r="F190" t="n">
-        <v>7345900</v>
+        <v>6684700</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>147.598177848302</v>
+        <v>148.2731427996088</v>
       </c>
       <c r="C191" t="n">
-        <v>148.5113591270304</v>
+        <v>149.087058964007</v>
       </c>
       <c r="D191" t="n">
-        <v>146.6750761188154</v>
+        <v>147.2011434657927</v>
       </c>
       <c r="E191" t="n">
-        <v>147.2408447265625</v>
+        <v>148.5014343261719</v>
       </c>
       <c r="F191" t="n">
-        <v>6684700</v>
+        <v>6832000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>148.2731427996088</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="C192" t="n">
-        <v>149.087058964007</v>
+        <v>150.377425765528</v>
       </c>
       <c r="D192" t="n">
-        <v>147.2011434657927</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="E192" t="n">
-        <v>148.5014343261719</v>
+        <v>149.3451385498047</v>
       </c>
       <c r="F192" t="n">
-        <v>6832000</v>
+        <v>9158900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>147.6577229757893</v>
+        <v>150.3873579771785</v>
       </c>
       <c r="C193" t="n">
-        <v>150.377425765528</v>
+        <v>151.8861790939718</v>
       </c>
       <c r="D193" t="n">
-        <v>147.6577229757893</v>
+        <v>149.4344797259463</v>
       </c>
       <c r="E193" t="n">
-        <v>149.3451385498047</v>
+        <v>151.360107421875</v>
       </c>
       <c r="F193" t="n">
-        <v>9158900</v>
+        <v>8518900</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>150.3873579771785</v>
+        <v>151.2509186348782</v>
       </c>
       <c r="C194" t="n">
-        <v>151.8861790939718</v>
+        <v>151.8067667938</v>
       </c>
       <c r="D194" t="n">
-        <v>149.4344797259463</v>
+        <v>148.6602572796902</v>
       </c>
       <c r="E194" t="n">
-        <v>151.360107421875</v>
+        <v>149.4443969726562</v>
       </c>
       <c r="F194" t="n">
-        <v>8518900</v>
+        <v>7055800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>151.2509186348782</v>
+        <v>149.7520913576046</v>
       </c>
       <c r="C195" t="n">
-        <v>151.8067667938</v>
+        <v>151.1615677439354</v>
       </c>
       <c r="D195" t="n">
-        <v>148.6602572796902</v>
+        <v>149.067201638067</v>
       </c>
       <c r="E195" t="n">
-        <v>149.4443969726562</v>
+        <v>149.2657318115234</v>
       </c>
       <c r="F195" t="n">
-        <v>7055800</v>
+        <v>17076100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>149.7520913576046</v>
+        <v>148.9977261100366</v>
       </c>
       <c r="C196" t="n">
-        <v>151.1615677439354</v>
+        <v>149.7719453093657</v>
       </c>
       <c r="D196" t="n">
-        <v>149.067201638067</v>
+        <v>146.4765534870951</v>
       </c>
       <c r="E196" t="n">
-        <v>149.2657318115234</v>
+        <v>146.5857238769531</v>
       </c>
       <c r="F196" t="n">
-        <v>17076100</v>
+        <v>10533000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>148.9977261100366</v>
+        <v>148.5510669184904</v>
       </c>
       <c r="C197" t="n">
-        <v>149.7719453093657</v>
+        <v>150.2483878382925</v>
       </c>
       <c r="D197" t="n">
-        <v>146.4765534870951</v>
+        <v>148.2632072518497</v>
       </c>
       <c r="E197" t="n">
-        <v>146.5857238769531</v>
+        <v>149.7421722412109</v>
       </c>
       <c r="F197" t="n">
-        <v>10533000</v>
+        <v>7259600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>148.5510669184904</v>
+        <v>150.8638042327417</v>
       </c>
       <c r="C198" t="n">
-        <v>150.2483878382925</v>
+        <v>152.213727638368</v>
       </c>
       <c r="D198" t="n">
-        <v>148.2632072518497</v>
+        <v>149.8017253482469</v>
       </c>
       <c r="E198" t="n">
-        <v>149.7421722412109</v>
+        <v>150.9134216308594</v>
       </c>
       <c r="F198" t="n">
-        <v>7259600</v>
+        <v>8618500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>150.8638042327417</v>
+        <v>150.446917666229</v>
       </c>
       <c r="C199" t="n">
-        <v>152.213727638368</v>
+        <v>151.1615687416308</v>
       </c>
       <c r="D199" t="n">
-        <v>149.8017253482469</v>
+        <v>146.7247040752409</v>
       </c>
       <c r="E199" t="n">
-        <v>150.9134216308594</v>
+        <v>147.399658203125</v>
       </c>
       <c r="F199" t="n">
-        <v>8618500</v>
+        <v>11197200</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>150.446917666229</v>
+        <v>149.226028638664</v>
       </c>
       <c r="C200" t="n">
-        <v>151.1615687416308</v>
+        <v>149.7620359058753</v>
       </c>
       <c r="D200" t="n">
-        <v>146.7247040752409</v>
+        <v>147.3202569962244</v>
       </c>
       <c r="E200" t="n">
-        <v>147.399658203125</v>
+        <v>147.9158172607422</v>
       </c>
       <c r="F200" t="n">
-        <v>11197200</v>
+        <v>16724600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>149.226028638664</v>
+        <v>147.627945424002</v>
       </c>
       <c r="C201" t="n">
-        <v>149.7620359058753</v>
+        <v>147.945581577785</v>
       </c>
       <c r="D201" t="n">
-        <v>147.3202569962244</v>
+        <v>145.9504654579339</v>
       </c>
       <c r="E201" t="n">
-        <v>147.9158172607422</v>
+        <v>147.3500213623047</v>
       </c>
       <c r="F201" t="n">
-        <v>16724600</v>
+        <v>10387700</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>147.627945424002</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="C202" t="n">
-        <v>147.945581577785</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="D202" t="n">
-        <v>145.9504654579339</v>
+        <v>143.1017371059213</v>
       </c>
       <c r="E202" t="n">
-        <v>147.3500213623047</v>
+        <v>145.5534362792969</v>
       </c>
       <c r="F202" t="n">
-        <v>10387700</v>
+        <v>9353800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>146.4368410119005</v>
+        <v>145.4442602082673</v>
       </c>
       <c r="C203" t="n">
-        <v>146.4368410119005</v>
+        <v>146.4070740424418</v>
       </c>
       <c r="D203" t="n">
-        <v>143.1017371059213</v>
+        <v>144.4715259232294</v>
       </c>
       <c r="E203" t="n">
-        <v>145.5534362792969</v>
+        <v>146.3375854492188</v>
       </c>
       <c r="F203" t="n">
-        <v>9353800</v>
+        <v>9571700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>145.4442602082673</v>
+        <v>147.4790688253476</v>
       </c>
       <c r="C204" t="n">
-        <v>146.4070740424418</v>
+        <v>150.5461692222369</v>
       </c>
       <c r="D204" t="n">
-        <v>144.4715259232294</v>
+        <v>146.6452966069997</v>
       </c>
       <c r="E204" t="n">
-        <v>146.3375854492188</v>
+        <v>150.2881011962891</v>
       </c>
       <c r="F204" t="n">
-        <v>9571700</v>
+        <v>9256000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>147.4790688253476</v>
+        <v>149.5635029567411</v>
       </c>
       <c r="C205" t="n">
-        <v>150.5461692222369</v>
+        <v>150.0995102140475</v>
       </c>
       <c r="D205" t="n">
-        <v>146.6452966069997</v>
+        <v>145.8710808804345</v>
       </c>
       <c r="E205" t="n">
-        <v>150.2881011962891</v>
+        <v>148.2036590576172</v>
       </c>
       <c r="F205" t="n">
-        <v>9256000</v>
+        <v>8323100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>149.5635029567411</v>
+        <v>151.5288345729856</v>
       </c>
       <c r="C206" t="n">
-        <v>150.0995102140475</v>
+        <v>152.3526863163115</v>
       </c>
       <c r="D206" t="n">
-        <v>145.8710808804345</v>
+        <v>149.4940214860459</v>
       </c>
       <c r="E206" t="n">
-        <v>148.2036590576172</v>
+        <v>151.6181640625</v>
       </c>
       <c r="F206" t="n">
-        <v>8323100</v>
+        <v>8061400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>151.5288345729856</v>
+        <v>149.8414437624326</v>
       </c>
       <c r="C207" t="n">
-        <v>152.3526863163115</v>
+        <v>149.950629305204</v>
       </c>
       <c r="D207" t="n">
-        <v>149.4940214860459</v>
+        <v>147.2507823800627</v>
       </c>
       <c r="E207" t="n">
-        <v>151.6181640625</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F207" t="n">
-        <v>8061400</v>
+        <v>14272300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>149.8414437624326</v>
+        <v>145.6824775579256</v>
       </c>
       <c r="C208" t="n">
-        <v>149.950629305204</v>
+        <v>146.5658822886928</v>
       </c>
       <c r="D208" t="n">
-        <v>147.2507823800627</v>
+        <v>144.5211487643815</v>
       </c>
       <c r="E208" t="n">
-        <v>147.3003997802734</v>
+        <v>145.7618865966797</v>
       </c>
       <c r="F208" t="n">
-        <v>14272300</v>
+        <v>7748000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>145.6824775579256</v>
+        <v>146.0100381106733</v>
       </c>
       <c r="C209" t="n">
-        <v>146.5658822886928</v>
+        <v>147.4889879534934</v>
       </c>
       <c r="D209" t="n">
-        <v>144.5211487643815</v>
+        <v>145.6229285023594</v>
       </c>
       <c r="E209" t="n">
-        <v>145.7618865966797</v>
+        <v>145.9504699707031</v>
       </c>
       <c r="F209" t="n">
-        <v>7748000</v>
+        <v>12473000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>146.0100381106733</v>
+        <v>146.9827701076717</v>
       </c>
       <c r="C210" t="n">
-        <v>147.4889879534934</v>
+        <v>148.9381741659779</v>
       </c>
       <c r="D210" t="n">
-        <v>145.6229285023594</v>
+        <v>146.0199563268518</v>
       </c>
       <c r="E210" t="n">
-        <v>145.9504699707031</v>
+        <v>147.2706146240234</v>
       </c>
       <c r="F210" t="n">
-        <v>12473000</v>
+        <v>7816100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>146.9827701076717</v>
+        <v>147.2706141757336</v>
       </c>
       <c r="C211" t="n">
-        <v>148.9381741659779</v>
+        <v>147.6478033266625</v>
       </c>
       <c r="D211" t="n">
-        <v>146.0199563268518</v>
+        <v>144.5112144243791</v>
       </c>
       <c r="E211" t="n">
-        <v>147.2706146240234</v>
+        <v>144.9975891113281</v>
       </c>
       <c r="F211" t="n">
-        <v>7816100</v>
+        <v>7668100</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>147.2706141757336</v>
+        <v>144.2035234458952</v>
       </c>
       <c r="C212" t="n">
-        <v>147.6478033266625</v>
+        <v>147.4889950493996</v>
       </c>
       <c r="D212" t="n">
-        <v>144.5112144243791</v>
+        <v>143.5881222814616</v>
       </c>
       <c r="E212" t="n">
-        <v>144.9975891113281</v>
+        <v>146.9530029296875</v>
       </c>
       <c r="F212" t="n">
-        <v>7668100</v>
+        <v>6180000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>144.2035234458952</v>
+        <v>148.3823251540053</v>
       </c>
       <c r="C213" t="n">
-        <v>147.4889950493996</v>
+        <v>150.3972821936961</v>
       </c>
       <c r="D213" t="n">
-        <v>143.5881222814616</v>
+        <v>147.0820191757993</v>
       </c>
       <c r="E213" t="n">
-        <v>146.9530029296875</v>
+        <v>150.3774261474609</v>
       </c>
       <c r="F213" t="n">
-        <v>6180000</v>
+        <v>6485400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>148.3823251540053</v>
+        <v>151.7273476549808</v>
       </c>
       <c r="C214" t="n">
-        <v>150.3972821936961</v>
+        <v>153.1765360977979</v>
       </c>
       <c r="D214" t="n">
-        <v>147.0820191757993</v>
+        <v>148.2036492050291</v>
       </c>
       <c r="E214" t="n">
-        <v>150.3774261474609</v>
+        <v>148.8686828613281</v>
       </c>
       <c r="F214" t="n">
-        <v>6485400</v>
+        <v>8917400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>151.7273476549808</v>
+        <v>148.4518004486472</v>
       </c>
       <c r="C215" t="n">
-        <v>153.1765360977979</v>
+        <v>148.9878076836025</v>
       </c>
       <c r="D215" t="n">
-        <v>148.2036492050291</v>
+        <v>147.3301685811182</v>
       </c>
       <c r="E215" t="n">
-        <v>148.8686828613281</v>
+        <v>148.0249938964844</v>
       </c>
       <c r="F215" t="n">
-        <v>8917400</v>
+        <v>5788300</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>148.4518004486472</v>
+        <v>146.7643973953222</v>
       </c>
       <c r="C216" t="n">
-        <v>148.9878076836025</v>
+        <v>147.3103250709858</v>
       </c>
       <c r="D216" t="n">
-        <v>147.3301685811182</v>
+        <v>145.7916631750561</v>
       </c>
       <c r="E216" t="n">
-        <v>148.0249938964844</v>
+        <v>147.0026245117188</v>
       </c>
       <c r="F216" t="n">
-        <v>5788300</v>
+        <v>7027600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>146.7643973953222</v>
+        <v>148.3922474549245</v>
       </c>
       <c r="C217" t="n">
-        <v>147.3103250709858</v>
+        <v>149.3451407916641</v>
       </c>
       <c r="D217" t="n">
-        <v>145.7916631750561</v>
+        <v>147.7172933317669</v>
       </c>
       <c r="E217" t="n">
-        <v>147.0026245117188</v>
+        <v>148.0249938964844</v>
       </c>
       <c r="F217" t="n">
-        <v>7027600</v>
+        <v>5371200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>148.3922474549245</v>
+        <v>145.057144942689</v>
       </c>
       <c r="C218" t="n">
-        <v>149.3451407916641</v>
+        <v>146.5162538863596</v>
       </c>
       <c r="D218" t="n">
-        <v>147.7172933317669</v>
+        <v>144.5112172519064</v>
       </c>
       <c r="E218" t="n">
-        <v>148.0249938964844</v>
+        <v>145.8809967041016</v>
       </c>
       <c r="F218" t="n">
-        <v>5371200</v>
+        <v>6499200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,25 +6111,25 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>145.057144942689</v>
+        <v>146.4499969482422</v>
       </c>
       <c r="C219" t="n">
-        <v>146.5162538863596</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="D219" t="n">
-        <v>144.5112172519064</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E219" t="n">
-        <v>145.8809967041016</v>
+        <v>147.4100036621094</v>
       </c>
       <c r="F219" t="n">
-        <v>6499200</v>
+        <v>6620700</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6137,25 +6137,25 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>146.4499969482422</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C220" t="n">
-        <v>147.9900054931641</v>
+        <v>150.25</v>
       </c>
       <c r="D220" t="n">
-        <v>145.3999938964844</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="E220" t="n">
-        <v>147.4100036621094</v>
+        <v>148.6300048828125</v>
       </c>
       <c r="F220" t="n">
-        <v>6620700</v>
+        <v>7301800</v>
       </c>
       <c r="G220" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>147.8500061035156</v>
+        <v>151.5</v>
       </c>
       <c r="C221" t="n">
-        <v>150.25</v>
+        <v>153.6799926757812</v>
       </c>
       <c r="D221" t="n">
-        <v>147.8500061035156</v>
+        <v>148.5200042724609</v>
       </c>
       <c r="E221" t="n">
-        <v>148.6300048828125</v>
+        <v>148.8800048828125</v>
       </c>
       <c r="F221" t="n">
-        <v>7301800</v>
+        <v>12848800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>151.5</v>
+        <v>141.3800048828125</v>
       </c>
       <c r="C222" t="n">
-        <v>153.6799926757812</v>
+        <v>146.3800048828125</v>
       </c>
       <c r="D222" t="n">
-        <v>148.5200042724609</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="E222" t="n">
-        <v>148.8800048828125</v>
+        <v>146.1000061035156</v>
       </c>
       <c r="F222" t="n">
-        <v>12848800</v>
+        <v>14616800</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>141.3800048828125</v>
+        <v>143.7599945068359</v>
       </c>
       <c r="C223" t="n">
-        <v>146.3800048828125</v>
+        <v>144.4499969482422</v>
       </c>
       <c r="D223" t="n">
-        <v>140.1999969482422</v>
+        <v>142.25</v>
       </c>
       <c r="E223" t="n">
-        <v>146.1000061035156</v>
+        <v>143.9600067138672</v>
       </c>
       <c r="F223" t="n">
-        <v>14616800</v>
+        <v>9571100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>143.7599945068359</v>
+        <v>143.5099945068359</v>
       </c>
       <c r="C224" t="n">
-        <v>144.4499969482422</v>
+        <v>144.6999969482422</v>
       </c>
       <c r="D224" t="n">
-        <v>142.25</v>
+        <v>141.4600067138672</v>
       </c>
       <c r="E224" t="n">
-        <v>143.9600067138672</v>
+        <v>144.4900054931641</v>
       </c>
       <c r="F224" t="n">
-        <v>9571100</v>
+        <v>9152600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>143.5099945068359</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C225" t="n">
-        <v>144.6999969482422</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D225" t="n">
-        <v>141.4600067138672</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="E225" t="n">
-        <v>144.4900054931641</v>
+        <v>144.9700012207031</v>
       </c>
       <c r="F225" t="n">
-        <v>9152600</v>
+        <v>8843600</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>145.8500061035156</v>
+        <v>144.0399932861328</v>
       </c>
       <c r="C226" t="n">
-        <v>147.1499938964844</v>
+        <v>148.25</v>
       </c>
       <c r="D226" t="n">
-        <v>144.2599945068359</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E226" t="n">
-        <v>144.9700012207031</v>
+        <v>148.0099945068359</v>
       </c>
       <c r="F226" t="n">
-        <v>8843600</v>
+        <v>7362300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>144.0399932861328</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C227" t="n">
-        <v>148.25</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="D227" t="n">
-        <v>143.7899932861328</v>
+        <v>144.6600036621094</v>
       </c>
       <c r="E227" t="n">
-        <v>148.0099945068359</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="F227" t="n">
-        <v>7362300</v>
+        <v>9753300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>147.8500061035156</v>
+        <v>147.8200073242188</v>
       </c>
       <c r="C228" t="n">
-        <v>147.8500061035156</v>
+        <v>148.5</v>
       </c>
       <c r="D228" t="n">
-        <v>144.6600036621094</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="E228" t="n">
-        <v>146.8000030517578</v>
+        <v>146.9700012207031</v>
       </c>
       <c r="F228" t="n">
-        <v>9753300</v>
+        <v>8766700</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>147.8200073242188</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C229" t="n">
-        <v>148.5</v>
+        <v>146</v>
       </c>
       <c r="D229" t="n">
-        <v>145.4499969482422</v>
+        <v>143.8800048828125</v>
       </c>
       <c r="E229" t="n">
-        <v>146.9700012207031</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="F229" t="n">
-        <v>8766700</v>
+        <v>7565500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>144.8999938964844</v>
+        <v>144.7299957275391</v>
       </c>
       <c r="C230" t="n">
-        <v>146</v>
+        <v>146.4600067138672</v>
       </c>
       <c r="D230" t="n">
-        <v>143.8800048828125</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="E230" t="n">
-        <v>145.7899932861328</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F230" t="n">
-        <v>7565500</v>
+        <v>7386500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>144.7299957275391</v>
+        <v>145.4100036621094</v>
       </c>
       <c r="C231" t="n">
-        <v>146.4600067138672</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="D231" t="n">
-        <v>144.1499938964844</v>
+        <v>143.9299926757812</v>
       </c>
       <c r="E231" t="n">
-        <v>146.4400024414062</v>
+        <v>145.2100067138672</v>
       </c>
       <c r="F231" t="n">
-        <v>7386500</v>
+        <v>7936700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>145.4100036621094</v>
+        <v>144.0500030517578</v>
       </c>
       <c r="C232" t="n">
-        <v>145.7100067138672</v>
+        <v>144.9400024414062</v>
       </c>
       <c r="D232" t="n">
-        <v>143.9299926757812</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E232" t="n">
-        <v>145.2100067138672</v>
+        <v>144.0800018310547</v>
       </c>
       <c r="F232" t="n">
-        <v>7936700</v>
+        <v>7195000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>144.0500030517578</v>
+        <v>144.5899963378906</v>
       </c>
       <c r="C233" t="n">
-        <v>144.9400024414062</v>
+        <v>145.8000030517578</v>
       </c>
       <c r="D233" t="n">
-        <v>143.7899932861328</v>
+        <v>144</v>
       </c>
       <c r="E233" t="n">
-        <v>144.0800018310547</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="F233" t="n">
-        <v>7195000</v>
+        <v>7491300</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>144.5899963378906</v>
+        <v>144.3300018310547</v>
       </c>
       <c r="C234" t="n">
-        <v>145.8000030517578</v>
+        <v>144.9100036621094</v>
       </c>
       <c r="D234" t="n">
-        <v>144</v>
+        <v>143.4199981689453</v>
       </c>
       <c r="E234" t="n">
-        <v>144.2599945068359</v>
+        <v>144.5500030517578</v>
       </c>
       <c r="F234" t="n">
-        <v>7491300</v>
+        <v>7249600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>144.3300018310547</v>
+        <v>143.6399993896484</v>
       </c>
       <c r="C235" t="n">
-        <v>144.9100036621094</v>
+        <v>143.9700012207031</v>
       </c>
       <c r="D235" t="n">
-        <v>143.4199981689453</v>
+        <v>142.4799957275391</v>
       </c>
       <c r="E235" t="n">
-        <v>144.5500030517578</v>
+        <v>143.1199951171875</v>
       </c>
       <c r="F235" t="n">
-        <v>7249600</v>
+        <v>9867500</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>143.6399993896484</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="C236" t="n">
-        <v>143.9700012207031</v>
+        <v>144.4199981689453</v>
       </c>
       <c r="D236" t="n">
-        <v>142.4799957275391</v>
+        <v>142.6799926757812</v>
       </c>
       <c r="E236" t="n">
-        <v>143.1199951171875</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F236" t="n">
-        <v>9867500</v>
+        <v>12746100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>143.2799987792969</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="C237" t="n">
-        <v>144.4199981689453</v>
+        <v>146.2299957275391</v>
       </c>
       <c r="D237" t="n">
-        <v>142.6799926757812</v>
+        <v>143.6199951171875</v>
       </c>
       <c r="E237" t="n">
-        <v>143.4499969482422</v>
+        <v>144.3800048828125</v>
       </c>
       <c r="F237" t="n">
-        <v>12746100</v>
+        <v>13948500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>144.3000030517578</v>
+        <v>144.4700012207031</v>
       </c>
       <c r="C238" t="n">
-        <v>146.2299957275391</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="D238" t="n">
-        <v>143.6199951171875</v>
+        <v>142.5599975585938</v>
       </c>
       <c r="E238" t="n">
-        <v>144.3800048828125</v>
+        <v>142.9700012207031</v>
       </c>
       <c r="F238" t="n">
-        <v>13948500</v>
+        <v>15794100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>144.4700012207031</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C239" t="n">
-        <v>144.9199981689453</v>
+        <v>145.2700042724609</v>
       </c>
       <c r="D239" t="n">
-        <v>142.5599975585938</v>
+        <v>142.1399993896484</v>
       </c>
       <c r="E239" t="n">
-        <v>142.9700012207031</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="F239" t="n">
-        <v>15794100</v>
+        <v>9785200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>143.0200042724609</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="C240" t="n">
-        <v>145.2700042724609</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="D240" t="n">
-        <v>142.1399993896484</v>
+        <v>145</v>
       </c>
       <c r="E240" t="n">
-        <v>144.6799926757812</v>
+        <v>146.6000061035156</v>
       </c>
       <c r="F240" t="n">
-        <v>9785200</v>
+        <v>7061800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>145.2400054931641</v>
+        <v>145.7299957275391</v>
       </c>
       <c r="C241" t="n">
-        <v>146.8000030517578</v>
+        <v>146.1199951171875</v>
       </c>
       <c r="D241" t="n">
-        <v>145</v>
+        <v>144.9499969482422</v>
       </c>
       <c r="E241" t="n">
-        <v>146.6000061035156</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F241" t="n">
-        <v>7061800</v>
+        <v>9125700</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>145.7299957275391</v>
+        <v>145.2799987792969</v>
       </c>
       <c r="C242" t="n">
-        <v>146.1199951171875</v>
+        <v>145.9299926757812</v>
       </c>
       <c r="D242" t="n">
-        <v>144.9499969482422</v>
+        <v>144.5</v>
       </c>
       <c r="E242" t="n">
-        <v>145.3999938964844</v>
+        <v>145</v>
       </c>
       <c r="F242" t="n">
-        <v>9125700</v>
+        <v>8249100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>145.2799987792969</v>
+        <v>143.6999969482422</v>
       </c>
       <c r="C243" t="n">
-        <v>145.9299926757812</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="D243" t="n">
-        <v>144.5</v>
+        <v>142.7100067138672</v>
       </c>
       <c r="E243" t="n">
-        <v>145</v>
+        <v>143.1399993896484</v>
       </c>
       <c r="F243" t="n">
-        <v>8249100</v>
+        <v>7817200</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>143.6999969482422</v>
+        <v>143.25</v>
       </c>
       <c r="C244" t="n">
-        <v>144.1499938964844</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D244" t="n">
-        <v>142.7100067138672</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="E244" t="n">
-        <v>143.1399993896484</v>
+        <v>143.7799987792969</v>
       </c>
       <c r="F244" t="n">
-        <v>7817200</v>
+        <v>5868900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>143.25</v>
+        <v>143.4400024414062</v>
       </c>
       <c r="C245" t="n">
-        <v>144.3999938964844</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D245" t="n">
-        <v>143.0099945068359</v>
+        <v>142.5</v>
       </c>
       <c r="E245" t="n">
-        <v>143.7799987792969</v>
+        <v>145.1199951171875</v>
       </c>
       <c r="F245" t="n">
-        <v>5868900</v>
+        <v>12097900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>143.4400024414062</v>
+        <v>145.7599945068359</v>
       </c>
       <c r="C246" t="n">
-        <v>145.8999938964844</v>
+        <v>148.3600006103516</v>
       </c>
       <c r="D246" t="n">
-        <v>142.5</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E246" t="n">
-        <v>145.1199951171875</v>
+        <v>146.2100067138672</v>
       </c>
       <c r="F246" t="n">
-        <v>12097900</v>
+        <v>8503800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>145.7599945068359</v>
+        <v>146.4199981689453</v>
       </c>
       <c r="C247" t="n">
-        <v>148.3600006103516</v>
+        <v>148.3200073242188</v>
       </c>
       <c r="D247" t="n">
-        <v>145.0899963378906</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="E247" t="n">
-        <v>146.2100067138672</v>
+        <v>147.6399993896484</v>
       </c>
       <c r="F247" t="n">
-        <v>8503800</v>
+        <v>7431100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>146.4199981689453</v>
+        <v>147.6799926757812</v>
       </c>
       <c r="C248" t="n">
-        <v>148.3200073242188</v>
+        <v>148.2200012207031</v>
       </c>
       <c r="D248" t="n">
-        <v>145.7899932861328</v>
+        <v>146.5</v>
       </c>
       <c r="E248" t="n">
-        <v>147.6399993896484</v>
+        <v>146.9199981689453</v>
       </c>
       <c r="F248" t="n">
-        <v>7431100</v>
+        <v>6105800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>147.6799926757812</v>
+        <v>146.4700012207031</v>
       </c>
       <c r="C249" t="n">
-        <v>148.2200012207031</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D249" t="n">
-        <v>146.5</v>
+        <v>145.8200073242188</v>
       </c>
       <c r="E249" t="n">
-        <v>146.9199981689453</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F249" t="n">
-        <v>6105800</v>
+        <v>5588200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>146.4700012207031</v>
+        <v>145.6000061035156</v>
       </c>
       <c r="C250" t="n">
-        <v>147.1499938964844</v>
+        <v>146.1600036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>145.8200073242188</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="E250" t="n">
-        <v>146.4400024414062</v>
+        <v>145.5800018310547</v>
       </c>
       <c r="F250" t="n">
-        <v>5588200</v>
+        <v>8325100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>145.6000061035156</v>
+        <v>144.1600036621094</v>
       </c>
       <c r="C251" t="n">
-        <v>146.1600036621094</v>
+        <v>144.4700012207031</v>
       </c>
       <c r="D251" t="n">
-        <v>144.3000030517578</v>
+        <v>142.3399963378906</v>
       </c>
       <c r="E251" t="n">
-        <v>145.5800018310547</v>
+        <v>142.6399993896484</v>
       </c>
       <c r="F251" t="n">
-        <v>8325100</v>
+        <v>9270000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>144.1600036621094</v>
+        <v>142.6000061035156</v>
       </c>
       <c r="C252" t="n">
-        <v>144.4700012207031</v>
+        <v>143.5099945068359</v>
       </c>
       <c r="D252" t="n">
-        <v>142.3399963378906</v>
+        <v>141.8600006103516</v>
       </c>
       <c r="E252" t="n">
-        <v>142.6399993896484</v>
+        <v>142.9700012207031</v>
       </c>
       <c r="F252" t="n">
-        <v>9270000</v>
+        <v>10925000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10806,37 +10806,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>142.97</v>
+      </c>
+      <c r="D2" t="n">
         <v>142.64</v>
       </c>
-      <c r="D2" t="n">
-        <v>145.58</v>
-      </c>
       <c r="E2" t="n">
-        <v>144.16</v>
+        <v>142.6</v>
       </c>
       <c r="F2" t="n">
-        <v>144.16</v>
+        <v>143.51</v>
       </c>
       <c r="G2" t="n">
-        <v>142.34</v>
+        <v>141.86</v>
       </c>
       <c r="H2" t="n">
-        <v>9260540</v>
+        <v>10893968</v>
       </c>
       <c r="I2" t="n">
-        <v>8970706</v>
+        <v>9001740</v>
       </c>
       <c r="J2" t="n">
-        <v>331305975808</v>
+        <v>332072484864</v>
       </c>
       <c r="K2" t="n">
-        <v>21.97843</v>
+        <v>21.564102</v>
       </c>
       <c r="L2" t="n">
-        <v>19.276197</v>
+        <v>19.320793</v>
       </c>
       <c r="M2" t="n">
-        <v>6.49</v>
+        <v>6.63</v>
       </c>
       <c r="N2" t="n">
         <v>167.25</v>
@@ -10872,7 +10872,7 @@
         <v>22.947</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.216063</v>
+        <v>6.230444</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.155</v>
@@ -10884,7 +10884,7 @@
         <v>87031996416</v>
       </c>
       <c r="AC2" t="n">
-        <v>357626118144</v>
+        <v>358393184256</v>
       </c>
       <c r="AD2" t="n">
         <v>24752001024</v>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:42</t>
+          <t>2026-09-11 19:03:17</t>
         </is>
       </c>
     </row>

--- a/data/PG_data.xlsx
+++ b/data/PG_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>153.2144571291697</v>
+        <v>153.4184545574236</v>
       </c>
       <c r="C2" t="n">
-        <v>154.7978981087861</v>
+        <v>154.5841863803252</v>
       </c>
       <c r="D2" t="n">
-        <v>152.8938823700691</v>
+        <v>153.2727454910088</v>
       </c>
       <c r="E2" t="n">
-        <v>154.0984649658203</v>
+        <v>153.3893127441406</v>
       </c>
       <c r="F2" t="n">
-        <v>5819500</v>
+        <v>5957000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>153.4184545574236</v>
+        <v>153.3698919481564</v>
       </c>
       <c r="C3" t="n">
-        <v>154.5841863803252</v>
+        <v>153.9916086583258</v>
       </c>
       <c r="D3" t="n">
-        <v>153.2727454910088</v>
+        <v>151.7378763196521</v>
       </c>
       <c r="E3" t="n">
-        <v>153.3893127441406</v>
+        <v>152.3498840332031</v>
       </c>
       <c r="F3" t="n">
-        <v>5957000</v>
+        <v>5995000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>153.3699073091056</v>
+        <v>152.6510263298436</v>
       </c>
       <c r="C4" t="n">
-        <v>153.9916240815438</v>
+        <v>153.865317940213</v>
       </c>
       <c r="D4" t="n">
-        <v>151.7378915171447</v>
+        <v>152.4081680077697</v>
       </c>
       <c r="E4" t="n">
-        <v>152.3498992919922</v>
+        <v>153.5350341796875</v>
       </c>
       <c r="F4" t="n">
-        <v>5995000</v>
+        <v>6559600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>152.6510263298436</v>
+        <v>153.9041611382593</v>
       </c>
       <c r="C5" t="n">
-        <v>153.865317940213</v>
+        <v>157.0516101729205</v>
       </c>
       <c r="D5" t="n">
-        <v>152.4081680077697</v>
+        <v>153.9041611382593</v>
       </c>
       <c r="E5" t="n">
-        <v>153.5350341796875</v>
+        <v>155.7498931884766</v>
       </c>
       <c r="F5" t="n">
-        <v>6559600</v>
+        <v>6764200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>153.9041762162224</v>
+        <v>153.6321738293003</v>
       </c>
       <c r="C6" t="n">
-        <v>157.0516255592386</v>
+        <v>154.4773308983724</v>
       </c>
       <c r="D6" t="n">
-        <v>153.9041762162224</v>
+        <v>152.670464327899</v>
       </c>
       <c r="E6" t="n">
-        <v>155.7499084472656</v>
+        <v>152.8258972167969</v>
       </c>
       <c r="F6" t="n">
-        <v>6764200</v>
+        <v>7651500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>153.6321891685915</v>
+        <v>153.1076006094224</v>
       </c>
       <c r="C7" t="n">
-        <v>154.4773463220477</v>
+        <v>153.1173096060279</v>
       </c>
       <c r="D7" t="n">
-        <v>152.670479571169</v>
+        <v>151.5144506152748</v>
       </c>
       <c r="E7" t="n">
-        <v>152.8259124755859</v>
+        <v>151.5824432373047</v>
       </c>
       <c r="F7" t="n">
-        <v>7651500</v>
+        <v>17224800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>153.1076006094224</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="C8" t="n">
-        <v>153.1173096060279</v>
+        <v>151.6213049173507</v>
       </c>
       <c r="D8" t="n">
-        <v>151.5144506152748</v>
+        <v>148.677863326978</v>
       </c>
       <c r="E8" t="n">
-        <v>151.5824432373047</v>
+        <v>148.6972961425781</v>
       </c>
       <c r="F8" t="n">
-        <v>17224800</v>
+        <v>8712900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>151.6213049173507</v>
+        <v>148.8235855824238</v>
       </c>
       <c r="C9" t="n">
-        <v>151.6213049173507</v>
+        <v>148.9110110260332</v>
       </c>
       <c r="D9" t="n">
-        <v>148.677863326978</v>
+        <v>146.657293372131</v>
       </c>
       <c r="E9" t="n">
-        <v>148.6972961425781</v>
+        <v>148.1435852050781</v>
       </c>
       <c r="F9" t="n">
-        <v>8712900</v>
+        <v>8853400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>148.8235702535947</v>
+        <v>147.7064465894999</v>
       </c>
       <c r="C10" t="n">
-        <v>148.9109956881993</v>
+        <v>149.2413130899007</v>
       </c>
       <c r="D10" t="n">
-        <v>146.65727826643</v>
+        <v>147.4538644271308</v>
       </c>
       <c r="E10" t="n">
-        <v>148.1435699462891</v>
+        <v>148.0658721923828</v>
       </c>
       <c r="F10" t="n">
-        <v>8853400</v>
+        <v>6483300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>147.7064465894999</v>
+        <v>148.852723372033</v>
       </c>
       <c r="C11" t="n">
-        <v>149.2413130899007</v>
+        <v>149.4841639233416</v>
       </c>
       <c r="D11" t="n">
-        <v>147.4538644271308</v>
+        <v>147.4441480235695</v>
       </c>
       <c r="E11" t="n">
-        <v>148.0658721923828</v>
+        <v>147.8035736083984</v>
       </c>
       <c r="F11" t="n">
-        <v>6483300</v>
+        <v>7511400</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>148.8527387391331</v>
+        <v>147.8812940513532</v>
       </c>
       <c r="C12" t="n">
-        <v>149.4841793556296</v>
+        <v>148.3184360922971</v>
       </c>
       <c r="D12" t="n">
-        <v>147.4441632452525</v>
+        <v>147.2012936740075</v>
       </c>
       <c r="E12" t="n">
-        <v>147.8035888671875</v>
+        <v>148.1435852050781</v>
       </c>
       <c r="F12" t="n">
-        <v>7511400</v>
+        <v>5721100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>147.8812788195801</v>
+        <v>148.0658733987316</v>
       </c>
       <c r="C13" t="n">
-        <v>148.3184208154984</v>
+        <v>149.3287397521754</v>
       </c>
       <c r="D13" t="n">
-        <v>147.2012785122745</v>
+        <v>147.4538656284933</v>
       </c>
       <c r="E13" t="n">
-        <v>148.1435699462891</v>
+        <v>149.1441650390625</v>
       </c>
       <c r="F13" t="n">
-        <v>5721100</v>
+        <v>8139700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>148.0658733987316</v>
+        <v>149.0761670451376</v>
       </c>
       <c r="C14" t="n">
-        <v>149.3287397521754</v>
+        <v>149.9698839401892</v>
       </c>
       <c r="D14" t="n">
-        <v>147.4538656284933</v>
+        <v>148.4738682940947</v>
       </c>
       <c r="E14" t="n">
-        <v>149.1441650390625</v>
+        <v>149.2607269287109</v>
       </c>
       <c r="F14" t="n">
-        <v>8139700</v>
+        <v>7762600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>149.0761670451376</v>
+        <v>149.3092876242202</v>
       </c>
       <c r="C15" t="n">
-        <v>149.9698839401892</v>
+        <v>149.4938623134623</v>
       </c>
       <c r="D15" t="n">
-        <v>148.4738682940947</v>
+        <v>147.0847120028435</v>
       </c>
       <c r="E15" t="n">
-        <v>149.2607269287109</v>
+        <v>148.8041381835938</v>
       </c>
       <c r="F15" t="n">
-        <v>7762600</v>
+        <v>7566000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>149.3093029348087</v>
+        <v>148.3572946891603</v>
       </c>
       <c r="C16" t="n">
-        <v>149.4938776429776</v>
+        <v>148.4350111318697</v>
       </c>
       <c r="D16" t="n">
-        <v>147.0847270853178</v>
+        <v>147.2984359501739</v>
       </c>
       <c r="E16" t="n">
-        <v>148.8041534423828</v>
+        <v>147.7064361572266</v>
       </c>
       <c r="F16" t="n">
-        <v>7566000</v>
+        <v>6892100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>148.3573100151862</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="C17" t="n">
-        <v>148.4350264659241</v>
+        <v>149.0470174793467</v>
       </c>
       <c r="D17" t="n">
-        <v>147.2984511668146</v>
+        <v>147.6578748506764</v>
       </c>
       <c r="E17" t="n">
-        <v>147.7064514160156</v>
+        <v>147.920166015625</v>
       </c>
       <c r="F17" t="n">
-        <v>6892100</v>
+        <v>5212600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>147.6578748506764</v>
+        <v>147.1721553229241</v>
       </c>
       <c r="C18" t="n">
-        <v>149.0470174793467</v>
+        <v>147.9687378000585</v>
       </c>
       <c r="D18" t="n">
-        <v>147.6578748506764</v>
+        <v>146.1035726884504</v>
       </c>
       <c r="E18" t="n">
-        <v>147.920166015625</v>
+        <v>146.1132965087891</v>
       </c>
       <c r="F18" t="n">
-        <v>5212600</v>
+        <v>6737000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>147.1721399535571</v>
+        <v>146.4532990159929</v>
       </c>
       <c r="C19" t="n">
-        <v>147.9687223475034</v>
+        <v>148.794457146909</v>
       </c>
       <c r="D19" t="n">
-        <v>146.1035574306768</v>
+        <v>145.763589579418</v>
       </c>
       <c r="E19" t="n">
-        <v>146.11328125</v>
+        <v>148.1824493408203</v>
       </c>
       <c r="F19" t="n">
-        <v>6737000</v>
+        <v>6844400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>146.4532839352596</v>
+        <v>148.4253009046995</v>
       </c>
       <c r="C20" t="n">
-        <v>148.7944418250997</v>
+        <v>148.4253009046995</v>
       </c>
       <c r="D20" t="n">
-        <v>145.7635745697061</v>
+        <v>146.3270160509716</v>
       </c>
       <c r="E20" t="n">
-        <v>148.1824340820312</v>
+        <v>146.3852996826172</v>
       </c>
       <c r="F20" t="n">
-        <v>6844400</v>
+        <v>5254700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>148.4252854332665</v>
+        <v>146.4338752834919</v>
       </c>
       <c r="C21" t="n">
-        <v>148.4252854332665</v>
+        <v>146.5601515452587</v>
       </c>
       <c r="D21" t="n">
-        <v>146.3270007982578</v>
+        <v>145.3070089879124</v>
       </c>
       <c r="E21" t="n">
-        <v>146.3852844238281</v>
+        <v>146.2784423828125</v>
       </c>
       <c r="F21" t="n">
-        <v>5254700</v>
+        <v>6134500</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>146.4338752834919</v>
+        <v>146.6281558533259</v>
       </c>
       <c r="C22" t="n">
-        <v>146.5601515452587</v>
+        <v>147.1818651686376</v>
       </c>
       <c r="D22" t="n">
-        <v>145.3070089879124</v>
+        <v>145.1807147897232</v>
       </c>
       <c r="E22" t="n">
-        <v>146.2784423828125</v>
+        <v>145.4138641357422</v>
       </c>
       <c r="F22" t="n">
-        <v>6134500</v>
+        <v>7374000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>146.6281558533259</v>
+        <v>144.7435618289234</v>
       </c>
       <c r="C23" t="n">
-        <v>147.1818651686376</v>
+        <v>145.1612710333055</v>
       </c>
       <c r="D23" t="n">
-        <v>145.1807147897232</v>
+        <v>142.7715534139986</v>
       </c>
       <c r="E23" t="n">
-        <v>145.4138641357422</v>
+        <v>143.2767028808594</v>
       </c>
       <c r="F23" t="n">
-        <v>7374000</v>
+        <v>7511100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>144.7435618289234</v>
+        <v>143.3544115097172</v>
       </c>
       <c r="C24" t="n">
-        <v>145.1612710333055</v>
+        <v>144.9864122512237</v>
       </c>
       <c r="D24" t="n">
-        <v>142.7715534139986</v>
+        <v>142.8784038819969</v>
       </c>
       <c r="E24" t="n">
-        <v>143.2767028808594</v>
+        <v>144.8989868164062</v>
       </c>
       <c r="F24" t="n">
-        <v>7511100</v>
+        <v>8585300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>143.3544266058526</v>
+        <v>144.2870013812095</v>
       </c>
       <c r="C25" t="n">
-        <v>144.9864275192193</v>
+        <v>145.1418675145521</v>
       </c>
       <c r="D25" t="n">
-        <v>142.8784189280057</v>
+        <v>143.0630006362941</v>
       </c>
       <c r="E25" t="n">
-        <v>144.8990020751953</v>
+        <v>143.2087097167969</v>
       </c>
       <c r="F25" t="n">
-        <v>8585300</v>
+        <v>10003100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>144.2869860075292</v>
+        <v>143.7818410230574</v>
       </c>
       <c r="C26" t="n">
-        <v>145.1418520497865</v>
+        <v>146.1035660756974</v>
       </c>
       <c r="D26" t="n">
-        <v>143.0629853930302</v>
+        <v>143.6944155813474</v>
       </c>
       <c r="E26" t="n">
-        <v>143.2086944580078</v>
+        <v>145.3264312744141</v>
       </c>
       <c r="F26" t="n">
-        <v>10003100</v>
+        <v>8809700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>143.7818259264451</v>
+        <v>146.2687203464973</v>
       </c>
       <c r="C27" t="n">
-        <v>146.1035507353118</v>
+        <v>147.6870046758011</v>
       </c>
       <c r="D27" t="n">
-        <v>143.6944004939145</v>
+        <v>146.1327054533545</v>
       </c>
       <c r="E27" t="n">
-        <v>145.326416015625</v>
+        <v>147.0749969482422</v>
       </c>
       <c r="F27" t="n">
-        <v>8809700</v>
+        <v>8612900</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>146.2687203464973</v>
+        <v>147.2595781352121</v>
       </c>
       <c r="C28" t="n">
-        <v>147.6870046758011</v>
+        <v>148.0367277806686</v>
       </c>
       <c r="D28" t="n">
-        <v>146.1327054533545</v>
+        <v>146.9778689854687</v>
       </c>
       <c r="E28" t="n">
-        <v>147.0749969482422</v>
+        <v>147.6190185546875</v>
       </c>
       <c r="F28" t="n">
-        <v>8612900</v>
+        <v>5601300</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>147.2595781352121</v>
+        <v>147.6189948407767</v>
       </c>
       <c r="C29" t="n">
-        <v>148.0367277806686</v>
+        <v>147.9298457552854</v>
       </c>
       <c r="D29" t="n">
-        <v>146.9778689854687</v>
+        <v>146.5601213927804</v>
       </c>
       <c r="E29" t="n">
-        <v>147.6190185546875</v>
+        <v>147.2886962890625</v>
       </c>
       <c r="F29" t="n">
-        <v>5601300</v>
+        <v>6013400</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>147.6189948407767</v>
+        <v>146.9778583106544</v>
       </c>
       <c r="C30" t="n">
-        <v>147.9298457552854</v>
+        <v>149.076157754121</v>
       </c>
       <c r="D30" t="n">
-        <v>146.5601213927804</v>
+        <v>146.4824178509246</v>
       </c>
       <c r="E30" t="n">
-        <v>147.2886962890625</v>
+        <v>147.8521423339844</v>
       </c>
       <c r="F30" t="n">
-        <v>6013400</v>
+        <v>6394400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>146.9778583106544</v>
+        <v>147.9978775181488</v>
       </c>
       <c r="C31" t="n">
-        <v>149.076157754121</v>
+        <v>148.9207362405373</v>
       </c>
       <c r="D31" t="n">
-        <v>146.4824178509246</v>
+        <v>146.2784363299136</v>
       </c>
       <c r="E31" t="n">
-        <v>147.8521423339844</v>
+        <v>147.8618774414062</v>
       </c>
       <c r="F31" t="n">
-        <v>6394400</v>
+        <v>8205400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,25 +1249,25 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>147.9978622453251</v>
+        <v>152.9946080342638</v>
       </c>
       <c r="C32" t="n">
-        <v>148.9207208724779</v>
+        <v>153.9728344665201</v>
       </c>
       <c r="D32" t="n">
-        <v>146.2784212345297</v>
+        <v>148.2306500856719</v>
       </c>
       <c r="E32" t="n">
-        <v>147.8618621826172</v>
+        <v>149.1697540283203</v>
       </c>
       <c r="F32" t="n">
-        <v>8205400</v>
+        <v>11968500</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1275,25 +1275,25 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>152.9946080342638</v>
+        <v>148.3089372141624</v>
       </c>
       <c r="C33" t="n">
-        <v>153.9728344665201</v>
+        <v>148.4556652353131</v>
       </c>
       <c r="D33" t="n">
-        <v>148.2306500856719</v>
+        <v>146.8611660081129</v>
       </c>
       <c r="E33" t="n">
-        <v>149.1697540283203</v>
+        <v>148.4361114501953</v>
       </c>
       <c r="F33" t="n">
-        <v>11968500</v>
+        <v>7775300</v>
       </c>
       <c r="G33" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>148.3089219684464</v>
+        <v>147.8295858278712</v>
       </c>
       <c r="C34" t="n">
-        <v>148.4556499745139</v>
+        <v>149.8349531642864</v>
       </c>
       <c r="D34" t="n">
-        <v>146.8611509112235</v>
+        <v>147.3404725715042</v>
       </c>
       <c r="E34" t="n">
-        <v>148.4360961914062</v>
+        <v>148.0741424560547</v>
       </c>
       <c r="F34" t="n">
-        <v>7775300</v>
+        <v>5819300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>147.8295858278712</v>
+        <v>147.3795937684592</v>
       </c>
       <c r="C35" t="n">
-        <v>149.8349531642864</v>
+        <v>147.6828415657792</v>
       </c>
       <c r="D35" t="n">
-        <v>147.3404725715042</v>
+        <v>145.2372755531334</v>
       </c>
       <c r="E35" t="n">
-        <v>148.0741424560547</v>
+        <v>145.5307464599609</v>
       </c>
       <c r="F35" t="n">
-        <v>5819300</v>
+        <v>7405500</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>147.3795937684592</v>
+        <v>146.2155298538287</v>
       </c>
       <c r="C36" t="n">
-        <v>147.6828415657792</v>
+        <v>147.516573011961</v>
       </c>
       <c r="D36" t="n">
-        <v>145.2372755531334</v>
+        <v>146.0883556204121</v>
       </c>
       <c r="E36" t="n">
-        <v>145.5307464599609</v>
+        <v>146.3231353759766</v>
       </c>
       <c r="F36" t="n">
-        <v>7405500</v>
+        <v>6760700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>146.2155146062609</v>
+        <v>145.4720720722042</v>
       </c>
       <c r="C37" t="n">
-        <v>147.5165576287185</v>
+        <v>147.8100328533669</v>
       </c>
       <c r="D37" t="n">
-        <v>146.0883403861062</v>
+        <v>145.2959835371417</v>
       </c>
       <c r="E37" t="n">
-        <v>146.3231201171875</v>
+        <v>147.0959167480469</v>
       </c>
       <c r="F37" t="n">
-        <v>6760700</v>
+        <v>7930300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>145.4720720722042</v>
+        <v>146.8318015049148</v>
       </c>
       <c r="C38" t="n">
-        <v>147.8100328533669</v>
+        <v>146.9491839067269</v>
       </c>
       <c r="D38" t="n">
-        <v>145.2959835371417</v>
+        <v>144.5525320015707</v>
       </c>
       <c r="E38" t="n">
-        <v>147.0959167480469</v>
+        <v>144.7970886230469</v>
       </c>
       <c r="F38" t="n">
-        <v>7930300</v>
+        <v>8946400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>146.8318015049148</v>
+        <v>145.3644630798614</v>
       </c>
       <c r="C39" t="n">
-        <v>146.9491839067269</v>
+        <v>146.2448609544514</v>
       </c>
       <c r="D39" t="n">
-        <v>144.5525320015707</v>
+        <v>143.0656248467459</v>
       </c>
       <c r="E39" t="n">
-        <v>144.7970886230469</v>
+        <v>143.9655914306641</v>
       </c>
       <c r="F39" t="n">
-        <v>8946400</v>
+        <v>9295400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>145.3644630798614</v>
+        <v>143.6721174868199</v>
       </c>
       <c r="C40" t="n">
-        <v>146.2448609544514</v>
+        <v>144.210145032931</v>
       </c>
       <c r="D40" t="n">
-        <v>143.0656248467459</v>
+        <v>142.478679994192</v>
       </c>
       <c r="E40" t="n">
-        <v>143.9655914306641</v>
+        <v>142.6156311035156</v>
       </c>
       <c r="F40" t="n">
-        <v>9295400</v>
+        <v>11199900</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>143.6721174868199</v>
+        <v>142.7036703315847</v>
       </c>
       <c r="C41" t="n">
-        <v>144.210145032931</v>
+        <v>143.4862395011485</v>
       </c>
       <c r="D41" t="n">
-        <v>142.478679994192</v>
+        <v>141.3145906510938</v>
       </c>
       <c r="E41" t="n">
-        <v>142.6156311035156</v>
+        <v>142.9482269287109</v>
       </c>
       <c r="F41" t="n">
-        <v>11199900</v>
+        <v>10024500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>142.703685564269</v>
+        <v>143.7503785207628</v>
       </c>
       <c r="C42" t="n">
-        <v>143.4862548173669</v>
+        <v>144.7188281113408</v>
       </c>
       <c r="D42" t="n">
-        <v>141.3146057355029</v>
+        <v>142.8210663483271</v>
       </c>
       <c r="E42" t="n">
-        <v>142.9482421875</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F42" t="n">
-        <v>10024500</v>
+        <v>8500100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>143.7503785207628</v>
+        <v>143.1927990477494</v>
       </c>
       <c r="C43" t="n">
-        <v>144.7188281113408</v>
+        <v>143.4275638534467</v>
       </c>
       <c r="D43" t="n">
-        <v>142.8210663483271</v>
+        <v>140.9526520163762</v>
       </c>
       <c r="E43" t="n">
-        <v>143.7797241210938</v>
+        <v>142.3319549560547</v>
       </c>
       <c r="F43" t="n">
-        <v>8500100</v>
+        <v>10208100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>143.192783696673</v>
+        <v>142.7819444175452</v>
       </c>
       <c r="C44" t="n">
-        <v>143.4275484772021</v>
+        <v>145.4133611257213</v>
       </c>
       <c r="D44" t="n">
-        <v>140.9526369054562</v>
+        <v>142.4982503778291</v>
       </c>
       <c r="E44" t="n">
-        <v>142.3319396972656</v>
+        <v>145.3057556152344</v>
       </c>
       <c r="F44" t="n">
-        <v>10208100</v>
+        <v>7332500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>142.7819444175452</v>
+        <v>145.2959744173796</v>
       </c>
       <c r="C45" t="n">
-        <v>145.4133611257213</v>
+        <v>145.9024700440282</v>
       </c>
       <c r="D45" t="n">
-        <v>142.4982503778291</v>
+        <v>144.298179252126</v>
       </c>
       <c r="E45" t="n">
-        <v>145.3057556152344</v>
+        <v>144.7872924804688</v>
       </c>
       <c r="F45" t="n">
-        <v>7332500</v>
+        <v>7851100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>145.2959744173796</v>
+        <v>144.9535841420777</v>
       </c>
       <c r="C46" t="n">
-        <v>145.9024700440282</v>
+        <v>145.7557369733869</v>
       </c>
       <c r="D46" t="n">
-        <v>144.298179252126</v>
+        <v>144.4253484415343</v>
       </c>
       <c r="E46" t="n">
-        <v>144.7872924804688</v>
+        <v>144.7383880615234</v>
       </c>
       <c r="F46" t="n">
-        <v>7851100</v>
+        <v>7566800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>144.9535841420777</v>
+        <v>145.8535682267802</v>
       </c>
       <c r="C47" t="n">
-        <v>145.7557369733869</v>
+        <v>146.1274704359541</v>
       </c>
       <c r="D47" t="n">
-        <v>144.4253484415343</v>
+        <v>144.3960054571006</v>
       </c>
       <c r="E47" t="n">
-        <v>144.7383880615234</v>
+        <v>144.4546966552734</v>
       </c>
       <c r="F47" t="n">
-        <v>7566800</v>
+        <v>9150800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>145.8535682267802</v>
+        <v>144.5329589094707</v>
       </c>
       <c r="C48" t="n">
-        <v>146.1274704359541</v>
+        <v>144.7579468149716</v>
       </c>
       <c r="D48" t="n">
-        <v>144.3960054571006</v>
+        <v>141.8526130458145</v>
       </c>
       <c r="E48" t="n">
-        <v>144.4546966552734</v>
+        <v>142.6449890136719</v>
       </c>
       <c r="F48" t="n">
-        <v>9150800</v>
+        <v>9902300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>144.5329589094707</v>
+        <v>143.1438871838678</v>
       </c>
       <c r="C49" t="n">
-        <v>144.7579468149716</v>
+        <v>144.1808048975551</v>
       </c>
       <c r="D49" t="n">
-        <v>141.8526130458145</v>
+        <v>142.3417342798896</v>
       </c>
       <c r="E49" t="n">
-        <v>142.6449890136719</v>
+        <v>143.7895202636719</v>
       </c>
       <c r="F49" t="n">
-        <v>9902300</v>
+        <v>10735200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>143.1438719935926</v>
+        <v>143.7601746624582</v>
       </c>
       <c r="C50" t="n">
-        <v>144.1807895972433</v>
+        <v>144.3275329036233</v>
       </c>
       <c r="D50" t="n">
-        <v>142.341719174738</v>
+        <v>142.6841195294514</v>
       </c>
       <c r="E50" t="n">
-        <v>143.7895050048828</v>
+        <v>143.7895202636719</v>
       </c>
       <c r="F50" t="n">
-        <v>10735200</v>
+        <v>6367000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>143.7601594067833</v>
+        <v>143.4471249350237</v>
       </c>
       <c r="C51" t="n">
-        <v>144.3275175877409</v>
+        <v>145.4231465283615</v>
       </c>
       <c r="D51" t="n">
-        <v>142.6841043879663</v>
+        <v>142.9482348228936</v>
       </c>
       <c r="E51" t="n">
-        <v>143.7895050048828</v>
+        <v>144.96337890625</v>
       </c>
       <c r="F51" t="n">
-        <v>6367000</v>
+        <v>9021300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>143.4471249350237</v>
+        <v>145.1492529070371</v>
       </c>
       <c r="C52" t="n">
-        <v>145.4231465283615</v>
+        <v>148.2013148118135</v>
       </c>
       <c r="D52" t="n">
-        <v>142.9482348228936</v>
+        <v>145.0709929958182</v>
       </c>
       <c r="E52" t="n">
-        <v>144.96337890625</v>
+        <v>147.6339416503906</v>
       </c>
       <c r="F52" t="n">
-        <v>9021300</v>
+        <v>12018000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>145.1492529070371</v>
+        <v>146.8318008944829</v>
       </c>
       <c r="C53" t="n">
-        <v>148.2013148118135</v>
+        <v>147.1350487156044</v>
       </c>
       <c r="D53" t="n">
-        <v>145.0709929958182</v>
+        <v>143.3493020808368</v>
       </c>
       <c r="E53" t="n">
-        <v>147.6339416503906</v>
+        <v>143.7797241210938</v>
       </c>
       <c r="F53" t="n">
-        <v>12018000</v>
+        <v>13846900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>146.8318008944829</v>
+        <v>144.112328038909</v>
       </c>
       <c r="C54" t="n">
-        <v>147.1350487156044</v>
+        <v>145.4133560843928</v>
       </c>
       <c r="D54" t="n">
-        <v>143.3493020808368</v>
+        <v>144.0144994231119</v>
       </c>
       <c r="E54" t="n">
-        <v>143.7797241210938</v>
+        <v>145.2568511962891</v>
       </c>
       <c r="F54" t="n">
-        <v>13846900</v>
+        <v>10477700</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>144.1123129003486</v>
+        <v>144.6992629297112</v>
       </c>
       <c r="C55" t="n">
-        <v>145.4133408091634</v>
+        <v>145.7264037459907</v>
       </c>
       <c r="D55" t="n">
-        <v>144.0144842948282</v>
+        <v>144.3960151011972</v>
       </c>
       <c r="E55" t="n">
-        <v>145.2568359375</v>
+        <v>145.0220794677734</v>
       </c>
       <c r="F55" t="n">
-        <v>10477700</v>
+        <v>9238500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>144.6992477048879</v>
+        <v>144.5818741313487</v>
       </c>
       <c r="C56" t="n">
-        <v>145.7263884130947</v>
+        <v>145.4720637945254</v>
       </c>
       <c r="D56" t="n">
-        <v>144.3959999082808</v>
+        <v>143.9753635745919</v>
       </c>
       <c r="E56" t="n">
-        <v>145.0220642089844</v>
+        <v>144.9340362548828</v>
       </c>
       <c r="F56" t="n">
-        <v>9238500</v>
+        <v>4707200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>144.5818741313487</v>
+        <v>144.8753541574702</v>
       </c>
       <c r="C57" t="n">
-        <v>145.4720637945254</v>
+        <v>145.6481465436537</v>
       </c>
       <c r="D57" t="n">
-        <v>143.9753635745919</v>
+        <v>144.1416842645591</v>
       </c>
       <c r="E57" t="n">
-        <v>144.9340362548828</v>
+        <v>144.2297210693359</v>
       </c>
       <c r="F57" t="n">
-        <v>4707200</v>
+        <v>8240700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>144.8753541574702</v>
+        <v>142.1265314991037</v>
       </c>
       <c r="C58" t="n">
-        <v>145.6481465436537</v>
+        <v>143.0069443662482</v>
       </c>
       <c r="D58" t="n">
-        <v>144.1416842645591</v>
+        <v>139.4070628341484</v>
       </c>
       <c r="E58" t="n">
-        <v>144.2297210693359</v>
+        <v>142.6841278076172</v>
       </c>
       <c r="F58" t="n">
-        <v>8240700</v>
+        <v>16376800</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>142.1265162999446</v>
+        <v>142.7428024831051</v>
       </c>
       <c r="C59" t="n">
-        <v>143.0069290729368</v>
+        <v>145.0611944043203</v>
       </c>
       <c r="D59" t="n">
-        <v>139.4070479258121</v>
+        <v>142.6841112840695</v>
       </c>
       <c r="E59" t="n">
-        <v>142.6841125488281</v>
+        <v>143.5156097412109</v>
       </c>
       <c r="F59" t="n">
-        <v>16376800</v>
+        <v>9125300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>142.7428024831051</v>
+        <v>143.47649707149</v>
       </c>
       <c r="C60" t="n">
-        <v>145.0611944043203</v>
+        <v>144.210167039084</v>
       </c>
       <c r="D60" t="n">
-        <v>142.6841112840695</v>
+        <v>141.3537470897712</v>
       </c>
       <c r="E60" t="n">
-        <v>143.5156097412109</v>
+        <v>142.1950225830078</v>
       </c>
       <c r="F60" t="n">
-        <v>9125300</v>
+        <v>10479300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>143.4764816751874</v>
+        <v>141.9993576904224</v>
       </c>
       <c r="C61" t="n">
-        <v>144.210151564052</v>
+        <v>142.4591253245491</v>
       </c>
       <c r="D61" t="n">
-        <v>141.3537319212585</v>
+        <v>140.1309415539968</v>
       </c>
       <c r="E61" t="n">
-        <v>142.1950073242188</v>
+        <v>140.3265838623047</v>
       </c>
       <c r="F61" t="n">
-        <v>10479300</v>
+        <v>12791700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>141.999373131105</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="C62" t="n">
-        <v>142.4591408152259</v>
+        <v>139.7983526087064</v>
       </c>
       <c r="D62" t="n">
-        <v>140.1309567915122</v>
+        <v>135.1322080272313</v>
       </c>
       <c r="E62" t="n">
-        <v>140.3265991210938</v>
+        <v>135.3278503417969</v>
       </c>
       <c r="F62" t="n">
-        <v>12791700</v>
+        <v>17507500</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>139.7983526087064</v>
+        <v>136.1593454188843</v>
       </c>
       <c r="C63" t="n">
-        <v>139.7983526087064</v>
+        <v>137.8125505495836</v>
       </c>
       <c r="D63" t="n">
-        <v>135.1322080272313</v>
+        <v>135.9734800004196</v>
       </c>
       <c r="E63" t="n">
-        <v>135.3278503417969</v>
+        <v>136.5897674560547</v>
       </c>
       <c r="F63" t="n">
-        <v>17507500</v>
+        <v>10375700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>136.1593454188843</v>
+        <v>136.6093231272403</v>
       </c>
       <c r="C64" t="n">
-        <v>137.8125505495836</v>
+        <v>138.2038370797448</v>
       </c>
       <c r="D64" t="n">
-        <v>135.9734800004196</v>
+        <v>136.5017176164599</v>
       </c>
       <c r="E64" t="n">
-        <v>136.5897674560547</v>
+        <v>136.775634765625</v>
       </c>
       <c r="F64" t="n">
-        <v>10375700</v>
+        <v>13650400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>136.6093231272403</v>
+        <v>137.9299396510316</v>
       </c>
       <c r="C65" t="n">
-        <v>138.2038370797448</v>
+        <v>138.7516463474312</v>
       </c>
       <c r="D65" t="n">
-        <v>136.5017176164599</v>
+        <v>137.3038752737911</v>
       </c>
       <c r="E65" t="n">
-        <v>136.775634765625</v>
+        <v>137.6951599121094</v>
       </c>
       <c r="F65" t="n">
-        <v>13650400</v>
+        <v>11798000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>137.9299396510316</v>
+        <v>137.9299404283357</v>
       </c>
       <c r="C66" t="n">
-        <v>138.7516463474312</v>
+        <v>139.9939989991835</v>
       </c>
       <c r="D66" t="n">
-        <v>137.3038752737911</v>
+        <v>137.7734206015055</v>
       </c>
       <c r="E66" t="n">
-        <v>137.6951599121094</v>
+        <v>139.7298736572266</v>
       </c>
       <c r="F66" t="n">
-        <v>11798000</v>
+        <v>10268800</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>137.929925366103</v>
+        <v>140.1504995323008</v>
       </c>
       <c r="C67" t="n">
-        <v>139.9939837115514</v>
+        <v>142.155866623658</v>
       </c>
       <c r="D67" t="n">
-        <v>137.7734055563651</v>
+        <v>140.0820165200331</v>
       </c>
       <c r="E67" t="n">
-        <v>139.7298583984375</v>
+        <v>141.9700012207031</v>
       </c>
       <c r="F67" t="n">
-        <v>10268800</v>
+        <v>13877700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>140.1504995323008</v>
+        <v>142.918899809868</v>
       </c>
       <c r="C68" t="n">
-        <v>142.155866623658</v>
+        <v>143.3493069381574</v>
       </c>
       <c r="D68" t="n">
-        <v>140.0820165200331</v>
+        <v>141.5004594218987</v>
       </c>
       <c r="E68" t="n">
-        <v>141.9700012207031</v>
+        <v>142.0482788085938</v>
       </c>
       <c r="F68" t="n">
-        <v>13877700</v>
+        <v>10251700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>142.918884457557</v>
+        <v>143.496050619897</v>
       </c>
       <c r="C69" t="n">
-        <v>143.3492915396123</v>
+        <v>145.2177239216924</v>
       </c>
       <c r="D69" t="n">
-        <v>141.5004442219562</v>
+        <v>143.2612708815172</v>
       </c>
       <c r="E69" t="n">
-        <v>142.0482635498047</v>
+        <v>144.5916595458984</v>
       </c>
       <c r="F69" t="n">
-        <v>10251700</v>
+        <v>9833300</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>143.496050619897</v>
+        <v>143.4275568592265</v>
       </c>
       <c r="C70" t="n">
-        <v>145.2177239216924</v>
+        <v>144.2884009089423</v>
       </c>
       <c r="D70" t="n">
-        <v>143.2612708815172</v>
+        <v>142.1852200188561</v>
       </c>
       <c r="E70" t="n">
-        <v>144.5916595458984</v>
+        <v>142.3515167236328</v>
       </c>
       <c r="F70" t="n">
-        <v>9833300</v>
+        <v>12239900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>143.4275568592265</v>
+        <v>142.3417162193598</v>
       </c>
       <c r="C71" t="n">
-        <v>144.2884009089423</v>
+        <v>142.8699668272841</v>
       </c>
       <c r="D71" t="n">
-        <v>142.1852200188561</v>
+        <v>140.8059085533541</v>
       </c>
       <c r="E71" t="n">
-        <v>142.3515167236328</v>
+        <v>141.3145904541016</v>
       </c>
       <c r="F71" t="n">
-        <v>12239900</v>
+        <v>19345600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>142.3417162193598</v>
+        <v>140.5809250079643</v>
       </c>
       <c r="C72" t="n">
-        <v>142.8699668272841</v>
+        <v>141.2558886976474</v>
       </c>
       <c r="D72" t="n">
-        <v>140.8059085533541</v>
+        <v>139.3190045706883</v>
       </c>
       <c r="E72" t="n">
-        <v>141.3145904541016</v>
+        <v>139.5831298828125</v>
       </c>
       <c r="F72" t="n">
-        <v>19345600</v>
+        <v>11731400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>140.5809250079643</v>
+        <v>139.387490519737</v>
       </c>
       <c r="C73" t="n">
-        <v>141.2558886976474</v>
+        <v>140.6004817498258</v>
       </c>
       <c r="D73" t="n">
-        <v>139.3190045706883</v>
+        <v>138.9864140977976</v>
       </c>
       <c r="E73" t="n">
-        <v>139.5831298828125</v>
+        <v>140.0624542236328</v>
       </c>
       <c r="F73" t="n">
-        <v>11731400</v>
+        <v>9541600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>139.387490519737</v>
+        <v>139.7885720199097</v>
       </c>
       <c r="C74" t="n">
-        <v>140.6004817498258</v>
+        <v>141.5885202675369</v>
       </c>
       <c r="D74" t="n">
-        <v>138.9864140977976</v>
+        <v>139.72010392126</v>
       </c>
       <c r="E74" t="n">
-        <v>140.0624542236328</v>
+        <v>141.3439636230469</v>
       </c>
       <c r="F74" t="n">
-        <v>9541600</v>
+        <v>3259200</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>139.7885720199097</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="C75" t="n">
-        <v>141.5885202675369</v>
+        <v>142.4688988061542</v>
       </c>
       <c r="D75" t="n">
-        <v>139.72010392126</v>
+        <v>141.1678558435435</v>
       </c>
       <c r="E75" t="n">
-        <v>141.3439636230469</v>
+        <v>141.5885009765625</v>
       </c>
       <c r="F75" t="n">
-        <v>3259200</v>
+        <v>4711500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>141.1678558435435</v>
+        <v>141.6471833233528</v>
       </c>
       <c r="C76" t="n">
-        <v>142.4688988061542</v>
+        <v>141.9113086263453</v>
       </c>
       <c r="D76" t="n">
-        <v>141.1678558435435</v>
+        <v>140.8156849267153</v>
       </c>
       <c r="E76" t="n">
-        <v>141.5885009765625</v>
+        <v>141.4221954345703</v>
       </c>
       <c r="F76" t="n">
-        <v>4711500</v>
+        <v>7662100</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>141.6471833233528</v>
+        <v>141.1482932462777</v>
       </c>
       <c r="C77" t="n">
-        <v>141.9113086263453</v>
+        <v>141.3146048844386</v>
       </c>
       <c r="D77" t="n">
-        <v>140.8156849267153</v>
+        <v>140.4439839080415</v>
       </c>
       <c r="E77" t="n">
-        <v>141.4221954345703</v>
+        <v>140.9135284423828</v>
       </c>
       <c r="F77" t="n">
-        <v>7662100</v>
+        <v>6006400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>141.1482779620671</v>
+        <v>140.8646302306951</v>
       </c>
       <c r="C78" t="n">
-        <v>141.3145895822191</v>
+        <v>141.0015813574684</v>
       </c>
       <c r="D78" t="n">
-        <v>140.443968700097</v>
+        <v>140.1113915701655</v>
       </c>
       <c r="E78" t="n">
-        <v>140.9135131835938</v>
+        <v>140.1896514892578</v>
       </c>
       <c r="F78" t="n">
-        <v>6006400</v>
+        <v>5293200</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>140.8646148984387</v>
+        <v>139.9939944106823</v>
       </c>
       <c r="C79" t="n">
-        <v>141.0015660103057</v>
+        <v>140.2189823252813</v>
       </c>
       <c r="D79" t="n">
-        <v>140.1113763198945</v>
+        <v>138.164715640037</v>
       </c>
       <c r="E79" t="n">
-        <v>140.1896362304688</v>
+        <v>138.7027282714844</v>
       </c>
       <c r="F79" t="n">
-        <v>5293200</v>
+        <v>8946100</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>139.9939944106823</v>
+        <v>138.0277758154179</v>
       </c>
       <c r="C80" t="n">
-        <v>140.2189823252813</v>
+        <v>138.2723324593669</v>
       </c>
       <c r="D80" t="n">
-        <v>138.164715640037</v>
+        <v>136.5604359517241</v>
       </c>
       <c r="E80" t="n">
-        <v>138.7027282714844</v>
+        <v>137.3136596679688</v>
       </c>
       <c r="F80" t="n">
-        <v>8946100</v>
+        <v>12297300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>138.0277758154179</v>
+        <v>137.3332072243459</v>
       </c>
       <c r="C81" t="n">
-        <v>138.2723324593669</v>
+        <v>138.3407792480867</v>
       </c>
       <c r="D81" t="n">
-        <v>136.5604359517241</v>
+        <v>136.4723631937515</v>
       </c>
       <c r="E81" t="n">
-        <v>137.3136596679688</v>
+        <v>136.8636627197266</v>
       </c>
       <c r="F81" t="n">
-        <v>12297300</v>
+        <v>10421800</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>137.333222535484</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="C82" t="n">
-        <v>138.340794671558</v>
+        <v>136.7560662263838</v>
       </c>
       <c r="D82" t="n">
-        <v>136.472378408915</v>
+        <v>134.6235247173271</v>
       </c>
       <c r="E82" t="n">
-        <v>136.8636779785156</v>
+        <v>135.0343780517578</v>
       </c>
       <c r="F82" t="n">
-        <v>10421800</v>
+        <v>14369100</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>136.7560662263838</v>
+        <v>134.8876360609042</v>
       </c>
       <c r="C83" t="n">
-        <v>136.7560662263838</v>
+        <v>138.6929361136317</v>
       </c>
       <c r="D83" t="n">
-        <v>134.6235247173271</v>
+        <v>134.8191679755417</v>
       </c>
       <c r="E83" t="n">
-        <v>135.0343780517578</v>
+        <v>138.4483795166016</v>
       </c>
       <c r="F83" t="n">
-        <v>14369100</v>
+        <v>9297100</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>134.8876360609042</v>
+        <v>138.6146938845888</v>
       </c>
       <c r="C84" t="n">
-        <v>138.6929361136317</v>
+        <v>139.2309813641768</v>
       </c>
       <c r="D84" t="n">
-        <v>134.8191679755417</v>
+        <v>137.7636415949117</v>
       </c>
       <c r="E84" t="n">
-        <v>138.4483795166016</v>
+        <v>138.7809906005859</v>
       </c>
       <c r="F84" t="n">
-        <v>9297100</v>
+        <v>9528500</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>138.6146938845888</v>
+        <v>139.1820498418749</v>
       </c>
       <c r="C85" t="n">
-        <v>139.2309813641768</v>
+        <v>140.7472180394953</v>
       </c>
       <c r="D85" t="n">
-        <v>137.7636415949117</v>
+        <v>138.6244685603122</v>
       </c>
       <c r="E85" t="n">
-        <v>138.7809906005859</v>
+        <v>140.3363647460938</v>
       </c>
       <c r="F85" t="n">
-        <v>9528500</v>
+        <v>12812000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>139.1820649751552</v>
+        <v>140.8646007849644</v>
       </c>
       <c r="C86" t="n">
-        <v>140.7472333429565</v>
+        <v>141.1971941766679</v>
       </c>
       <c r="D86" t="n">
-        <v>138.6244836329666</v>
+        <v>139.8570287929182</v>
       </c>
       <c r="E86" t="n">
-        <v>140.3363800048828</v>
+        <v>141.0993804931641</v>
       </c>
       <c r="F86" t="n">
-        <v>12812000</v>
+        <v>15549200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>140.8646007849644</v>
+        <v>141.529800782003</v>
       </c>
       <c r="C87" t="n">
-        <v>141.1971941766679</v>
+        <v>143.7014647743148</v>
       </c>
       <c r="D87" t="n">
-        <v>139.8570287929182</v>
+        <v>141.2265529596936</v>
       </c>
       <c r="E87" t="n">
-        <v>141.0993804931641</v>
+        <v>143.1634521484375</v>
       </c>
       <c r="F87" t="n">
-        <v>15549200</v>
+        <v>13475000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>141.5298158666727</v>
+        <v>142.5080218255822</v>
       </c>
       <c r="C88" t="n">
-        <v>143.7014800904468</v>
+        <v>143.1634466813173</v>
       </c>
       <c r="D88" t="n">
-        <v>141.2265680120421</v>
+        <v>141.20699378469</v>
       </c>
       <c r="E88" t="n">
-        <v>143.1634674072266</v>
+        <v>141.4808959960938</v>
       </c>
       <c r="F88" t="n">
-        <v>13475000</v>
+        <v>10102800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>142.5080218255822</v>
+        <v>140.6298333307039</v>
       </c>
       <c r="C89" t="n">
-        <v>143.1634466813173</v>
+        <v>141.5787142100195</v>
       </c>
       <c r="D89" t="n">
-        <v>141.20699378469</v>
+        <v>140.5320196386769</v>
       </c>
       <c r="E89" t="n">
-        <v>141.4808959960938</v>
+        <v>141.3830718994141</v>
       </c>
       <c r="F89" t="n">
-        <v>10102800</v>
+        <v>11729300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>140.6298333307039</v>
+        <v>141.3145973124275</v>
       </c>
       <c r="C90" t="n">
-        <v>141.5787142100195</v>
+        <v>143.7992858886719</v>
       </c>
       <c r="D90" t="n">
-        <v>140.5320196386769</v>
+        <v>140.9819889804792</v>
       </c>
       <c r="E90" t="n">
-        <v>141.3830718994141</v>
+        <v>143.7992858886719</v>
       </c>
       <c r="F90" t="n">
-        <v>11729300</v>
+        <v>12901400</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>141.314612307562</v>
+        <v>143.8579872458876</v>
       </c>
       <c r="C91" t="n">
-        <v>143.7993011474609</v>
+        <v>144.1612350737863</v>
       </c>
       <c r="D91" t="n">
-        <v>140.98200394032</v>
+        <v>141.8134974355268</v>
       </c>
       <c r="E91" t="n">
-        <v>143.7993011474609</v>
+        <v>142.8797607421875</v>
       </c>
       <c r="F91" t="n">
-        <v>12901400</v>
+        <v>14126800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>143.8579872458876</v>
+        <v>144.8557716267987</v>
       </c>
       <c r="C92" t="n">
-        <v>144.1612350737863</v>
+        <v>147.6241542164368</v>
       </c>
       <c r="D92" t="n">
-        <v>141.8134974355268</v>
+        <v>144.2883985058945</v>
       </c>
       <c r="E92" t="n">
-        <v>142.8797607421875</v>
+        <v>146.6654815673828</v>
       </c>
       <c r="F92" t="n">
-        <v>14126800</v>
+        <v>18501900</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,25 +2835,25 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>144.8557716267987</v>
+        <v>148.6033244770038</v>
       </c>
       <c r="C93" t="n">
-        <v>147.6241542164368</v>
+        <v>149.401311303758</v>
       </c>
       <c r="D93" t="n">
-        <v>144.2883985058945</v>
+        <v>147.5787523243573</v>
       </c>
       <c r="E93" t="n">
-        <v>146.6654815673828</v>
+        <v>147.9235534667969</v>
       </c>
       <c r="F93" t="n">
-        <v>18501900</v>
+        <v>14562600</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -2861,25 +2861,25 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>148.6033244770038</v>
+        <v>147.8940093166009</v>
       </c>
       <c r="C94" t="n">
-        <v>149.401311303758</v>
+        <v>148.642749624448</v>
       </c>
       <c r="D94" t="n">
-        <v>147.5787523243573</v>
+        <v>146.3177432055359</v>
       </c>
       <c r="E94" t="n">
-        <v>147.9235534667969</v>
+        <v>147.2733612060547</v>
       </c>
       <c r="F94" t="n">
-        <v>14562600</v>
+        <v>12655700</v>
       </c>
       <c r="G94" t="n">
-        <v>1.057</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>147.8940093166009</v>
+        <v>145.8744105284403</v>
       </c>
       <c r="C95" t="n">
-        <v>148.642749624448</v>
+        <v>147.4211225953709</v>
       </c>
       <c r="D95" t="n">
-        <v>146.3177432055359</v>
+        <v>145.7364720311358</v>
       </c>
       <c r="E95" t="n">
-        <v>147.2733612060547</v>
+        <v>146.1403961181641</v>
       </c>
       <c r="F95" t="n">
-        <v>12655700</v>
+        <v>9546000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>145.8744105284403</v>
+        <v>145.8054447387209</v>
       </c>
       <c r="C96" t="n">
-        <v>147.4211225953709</v>
+        <v>146.5049234190107</v>
       </c>
       <c r="D96" t="n">
-        <v>145.7364720311358</v>
+        <v>144.613380096476</v>
       </c>
       <c r="E96" t="n">
-        <v>146.1403961181641</v>
+        <v>145.1552276611328</v>
       </c>
       <c r="F96" t="n">
-        <v>9546000</v>
+        <v>7465800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>145.8054447387209</v>
+        <v>145.1059620999764</v>
       </c>
       <c r="C97" t="n">
-        <v>146.5049234190107</v>
+        <v>147.9038617122788</v>
       </c>
       <c r="D97" t="n">
-        <v>144.613380096476</v>
+        <v>144.9286383741246</v>
       </c>
       <c r="E97" t="n">
-        <v>145.1552276611328</v>
+        <v>147.6772613525391</v>
       </c>
       <c r="F97" t="n">
-        <v>7465800</v>
+        <v>11035600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>145.1059620999764</v>
+        <v>148.1994047112546</v>
       </c>
       <c r="C98" t="n">
-        <v>147.9038617122788</v>
+        <v>149.7165778862847</v>
       </c>
       <c r="D98" t="n">
-        <v>144.9286383741246</v>
+        <v>146.9383858562462</v>
       </c>
       <c r="E98" t="n">
-        <v>147.6772613525391</v>
+        <v>149.5195465087891</v>
       </c>
       <c r="F98" t="n">
-        <v>11035600</v>
+        <v>12651400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>148.1994047112546</v>
+        <v>150.1599009677594</v>
       </c>
       <c r="C99" t="n">
-        <v>149.7165778862847</v>
+        <v>151.4504737667986</v>
       </c>
       <c r="D99" t="n">
-        <v>146.9383858562462</v>
+        <v>149.0072516350481</v>
       </c>
       <c r="E99" t="n">
-        <v>149.5195465087891</v>
+        <v>150.9184875488281</v>
       </c>
       <c r="F99" t="n">
-        <v>12651400</v>
+        <v>10554900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>150.1599009677594</v>
+        <v>150.3273766276017</v>
       </c>
       <c r="C100" t="n">
-        <v>151.4504737667986</v>
+        <v>154.2089563191786</v>
       </c>
       <c r="D100" t="n">
-        <v>149.0072516350481</v>
+        <v>149.9431601878661</v>
       </c>
       <c r="E100" t="n">
-        <v>150.9184875488281</v>
+        <v>153.0169067382812</v>
       </c>
       <c r="F100" t="n">
-        <v>10554900</v>
+        <v>12424700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>150.3273766276017</v>
+        <v>153.8148971925123</v>
       </c>
       <c r="C101" t="n">
-        <v>154.2089563191786</v>
+        <v>156.0216726798457</v>
       </c>
       <c r="D101" t="n">
-        <v>149.9431601878661</v>
+        <v>153.450373358777</v>
       </c>
       <c r="E101" t="n">
-        <v>153.0169067382812</v>
+        <v>154.5439147949219</v>
       </c>
       <c r="F101" t="n">
-        <v>12424700</v>
+        <v>12178500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>153.8148971925123</v>
+        <v>156.4847030065954</v>
       </c>
       <c r="C102" t="n">
-        <v>156.0216726798457</v>
+        <v>157.2826898506833</v>
       </c>
       <c r="D102" t="n">
-        <v>153.450373358777</v>
+        <v>153.8050342014295</v>
       </c>
       <c r="E102" t="n">
-        <v>154.5439147949219</v>
+        <v>156.2581176757812</v>
       </c>
       <c r="F102" t="n">
-        <v>12178500</v>
+        <v>13077700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>156.4847030065954</v>
+        <v>155.8935966032756</v>
       </c>
       <c r="C103" t="n">
-        <v>157.2826898506833</v>
+        <v>157.6176473147596</v>
       </c>
       <c r="D103" t="n">
-        <v>153.8050342014295</v>
+        <v>155.6669962577738</v>
       </c>
       <c r="E103" t="n">
-        <v>156.2581176757812</v>
+        <v>156.8097991943359</v>
       </c>
       <c r="F103" t="n">
-        <v>13077700</v>
+        <v>10441700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>155.8935966032756</v>
+        <v>156.4058894678126</v>
       </c>
       <c r="C104" t="n">
-        <v>157.6176473147596</v>
+        <v>156.9181830781391</v>
       </c>
       <c r="D104" t="n">
-        <v>155.6669962577738</v>
+        <v>153.7065280129841</v>
       </c>
       <c r="E104" t="n">
-        <v>156.8097991943359</v>
+        <v>154.9971008300781</v>
       </c>
       <c r="F104" t="n">
-        <v>10441700</v>
+        <v>11439900</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>156.4058894678126</v>
+        <v>155.1941261981174</v>
       </c>
       <c r="C105" t="n">
-        <v>156.9181830781391</v>
+        <v>157.7752717323398</v>
       </c>
       <c r="D105" t="n">
-        <v>153.7065280129841</v>
+        <v>154.3961393746382</v>
       </c>
       <c r="E105" t="n">
-        <v>154.9971008300781</v>
+        <v>156.7211456298828</v>
       </c>
       <c r="F105" t="n">
-        <v>11439900</v>
+        <v>9910100</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>155.1941261981174</v>
+        <v>156.2876680693531</v>
       </c>
       <c r="C106" t="n">
-        <v>157.7752717323398</v>
+        <v>158.7505977950001</v>
       </c>
       <c r="D106" t="n">
-        <v>154.3961393746382</v>
+        <v>155.8443437252427</v>
       </c>
       <c r="E106" t="n">
-        <v>156.7211456298828</v>
+        <v>157.6275024414062</v>
       </c>
       <c r="F106" t="n">
-        <v>9910100</v>
+        <v>10217300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>156.2876680693531</v>
+        <v>157.6472078811371</v>
       </c>
       <c r="C107" t="n">
-        <v>158.7505977950001</v>
+        <v>160.7209393253002</v>
       </c>
       <c r="D107" t="n">
-        <v>155.8443437252427</v>
+        <v>157.2826840647245</v>
       </c>
       <c r="E107" t="n">
-        <v>157.6275024414062</v>
+        <v>158.8195648193359</v>
       </c>
       <c r="F107" t="n">
-        <v>10217300</v>
+        <v>13512900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>157.6472078811371</v>
+        <v>159.3417228437737</v>
       </c>
       <c r="C108" t="n">
-        <v>160.7209393253002</v>
+        <v>160.1594173981944</v>
       </c>
       <c r="D108" t="n">
-        <v>157.2826840647245</v>
+        <v>157.3418249095697</v>
       </c>
       <c r="E108" t="n">
-        <v>158.8195648193359</v>
+        <v>157.6964874267578</v>
       </c>
       <c r="F108" t="n">
-        <v>13512900</v>
+        <v>13998900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>159.3417228437737</v>
+        <v>157.5782363157609</v>
       </c>
       <c r="C109" t="n">
-        <v>160.1594173981944</v>
+        <v>159.765319051939</v>
       </c>
       <c r="D109" t="n">
-        <v>157.3418249095697</v>
+        <v>156.5241102403673</v>
       </c>
       <c r="E109" t="n">
-        <v>157.6964874267578</v>
+        <v>157.1841735839844</v>
       </c>
       <c r="F109" t="n">
-        <v>13998900</v>
+        <v>13319100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>157.5782363157609</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="C110" t="n">
-        <v>159.765319051939</v>
+        <v>156.6226326022383</v>
       </c>
       <c r="D110" t="n">
-        <v>156.5241102403673</v>
+        <v>153.4602390569104</v>
       </c>
       <c r="E110" t="n">
-        <v>157.1841735839844</v>
+        <v>154.5340728759766</v>
       </c>
       <c r="F110" t="n">
-        <v>13319100</v>
+        <v>14434300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>156.6226326022383</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="C111" t="n">
-        <v>156.6226326022383</v>
+        <v>157.588096663496</v>
       </c>
       <c r="D111" t="n">
-        <v>153.4602390569104</v>
+        <v>154.5045039445223</v>
       </c>
       <c r="E111" t="n">
-        <v>154.5340728759766</v>
+        <v>156.2088470458984</v>
       </c>
       <c r="F111" t="n">
-        <v>14434300</v>
+        <v>10724600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>154.5045039445223</v>
+        <v>156.7704074552917</v>
       </c>
       <c r="C112" t="n">
-        <v>157.588096663496</v>
+        <v>158.6717819848204</v>
       </c>
       <c r="D112" t="n">
-        <v>154.5045039445223</v>
+        <v>155.8147895206744</v>
       </c>
       <c r="E112" t="n">
-        <v>156.2088470458984</v>
+        <v>158.3959350585938</v>
       </c>
       <c r="F112" t="n">
-        <v>10724600</v>
+        <v>11508100</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>156.7704074552917</v>
+        <v>157.9427805830092</v>
       </c>
       <c r="C113" t="n">
-        <v>158.6717819848204</v>
+        <v>162.9080407961134</v>
       </c>
       <c r="D113" t="n">
-        <v>155.8147895206744</v>
+        <v>157.9230729341091</v>
       </c>
       <c r="E113" t="n">
-        <v>158.3959350585938</v>
+        <v>162.7208557128906</v>
       </c>
       <c r="F113" t="n">
-        <v>11508100</v>
+        <v>14772400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>157.9427805830092</v>
+        <v>162.4548534700461</v>
       </c>
       <c r="C114" t="n">
-        <v>162.9080407961134</v>
+        <v>164.3956434730223</v>
       </c>
       <c r="D114" t="n">
-        <v>157.9230729341091</v>
+        <v>161.509096787574</v>
       </c>
       <c r="E114" t="n">
-        <v>162.7208557128906</v>
+        <v>162.8292236328125</v>
       </c>
       <c r="F114" t="n">
-        <v>14772400</v>
+        <v>9709500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>162.4548534700461</v>
+        <v>162.1001810746762</v>
       </c>
       <c r="C115" t="n">
-        <v>164.3956434730223</v>
+        <v>162.5533667721119</v>
       </c>
       <c r="D115" t="n">
-        <v>161.509096787574</v>
+        <v>159.6963742176143</v>
       </c>
       <c r="E115" t="n">
-        <v>162.8292236328125</v>
+        <v>160.9672393798828</v>
       </c>
       <c r="F115" t="n">
-        <v>9709500</v>
+        <v>7878500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>162.1001810746762</v>
+        <v>161.7849314119297</v>
       </c>
       <c r="C116" t="n">
-        <v>162.5533667721119</v>
+        <v>162.0607783426765</v>
       </c>
       <c r="D116" t="n">
-        <v>159.6963742176143</v>
+        <v>160.4450970200751</v>
       </c>
       <c r="E116" t="n">
-        <v>160.9672393798828</v>
+        <v>161.3218994140625</v>
       </c>
       <c r="F116" t="n">
-        <v>7878500</v>
+        <v>7028600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>161.7849314119297</v>
+        <v>161.6075869258529</v>
       </c>
       <c r="C117" t="n">
-        <v>162.0607783426765</v>
+        <v>164.7699952425796</v>
       </c>
       <c r="D117" t="n">
-        <v>160.4450970200751</v>
+        <v>161.262785790902</v>
       </c>
       <c r="E117" t="n">
-        <v>161.3218994140625</v>
+        <v>164.7207336425781</v>
       </c>
       <c r="F117" t="n">
-        <v>7028600</v>
+        <v>14878500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>161.6075869258529</v>
+        <v>162.8390693932343</v>
       </c>
       <c r="C118" t="n">
-        <v>164.7699952425796</v>
+        <v>164.0803957045348</v>
       </c>
       <c r="D118" t="n">
-        <v>161.262785790902</v>
+        <v>161.0263565641498</v>
       </c>
       <c r="E118" t="n">
-        <v>164.7207336425781</v>
+        <v>161.0854644775391</v>
       </c>
       <c r="F118" t="n">
-        <v>14878500</v>
+        <v>9095500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>162.8390693932343</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="C119" t="n">
-        <v>164.0803957045348</v>
+        <v>159.7850298016668</v>
       </c>
       <c r="D119" t="n">
-        <v>161.0263565641498</v>
+        <v>156.2679589705066</v>
       </c>
       <c r="E119" t="n">
-        <v>161.0854644775391</v>
+        <v>157.3516540527344</v>
       </c>
       <c r="F119" t="n">
-        <v>9095500</v>
+        <v>10161000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>159.7850298016668</v>
+        <v>157.0758237333674</v>
       </c>
       <c r="C120" t="n">
-        <v>159.7850298016668</v>
+        <v>157.243301166956</v>
       </c>
       <c r="D120" t="n">
-        <v>156.2679589705066</v>
+        <v>154.9774025943761</v>
       </c>
       <c r="E120" t="n">
-        <v>157.3516540527344</v>
+        <v>155.9527282714844</v>
       </c>
       <c r="F120" t="n">
-        <v>10161000</v>
+        <v>8752700</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>157.0758237333674</v>
+        <v>154.6128887776175</v>
       </c>
       <c r="C121" t="n">
-        <v>157.243301166956</v>
+        <v>154.7705198979749</v>
       </c>
       <c r="D121" t="n">
-        <v>154.9774025943761</v>
+        <v>151.4898954891258</v>
       </c>
       <c r="E121" t="n">
-        <v>155.9527282714844</v>
+        <v>151.7066345214844</v>
       </c>
       <c r="F121" t="n">
-        <v>8752700</v>
+        <v>10060300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>154.6128887776175</v>
+        <v>151.3815284437877</v>
       </c>
       <c r="C122" t="n">
-        <v>154.7705198979749</v>
+        <v>152.1401000368933</v>
       </c>
       <c r="D122" t="n">
-        <v>151.4898954891258</v>
+        <v>149.6377698486339</v>
       </c>
       <c r="E122" t="n">
-        <v>151.7066345214844</v>
+        <v>151.3519744873047</v>
       </c>
       <c r="F122" t="n">
-        <v>10060300</v>
+        <v>8187900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>151.3815284437877</v>
+        <v>150.8790677258081</v>
       </c>
       <c r="C123" t="n">
-        <v>152.1401000368933</v>
+        <v>153.9133989264833</v>
       </c>
       <c r="D123" t="n">
-        <v>149.6377698486339</v>
+        <v>150.6327747552909</v>
       </c>
       <c r="E123" t="n">
-        <v>151.3519744873047</v>
+        <v>152.9183807373047</v>
       </c>
       <c r="F123" t="n">
-        <v>8187900</v>
+        <v>12494900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>150.8790677258081</v>
+        <v>153.1843919415674</v>
       </c>
       <c r="C124" t="n">
-        <v>153.9133989264833</v>
+        <v>154.8197659541039</v>
       </c>
       <c r="D124" t="n">
-        <v>150.6327747552909</v>
+        <v>151.3224175570726</v>
       </c>
       <c r="E124" t="n">
-        <v>152.9183807373047</v>
+        <v>153.6966705322266</v>
       </c>
       <c r="F124" t="n">
-        <v>12494900</v>
+        <v>7756800</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>153.1843919415674</v>
+        <v>152.9282368144603</v>
       </c>
       <c r="C125" t="n">
-        <v>154.8197659541039</v>
+        <v>153.07602162573</v>
       </c>
       <c r="D125" t="n">
-        <v>151.3224175570726</v>
+        <v>149.1845804169242</v>
       </c>
       <c r="E125" t="n">
-        <v>153.6966705322266</v>
+        <v>151.0465698242188</v>
       </c>
       <c r="F125" t="n">
-        <v>7756800</v>
+        <v>8855100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>152.9282368144603</v>
+        <v>149.9530221525258</v>
       </c>
       <c r="C126" t="n">
-        <v>153.07602162573</v>
+        <v>150.7805629442461</v>
       </c>
       <c r="D126" t="n">
-        <v>149.1845804169242</v>
+        <v>148.100894162221</v>
       </c>
       <c r="E126" t="n">
-        <v>151.0465698242188</v>
+        <v>148.2683715820312</v>
       </c>
       <c r="F126" t="n">
-        <v>8855100</v>
+        <v>8489300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>149.9530221525258</v>
+        <v>149.1254779831649</v>
       </c>
       <c r="C127" t="n">
-        <v>150.7805629442461</v>
+        <v>150.2879887378921</v>
       </c>
       <c r="D127" t="n">
-        <v>148.100894162221</v>
+        <v>147.9531209203371</v>
       </c>
       <c r="E127" t="n">
-        <v>148.2683715820312</v>
+        <v>148.4161529541016</v>
       </c>
       <c r="F127" t="n">
-        <v>8489300</v>
+        <v>7298900</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>149.1254779831649</v>
+        <v>149.6082100748309</v>
       </c>
       <c r="C128" t="n">
-        <v>150.2879887378921</v>
+        <v>150.3766429785721</v>
       </c>
       <c r="D128" t="n">
-        <v>147.9531209203371</v>
+        <v>148.4161454237534</v>
       </c>
       <c r="E128" t="n">
-        <v>148.4161529541016</v>
+        <v>149.8643493652344</v>
       </c>
       <c r="F128" t="n">
-        <v>7298900</v>
+        <v>6944000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>149.6082100748309</v>
+        <v>150.7411528047512</v>
       </c>
       <c r="C129" t="n">
-        <v>150.3766429785721</v>
+        <v>151.184492202826</v>
       </c>
       <c r="D129" t="n">
-        <v>148.4161454237534</v>
+        <v>148.9579940023762</v>
       </c>
       <c r="E129" t="n">
-        <v>149.8643493652344</v>
+        <v>149.2338409423828</v>
       </c>
       <c r="F129" t="n">
-        <v>6944000</v>
+        <v>6147700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>150.7411528047512</v>
+        <v>147.0960143427481</v>
       </c>
       <c r="C130" t="n">
-        <v>151.184492202826</v>
+        <v>147.4014152272885</v>
       </c>
       <c r="D130" t="n">
-        <v>148.9579940023762</v>
+        <v>144.2882834404146</v>
       </c>
       <c r="E130" t="n">
-        <v>149.2338409423828</v>
+        <v>144.5345764160156</v>
       </c>
       <c r="F130" t="n">
-        <v>6147700</v>
+        <v>10059300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>147.0960143427481</v>
+        <v>144.0518332623683</v>
       </c>
       <c r="C131" t="n">
-        <v>147.4014152272885</v>
+        <v>145.1946362491204</v>
       </c>
       <c r="D131" t="n">
-        <v>144.2882834404146</v>
+        <v>142.6430296593396</v>
       </c>
       <c r="E131" t="n">
-        <v>144.5345764160156</v>
+        <v>142.6922912597656</v>
       </c>
       <c r="F131" t="n">
-        <v>10059300</v>
+        <v>10340300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>144.0518332623683</v>
+        <v>142.8400884498559</v>
       </c>
       <c r="C132" t="n">
-        <v>145.1946362491204</v>
+        <v>143.6577829837524</v>
       </c>
       <c r="D132" t="n">
-        <v>142.6430296593396</v>
+        <v>142.111055784898</v>
       </c>
       <c r="E132" t="n">
-        <v>142.6922912597656</v>
+        <v>142.1406097412109</v>
       </c>
       <c r="F132" t="n">
-        <v>10340300</v>
+        <v>60620900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>142.8400884498559</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="C133" t="n">
-        <v>143.6577829837524</v>
+        <v>143.9828794949957</v>
       </c>
       <c r="D133" t="n">
-        <v>142.111055784898</v>
+        <v>141.3524721007716</v>
       </c>
       <c r="E133" t="n">
-        <v>142.1406097412109</v>
+        <v>141.8549194335938</v>
       </c>
       <c r="F133" t="n">
-        <v>60620900</v>
+        <v>10315600</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>143.9828794949957</v>
+        <v>141.2046936096272</v>
       </c>
       <c r="C134" t="n">
-        <v>143.9828794949957</v>
+        <v>143.0765142514037</v>
       </c>
       <c r="D134" t="n">
-        <v>141.3524721007716</v>
+        <v>140.1209984806846</v>
       </c>
       <c r="E134" t="n">
-        <v>141.8549194335938</v>
+        <v>141.0372161865234</v>
       </c>
       <c r="F134" t="n">
-        <v>10315600</v>
+        <v>8567600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>141.2046936096272</v>
+        <v>141.6086259660596</v>
       </c>
       <c r="C135" t="n">
-        <v>143.0765142514037</v>
+        <v>141.9632884805344</v>
       </c>
       <c r="D135" t="n">
-        <v>140.1209984806846</v>
+        <v>140.1210066538726</v>
       </c>
       <c r="E135" t="n">
-        <v>141.0372161865234</v>
+        <v>141.7859497070312</v>
       </c>
       <c r="F135" t="n">
-        <v>8567600</v>
+        <v>8418100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>141.6086259660596</v>
+        <v>141.559369693648</v>
       </c>
       <c r="C136" t="n">
-        <v>141.9632884805344</v>
+        <v>142.4263258800331</v>
       </c>
       <c r="D136" t="n">
-        <v>140.1210066538726</v>
+        <v>140.1308732738322</v>
       </c>
       <c r="E136" t="n">
-        <v>141.7859497070312</v>
+        <v>140.3081970214844</v>
       </c>
       <c r="F136" t="n">
-        <v>8418100</v>
+        <v>6443200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>141.559369693648</v>
+        <v>140.603748896169</v>
       </c>
       <c r="C137" t="n">
-        <v>142.4263258800331</v>
+        <v>141.9435834160748</v>
       </c>
       <c r="D137" t="n">
-        <v>140.1308732738322</v>
+        <v>139.9042701625835</v>
       </c>
       <c r="E137" t="n">
-        <v>140.3081970214844</v>
+        <v>140.5939025878906</v>
       </c>
       <c r="F137" t="n">
-        <v>6443200</v>
+        <v>11558300</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>140.603748896169</v>
+        <v>140.9189847788946</v>
       </c>
       <c r="C138" t="n">
-        <v>141.9435834160748</v>
+        <v>143.4114835656516</v>
       </c>
       <c r="D138" t="n">
-        <v>139.9042701625835</v>
+        <v>140.4559678065659</v>
       </c>
       <c r="E138" t="n">
-        <v>140.5939025878906</v>
+        <v>142.5740814208984</v>
       </c>
       <c r="F138" t="n">
-        <v>11558300</v>
+        <v>11616300</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>140.9189847788946</v>
+        <v>142.6726031682958</v>
       </c>
       <c r="C139" t="n">
-        <v>143.4114835656516</v>
+        <v>142.7711113397407</v>
       </c>
       <c r="D139" t="n">
-        <v>140.4559678065659</v>
+        <v>140.1702580996175</v>
       </c>
       <c r="E139" t="n">
-        <v>142.5740814208984</v>
+        <v>142.2982330322266</v>
       </c>
       <c r="F139" t="n">
-        <v>11616300</v>
+        <v>10407500</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>142.6726031682958</v>
+        <v>141.7859527393269</v>
       </c>
       <c r="C140" t="n">
-        <v>142.7711113397407</v>
+        <v>142.8203863480455</v>
       </c>
       <c r="D140" t="n">
-        <v>140.1702580996175</v>
+        <v>141.0864890360487</v>
       </c>
       <c r="E140" t="n">
-        <v>142.2982330322266</v>
+        <v>141.9534301757812</v>
       </c>
       <c r="F140" t="n">
-        <v>10407500</v>
+        <v>8061700</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>141.7859527393269</v>
+        <v>141.9534207153344</v>
       </c>
       <c r="C141" t="n">
-        <v>142.8203863480455</v>
+        <v>142.0716515698294</v>
       </c>
       <c r="D141" t="n">
-        <v>141.0864890360487</v>
+        <v>140.4658165030053</v>
       </c>
       <c r="E141" t="n">
-        <v>141.9534301757812</v>
+        <v>140.997802734375</v>
       </c>
       <c r="F141" t="n">
-        <v>8061700</v>
+        <v>5941700</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>141.9534207153344</v>
+        <v>140.8894315190035</v>
       </c>
       <c r="C142" t="n">
-        <v>142.0716515698294</v>
+        <v>141.5396485970176</v>
       </c>
       <c r="D142" t="n">
-        <v>140.4658165030053</v>
+        <v>139.8155977290451</v>
       </c>
       <c r="E142" t="n">
-        <v>140.997802734375</v>
+        <v>140.6529998779297</v>
       </c>
       <c r="F142" t="n">
-        <v>5941700</v>
+        <v>6823100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>140.8894315190035</v>
+        <v>140.4066990917555</v>
       </c>
       <c r="C143" t="n">
-        <v>141.5396485970176</v>
+        <v>140.6529920592033</v>
       </c>
       <c r="D143" t="n">
-        <v>139.8155977290451</v>
+        <v>138.6530943661295</v>
       </c>
       <c r="E143" t="n">
-        <v>140.6529998779297</v>
+        <v>139.2047882080078</v>
       </c>
       <c r="F143" t="n">
-        <v>6823100</v>
+        <v>7207500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>140.4066990917555</v>
+        <v>141.0273529653376</v>
       </c>
       <c r="C144" t="n">
-        <v>140.6529920592033</v>
+        <v>142.9582965240978</v>
       </c>
       <c r="D144" t="n">
-        <v>138.6530943661295</v>
+        <v>139.766334122587</v>
       </c>
       <c r="E144" t="n">
-        <v>139.2047882080078</v>
+        <v>142.7514038085938</v>
       </c>
       <c r="F144" t="n">
-        <v>7207500</v>
+        <v>10849700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>141.0273529653376</v>
+        <v>142.2489765209199</v>
       </c>
       <c r="C145" t="n">
-        <v>142.9582965240978</v>
+        <v>144.7611679868877</v>
       </c>
       <c r="D145" t="n">
-        <v>139.766334122587</v>
+        <v>140.8795881188284</v>
       </c>
       <c r="E145" t="n">
-        <v>142.7514038085938</v>
+        <v>144.4853210449219</v>
       </c>
       <c r="F145" t="n">
-        <v>10849700</v>
+        <v>6794800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>142.2489765209199</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="C146" t="n">
-        <v>144.7611679868877</v>
+        <v>144.7119116772724</v>
       </c>
       <c r="D146" t="n">
-        <v>140.8795881188284</v>
+        <v>142.6134905474848</v>
       </c>
       <c r="E146" t="n">
-        <v>144.4853210449219</v>
+        <v>143.007568359375</v>
       </c>
       <c r="F146" t="n">
-        <v>6794800</v>
+        <v>9790300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>144.7119116772724</v>
+        <v>142.8499157089539</v>
       </c>
       <c r="C147" t="n">
-        <v>144.7119116772724</v>
+        <v>142.9385775660697</v>
       </c>
       <c r="D147" t="n">
-        <v>142.6134905474848</v>
+        <v>140.5150632763963</v>
       </c>
       <c r="E147" t="n">
-        <v>143.007568359375</v>
+        <v>141.4509735107422</v>
       </c>
       <c r="F147" t="n">
-        <v>9790300</v>
+        <v>7121400</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>142.8499157089539</v>
+        <v>141.1160402826616</v>
       </c>
       <c r="C148" t="n">
-        <v>142.9385775660697</v>
+        <v>142.5740906086617</v>
       </c>
       <c r="D148" t="n">
-        <v>140.5150632763963</v>
+        <v>140.6530082479637</v>
       </c>
       <c r="E148" t="n">
-        <v>141.4509735107422</v>
+        <v>142.2391357421875</v>
       </c>
       <c r="F148" t="n">
-        <v>7121400</v>
+        <v>6621600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>141.1160402826616</v>
+        <v>142.2194162805844</v>
       </c>
       <c r="C149" t="n">
-        <v>142.5740906086617</v>
+        <v>142.2588165423252</v>
       </c>
       <c r="D149" t="n">
-        <v>140.6530082479637</v>
+        <v>140.1505492747316</v>
       </c>
       <c r="E149" t="n">
-        <v>142.2391357421875</v>
+        <v>141.2539520263672</v>
       </c>
       <c r="F149" t="n">
-        <v>6621600</v>
+        <v>7698200</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>142.2194162805844</v>
+        <v>141.0766226846627</v>
       </c>
       <c r="C150" t="n">
-        <v>142.2588165423252</v>
+        <v>142.1504565210129</v>
       </c>
       <c r="D150" t="n">
-        <v>140.1505492747316</v>
+        <v>140.5446364367332</v>
       </c>
       <c r="E150" t="n">
-        <v>141.2539520263672</v>
+        <v>140.9879608154297</v>
       </c>
       <c r="F150" t="n">
-        <v>7698200</v>
+        <v>6947100</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>141.0766226846627</v>
+        <v>141.2835176988996</v>
       </c>
       <c r="C151" t="n">
-        <v>142.1504565210129</v>
+        <v>145.4015293724886</v>
       </c>
       <c r="D151" t="n">
-        <v>140.5446364367332</v>
+        <v>141.0372247031338</v>
       </c>
       <c r="E151" t="n">
-        <v>140.9879608154297</v>
+        <v>144.7513122558594</v>
       </c>
       <c r="F151" t="n">
-        <v>6947100</v>
+        <v>10886000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>141.2835176988996</v>
+        <v>143.8942158414082</v>
       </c>
       <c r="C152" t="n">
-        <v>145.4015293724886</v>
+        <v>144.4853250376877</v>
       </c>
       <c r="D152" t="n">
-        <v>141.0372247031338</v>
+        <v>141.4608398676902</v>
       </c>
       <c r="E152" t="n">
-        <v>144.7513122558594</v>
+        <v>142.3475036621094</v>
       </c>
       <c r="F152" t="n">
-        <v>10886000</v>
+        <v>8084700</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>143.8942158414082</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="C153" t="n">
-        <v>144.4853250376877</v>
+        <v>142.4755698536542</v>
       </c>
       <c r="D153" t="n">
-        <v>141.4608398676902</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="E153" t="n">
-        <v>142.3475036621094</v>
+        <v>140.2096862792969</v>
       </c>
       <c r="F153" t="n">
-        <v>8084700</v>
+        <v>11197200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>142.4755698536542</v>
+        <v>140.3869953464167</v>
       </c>
       <c r="C154" t="n">
-        <v>142.4755698536542</v>
+        <v>141.175135870657</v>
       </c>
       <c r="D154" t="n">
-        <v>140.2096862792969</v>
+        <v>140.1111484178121</v>
       </c>
       <c r="E154" t="n">
-        <v>140.2096862792969</v>
+        <v>140.7318115234375</v>
       </c>
       <c r="F154" t="n">
-        <v>11197200</v>
+        <v>7236300</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>140.3869953464167</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="C155" t="n">
-        <v>141.175135870657</v>
+        <v>144.0616865371081</v>
       </c>
       <c r="D155" t="n">
-        <v>140.1111484178121</v>
+        <v>141.2736481824844</v>
       </c>
       <c r="E155" t="n">
-        <v>140.7318115234375</v>
+        <v>143.5494079589844</v>
       </c>
       <c r="F155" t="n">
-        <v>7236300</v>
+        <v>11288800</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,25 +4473,25 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>141.2736481824844</v>
+        <v>150.8836541197979</v>
       </c>
       <c r="C156" t="n">
-        <v>144.0616865371081</v>
+        <v>151.2906197995367</v>
       </c>
       <c r="D156" t="n">
-        <v>141.2736481824844</v>
+        <v>146.5261830755894</v>
       </c>
       <c r="E156" t="n">
-        <v>143.5494079589844</v>
+        <v>147.08203125</v>
       </c>
       <c r="F156" t="n">
-        <v>11288800</v>
+        <v>13786200</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4499,25 +4499,25 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>150.8836541197979</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="C157" t="n">
-        <v>151.2906197995367</v>
+        <v>148.59077024601</v>
       </c>
       <c r="D157" t="n">
-        <v>146.5261830755894</v>
+        <v>146.3276654919543</v>
       </c>
       <c r="E157" t="n">
-        <v>147.08203125</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F157" t="n">
-        <v>13786200</v>
+        <v>9166400</v>
       </c>
       <c r="G157" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>146.3276654919543</v>
+        <v>148.9183255527001</v>
       </c>
       <c r="C158" t="n">
-        <v>148.59077024601</v>
+        <v>150.0697339670296</v>
       </c>
       <c r="D158" t="n">
-        <v>146.3276654919543</v>
+        <v>147.3301749711611</v>
       </c>
       <c r="E158" t="n">
-        <v>147.3003997802734</v>
+        <v>148.064697265625</v>
       </c>
       <c r="F158" t="n">
-        <v>9166400</v>
+        <v>7965700</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>148.9183255527001</v>
+        <v>147.2011489489405</v>
       </c>
       <c r="C159" t="n">
-        <v>150.0697339670296</v>
+        <v>147.6478115682369</v>
       </c>
       <c r="D159" t="n">
-        <v>147.3301749711611</v>
+        <v>144.8090026189782</v>
       </c>
       <c r="E159" t="n">
-        <v>148.064697265625</v>
+        <v>145.3747863769531</v>
       </c>
       <c r="F159" t="n">
-        <v>7965700</v>
+        <v>9002400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>147.2011489489405</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="C160" t="n">
-        <v>147.6478115682369</v>
+        <v>146.6254435609453</v>
       </c>
       <c r="D160" t="n">
-        <v>144.8090026189782</v>
+        <v>144.8685544504002</v>
       </c>
       <c r="E160" t="n">
-        <v>145.3747863769531</v>
+        <v>146.0001068115234</v>
       </c>
       <c r="F160" t="n">
-        <v>9002400</v>
+        <v>9491700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>146.0001068115234</v>
+        <v>146.7743191747914</v>
       </c>
       <c r="C161" t="n">
-        <v>146.6254435609453</v>
+        <v>148.1738750980608</v>
       </c>
       <c r="D161" t="n">
-        <v>144.8685544504002</v>
+        <v>145.3747783972478</v>
       </c>
       <c r="E161" t="n">
-        <v>146.0001068115234</v>
+        <v>146.1688385009766</v>
       </c>
       <c r="F161" t="n">
-        <v>9491700</v>
+        <v>6814800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>146.7743191747914</v>
+        <v>144.977737605514</v>
       </c>
       <c r="C162" t="n">
-        <v>148.1738750980608</v>
+        <v>144.977737605514</v>
       </c>
       <c r="D162" t="n">
-        <v>145.3747783972478</v>
+        <v>142.2084173171452</v>
       </c>
       <c r="E162" t="n">
-        <v>146.1688385009766</v>
+        <v>142.3572998046875</v>
       </c>
       <c r="F162" t="n">
-        <v>6814800</v>
+        <v>9642800</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>144.977737605514</v>
+        <v>142.3175981532361</v>
       </c>
       <c r="C163" t="n">
-        <v>144.977737605514</v>
+        <v>144.8189147356386</v>
       </c>
       <c r="D163" t="n">
-        <v>142.2084173171452</v>
+        <v>141.1264777093581</v>
       </c>
       <c r="E163" t="n">
-        <v>142.3572998046875</v>
+        <v>143.8263244628906</v>
       </c>
       <c r="F163" t="n">
-        <v>9642800</v>
+        <v>7664300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>142.3175981532361</v>
+        <v>145.3152221312864</v>
       </c>
       <c r="C164" t="n">
-        <v>144.8189147356386</v>
+        <v>147.8463305694715</v>
       </c>
       <c r="D164" t="n">
-        <v>141.1264777093581</v>
+        <v>144.8586390489098</v>
       </c>
       <c r="E164" t="n">
-        <v>143.8263244628906</v>
+        <v>146.8041076660156</v>
       </c>
       <c r="F164" t="n">
-        <v>7664300</v>
+        <v>9399500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>145.3152221312864</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="C165" t="n">
-        <v>147.8463305694715</v>
+        <v>146.8934445898874</v>
       </c>
       <c r="D165" t="n">
-        <v>144.8586390489098</v>
+        <v>144.9380404787042</v>
       </c>
       <c r="E165" t="n">
-        <v>146.8041076660156</v>
+        <v>144.9777374267578</v>
       </c>
       <c r="F165" t="n">
-        <v>9399500</v>
+        <v>9545800</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>146.8934445898874</v>
+        <v>145.4641093327384</v>
       </c>
       <c r="C166" t="n">
-        <v>146.8934445898874</v>
+        <v>146.4269231210903</v>
       </c>
       <c r="D166" t="n">
-        <v>144.9380404787042</v>
+        <v>145.1266322707271</v>
       </c>
       <c r="E166" t="n">
-        <v>144.9777374267578</v>
+        <v>145.3350677490234</v>
       </c>
       <c r="F166" t="n">
-        <v>9545800</v>
+        <v>5741000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>145.4641093327384</v>
+        <v>144.7097318886224</v>
       </c>
       <c r="C167" t="n">
-        <v>146.4269231210903</v>
+        <v>144.8685499701872</v>
       </c>
       <c r="D167" t="n">
-        <v>145.1266322707271</v>
+        <v>140.9180448520501</v>
       </c>
       <c r="E167" t="n">
-        <v>145.3350677490234</v>
+        <v>142.2977447509766</v>
       </c>
       <c r="F167" t="n">
-        <v>5741000</v>
+        <v>7489500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>144.7097318886224</v>
+        <v>143.280415861365</v>
       </c>
       <c r="C168" t="n">
-        <v>144.8685499701872</v>
+        <v>144.7792217618835</v>
       </c>
       <c r="D168" t="n">
-        <v>140.9180448520501</v>
+        <v>141.8014508619235</v>
       </c>
       <c r="E168" t="n">
-        <v>142.2977447509766</v>
+        <v>142.8436737060547</v>
       </c>
       <c r="F168" t="n">
-        <v>7489500</v>
+        <v>9051200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>143.280415861365</v>
+        <v>142.0892960817053</v>
       </c>
       <c r="C169" t="n">
-        <v>144.7792217618835</v>
+        <v>143.5980375858882</v>
       </c>
       <c r="D169" t="n">
-        <v>141.8014508619235</v>
+        <v>140.610346220736</v>
       </c>
       <c r="E169" t="n">
-        <v>142.8436737060547</v>
+        <v>141.1860504150391</v>
       </c>
       <c r="F169" t="n">
-        <v>9051200</v>
+        <v>6685900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>142.0892960817053</v>
+        <v>142.1190761527801</v>
       </c>
       <c r="C170" t="n">
-        <v>143.5980375858882</v>
+        <v>143.2109315738657</v>
       </c>
       <c r="D170" t="n">
-        <v>140.610346220736</v>
+        <v>141.5731635879637</v>
       </c>
       <c r="E170" t="n">
-        <v>141.1860504150391</v>
+        <v>141.6525726318359</v>
       </c>
       <c r="F170" t="n">
-        <v>6685900</v>
+        <v>9636200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>142.1190761527801</v>
+        <v>142.337438212696</v>
       </c>
       <c r="C171" t="n">
-        <v>143.2109315738657</v>
+        <v>142.337438212696</v>
       </c>
       <c r="D171" t="n">
-        <v>141.5731635879637</v>
+        <v>140.1537426546991</v>
       </c>
       <c r="E171" t="n">
-        <v>141.6525726318359</v>
+        <v>140.5210113525391</v>
       </c>
       <c r="F171" t="n">
-        <v>9636200</v>
+        <v>6989400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>142.337438212696</v>
+        <v>141.0470859006894</v>
       </c>
       <c r="C172" t="n">
-        <v>142.337438212696</v>
+        <v>143.3598079421396</v>
       </c>
       <c r="D172" t="n">
-        <v>140.1537426546991</v>
+        <v>140.5805672539439</v>
       </c>
       <c r="E172" t="n">
-        <v>140.5210113525391</v>
+        <v>141.3349304199219</v>
       </c>
       <c r="F172" t="n">
-        <v>6989400</v>
+        <v>7731200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>141.0470859006894</v>
+        <v>141.4143347616525</v>
       </c>
       <c r="C173" t="n">
-        <v>143.3598079421396</v>
+        <v>142.6451521296186</v>
       </c>
       <c r="D173" t="n">
-        <v>140.5805672539439</v>
+        <v>139.8063433960926</v>
       </c>
       <c r="E173" t="n">
-        <v>141.3349304199219</v>
+        <v>140.2530059814453</v>
       </c>
       <c r="F173" t="n">
-        <v>7731200</v>
+        <v>8355800</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>141.4143347616525</v>
+        <v>140.4018973938673</v>
       </c>
       <c r="C174" t="n">
-        <v>142.6451521296186</v>
+        <v>142.1587864968038</v>
       </c>
       <c r="D174" t="n">
-        <v>139.8063433960926</v>
+        <v>139.578045612781</v>
       </c>
       <c r="E174" t="n">
-        <v>140.2530059814453</v>
+        <v>141.3845672607422</v>
       </c>
       <c r="F174" t="n">
-        <v>8355800</v>
+        <v>8375600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>140.4018973938673</v>
+        <v>140.8287217143626</v>
       </c>
       <c r="C175" t="n">
-        <v>142.1587864968038</v>
+        <v>142.655084297577</v>
       </c>
       <c r="D175" t="n">
-        <v>139.578045612781</v>
+        <v>139.0519765313656</v>
       </c>
       <c r="E175" t="n">
-        <v>141.3845672607422</v>
+        <v>142.3374481201172</v>
       </c>
       <c r="F175" t="n">
-        <v>8375600</v>
+        <v>6297300</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>140.8287217143626</v>
+        <v>142.8039672134308</v>
       </c>
       <c r="C176" t="n">
-        <v>142.655084297577</v>
+        <v>143.5682660152007</v>
       </c>
       <c r="D176" t="n">
-        <v>139.0519765313656</v>
+        <v>142.4664901331732</v>
       </c>
       <c r="E176" t="n">
-        <v>142.3374481201172</v>
+        <v>143.3697509765625</v>
       </c>
       <c r="F176" t="n">
-        <v>6297300</v>
+        <v>4616700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>142.8039672134308</v>
+        <v>143.439213854944</v>
       </c>
       <c r="C177" t="n">
-        <v>143.5682660152007</v>
+        <v>144.5310692055886</v>
       </c>
       <c r="D177" t="n">
-        <v>142.4664901331732</v>
+        <v>141.473889369509</v>
       </c>
       <c r="E177" t="n">
-        <v>143.3697509765625</v>
+        <v>141.9007110595703</v>
       </c>
       <c r="F177" t="n">
-        <v>4616700</v>
+        <v>8157200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>143.439213854944</v>
+        <v>142.397017874141</v>
       </c>
       <c r="C178" t="n">
-        <v>144.5310692055886</v>
+        <v>147.4393635097026</v>
       </c>
       <c r="D178" t="n">
-        <v>141.473889369509</v>
+        <v>142.397017874141</v>
       </c>
       <c r="E178" t="n">
-        <v>141.9007110595703</v>
+        <v>146.3971557617188</v>
       </c>
       <c r="F178" t="n">
-        <v>8157200</v>
+        <v>10048900</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>142.397017874141</v>
+        <v>145.612997111615</v>
       </c>
       <c r="C179" t="n">
-        <v>147.4393635097026</v>
+        <v>145.612997111615</v>
       </c>
       <c r="D179" t="n">
-        <v>142.397017874141</v>
+        <v>143.9355170452321</v>
       </c>
       <c r="E179" t="n">
-        <v>146.3971557617188</v>
+        <v>144.828857421875</v>
       </c>
       <c r="F179" t="n">
-        <v>10048900</v>
+        <v>10196700</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>145.612997111615</v>
+        <v>144.4417452563355</v>
       </c>
       <c r="C180" t="n">
-        <v>145.612997111615</v>
+        <v>144.5608512461645</v>
       </c>
       <c r="D180" t="n">
-        <v>143.9355170452321</v>
+        <v>142.1389284814664</v>
       </c>
       <c r="E180" t="n">
-        <v>144.828857421875</v>
+        <v>142.4962615966797</v>
       </c>
       <c r="F180" t="n">
-        <v>10196700</v>
+        <v>12355800</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>144.4417452563355</v>
+        <v>140.4713875281435</v>
       </c>
       <c r="C181" t="n">
-        <v>144.5608512461645</v>
+        <v>140.7691676558347</v>
       </c>
       <c r="D181" t="n">
-        <v>142.1389284814664</v>
+        <v>137.8310936193964</v>
       </c>
       <c r="E181" t="n">
-        <v>142.4962615966797</v>
+        <v>139.2405700683594</v>
       </c>
       <c r="F181" t="n">
-        <v>12355800</v>
+        <v>11093800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>140.4713875281435</v>
+        <v>139.0817554467106</v>
       </c>
       <c r="C182" t="n">
-        <v>140.7691676558347</v>
+        <v>140.0743457999317</v>
       </c>
       <c r="D182" t="n">
-        <v>137.8310936193964</v>
+        <v>137.999835596674</v>
       </c>
       <c r="E182" t="n">
-        <v>139.2405700683594</v>
+        <v>139.7765808105469</v>
       </c>
       <c r="F182" t="n">
-        <v>11093800</v>
+        <v>9599500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>139.0817554467106</v>
+        <v>139.8857522909846</v>
       </c>
       <c r="C183" t="n">
-        <v>140.0743457999317</v>
+        <v>141.3944938803485</v>
       </c>
       <c r="D183" t="n">
-        <v>137.999835596674</v>
+        <v>138.9626505253011</v>
       </c>
       <c r="E183" t="n">
-        <v>139.7765808105469</v>
+        <v>139.1512451171875</v>
       </c>
       <c r="F183" t="n">
-        <v>9599500</v>
+        <v>9351000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>139.8857522909846</v>
+        <v>141.6426337542266</v>
       </c>
       <c r="C184" t="n">
-        <v>141.3944938803485</v>
+        <v>142.079375912544</v>
       </c>
       <c r="D184" t="n">
-        <v>138.9626505253011</v>
+        <v>138.8534574153755</v>
       </c>
       <c r="E184" t="n">
-        <v>139.1512451171875</v>
+        <v>139.7368621826172</v>
       </c>
       <c r="F184" t="n">
-        <v>9351000</v>
+        <v>8194000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>141.6426337542266</v>
+        <v>141.1661955784844</v>
       </c>
       <c r="C185" t="n">
-        <v>142.079375912544</v>
+        <v>147.131657909349</v>
       </c>
       <c r="D185" t="n">
-        <v>138.8534574153755</v>
+        <v>140.7493094643581</v>
       </c>
       <c r="E185" t="n">
-        <v>139.7368621826172</v>
+        <v>145.4541778564453</v>
       </c>
       <c r="F185" t="n">
-        <v>8194000</v>
+        <v>10963200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>141.1661955784844</v>
+        <v>144.709731142363</v>
       </c>
       <c r="C186" t="n">
-        <v>147.131657909349</v>
+        <v>145.4641094530425</v>
       </c>
       <c r="D186" t="n">
-        <v>140.7493094643581</v>
+        <v>143.9454475270099</v>
       </c>
       <c r="E186" t="n">
-        <v>145.4541778564453</v>
+        <v>144.0248565673828</v>
       </c>
       <c r="F186" t="n">
-        <v>10963200</v>
+        <v>7200700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>144.709731142363</v>
+        <v>143.598043761205</v>
       </c>
       <c r="C187" t="n">
-        <v>145.4641094530425</v>
+        <v>148.3724009095588</v>
       </c>
       <c r="D187" t="n">
-        <v>143.9454475270099</v>
+        <v>143.4590817183783</v>
       </c>
       <c r="E187" t="n">
-        <v>144.0248565673828</v>
+        <v>147.5684051513672</v>
       </c>
       <c r="F187" t="n">
-        <v>7200700</v>
+        <v>8259300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>143.598043761205</v>
+        <v>148.7992154215363</v>
       </c>
       <c r="C188" t="n">
-        <v>148.3724009095588</v>
+        <v>149.3153514723138</v>
       </c>
       <c r="D188" t="n">
-        <v>143.4590817183783</v>
+        <v>147.2805534750766</v>
       </c>
       <c r="E188" t="n">
-        <v>147.5684051513672</v>
+        <v>147.9455871582031</v>
       </c>
       <c r="F188" t="n">
-        <v>8259300</v>
+        <v>7345900</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>148.7992154215363</v>
+        <v>147.598177848302</v>
       </c>
       <c r="C189" t="n">
-        <v>149.3153514723138</v>
+        <v>148.5113591270304</v>
       </c>
       <c r="D189" t="n">
-        <v>147.2805534750766</v>
+        <v>146.6750761188154</v>
       </c>
       <c r="E189" t="n">
-        <v>147.9455871582031</v>
+        <v>147.2408447265625</v>
       </c>
       <c r="F189" t="n">
-        <v>7345900</v>
+        <v>6684700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>147.598177848302</v>
+        <v>148.2731427996088</v>
       </c>
       <c r="C190" t="n">
-        <v>148.5113591270304</v>
+        <v>149.087058964007</v>
       </c>
       <c r="D190" t="n">
-        <v>146.6750761188154</v>
+        <v>147.2011434657927</v>
       </c>
       <c r="E190" t="n">
-        <v>147.2408447265625</v>
+        <v>148.5014343261719</v>
       </c>
       <c r="F190" t="n">
-        <v>6684700</v>
+        <v>6832000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>148.2731427996088</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="C191" t="n">
-        <v>149.087058964007</v>
+        <v>150.377425765528</v>
       </c>
       <c r="D191" t="n">
-        <v>147.2011434657927</v>
+        <v>147.6577229757893</v>
       </c>
       <c r="E191" t="n">
-        <v>148.5014343261719</v>
+        <v>149.3451385498047</v>
       </c>
       <c r="F191" t="n">
-        <v>6832000</v>
+        <v>9158900</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>147.6577229757893</v>
+        <v>150.3873579771785</v>
       </c>
       <c r="C192" t="n">
-        <v>150.377425765528</v>
+        <v>151.8861790939718</v>
       </c>
       <c r="D192" t="n">
-        <v>147.6577229757893</v>
+        <v>149.4344797259463</v>
       </c>
       <c r="E192" t="n">
-        <v>149.3451385498047</v>
+        <v>151.360107421875</v>
       </c>
       <c r="F192" t="n">
-        <v>9158900</v>
+        <v>8518900</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>150.3873579771785</v>
+        <v>151.2509186348782</v>
       </c>
       <c r="C193" t="n">
-        <v>151.8861790939718</v>
+        <v>151.8067667938</v>
       </c>
       <c r="D193" t="n">
-        <v>149.4344797259463</v>
+        <v>148.6602572796902</v>
       </c>
       <c r="E193" t="n">
-        <v>151.360107421875</v>
+        <v>149.4443969726562</v>
       </c>
       <c r="F193" t="n">
-        <v>8518900</v>
+        <v>7055800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>151.2509186348782</v>
+        <v>149.7520913576046</v>
       </c>
       <c r="C194" t="n">
-        <v>151.8067667938</v>
+        <v>151.1615677439354</v>
       </c>
       <c r="D194" t="n">
-        <v>148.6602572796902</v>
+        <v>149.067201638067</v>
       </c>
       <c r="E194" t="n">
-        <v>149.4443969726562</v>
+        <v>149.2657318115234</v>
       </c>
       <c r="F194" t="n">
-        <v>7055800</v>
+        <v>17076100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>149.7520913576046</v>
+        <v>148.9977261100366</v>
       </c>
       <c r="C195" t="n">
-        <v>151.1615677439354</v>
+        <v>149.7719453093657</v>
       </c>
       <c r="D195" t="n">
-        <v>149.067201638067</v>
+        <v>146.4765534870951</v>
       </c>
       <c r="E195" t="n">
-        <v>149.2657318115234</v>
+        <v>146.5857238769531</v>
       </c>
       <c r="F195" t="n">
-        <v>17076100</v>
+        <v>10533000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>148.9977261100366</v>
+        <v>148.5510669184904</v>
       </c>
       <c r="C196" t="n">
-        <v>149.7719453093657</v>
+        <v>150.2483878382925</v>
       </c>
       <c r="D196" t="n">
-        <v>146.4765534870951</v>
+        <v>148.2632072518497</v>
       </c>
       <c r="E196" t="n">
-        <v>146.5857238769531</v>
+        <v>149.7421722412109</v>
       </c>
       <c r="F196" t="n">
-        <v>10533000</v>
+        <v>7259600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>148.5510669184904</v>
+        <v>150.8638042327417</v>
       </c>
       <c r="C197" t="n">
-        <v>150.2483878382925</v>
+        <v>152.213727638368</v>
       </c>
       <c r="D197" t="n">
-        <v>148.2632072518497</v>
+        <v>149.8017253482469</v>
       </c>
       <c r="E197" t="n">
-        <v>149.7421722412109</v>
+        <v>150.9134216308594</v>
       </c>
       <c r="F197" t="n">
-        <v>7259600</v>
+        <v>8618500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>150.8638042327417</v>
+        <v>150.446917666229</v>
       </c>
       <c r="C198" t="n">
-        <v>152.213727638368</v>
+        <v>151.1615687416308</v>
       </c>
       <c r="D198" t="n">
-        <v>149.8017253482469</v>
+        <v>146.7247040752409</v>
       </c>
       <c r="E198" t="n">
-        <v>150.9134216308594</v>
+        <v>147.399658203125</v>
       </c>
       <c r="F198" t="n">
-        <v>8618500</v>
+        <v>11197200</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>150.446917666229</v>
+        <v>149.226028638664</v>
       </c>
       <c r="C199" t="n">
-        <v>151.1615687416308</v>
+        <v>149.7620359058753</v>
       </c>
       <c r="D199" t="n">
-        <v>146.7247040752409</v>
+        <v>147.3202569962244</v>
       </c>
       <c r="E199" t="n">
-        <v>147.399658203125</v>
+        <v>147.9158172607422</v>
       </c>
       <c r="F199" t="n">
-        <v>11197200</v>
+        <v>16724600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>149.226028638664</v>
+        <v>147.627945424002</v>
       </c>
       <c r="C200" t="n">
-        <v>149.7620359058753</v>
+        <v>147.945581577785</v>
       </c>
       <c r="D200" t="n">
-        <v>147.3202569962244</v>
+        <v>145.9504654579339</v>
       </c>
       <c r="E200" t="n">
-        <v>147.9158172607422</v>
+        <v>147.3500213623047</v>
       </c>
       <c r="F200" t="n">
-        <v>16724600</v>
+        <v>10387700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>147.627945424002</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="C201" t="n">
-        <v>147.945581577785</v>
+        <v>146.4368410119005</v>
       </c>
       <c r="D201" t="n">
-        <v>145.9504654579339</v>
+        <v>143.1017371059213</v>
       </c>
       <c r="E201" t="n">
-        <v>147.3500213623047</v>
+        <v>145.5534362792969</v>
       </c>
       <c r="F201" t="n">
-        <v>10387700</v>
+        <v>9353800</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>146.4368410119005</v>
+        <v>145.4442602082673</v>
       </c>
       <c r="C202" t="n">
-        <v>146.4368410119005</v>
+        <v>146.4070740424418</v>
       </c>
       <c r="D202" t="n">
-        <v>143.1017371059213</v>
+        <v>144.4715259232294</v>
       </c>
       <c r="E202" t="n">
-        <v>145.5534362792969</v>
+        <v>146.3375854492188</v>
       </c>
       <c r="F202" t="n">
-        <v>9353800</v>
+        <v>9571700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>145.4442602082673</v>
+        <v>147.4790688253476</v>
       </c>
       <c r="C203" t="n">
-        <v>146.4070740424418</v>
+        <v>150.5461692222369</v>
       </c>
       <c r="D203" t="n">
-        <v>144.4715259232294</v>
+        <v>146.6452966069997</v>
       </c>
       <c r="E203" t="n">
-        <v>146.3375854492188</v>
+        <v>150.2881011962891</v>
       </c>
       <c r="F203" t="n">
-        <v>9571700</v>
+        <v>9256000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>147.4790688253476</v>
+        <v>149.5635029567411</v>
       </c>
       <c r="C204" t="n">
-        <v>150.5461692222369</v>
+        <v>150.0995102140475</v>
       </c>
       <c r="D204" t="n">
-        <v>146.6452966069997</v>
+        <v>145.8710808804345</v>
       </c>
       <c r="E204" t="n">
-        <v>150.2881011962891</v>
+        <v>148.2036590576172</v>
       </c>
       <c r="F204" t="n">
-        <v>9256000</v>
+        <v>8323100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>149.5635029567411</v>
+        <v>151.5288345729856</v>
       </c>
       <c r="C205" t="n">
-        <v>150.0995102140475</v>
+        <v>152.3526863163115</v>
       </c>
       <c r="D205" t="n">
-        <v>145.8710808804345</v>
+        <v>149.4940214860459</v>
       </c>
       <c r="E205" t="n">
-        <v>148.2036590576172</v>
+        <v>151.6181640625</v>
       </c>
       <c r="F205" t="n">
-        <v>8323100</v>
+        <v>8061400</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>151.5288345729856</v>
+        <v>149.8414437624326</v>
       </c>
       <c r="C206" t="n">
-        <v>152.3526863163115</v>
+        <v>149.950629305204</v>
       </c>
       <c r="D206" t="n">
-        <v>149.4940214860459</v>
+        <v>147.2507823800627</v>
       </c>
       <c r="E206" t="n">
-        <v>151.6181640625</v>
+        <v>147.3003997802734</v>
       </c>
       <c r="F206" t="n">
-        <v>8061400</v>
+        <v>14272300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>149.8414437624326</v>
+        <v>145.6824775579256</v>
       </c>
       <c r="C207" t="n">
-        <v>149.950629305204</v>
+        <v>146.5658822886928</v>
       </c>
       <c r="D207" t="n">
-        <v>147.2507823800627</v>
+        <v>144.5211487643815</v>
       </c>
       <c r="E207" t="n">
-        <v>147.3003997802734</v>
+        <v>145.7618865966797</v>
       </c>
       <c r="F207" t="n">
-        <v>14272300</v>
+        <v>7748000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>145.6824775579256</v>
+        <v>146.0100381106733</v>
       </c>
       <c r="C208" t="n">
-        <v>146.5658822886928</v>
+        <v>147.4889879534934</v>
       </c>
       <c r="D208" t="n">
-        <v>144.5211487643815</v>
+        <v>145.6229285023594</v>
       </c>
       <c r="E208" t="n">
-        <v>145.7618865966797</v>
+        <v>145.9504699707031</v>
       </c>
       <c r="F208" t="n">
-        <v>7748000</v>
+        <v>12473000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>146.0100381106733</v>
+        <v>146.9827701076717</v>
       </c>
       <c r="C209" t="n">
-        <v>147.4889879534934</v>
+        <v>148.9381741659779</v>
       </c>
       <c r="D209" t="n">
-        <v>145.6229285023594</v>
+        <v>146.0199563268518</v>
       </c>
       <c r="E209" t="n">
-        <v>145.9504699707031</v>
+        <v>147.2706146240234</v>
       </c>
       <c r="F209" t="n">
-        <v>12473000</v>
+        <v>7816100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>146.9827701076717</v>
+        <v>147.2706141757336</v>
       </c>
       <c r="C210" t="n">
-        <v>148.9381741659779</v>
+        <v>147.6478033266625</v>
       </c>
       <c r="D210" t="n">
-        <v>146.0199563268518</v>
+        <v>144.5112144243791</v>
       </c>
       <c r="E210" t="n">
-        <v>147.2706146240234</v>
+        <v>144.9975891113281</v>
       </c>
       <c r="F210" t="n">
-        <v>7816100</v>
+        <v>7668100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>147.2706141757336</v>
+        <v>144.2035234458952</v>
       </c>
       <c r="C211" t="n">
-        <v>147.6478033266625</v>
+        <v>147.4889950493996</v>
       </c>
       <c r="D211" t="n">
-        <v>144.5112144243791</v>
+        <v>143.5881222814616</v>
       </c>
       <c r="E211" t="n">
-        <v>144.9975891113281</v>
+        <v>146.9530029296875</v>
       </c>
       <c r="F211" t="n">
-        <v>7668100</v>
+        <v>6180000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>144.2035234458952</v>
+        <v>148.3823251540053</v>
       </c>
       <c r="C212" t="n">
-        <v>147.4889950493996</v>
+        <v>150.3972821936961</v>
       </c>
       <c r="D212" t="n">
-        <v>143.5881222814616</v>
+        <v>147.0820191757993</v>
       </c>
       <c r="E212" t="n">
-        <v>146.9530029296875</v>
+        <v>150.3774261474609</v>
       </c>
       <c r="F212" t="n">
-        <v>6180000</v>
+        <v>6485400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>148.3823251540053</v>
+        <v>151.7273476549808</v>
       </c>
       <c r="C213" t="n">
-        <v>150.3972821936961</v>
+        <v>153.1765360977979</v>
       </c>
       <c r="D213" t="n">
-        <v>147.0820191757993</v>
+        <v>148.2036492050291</v>
       </c>
       <c r="E213" t="n">
-        <v>150.3774261474609</v>
+        <v>148.8686828613281</v>
       </c>
       <c r="F213" t="n">
-        <v>6485400</v>
+        <v>8917400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>151.7273476549808</v>
+        <v>148.4518004486472</v>
       </c>
       <c r="C214" t="n">
-        <v>153.1765360977979</v>
+        <v>148.9878076836025</v>
       </c>
       <c r="D214" t="n">
-        <v>148.2036492050291</v>
+        <v>147.3301685811182</v>
       </c>
       <c r="E214" t="n">
-        <v>148.8686828613281</v>
+        <v>148.0249938964844</v>
       </c>
       <c r="F214" t="n">
-        <v>8917400</v>
+        <v>5788300</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>148.4518004486472</v>
+        <v>146.7643973953222</v>
       </c>
       <c r="C215" t="n">
-        <v>148.9878076836025</v>
+        <v>147.3103250709858</v>
       </c>
       <c r="D215" t="n">
-        <v>147.3301685811182</v>
+        <v>145.7916631750561</v>
       </c>
       <c r="E215" t="n">
-        <v>148.0249938964844</v>
+        <v>147.0026245117188</v>
       </c>
       <c r="F215" t="n">
-        <v>5788300</v>
+        <v>7027600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>146.7643973953222</v>
+        <v>148.3922474549245</v>
       </c>
       <c r="C216" t="n">
-        <v>147.3103250709858</v>
+        <v>149.3451407916641</v>
       </c>
       <c r="D216" t="n">
-        <v>145.7916631750561</v>
+        <v>147.7172933317669</v>
       </c>
       <c r="E216" t="n">
-        <v>147.0026245117188</v>
+        <v>148.0249938964844</v>
       </c>
       <c r="F216" t="n">
-        <v>7027600</v>
+        <v>5371200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>148.3922474549245</v>
+        <v>145.057144942689</v>
       </c>
       <c r="C217" t="n">
-        <v>149.3451407916641</v>
+        <v>146.5162538863596</v>
       </c>
       <c r="D217" t="n">
-        <v>147.7172933317669</v>
+        <v>144.5112172519064</v>
       </c>
       <c r="E217" t="n">
-        <v>148.0249938964844</v>
+        <v>145.8809967041016</v>
       </c>
       <c r="F217" t="n">
-        <v>5371200</v>
+        <v>6499200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,25 +6085,25 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>145.057144942689</v>
+        <v>146.4499969482422</v>
       </c>
       <c r="C218" t="n">
-        <v>146.5162538863596</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="D218" t="n">
-        <v>144.5112172519064</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="E218" t="n">
-        <v>145.8809967041016</v>
+        <v>147.4100036621094</v>
       </c>
       <c r="F218" t="n">
-        <v>6499200</v>
+        <v>6620700</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1.089</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6111,25 +6111,25 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>146.4499969482422</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C219" t="n">
-        <v>147.9900054931641</v>
+        <v>150.25</v>
       </c>
       <c r="D219" t="n">
-        <v>145.3999938964844</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="E219" t="n">
-        <v>147.4100036621094</v>
+        <v>148.6300048828125</v>
       </c>
       <c r="F219" t="n">
-        <v>6620700</v>
+        <v>7301800</v>
       </c>
       <c r="G219" t="n">
-        <v>1.089</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>147.8500061035156</v>
+        <v>151.5</v>
       </c>
       <c r="C220" t="n">
-        <v>150.25</v>
+        <v>153.6799926757812</v>
       </c>
       <c r="D220" t="n">
-        <v>147.8500061035156</v>
+        <v>148.5200042724609</v>
       </c>
       <c r="E220" t="n">
-        <v>148.6300048828125</v>
+        <v>148.8800048828125</v>
       </c>
       <c r="F220" t="n">
-        <v>7301800</v>
+        <v>12848800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>151.5</v>
+        <v>141.3800048828125</v>
       </c>
       <c r="C221" t="n">
-        <v>153.6799926757812</v>
+        <v>146.3800048828125</v>
       </c>
       <c r="D221" t="n">
-        <v>148.5200042724609</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="E221" t="n">
-        <v>148.8800048828125</v>
+        <v>146.1000061035156</v>
       </c>
       <c r="F221" t="n">
-        <v>12848800</v>
+        <v>14616800</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>141.3800048828125</v>
+        <v>143.7599945068359</v>
       </c>
       <c r="C222" t="n">
-        <v>146.3800048828125</v>
+        <v>144.4499969482422</v>
       </c>
       <c r="D222" t="n">
-        <v>140.1999969482422</v>
+        <v>142.25</v>
       </c>
       <c r="E222" t="n">
-        <v>146.1000061035156</v>
+        <v>143.9600067138672</v>
       </c>
       <c r="F222" t="n">
-        <v>14616800</v>
+        <v>9571100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>143.7599945068359</v>
+        <v>143.5099945068359</v>
       </c>
       <c r="C223" t="n">
-        <v>144.4499969482422</v>
+        <v>144.6999969482422</v>
       </c>
       <c r="D223" t="n">
-        <v>142.25</v>
+        <v>141.4600067138672</v>
       </c>
       <c r="E223" t="n">
-        <v>143.9600067138672</v>
+        <v>144.4900054931641</v>
       </c>
       <c r="F223" t="n">
-        <v>9571100</v>
+        <v>9152600</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>143.5099945068359</v>
+        <v>145.8500061035156</v>
       </c>
       <c r="C224" t="n">
-        <v>144.6999969482422</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D224" t="n">
-        <v>141.4600067138672</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="E224" t="n">
-        <v>144.4900054931641</v>
+        <v>144.9700012207031</v>
       </c>
       <c r="F224" t="n">
-        <v>9152600</v>
+        <v>8843600</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>145.8500061035156</v>
+        <v>144.0399932861328</v>
       </c>
       <c r="C225" t="n">
-        <v>147.1499938964844</v>
+        <v>148.25</v>
       </c>
       <c r="D225" t="n">
-        <v>144.2599945068359</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E225" t="n">
-        <v>144.9700012207031</v>
+        <v>148.0099945068359</v>
       </c>
       <c r="F225" t="n">
-        <v>8843600</v>
+        <v>7362300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>144.0399932861328</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="C226" t="n">
-        <v>148.25</v>
+        <v>147.8500061035156</v>
       </c>
       <c r="D226" t="n">
-        <v>143.7899932861328</v>
+        <v>144.6600036621094</v>
       </c>
       <c r="E226" t="n">
-        <v>148.0099945068359</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="F226" t="n">
-        <v>7362300</v>
+        <v>9753300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>147.8500061035156</v>
+        <v>147.8200073242188</v>
       </c>
       <c r="C227" t="n">
-        <v>147.8500061035156</v>
+        <v>148.5</v>
       </c>
       <c r="D227" t="n">
-        <v>144.6600036621094</v>
+        <v>145.4499969482422</v>
       </c>
       <c r="E227" t="n">
-        <v>146.8000030517578</v>
+        <v>146.9700012207031</v>
       </c>
       <c r="F227" t="n">
-        <v>9753300</v>
+        <v>8766700</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>147.8200073242188</v>
+        <v>144.8999938964844</v>
       </c>
       <c r="C228" t="n">
-        <v>148.5</v>
+        <v>146</v>
       </c>
       <c r="D228" t="n">
-        <v>145.4499969482422</v>
+        <v>143.8800048828125</v>
       </c>
       <c r="E228" t="n">
-        <v>146.9700012207031</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="F228" t="n">
-        <v>8766700</v>
+        <v>7565500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>144.8999938964844</v>
+        <v>144.7299957275391</v>
       </c>
       <c r="C229" t="n">
-        <v>146</v>
+        <v>146.4600067138672</v>
       </c>
       <c r="D229" t="n">
-        <v>143.8800048828125</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="E229" t="n">
-        <v>145.7899932861328</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F229" t="n">
-        <v>7565500</v>
+        <v>7386500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>144.7299957275391</v>
+        <v>145.4100036621094</v>
       </c>
       <c r="C230" t="n">
-        <v>146.4600067138672</v>
+        <v>145.7100067138672</v>
       </c>
       <c r="D230" t="n">
-        <v>144.1499938964844</v>
+        <v>143.9299926757812</v>
       </c>
       <c r="E230" t="n">
-        <v>146.4400024414062</v>
+        <v>145.2100067138672</v>
       </c>
       <c r="F230" t="n">
-        <v>7386500</v>
+        <v>7936700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>145.4100036621094</v>
+        <v>144.0500030517578</v>
       </c>
       <c r="C231" t="n">
-        <v>145.7100067138672</v>
+        <v>144.9400024414062</v>
       </c>
       <c r="D231" t="n">
-        <v>143.9299926757812</v>
+        <v>143.7899932861328</v>
       </c>
       <c r="E231" t="n">
-        <v>145.2100067138672</v>
+        <v>144.0800018310547</v>
       </c>
       <c r="F231" t="n">
-        <v>7936700</v>
+        <v>7195000</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>144.0500030517578</v>
+        <v>144.5899963378906</v>
       </c>
       <c r="C232" t="n">
-        <v>144.9400024414062</v>
+        <v>145.8000030517578</v>
       </c>
       <c r="D232" t="n">
-        <v>143.7899932861328</v>
+        <v>144</v>
       </c>
       <c r="E232" t="n">
-        <v>144.0800018310547</v>
+        <v>144.2599945068359</v>
       </c>
       <c r="F232" t="n">
-        <v>7195000</v>
+        <v>7491300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>144.5899963378906</v>
+        <v>144.3300018310547</v>
       </c>
       <c r="C233" t="n">
-        <v>145.8000030517578</v>
+        <v>144.9100036621094</v>
       </c>
       <c r="D233" t="n">
-        <v>144</v>
+        <v>143.4199981689453</v>
       </c>
       <c r="E233" t="n">
-        <v>144.2599945068359</v>
+        <v>144.5500030517578</v>
       </c>
       <c r="F233" t="n">
-        <v>7491300</v>
+        <v>7249600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>144.3300018310547</v>
+        <v>143.6399993896484</v>
       </c>
       <c r="C234" t="n">
-        <v>144.9100036621094</v>
+        <v>143.9700012207031</v>
       </c>
       <c r="D234" t="n">
-        <v>143.4199981689453</v>
+        <v>142.4799957275391</v>
       </c>
       <c r="E234" t="n">
-        <v>144.5500030517578</v>
+        <v>143.1199951171875</v>
       </c>
       <c r="F234" t="n">
-        <v>7249600</v>
+        <v>9867500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>143.6399993896484</v>
+        <v>143.2799987792969</v>
       </c>
       <c r="C235" t="n">
-        <v>143.9700012207031</v>
+        <v>144.4199981689453</v>
       </c>
       <c r="D235" t="n">
-        <v>142.4799957275391</v>
+        <v>142.6799926757812</v>
       </c>
       <c r="E235" t="n">
-        <v>143.1199951171875</v>
+        <v>143.4499969482422</v>
       </c>
       <c r="F235" t="n">
-        <v>9867500</v>
+        <v>12746100</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>143.2799987792969</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="C236" t="n">
-        <v>144.4199981689453</v>
+        <v>146.2299957275391</v>
       </c>
       <c r="D236" t="n">
-        <v>142.6799926757812</v>
+        <v>143.6199951171875</v>
       </c>
       <c r="E236" t="n">
-        <v>143.4499969482422</v>
+        <v>144.3800048828125</v>
       </c>
       <c r="F236" t="n">
-        <v>12746100</v>
+        <v>13948500</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>144.3000030517578</v>
+        <v>144.4700012207031</v>
       </c>
       <c r="C237" t="n">
-        <v>146.2299957275391</v>
+        <v>144.9199981689453</v>
       </c>
       <c r="D237" t="n">
-        <v>143.6199951171875</v>
+        <v>142.5599975585938</v>
       </c>
       <c r="E237" t="n">
-        <v>144.3800048828125</v>
+        <v>142.9700012207031</v>
       </c>
       <c r="F237" t="n">
-        <v>13948500</v>
+        <v>15794100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>144.4700012207031</v>
+        <v>143.0200042724609</v>
       </c>
       <c r="C238" t="n">
-        <v>144.9199981689453</v>
+        <v>145.2700042724609</v>
       </c>
       <c r="D238" t="n">
-        <v>142.5599975585938</v>
+        <v>142.1399993896484</v>
       </c>
       <c r="E238" t="n">
-        <v>142.9700012207031</v>
+        <v>144.6799926757812</v>
       </c>
       <c r="F238" t="n">
-        <v>15794100</v>
+        <v>9785200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>143.0200042724609</v>
+        <v>145.2400054931641</v>
       </c>
       <c r="C239" t="n">
-        <v>145.2700042724609</v>
+        <v>146.8000030517578</v>
       </c>
       <c r="D239" t="n">
-        <v>142.1399993896484</v>
+        <v>145</v>
       </c>
       <c r="E239" t="n">
-        <v>144.6799926757812</v>
+        <v>146.6000061035156</v>
       </c>
       <c r="F239" t="n">
-        <v>9785200</v>
+        <v>7061800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>145.2400054931641</v>
+        <v>145.7299957275391</v>
       </c>
       <c r="C240" t="n">
-        <v>146.8000030517578</v>
+        <v>146.1199951171875</v>
       </c>
       <c r="D240" t="n">
-        <v>145</v>
+        <v>144.9499969482422</v>
       </c>
       <c r="E240" t="n">
-        <v>146.6000061035156</v>
+        <v>145.3999938964844</v>
       </c>
       <c r="F240" t="n">
-        <v>7061800</v>
+        <v>9125700</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>145.7299957275391</v>
+        <v>145.2799987792969</v>
       </c>
       <c r="C241" t="n">
-        <v>146.1199951171875</v>
+        <v>145.9299926757812</v>
       </c>
       <c r="D241" t="n">
-        <v>144.9499969482422</v>
+        <v>144.5</v>
       </c>
       <c r="E241" t="n">
-        <v>145.3999938964844</v>
+        <v>145</v>
       </c>
       <c r="F241" t="n">
-        <v>9125700</v>
+        <v>8249100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>145.2799987792969</v>
+        <v>143.6999969482422</v>
       </c>
       <c r="C242" t="n">
-        <v>145.9299926757812</v>
+        <v>144.1499938964844</v>
       </c>
       <c r="D242" t="n">
-        <v>144.5</v>
+        <v>142.7100067138672</v>
       </c>
       <c r="E242" t="n">
-        <v>145</v>
+        <v>143.1399993896484</v>
       </c>
       <c r="F242" t="n">
-        <v>8249100</v>
+        <v>7817200</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>143.6999969482422</v>
+        <v>143.25</v>
       </c>
       <c r="C243" t="n">
-        <v>144.1499938964844</v>
+        <v>144.3999938964844</v>
       </c>
       <c r="D243" t="n">
-        <v>142.7100067138672</v>
+        <v>143.0099945068359</v>
       </c>
       <c r="E243" t="n">
-        <v>143.1399993896484</v>
+        <v>143.7799987792969</v>
       </c>
       <c r="F243" t="n">
-        <v>7817200</v>
+        <v>5868900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>143.25</v>
+        <v>143.4400024414062</v>
       </c>
       <c r="C244" t="n">
-        <v>144.3999938964844</v>
+        <v>145.8999938964844</v>
       </c>
       <c r="D244" t="n">
-        <v>143.0099945068359</v>
+        <v>142.5</v>
       </c>
       <c r="E244" t="n">
-        <v>143.7799987792969</v>
+        <v>145.1199951171875</v>
       </c>
       <c r="F244" t="n">
-        <v>5868900</v>
+        <v>12097900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>143.4400024414062</v>
+        <v>145.7599945068359</v>
       </c>
       <c r="C245" t="n">
-        <v>145.8999938964844</v>
+        <v>148.3600006103516</v>
       </c>
       <c r="D245" t="n">
-        <v>142.5</v>
+        <v>145.0899963378906</v>
       </c>
       <c r="E245" t="n">
-        <v>145.1199951171875</v>
+        <v>146.2100067138672</v>
       </c>
       <c r="F245" t="n">
-        <v>12097900</v>
+        <v>8503800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>145.7599945068359</v>
+        <v>146.4199981689453</v>
       </c>
       <c r="C246" t="n">
-        <v>148.3600006103516</v>
+        <v>148.3200073242188</v>
       </c>
       <c r="D246" t="n">
-        <v>145.0899963378906</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="E246" t="n">
-        <v>146.2100067138672</v>
+        <v>147.6399993896484</v>
       </c>
       <c r="F246" t="n">
-        <v>8503800</v>
+        <v>7431100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>146.4199981689453</v>
+        <v>147.6799926757812</v>
       </c>
       <c r="C247" t="n">
-        <v>148.3200073242188</v>
+        <v>148.2200012207031</v>
       </c>
       <c r="D247" t="n">
-        <v>145.7899932861328</v>
+        <v>146.5</v>
       </c>
       <c r="E247" t="n">
-        <v>147.6399993896484</v>
+        <v>146.9199981689453</v>
       </c>
       <c r="F247" t="n">
-        <v>7431100</v>
+        <v>6105800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>147.6799926757812</v>
+        <v>146.4700012207031</v>
       </c>
       <c r="C248" t="n">
-        <v>148.2200012207031</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="D248" t="n">
-        <v>146.5</v>
+        <v>145.8200073242188</v>
       </c>
       <c r="E248" t="n">
-        <v>146.9199981689453</v>
+        <v>146.4400024414062</v>
       </c>
       <c r="F248" t="n">
-        <v>6105800</v>
+        <v>5588200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>146.4700012207031</v>
+        <v>145.6000061035156</v>
       </c>
       <c r="C249" t="n">
-        <v>147.1499938964844</v>
+        <v>146.1600036621094</v>
       </c>
       <c r="D249" t="n">
-        <v>145.8200073242188</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="E249" t="n">
-        <v>146.4400024414062</v>
+        <v>145.5800018310547</v>
       </c>
       <c r="F249" t="n">
-        <v>5588200</v>
+        <v>8325100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>145.6000061035156</v>
+        <v>144.1600036621094</v>
       </c>
       <c r="C250" t="n">
-        <v>146.1600036621094</v>
+        <v>144.4700012207031</v>
       </c>
       <c r="D250" t="n">
-        <v>144.3000030517578</v>
+        <v>142.3399963378906</v>
       </c>
       <c r="E250" t="n">
-        <v>145.5800018310547</v>
+        <v>142.6399993896484</v>
       </c>
       <c r="F250" t="n">
-        <v>8325100</v>
+        <v>9270000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>144.1600036621094</v>
+        <v>142.6000061035156</v>
       </c>
       <c r="C251" t="n">
-        <v>144.4700012207031</v>
+        <v>143.5099945068359</v>
       </c>
       <c r="D251" t="n">
-        <v>142.3399963378906</v>
+        <v>141.8600006103516</v>
       </c>
       <c r="E251" t="n">
-        <v>142.6399993896484</v>
+        <v>142.9700012207031</v>
       </c>
       <c r="F251" t="n">
-        <v>9270000</v>
+        <v>10925000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>142.6000061035156</v>
+        <v>143.7200012207031</v>
       </c>
       <c r="C252" t="n">
-        <v>143.5099945068359</v>
+        <v>145.4900054931641</v>
       </c>
       <c r="D252" t="n">
-        <v>141.8600006103516</v>
+        <v>143.5500030517578</v>
       </c>
       <c r="E252" t="n">
-        <v>142.9700012207031</v>
+        <v>145.2700042724609</v>
       </c>
       <c r="F252" t="n">
-        <v>10925000</v>
+        <v>11526600</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10806,37 +10806,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>145.27</v>
+      </c>
+      <c r="D2" t="n">
         <v>142.97</v>
       </c>
-      <c r="D2" t="n">
-        <v>142.64</v>
-      </c>
       <c r="E2" t="n">
-        <v>142.6</v>
+        <v>143.715</v>
       </c>
       <c r="F2" t="n">
-        <v>143.51</v>
+        <v>145.48</v>
       </c>
       <c r="G2" t="n">
-        <v>141.86</v>
+        <v>143.5501</v>
       </c>
       <c r="H2" t="n">
-        <v>10893968</v>
+        <v>11508718</v>
       </c>
       <c r="I2" t="n">
-        <v>9001740</v>
+        <v>9145851</v>
       </c>
       <c r="J2" t="n">
-        <v>332072484864</v>
+        <v>337414619136</v>
       </c>
       <c r="K2" t="n">
-        <v>21.564102</v>
+        <v>21.944109</v>
       </c>
       <c r="L2" t="n">
-        <v>19.320793</v>
+        <v>19.631613</v>
       </c>
       <c r="M2" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
       <c r="N2" t="n">
         <v>167.25</v>
@@ -10872,7 +10872,7 @@
         <v>22.947</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.230444</v>
+        <v>6.330675</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.155</v>
@@ -10884,7 +10884,7 @@
         <v>87031996416</v>
       </c>
       <c r="AC2" t="n">
-        <v>358393184256</v>
+        <v>363739381760</v>
       </c>
       <c r="AD2" t="n">
         <v>24752001024</v>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:17</t>
+          <t>2026-09-12 21:47:21</t>
         </is>
       </c>
     </row>
